--- a/research/traditional_assets/database/data/china/china_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/china/china_brokerage_investment_banking.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0788</v>
+        <v>0.104</v>
       </c>
       <c r="E2">
-        <v>0.04705</v>
+        <v>0.0505</v>
       </c>
       <c r="F2">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="G2">
-        <v>0.01111175039267164</v>
+        <v>0.002668168370168764</v>
       </c>
       <c r="H2">
-        <v>0.008170771670389359</v>
+        <v>0.0005921725142265136</v>
       </c>
       <c r="I2">
-        <v>0.01093966281218215</v>
+        <v>1.736248557630665e-05</v>
       </c>
       <c r="J2">
-        <v>0.008687213280204473</v>
+        <v>1.468566889174114e-05</v>
       </c>
       <c r="K2">
-        <v>29239.6</v>
+        <v>21262.185</v>
       </c>
       <c r="L2">
-        <v>0.2753372079445853</v>
+        <v>0.2444831368815391</v>
       </c>
       <c r="M2">
-        <v>22864.9576</v>
+        <v>21098.6339</v>
       </c>
       <c r="N2">
-        <v>0.04568798276941424</v>
+        <v>0.05882254153251843</v>
       </c>
       <c r="O2">
-        <v>0.7819859916004324</v>
+        <v>0.9923078883943489</v>
       </c>
       <c r="P2">
-        <v>20845.0976</v>
+        <v>20919.1039</v>
       </c>
       <c r="Q2">
-        <v>0.04165196702466477</v>
+        <v>0.058322015719739</v>
       </c>
       <c r="R2">
-        <v>0.7129063872282795</v>
+        <v>0.9838642594822685</v>
       </c>
       <c r="S2">
-        <v>2019.86</v>
+        <v>179.5299999999999</v>
       </c>
       <c r="T2">
-        <v>0.08833867244958284</v>
+        <v>0.008509081718319206</v>
       </c>
       <c r="U2">
-        <v>110803.6</v>
+        <v>122316.1</v>
       </c>
       <c r="V2">
-        <v>0.22140399541301</v>
+        <v>0.3410146792653565</v>
       </c>
       <c r="W2">
-        <v>0.09098529810069646</v>
+        <v>0.04898971057045419</v>
       </c>
       <c r="X2">
-        <v>0.05589289236801551</v>
+        <v>0.1109174792403322</v>
       </c>
       <c r="Y2">
-        <v>0.03509240573268095</v>
+        <v>-0.06192776866987802</v>
       </c>
       <c r="Z2">
-        <v>0.1289364681532593</v>
+        <v>0.08740600019080309</v>
       </c>
       <c r="AA2">
-        <v>7.489711999865844e-05</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03747258163613007</v>
+        <v>0.07030027514289208</v>
       </c>
       <c r="AC2">
-        <v>-0.03718852783392644</v>
+        <v>-0.07030027514289208</v>
       </c>
       <c r="AD2">
-        <v>762735.7</v>
+        <v>747936</v>
       </c>
       <c r="AE2">
-        <v>1317.779719313146</v>
+        <v>12.1951054532416</v>
       </c>
       <c r="AF2">
-        <v>764053.4797193131</v>
+        <v>747948.1951054533</v>
       </c>
       <c r="AG2">
-        <v>653249.8797193131</v>
+        <v>625632.0951054533</v>
       </c>
       <c r="AH2">
-        <v>0.60422775765067</v>
+        <v>0.6758785886294281</v>
       </c>
       <c r="AI2">
-        <v>0.6859287472544968</v>
+        <v>0.678995277414043</v>
       </c>
       <c r="AJ2">
-        <v>0.5662173082172807</v>
+        <v>0.6356015724403186</v>
       </c>
       <c r="AK2">
-        <v>0.6512358159189303</v>
+        <v>0.6388986367552032</v>
       </c>
       <c r="AL2">
-        <v>746.8</v>
+        <v>55.9</v>
       </c>
       <c r="AM2">
-        <v>-804.55</v>
+        <v>-638.8000000000001</v>
       </c>
       <c r="AN2">
-        <v>534.8027625858925</v>
+        <v>113858.4259400213</v>
       </c>
       <c r="AO2">
-        <v>1.291778253883235</v>
+        <v>-0.02182468694096601</v>
       </c>
       <c r="AP2">
-        <v>458.0352543256998</v>
+        <v>95240.08145919521</v>
       </c>
       <c r="AQ2">
-        <v>-1.199055372568516</v>
+        <v>0.001909830932999374</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Xiangcai Co.,Ltd (SHSE:600095)</t>
+          <t>Shenwan Hongyuan Group Co., Ltd. (SZSE:000166)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.762</v>
+        <v>0.135</v>
       </c>
       <c r="E3">
-        <v>0.966</v>
+        <v>0.0403</v>
       </c>
       <c r="G3">
-        <v>0.1682787610619469</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.1679941002949853</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.1438856922769011</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.100670311742642</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>60.5</v>
+        <v>881</v>
       </c>
       <c r="L3">
-        <v>0.08923303834808259</v>
+        <v>0.2336188380048262</v>
       </c>
       <c r="M3">
-        <v>73.3</v>
+        <v>1248.5</v>
       </c>
       <c r="N3">
-        <v>0.01611662012708603</v>
+        <v>0.09268814170855018</v>
       </c>
       <c r="O3">
-        <v>1.211570247933884</v>
+        <v>1.417139614074915</v>
       </c>
       <c r="P3">
-        <v>73.3</v>
+        <v>1248.5</v>
       </c>
       <c r="Q3">
-        <v>0.01611662012708603</v>
+        <v>0.09268814170855018</v>
       </c>
       <c r="R3">
-        <v>1.211570247933884</v>
+        <v>1.417139614074915</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +773,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2137.4</v>
+        <v>5761.6</v>
       </c>
       <c r="V3">
-        <v>0.4699544864888635</v>
+        <v>0.4277388844757571</v>
       </c>
       <c r="W3">
-        <v>0.03871256718710007</v>
+        <v>0.05760391261989917</v>
       </c>
       <c r="X3">
-        <v>0.04206222012709053</v>
+        <v>0.1588223251413954</v>
       </c>
       <c r="Y3">
-        <v>-0.003349652939990455</v>
+        <v>-0.1012184125214963</v>
       </c>
       <c r="Z3">
-        <v>0.5321079663604186</v>
+        <v>0.06210240119623411</v>
       </c>
       <c r="AA3">
-        <v>0.05356747485424657</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03773597476215772</v>
+        <v>0.06744470597468225</v>
       </c>
       <c r="AC3">
-        <v>0.01583150009208886</v>
+        <v>-0.06744470597468225</v>
       </c>
       <c r="AD3">
-        <v>1588.9</v>
+        <v>48271.6</v>
       </c>
       <c r="AE3">
-        <v>14.37750318130533</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1603.277503181306</v>
+        <v>48271.6</v>
       </c>
       <c r="AG3">
-        <v>-534.1224968186946</v>
+        <v>42510</v>
       </c>
       <c r="AH3">
-        <v>0.2606371503540693</v>
+        <v>0.781833936655248</v>
       </c>
       <c r="AI3">
-        <v>0.4520760393215842</v>
+        <v>0.7432071242055477</v>
       </c>
       <c r="AJ3">
-        <v>-0.133065642843133</v>
+        <v>0.7593797059301642</v>
       </c>
       <c r="AK3">
-        <v>-0.3790582814733713</v>
+        <v>0.7182102019300949</v>
       </c>
       <c r="AL3">
-        <v>85.3</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>47.2</v>
-      </c>
-      <c r="AN3">
-        <v>15.14247593633851</v>
-      </c>
-      <c r="AO3">
-        <v>1.107854630715123</v>
-      </c>
-      <c r="AP3">
-        <v>-5.090274438375055</v>
-      </c>
-      <c r="AQ3">
-        <v>2.002118644067797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Caida Securities Co., Ltd. (SHSE:600906)</t>
+          <t>SDIC Capital Co.,Ltd (SHSE:600061)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,46 +847,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00601</v>
+        <v>0.109</v>
       </c>
       <c r="E4">
-        <v>-0.0885</v>
+        <v>0.028</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.006799390774586597</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.003782111328239002</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.002707399770567496</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>111.5</v>
+        <v>421.7</v>
       </c>
       <c r="L4">
-        <v>0.2955991516436904</v>
+        <v>0.2293842471714534</v>
       </c>
       <c r="M4">
-        <v>152.6</v>
+        <v>494.4</v>
       </c>
       <c r="N4">
-        <v>0.02341208959803621</v>
+        <v>0.0830533530439457</v>
       </c>
       <c r="O4">
-        <v>1.368609865470852</v>
+        <v>1.172397438937633</v>
       </c>
       <c r="P4">
-        <v>152.6</v>
+        <v>494.4</v>
       </c>
       <c r="Q4">
-        <v>0.02341208959803621</v>
+        <v>0.0830533530439457</v>
       </c>
       <c r="R4">
-        <v>1.368609865470852</v>
+        <v>1.172397438937633</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,61 +895,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>160.1</v>
+        <v>13095.9</v>
       </c>
       <c r="V4">
-        <v>0.02456274930960417</v>
+        <v>2.199956323074856</v>
+      </c>
+      <c r="W4">
+        <v>0.05598109625774934</v>
       </c>
       <c r="X4">
-        <v>0.04433881388640738</v>
+        <v>0.1563442190543497</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1003631227966004</v>
       </c>
       <c r="Z4">
-        <v>20.04576936479122</v>
+        <v>0.117032925059204</v>
       </c>
       <c r="AA4">
-        <v>0.05427191137908471</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03884672799808502</v>
+        <v>0.06746936522196537</v>
       </c>
       <c r="AC4">
-        <v>0.01542518338099969</v>
+        <v>-0.06746936522196537</v>
       </c>
       <c r="AD4">
-        <v>3206.7</v>
+        <v>20728.5</v>
       </c>
       <c r="AE4">
-        <v>18.81693803494124</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>3225.516938034941</v>
+        <v>20728.5</v>
       </c>
       <c r="AG4">
-        <v>3065.416938034941</v>
+        <v>7632.6</v>
       </c>
       <c r="AH4">
-        <v>0.3310423698699351</v>
+        <v>0.7768924302788844</v>
       </c>
       <c r="AI4">
-        <v>0.6533464059694724</v>
+        <v>0.7240840878604963</v>
       </c>
       <c r="AJ4">
-        <v>0.3198668030260508</v>
+        <v>0.5618237225256525</v>
       </c>
       <c r="AK4">
-        <v>0.6417279493436009</v>
+        <v>0.491433427980916</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>617.8612716763005</v>
-      </c>
-      <c r="AP4">
-        <v>590.6391017408364</v>
+        <v>-190</v>
+      </c>
+      <c r="AQ4">
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Guangzhou Yuexiu Financial Holdings Group Co., Ltd. (SZSE:000987)</t>
+          <t>Changjiang Securities Company Limited (SZSE:000783)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,46 +972,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.223</v>
+        <v>-0.00164</v>
       </c>
       <c r="E5">
-        <v>0.356</v>
+        <v>-0.09759999999999999</v>
       </c>
       <c r="G5">
-        <v>0.3748362295945234</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.3744075829383886</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.4259083728278041</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.3510248830976313</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>327.7</v>
+        <v>163.9</v>
       </c>
       <c r="L5">
-        <v>0.1725645076355977</v>
+        <v>0.1939185991481306</v>
       </c>
       <c r="M5">
-        <v>463.6</v>
+        <v>459.7</v>
       </c>
       <c r="N5">
-        <v>0.09108591861995796</v>
+        <v>0.1075724247671643</v>
       </c>
       <c r="O5">
-        <v>1.414708574916082</v>
+        <v>2.804758999389872</v>
       </c>
       <c r="P5">
-        <v>463.6</v>
+        <v>459.7</v>
       </c>
       <c r="Q5">
-        <v>0.09108591861995796</v>
+        <v>0.1075724247671643</v>
       </c>
       <c r="R5">
-        <v>1.414708574916082</v>
+        <v>2.804758999389872</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,73 +1020,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2196.5</v>
+        <v>1184.6</v>
       </c>
       <c r="V5">
-        <v>0.4315578521327387</v>
+        <v>0.2772031637571957</v>
       </c>
       <c r="W5">
-        <v>0.0952727061286196</v>
+        <v>0.03465629162878228</v>
       </c>
       <c r="X5">
-        <v>0.08168321507364967</v>
+        <v>0.1412428845493386</v>
       </c>
       <c r="Y5">
-        <v>0.01358949105496993</v>
+        <v>-0.1065865929205563</v>
       </c>
       <c r="Z5">
-        <v>0.1552091932227771</v>
+        <v>0.05500670337251228</v>
       </c>
       <c r="AA5">
-        <v>0.054482288906703</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04014276062258641</v>
+        <v>0.06764764794763661</v>
       </c>
       <c r="AC5">
-        <v>0.01433952828411659</v>
+        <v>-0.06764764794763661</v>
       </c>
       <c r="AD5">
-        <v>14403.2</v>
+        <v>12236.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>14403.2</v>
+        <v>12236.8</v>
       </c>
       <c r="AG5">
-        <v>12206.7</v>
+        <v>11052.2</v>
       </c>
       <c r="AH5">
-        <v>0.7388946744712177</v>
+        <v>0.7411660670373467</v>
       </c>
       <c r="AI5">
-        <v>0.7325920877287571</v>
+        <v>0.7372010362070004</v>
       </c>
       <c r="AJ5">
-        <v>0.7057364538285423</v>
+        <v>0.7211593673330897</v>
       </c>
       <c r="AK5">
-        <v>0.6989595799382735</v>
+        <v>0.7170048785551173</v>
       </c>
       <c r="AL5">
-        <v>595.8</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>293.4999999999999</v>
-      </c>
-      <c r="AN5">
-        <v>17.88772975658221</v>
-      </c>
-      <c r="AO5">
-        <v>1.357502517623363</v>
-      </c>
-      <c r="AP5">
-        <v>15.15983606557377</v>
-      </c>
-      <c r="AQ5">
-        <v>2.755706984667803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shanghai Chinafortune Co., Ltd. (SHSE:600621)</t>
+          <t>Minmetals Capital Company Limited (SHSE:600390)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1115,46 +1094,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0347</v>
+        <v>-0.0258</v>
       </c>
       <c r="E6">
-        <v>0.14</v>
+        <v>-0.0174</v>
       </c>
       <c r="G6">
-        <v>0.149311716121138</v>
+        <v>0.003976516634050881</v>
       </c>
       <c r="H6">
-        <v>0.1309268889568675</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.187825022942796</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.1375358433947697</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>80.90000000000001</v>
+        <v>299.2</v>
       </c>
       <c r="L6">
-        <v>0.2474762924441726</v>
+        <v>0.2342074363992172</v>
       </c>
       <c r="M6">
-        <v>63.6</v>
+        <v>85.46390000000001</v>
       </c>
       <c r="N6">
-        <v>0.02751698178514256</v>
+        <v>0.02579652882583761</v>
       </c>
       <c r="O6">
-        <v>0.7861557478368356</v>
+        <v>0.2856413770053476</v>
       </c>
       <c r="P6">
-        <v>63.6</v>
+        <v>85.46390000000001</v>
       </c>
       <c r="Q6">
-        <v>0.02751698178514256</v>
+        <v>0.02579652882583761</v>
       </c>
       <c r="R6">
-        <v>0.7861557478368356</v>
+        <v>0.2856413770053476</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1163,73 +1142,64 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1325.9</v>
+        <v>2885</v>
       </c>
       <c r="V6">
-        <v>0.5736598451088132</v>
+        <v>0.8708119529127679</v>
       </c>
       <c r="W6">
-        <v>0.07971228692482019</v>
+        <v>0.04863300932999577</v>
       </c>
       <c r="X6">
-        <v>0.05061020216733955</v>
+        <v>0.1378771578652744</v>
       </c>
       <c r="Y6">
-        <v>0.02910208475748063</v>
+        <v>-0.08924414853527861</v>
       </c>
       <c r="Z6">
-        <v>0.2706372268998005</v>
+        <v>0.08927074016100178</v>
       </c>
       <c r="AA6">
-        <v>0.03722231925568572</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03878985277888419</v>
+        <v>0.06769545177875115</v>
       </c>
       <c r="AC6">
-        <v>-0.001567533523198467</v>
+        <v>-0.06769545177875115</v>
       </c>
       <c r="AD6">
-        <v>2050.1</v>
+        <v>9029.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2050.1</v>
+        <v>9029.9</v>
       </c>
       <c r="AG6">
-        <v>724.1999999999998</v>
+        <v>6144.9</v>
       </c>
       <c r="AH6">
-        <v>0.4700554867703031</v>
+        <v>0.7315865801391893</v>
       </c>
       <c r="AI6">
-        <v>0.6421613155833985</v>
+        <v>0.5228056970819823</v>
       </c>
       <c r="AJ6">
-        <v>0.2385768407181683</v>
+        <v>0.649710823755802</v>
       </c>
       <c r="AK6">
-        <v>0.3879781420765027</v>
+        <v>0.427114756377285</v>
       </c>
       <c r="AL6">
-        <v>65.7</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>-41.3</v>
-      </c>
-      <c r="AN6">
-        <v>33.38925081433225</v>
-      </c>
-      <c r="AO6">
-        <v>0.9345509893455098</v>
-      </c>
-      <c r="AP6">
-        <v>11.79478827361563</v>
+        <v>-72.5</v>
       </c>
       <c r="AQ6">
-        <v>-1.486682808716707</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -1240,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Guangdong Golden Dragon Development Inc. (SZSE:000712)</t>
+          <t>China Merchants Securities Co., Ltd. (SHSE:600999)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1249,7 +1219,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.129</v>
+        <v>0.13</v>
+      </c>
+      <c r="E7">
+        <v>0.11</v>
+      </c>
+      <c r="F7">
+        <v>0.193</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1258,34 +1234,34 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.02297655989722515</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.02297655989722515</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>-15.8</v>
+        <v>1324.7</v>
       </c>
       <c r="L7">
-        <v>-0.09283196239717979</v>
+        <v>0.4073743772679747</v>
       </c>
       <c r="M7">
-        <v>69.59999999999999</v>
+        <v>1589.6</v>
       </c>
       <c r="N7">
-        <v>0.03133018230925051</v>
+        <v>0.1021436282321493</v>
       </c>
       <c r="O7">
-        <v>-4.40506329113924</v>
+        <v>1.199969804484034</v>
       </c>
       <c r="P7">
-        <v>69.59999999999999</v>
+        <v>1589.6</v>
       </c>
       <c r="Q7">
-        <v>0.03133018230925051</v>
+        <v>0.1021436282321493</v>
       </c>
       <c r="R7">
-        <v>-4.40506329113924</v>
+        <v>1.199969804484034</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1294,67 +1270,61 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>122.5</v>
+        <v>2020.4</v>
       </c>
       <c r="V7">
-        <v>0.05514292144947108</v>
+        <v>0.1298257338199764</v>
       </c>
       <c r="W7">
-        <v>-0.03039630627164294</v>
+        <v>0.07787359869260298</v>
       </c>
       <c r="X7">
-        <v>0.04653934515230765</v>
+        <v>0.1371923221293815</v>
       </c>
       <c r="Y7">
-        <v>-0.07693565142395059</v>
+        <v>-0.05931872343677848</v>
       </c>
       <c r="Z7">
-        <v>0.1195143352392573</v>
+        <v>0.04873501478476293</v>
       </c>
       <c r="AA7">
-        <v>0.00274602828220184</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03703222815446437</v>
+        <v>0.06770561511169933</v>
       </c>
       <c r="AC7">
-        <v>-0.03428619987226253</v>
+        <v>-0.06770561511169933</v>
       </c>
       <c r="AD7">
-        <v>1395.4</v>
+        <v>41980.2</v>
       </c>
       <c r="AE7">
-        <v>9.596947527461404</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1404.996947527462</v>
+        <v>41980.2</v>
       </c>
       <c r="AG7">
-        <v>1282.496947527462</v>
+        <v>39959.8</v>
       </c>
       <c r="AH7">
-        <v>0.3874253771219595</v>
+        <v>0.7295499334406161</v>
       </c>
       <c r="AI7">
-        <v>0.6243052002674699</v>
+        <v>0.7242273421259197</v>
       </c>
       <c r="AJ7">
-        <v>0.3660097216786775</v>
+        <v>0.7197085129911999</v>
       </c>
       <c r="AK7">
-        <v>0.6026780014969505</v>
+        <v>0.7142680949716776</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>239.3481989708405</v>
-      </c>
-      <c r="AP7">
-        <v>219.9823237611426</v>
       </c>
     </row>
     <row r="8">
@@ -1365,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ruida Futures Co., Ltd. (SZSE:002961)</t>
+          <t>GF Securities Co., Ltd. (SZSE:000776)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1373,110 +1343,113 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.0277</v>
+      </c>
+      <c r="E8">
+        <v>-0.0194</v>
+      </c>
+      <c r="F8">
+        <v>0.07539999999999999</v>
+      </c>
       <c r="G8">
-        <v>0.002416087962962963</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.002059384495974943</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.001523380312091053</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>75.59999999999999</v>
+        <v>1046.8</v>
       </c>
       <c r="L8">
-        <v>0.21875</v>
+        <v>0.3124216558228377</v>
       </c>
       <c r="M8">
-        <v>18.3</v>
+        <v>1357.6</v>
       </c>
       <c r="N8">
-        <v>0.01060193499797231</v>
+        <v>0.08642564758758109</v>
       </c>
       <c r="O8">
-        <v>0.2420634920634921</v>
+        <v>1.296904852884983</v>
       </c>
       <c r="P8">
-        <v>18.3</v>
+        <v>1324.8</v>
       </c>
       <c r="Q8">
-        <v>0.01060193499797231</v>
+        <v>0.08433757949618992</v>
       </c>
       <c r="R8">
-        <v>0.2420634920634921</v>
+        <v>1.265571264807031</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>32.79999999999995</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.0241602828520919</v>
       </c>
       <c r="U8">
-        <v>95.3</v>
+        <v>2998.7</v>
       </c>
       <c r="V8">
-        <v>0.05521116968889404</v>
+        <v>0.1908990788309365</v>
       </c>
       <c r="W8">
-        <v>0.2748091603053435</v>
+        <v>0.06480329340390627</v>
       </c>
       <c r="X8">
-        <v>0.03785439992786301</v>
+        <v>0.1353837420642991</v>
       </c>
       <c r="Y8">
-        <v>0.2369547603774805</v>
+        <v>-0.07058044866039283</v>
       </c>
       <c r="Z8">
-        <v>1.186277962024307</v>
+        <v>0.0670647598465713</v>
       </c>
       <c r="AA8">
-        <v>0.001807152492015327</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.03655312518494212</v>
+        <v>0.06773321207413101</v>
       </c>
       <c r="AC8">
-        <v>-0.03474597269292679</v>
+        <v>-0.06773321207413101</v>
       </c>
       <c r="AD8">
-        <v>151.9</v>
+        <v>41209.9</v>
       </c>
       <c r="AE8">
-        <v>2.441383590955299</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>154.3413835909553</v>
+        <v>41209.9</v>
       </c>
       <c r="AG8">
-        <v>59.04138359095531</v>
+        <v>38211.2</v>
       </c>
       <c r="AH8">
-        <v>0.08207721066860363</v>
+        <v>0.72401973358258</v>
       </c>
       <c r="AI8">
-        <v>0.3045161436847391</v>
+        <v>0.7053808312593501</v>
       </c>
       <c r="AJ8">
-        <v>0.03307378571448992</v>
+        <v>0.7086712599337903</v>
       </c>
       <c r="AK8">
-        <v>0.1434640256000075</v>
+        <v>0.689440399830397</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
         <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>126.5833333333333</v>
-      </c>
-      <c r="AP8">
-        <v>49.20115299246276</v>
       </c>
     </row>
     <row r="9">
@@ -1487,7 +1460,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SDIC Capital Co.,Ltd (SHSE:600061)</t>
+          <t>Northeast Securities Co., Ltd. (SZSE:000686)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1496,46 +1469,46 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.078</v>
+        <v>0.0545</v>
       </c>
       <c r="E9">
-        <v>0.0579</v>
+        <v>-0.0299</v>
       </c>
       <c r="G9">
-        <v>1.373766154472372e-05</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.0161830001895992</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.01265702358810706</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>703</v>
+        <v>96.2</v>
       </c>
       <c r="L9">
-        <v>0.3576880024422509</v>
+        <v>0.1066637099456703</v>
       </c>
       <c r="M9">
-        <v>459.6</v>
+        <v>185.3</v>
       </c>
       <c r="N9">
-        <v>0.05527958528283278</v>
+        <v>0.08400961146121413</v>
       </c>
       <c r="O9">
-        <v>0.6537695590327169</v>
+        <v>1.926195426195426</v>
       </c>
       <c r="P9">
-        <v>459.6</v>
+        <v>185.3</v>
       </c>
       <c r="Q9">
-        <v>0.05527958528283278</v>
+        <v>0.08400961146121413</v>
       </c>
       <c r="R9">
-        <v>0.6537695590327169</v>
+        <v>1.926195426195426</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1544,70 +1517,61 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>10802.5</v>
+        <v>971.9</v>
       </c>
       <c r="V9">
-        <v>1.299298781587905</v>
+        <v>0.4406310921702861</v>
       </c>
       <c r="W9">
-        <v>0.1061580743559542</v>
+        <v>0.0351248722068059</v>
       </c>
       <c r="X9">
-        <v>0.07454987357259267</v>
+        <v>0.1344138831914123</v>
       </c>
       <c r="Y9">
-        <v>0.03160820078336155</v>
+        <v>-0.09928901098460638</v>
       </c>
       <c r="Z9">
-        <v>0.1851361734703827</v>
+        <v>0.1042996576926635</v>
       </c>
       <c r="AA9">
-        <v>0.002343272914626515</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.037529696886424</v>
+        <v>0.06774848110730494</v>
       </c>
       <c r="AC9">
-        <v>-0.03518642397179749</v>
+        <v>-0.06774848110730494</v>
       </c>
       <c r="AD9">
-        <v>19691.6</v>
+        <v>5698.9</v>
       </c>
       <c r="AE9">
-        <v>127.9696571368087</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>19819.56965713681</v>
+        <v>5698.9</v>
       </c>
       <c r="AG9">
-        <v>9017.069657136806</v>
+        <v>4727</v>
       </c>
       <c r="AH9">
-        <v>0.7044786513340281</v>
+        <v>0.7209599473724161</v>
       </c>
       <c r="AI9">
-        <v>0.7040332138436779</v>
+        <v>0.6840184840664946</v>
       </c>
       <c r="AJ9">
-        <v>0.5202805024428149</v>
+        <v>0.6818411297185801</v>
       </c>
       <c r="AK9">
-        <v>0.5197466959328894</v>
+        <v>0.6422903418664058</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-491.4</v>
-      </c>
-      <c r="AN9">
-        <v>343.0592334494773</v>
-      </c>
-      <c r="AP9">
-        <v>157.0918058734635</v>
-      </c>
-      <c r="AQ9">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1618,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Pacific Securities Co., Ltd (SHSE:601099)</t>
+          <t>Guoyuan Securities Company Limited (SZSE:000728)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1627,7 +1591,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0226</v>
+        <v>0.123</v>
+      </c>
+      <c r="E10">
+        <v>0.0536</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1636,34 +1603,34 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.008689210735133996</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.008689210735133996</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>-80.59999999999999</v>
+        <v>245</v>
       </c>
       <c r="L10">
-        <v>-0.315213140398905</v>
+        <v>0.2794889345197353</v>
       </c>
       <c r="M10">
-        <v>22.4</v>
+        <v>292.9</v>
       </c>
       <c r="N10">
-        <v>0.006364721259305563</v>
+        <v>0.07313540912382331</v>
       </c>
       <c r="O10">
-        <v>-0.2779156327543424</v>
+        <v>1.195510204081633</v>
       </c>
       <c r="P10">
-        <v>22.4</v>
+        <v>292.9</v>
       </c>
       <c r="Q10">
-        <v>0.006364721259305563</v>
+        <v>0.07313540912382331</v>
       </c>
       <c r="R10">
-        <v>-0.2779156327543424</v>
+        <v>1.195510204081633</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1672,67 +1639,61 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>160.8</v>
+        <v>554.9</v>
       </c>
       <c r="V10">
-        <v>0.04568960618287208</v>
+        <v>0.1385552697945017</v>
       </c>
       <c r="W10">
-        <v>-0.05230369889682025</v>
+        <v>0.04934641181091261</v>
       </c>
       <c r="X10">
-        <v>0.03960691129776175</v>
+        <v>0.1307196110015128</v>
       </c>
       <c r="Y10">
-        <v>-0.09191061019458199</v>
+        <v>-0.0813731991906002</v>
       </c>
       <c r="Z10">
-        <v>0.09634728693024376</v>
+        <v>0.07298066836505319</v>
       </c>
       <c r="AA10">
-        <v>0.0008371818798953095</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03668475263621072</v>
+        <v>0.06780987988353795</v>
       </c>
       <c r="AC10">
-        <v>-0.03584757075631541</v>
+        <v>-0.06780987988353795</v>
       </c>
       <c r="AD10">
-        <v>691.8</v>
+        <v>9741.4</v>
       </c>
       <c r="AE10">
-        <v>8.540844075131186</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>700.3408440751311</v>
+        <v>9741.4</v>
       </c>
       <c r="AG10">
-        <v>539.5408440751312</v>
+        <v>9186.5</v>
       </c>
       <c r="AH10">
-        <v>0.1659677382933286</v>
+        <v>0.7086561474724108</v>
       </c>
       <c r="AI10">
-        <v>0.3114645864319156</v>
+        <v>0.6774740941651018</v>
       </c>
       <c r="AJ10">
-        <v>0.1329265108316874</v>
+        <v>0.6964006852949649</v>
       </c>
       <c r="AK10">
-        <v>0.2584328632580581</v>
+        <v>0.664527889699872</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>176.030534351145</v>
-      </c>
-      <c r="AP10">
-        <v>137.2877465840028</v>
       </c>
     </row>
     <row r="11">
@@ -1743,7 +1704,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ChinaLin Securities Co., Ltd. (SZSE:002945)</t>
+          <t>Shanxi Securities Co., Ltd. (SZSE:002500)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1751,6 +1712,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D11">
+        <v>-0.00101</v>
+      </c>
+      <c r="E11">
+        <v>0.0154</v>
+      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1758,34 +1725,34 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.01980186504975932</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.01814493660296509</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>98.2</v>
+        <v>79.3</v>
       </c>
       <c r="L11">
-        <v>0.4671741198858231</v>
+        <v>0.1368657231618916</v>
       </c>
       <c r="M11">
-        <v>53.2</v>
+        <v>149</v>
       </c>
       <c r="N11">
-        <v>0.009163250542560888</v>
+        <v>0.05401486315026283</v>
       </c>
       <c r="O11">
-        <v>0.5417515274949084</v>
+        <v>1.878940731399748</v>
       </c>
       <c r="P11">
-        <v>53.2</v>
+        <v>149</v>
       </c>
       <c r="Q11">
-        <v>0.009163250542560888</v>
+        <v>0.05401486315026283</v>
       </c>
       <c r="R11">
-        <v>0.5417515274949084</v>
+        <v>1.878940731399748</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1794,67 +1761,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>83.90000000000001</v>
+        <v>1507.4</v>
       </c>
       <c r="V11">
-        <v>0.01445106617520411</v>
+        <v>0.5464564074678268</v>
       </c>
       <c r="W11">
-        <v>0.114398881640261</v>
+        <v>0.02989519716504561</v>
       </c>
       <c r="X11">
-        <v>0.0395854704225987</v>
+        <v>0.1305913586524849</v>
       </c>
       <c r="Y11">
-        <v>0.07481341121766227</v>
+        <v>-0.1006961614874392</v>
       </c>
       <c r="Z11">
-        <v>0.0725368300792853</v>
+        <v>0.07618872291184516</v>
       </c>
       <c r="AA11">
-        <v>0.001316176183168684</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03725486166524566</v>
+        <v>0.06781210883586269</v>
       </c>
       <c r="AC11">
-        <v>-0.03593868548207698</v>
+        <v>-0.06781210883586269</v>
       </c>
       <c r="AD11">
-        <v>1130</v>
+        <v>6695.2</v>
       </c>
       <c r="AE11">
-        <v>17.53823983270295</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1147.538239832703</v>
+        <v>6695.2</v>
       </c>
       <c r="AG11">
-        <v>1063.638239832703</v>
+        <v>5187.799999999999</v>
       </c>
       <c r="AH11">
-        <v>0.1650341462261891</v>
+        <v>0.7082094841173296</v>
       </c>
       <c r="AI11">
-        <v>0.5414095477339815</v>
+        <v>0.7291737004323724</v>
       </c>
       <c r="AJ11">
-        <v>0.1548362766645394</v>
+        <v>0.6528573046575136</v>
       </c>
       <c r="AK11">
-        <v>0.522508478677487</v>
+        <v>0.6759788911329728</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>147.3272490221643</v>
-      </c>
-      <c r="AP11">
-        <v>138.6751290525036</v>
       </c>
     </row>
     <row r="12">
@@ -1865,7 +1826,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Founder Securities Co., Ltd. (SHSE:601901)</t>
+          <t>Sealand Securities Co., Ltd. (SZSE:000750)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1874,10 +1835,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0231</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="E12">
-        <v>-0.113</v>
+        <v>-0.137</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1886,34 +1847,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.008522546768048742</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.006320036111011559</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>239.3</v>
+        <v>40.2</v>
       </c>
       <c r="L12">
-        <v>0.1892447607750099</v>
+        <v>0.06702234078026009</v>
       </c>
       <c r="M12">
-        <v>142.3</v>
+        <v>109.3</v>
       </c>
       <c r="N12">
-        <v>0.0140064569471239</v>
+        <v>0.04158106977098075</v>
       </c>
       <c r="O12">
-        <v>0.5946510656080234</v>
+        <v>2.718905472636816</v>
       </c>
       <c r="P12">
-        <v>142.3</v>
+        <v>109.3</v>
       </c>
       <c r="Q12">
-        <v>0.0140064569471239</v>
+        <v>0.04158106977098075</v>
       </c>
       <c r="R12">
-        <v>0.5946510656080234</v>
+        <v>2.718905472636816</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1922,67 +1883,61 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1094.4</v>
+        <v>1803</v>
       </c>
       <c r="V12">
-        <v>0.10772077640852</v>
+        <v>0.6859164574298106</v>
       </c>
       <c r="W12">
-        <v>0.04070073985883153</v>
+        <v>0.01395687949171961</v>
       </c>
       <c r="X12">
-        <v>0.05007017634942592</v>
+        <v>0.1240091441873045</v>
       </c>
       <c r="Y12">
-        <v>-0.009369436490594386</v>
+        <v>-0.1100522646955849</v>
       </c>
       <c r="Z12">
-        <v>0.13298884614903</v>
+        <v>0.1265569052426799</v>
       </c>
       <c r="AA12">
-        <v>0.0008404943100236304</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.03714672792808641</v>
+        <v>0.06793646397274622</v>
       </c>
       <c r="AC12">
-        <v>-0.03630623361806278</v>
+        <v>-0.06793646397274622</v>
       </c>
       <c r="AD12">
-        <v>8564.299999999999</v>
+        <v>5671.1</v>
       </c>
       <c r="AE12">
-        <v>104.1161980590118</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>8668.416198059011</v>
+        <v>5671.1</v>
       </c>
       <c r="AG12">
-        <v>7574.016198059011</v>
+        <v>3868.1</v>
       </c>
       <c r="AH12">
-        <v>0.4603998693687464</v>
+        <v>0.6832897574611131</v>
       </c>
       <c r="AI12">
-        <v>0.5697726385813005</v>
+        <v>0.6757825998879872</v>
       </c>
       <c r="AJ12">
-        <v>0.4270993639124775</v>
+        <v>0.5953945849431249</v>
       </c>
       <c r="AK12">
-        <v>0.536425592376844</v>
+        <v>0.5870630909560017</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>271.0221518987341</v>
-      </c>
-      <c r="AP12">
-        <v>239.6840569006016</v>
       </c>
     </row>
     <row r="13">
@@ -1993,7 +1948,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sealand Securities Co., Ltd. (SZSE:000750)</t>
+          <t>Tianfeng Securities Co., Ltd. (SHSE:601162)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2001,12 +1956,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.0181</v>
-      </c>
-      <c r="E13">
-        <v>-0.155</v>
-      </c>
       <c r="G13">
         <v>0</v>
       </c>
@@ -2014,34 +1963,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.01163957330128873</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0.009134854995948119</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>91</v>
+        <v>0.495</v>
       </c>
       <c r="L13">
-        <v>0.1273083379966424</v>
+        <v>0.001070964950237992</v>
       </c>
       <c r="M13">
-        <v>183.4</v>
+        <v>283.1</v>
       </c>
       <c r="N13">
-        <v>0.0520652945351313</v>
+        <v>0.07851021936271112</v>
       </c>
       <c r="O13">
-        <v>2.015384615384615</v>
+        <v>571.9191919191919</v>
       </c>
       <c r="P13">
-        <v>183.4</v>
+        <v>283.1</v>
       </c>
       <c r="Q13">
-        <v>0.0520652945351313</v>
+        <v>0.07851021936271112</v>
       </c>
       <c r="R13">
-        <v>2.015384615384615</v>
+        <v>571.9191919191919</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2050,67 +1999,61 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1544.8</v>
+        <v>1241.7</v>
       </c>
       <c r="V13">
-        <v>0.4385521646557842</v>
+        <v>0.3443523114895033</v>
       </c>
       <c r="W13">
-        <v>0.03311981365555394</v>
+        <v>0.0001220865704772475</v>
       </c>
       <c r="X13">
-        <v>0.05204847326598777</v>
+        <v>0.1237777271433114</v>
       </c>
       <c r="Y13">
-        <v>-0.01892865961043383</v>
+        <v>-0.1236556405728342</v>
       </c>
       <c r="Z13">
-        <v>0.09266689371542636</v>
+        <v>0.04035764804498541</v>
       </c>
       <c r="AA13">
-        <v>0.0008464986370153557</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.03719970294254038</v>
+        <v>0.06794122372061598</v>
       </c>
       <c r="AC13">
-        <v>-0.03635320430552502</v>
+        <v>-0.06794122372061598</v>
       </c>
       <c r="AD13">
-        <v>3407.3</v>
+        <v>7745.4</v>
       </c>
       <c r="AE13">
-        <v>33.90016502119407</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>3441.200165021194</v>
+        <v>7745.4</v>
       </c>
       <c r="AG13">
-        <v>1896.400165021194</v>
+        <v>6503.7</v>
       </c>
       <c r="AH13">
-        <v>0.4941625979685931</v>
+        <v>0.6823359439006986</v>
       </c>
       <c r="AI13">
-        <v>0.5362212818906611</v>
+        <v>0.6817353647910011</v>
       </c>
       <c r="AJ13">
-        <v>0.3499603438465962</v>
+        <v>0.6433192213341774</v>
       </c>
       <c r="AK13">
-        <v>0.3891887661454223</v>
+        <v>0.6426835052768883</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>225.6490066225166</v>
-      </c>
-      <c r="AP13">
-        <v>125.5894149020658</v>
       </c>
     </row>
     <row r="14">
@@ -2121,7 +2064,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minmetals Capital Company Limited (SHSE:600390)</t>
+          <t>Polaris Bay Group Co.,Ltd. (SHSE:600155)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2130,118 +2073,109 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.122</v>
+        <v>0.13</v>
       </c>
       <c r="E14">
-        <v>0.0432</v>
+        <v>0.468</v>
       </c>
       <c r="G14">
-        <v>0.001423027166882277</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0.009119944528185117</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0.006907553948789747</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>592.3</v>
+        <v>88.7</v>
       </c>
       <c r="L14">
-        <v>0.3064941785252264</v>
+        <v>0.2164998779594826</v>
       </c>
       <c r="M14">
-        <v>320.5</v>
+        <v>162</v>
       </c>
       <c r="N14">
-        <v>0.08508322493296876</v>
+        <v>0.09944140936713523</v>
       </c>
       <c r="O14">
-        <v>0.5411109235184873</v>
+        <v>1.826381059751973</v>
       </c>
       <c r="P14">
-        <v>320.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q14">
-        <v>0.08508322493296876</v>
+        <v>0.05641151556073906</v>
       </c>
       <c r="R14">
-        <v>0.5411109235184873</v>
+        <v>1.036076662908681</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>0.432716049382716</v>
       </c>
       <c r="U14">
-        <v>2527.4</v>
+        <v>389.9</v>
       </c>
       <c r="V14">
-        <v>0.6709495871937137</v>
+        <v>0.2393346019274446</v>
       </c>
       <c r="W14">
-        <v>0.1080031363395999</v>
+        <v>0.03600860634108716</v>
       </c>
       <c r="X14">
-        <v>0.07773270071431843</v>
+        <v>0.1219995751494549</v>
       </c>
       <c r="Y14">
-        <v>0.03027043562528149</v>
+        <v>-0.08599096880836778</v>
       </c>
       <c r="Z14">
-        <v>0.165857355209831</v>
+        <v>0.08136071173246484</v>
       </c>
       <c r="AA14">
-        <v>0.001145668628915492</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.03755545230407513</v>
+        <v>0.06797877557626553</v>
       </c>
       <c r="AC14">
-        <v>-0.03640978367515964</v>
+        <v>-0.06797877557626553</v>
       </c>
       <c r="AD14">
-        <v>9665.5</v>
+        <v>3380.6</v>
       </c>
       <c r="AE14">
-        <v>63.87853599641129</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>9729.378535996411</v>
+        <v>3380.6</v>
       </c>
       <c r="AG14">
-        <v>7201.978535996412</v>
+        <v>2990.7</v>
       </c>
       <c r="AH14">
-        <v>0.7208934307369869</v>
+        <v>0.6748108669181787</v>
       </c>
       <c r="AI14">
-        <v>0.5208034533909806</v>
+        <v>0.5943076138740925</v>
       </c>
       <c r="AJ14">
-        <v>0.6565829416709996</v>
+        <v>0.6473656868262696</v>
       </c>
       <c r="AK14">
-        <v>0.4458303529940206</v>
+        <v>0.5644534199003473</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-386.7</v>
-      </c>
-      <c r="AN14">
-        <v>317.9440789473684</v>
-      </c>
-      <c r="AP14">
-        <v>236.9071886840925</v>
-      </c>
-      <c r="AQ14">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2252,7 +2186,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shanxi Securities Co., Ltd. (SZSE:002500)</t>
+          <t>HUAXI Securities Co., Ltd. (SZSE:002926)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2261,10 +2195,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.06059999999999999</v>
+        <v>0.0578</v>
       </c>
       <c r="E15">
-        <v>0.0454</v>
+        <v>-0.138</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2273,34 +2207,34 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.01321323391194478</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0.01072184973999559</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>101</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L15">
-        <v>0.1882221393961983</v>
+        <v>0.1538759689922481</v>
       </c>
       <c r="M15">
-        <v>138.2</v>
+        <v>127</v>
       </c>
       <c r="N15">
-        <v>0.03705491205491205</v>
+        <v>0.04431572335822458</v>
       </c>
       <c r="O15">
-        <v>1.368316831683168</v>
+        <v>1.599496221662468</v>
       </c>
       <c r="P15">
-        <v>138.2</v>
+        <v>127</v>
       </c>
       <c r="Q15">
-        <v>0.03705491205491205</v>
+        <v>0.04431572335822458</v>
       </c>
       <c r="R15">
-        <v>1.368316831683168</v>
+        <v>1.599496221662468</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2309,67 +2243,61 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1197.5</v>
+        <v>501.6</v>
       </c>
       <c r="V15">
-        <v>0.3210800085800086</v>
+        <v>0.1750296601298067</v>
       </c>
       <c r="W15">
-        <v>0.04074880981199064</v>
+        <v>0.02278989667049369</v>
       </c>
       <c r="X15">
-        <v>0.06326094307051222</v>
+        <v>0.1164025241611963</v>
       </c>
       <c r="Y15">
-        <v>-0.02251213325852158</v>
+        <v>-0.09361262749070259</v>
       </c>
       <c r="Z15">
-        <v>0.0810347696900294</v>
+        <v>0.05812663269938504</v>
       </c>
       <c r="AA15">
-        <v>0.0008688426243316445</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03740748074230058</v>
+        <v>0.06810952616987892</v>
       </c>
       <c r="AC15">
-        <v>-0.03653863811796893</v>
+        <v>-0.06810952616987892</v>
       </c>
       <c r="AD15">
-        <v>6223.7</v>
+        <v>5289.8</v>
       </c>
       <c r="AE15">
-        <v>34.54889341425216</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>6258.248893414252</v>
+        <v>5289.8</v>
       </c>
       <c r="AG15">
-        <v>5060.748893414252</v>
+        <v>4788.2</v>
       </c>
       <c r="AH15">
-        <v>0.6265862609856655</v>
+        <v>0.648609544362156</v>
       </c>
       <c r="AI15">
-        <v>0.6968903610237124</v>
+        <v>0.6280483461164011</v>
       </c>
       <c r="AJ15">
-        <v>0.5757164993992191</v>
+        <v>0.6255813953488372</v>
       </c>
       <c r="AK15">
-        <v>0.6502521104974425</v>
+        <v>0.6044943820224719</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
         <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>444.55</v>
-      </c>
-      <c r="AP15">
-        <v>361.4820638153037</v>
       </c>
     </row>
     <row r="16">
@@ -2380,7 +2308,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>China Great Wall Securities Co., Ltd. (SZSE:002939)</t>
+          <t>Western Securities Co., Ltd. (SZSE:002673)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2389,10 +2317,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.161</v>
+        <v>0.154</v>
       </c>
       <c r="E16">
-        <v>0.129</v>
+        <v>0.00387</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2401,34 +2329,34 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0.005026393649174124</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0.004276443767830346</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>264</v>
+        <v>128.9</v>
       </c>
       <c r="L16">
-        <v>0.2166598276569553</v>
+        <v>0.1455674760022586</v>
       </c>
       <c r="M16">
-        <v>178.2</v>
+        <v>139.5</v>
       </c>
       <c r="N16">
-        <v>0.02816767830045524</v>
+        <v>0.03534777651083238</v>
       </c>
       <c r="O16">
-        <v>0.6749999999999999</v>
+        <v>1.082234290147401</v>
       </c>
       <c r="P16">
-        <v>178.2</v>
+        <v>139.5</v>
       </c>
       <c r="Q16">
-        <v>0.02816767830045524</v>
+        <v>0.03534777651083238</v>
       </c>
       <c r="R16">
-        <v>0.6749999999999999</v>
+        <v>1.082234290147401</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2437,67 +2365,61 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>214.1</v>
+        <v>699.9</v>
       </c>
       <c r="V16">
-        <v>0.03384231158320688</v>
+        <v>0.1773470163435956</v>
       </c>
       <c r="W16">
-        <v>0.1008287820341443</v>
+        <v>0.03114880866077039</v>
       </c>
       <c r="X16">
-        <v>0.05383196759273006</v>
+        <v>0.1160425723846438</v>
       </c>
       <c r="Y16">
-        <v>0.04699681444141423</v>
+        <v>-0.08489376372387339</v>
       </c>
       <c r="Z16">
-        <v>0.1577220366785321</v>
+        <v>0.1134350238930926</v>
       </c>
       <c r="AA16">
-        <v>0.0006744894208034178</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.03724208268207346</v>
+        <v>0.0681186597049033</v>
       </c>
       <c r="AC16">
-        <v>-0.03656759326127004</v>
+        <v>-0.0681186597049033</v>
       </c>
       <c r="AD16">
-        <v>6811.5</v>
+        <v>7226.4</v>
       </c>
       <c r="AE16">
-        <v>74.37669669240665</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>6885.876696692407</v>
+        <v>7226.4</v>
       </c>
       <c r="AG16">
-        <v>6671.776696692406</v>
+        <v>6526.5</v>
       </c>
       <c r="AH16">
-        <v>0.5211726074747007</v>
+        <v>0.6467792605321805</v>
       </c>
       <c r="AI16">
-        <v>0.6930106928336534</v>
+        <v>0.6537539466423007</v>
       </c>
       <c r="AJ16">
-        <v>0.5132855824609729</v>
+        <v>0.6231738756803208</v>
       </c>
       <c r="AK16">
-        <v>0.6862501608285237</v>
+        <v>0.6303482779269447</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
         <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>324.3571428571428</v>
-      </c>
-      <c r="AP16">
-        <v>317.7036522234479</v>
       </c>
     </row>
     <row r="17">
@@ -2508,7 +2430,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nanjing Securities Co., Ltd. (SHSE:601990)</t>
+          <t>Southwest Securities Co., Ltd. (SHSE:600369)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2517,10 +2439,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.07400000000000001</v>
+        <v>-0.108</v>
       </c>
       <c r="E17">
-        <v>0.0809</v>
+        <v>-0.044</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2529,34 +2451,34 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0.006667423685099853</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>0.005229621047911568</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>151.7</v>
+        <v>50.7</v>
       </c>
       <c r="L17">
-        <v>0.3948464341488808</v>
+        <v>0.213743676222597</v>
       </c>
       <c r="M17">
-        <v>142.7</v>
+        <v>170.4</v>
       </c>
       <c r="N17">
-        <v>0.02481437042447006</v>
+        <v>0.0471643278252927</v>
       </c>
       <c r="O17">
-        <v>0.94067237969677</v>
+        <v>3.36094674556213</v>
       </c>
       <c r="P17">
-        <v>142.7</v>
+        <v>170.4</v>
       </c>
       <c r="Q17">
-        <v>0.02481437042447006</v>
+        <v>0.0471643278252927</v>
       </c>
       <c r="R17">
-        <v>0.94067237969677</v>
+        <v>3.36094674556213</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2565,67 +2487,61 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>194.9</v>
+        <v>685</v>
       </c>
       <c r="V17">
-        <v>0.03389152624897838</v>
+        <v>0.1895983835699853</v>
       </c>
       <c r="W17">
-        <v>0.09048613182224872</v>
+        <v>0.01293499336667007</v>
       </c>
       <c r="X17">
-        <v>0.04663414625899558</v>
+        <v>0.111132476235977</v>
       </c>
       <c r="Y17">
-        <v>0.04385198556325314</v>
+        <v>-0.09819748286930696</v>
       </c>
       <c r="Z17">
-        <v>0.08488392538044505</v>
+        <v>0.02510106033990138</v>
       </c>
       <c r="AA17">
-        <v>0.0004439107627989305</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.03703570554873754</v>
+        <v>0.06825347812683331</v>
       </c>
       <c r="AC17">
-        <v>-0.03659179478593861</v>
+        <v>-0.06825347812683331</v>
       </c>
       <c r="AD17">
-        <v>3656.5</v>
+        <v>5888.8</v>
       </c>
       <c r="AE17">
-        <v>14.64187910092318</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>3671.141879100923</v>
+        <v>5888.8</v>
       </c>
       <c r="AG17">
-        <v>3476.241879100923</v>
+        <v>5203.8</v>
       </c>
       <c r="AH17">
-        <v>0.3896416354899856</v>
+        <v>0.6197627792921266</v>
       </c>
       <c r="AI17">
-        <v>0.5866560094722814</v>
+        <v>0.6273223112323163</v>
       </c>
       <c r="AJ17">
-        <v>0.3767490816187573</v>
+        <v>0.5902208309231345</v>
       </c>
       <c r="AK17">
-        <v>0.573368388689765</v>
+        <v>0.5979867160028498</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
         <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>666.0291438979963</v>
-      </c>
-      <c r="AP17">
-        <v>633.1952420948858</v>
       </c>
     </row>
     <row r="18">
@@ -2636,7 +2552,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hongta Securities Co., Ltd. (SHSE:601236)</t>
+          <t>Caitong Securities Co.,Ltd. (SHSE:601108)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2644,6 +2560,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.06179999999999999</v>
+      </c>
+      <c r="E18">
+        <v>0.0482</v>
+      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2657,28 +2579,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>239.6</v>
+        <v>288.3</v>
       </c>
       <c r="L18">
-        <v>0.2006700167504188</v>
+        <v>0.3879171151776103</v>
       </c>
       <c r="M18">
-        <v>189.3</v>
+        <v>272.5</v>
       </c>
       <c r="N18">
-        <v>0.02138838044878313</v>
+        <v>0.05684544297724096</v>
       </c>
       <c r="O18">
-        <v>0.7900667779632722</v>
+        <v>0.9451959764134582</v>
       </c>
       <c r="P18">
-        <v>189.3</v>
+        <v>272.5</v>
       </c>
       <c r="Q18">
-        <v>0.02138838044878313</v>
+        <v>0.05684544297724096</v>
       </c>
       <c r="R18">
-        <v>0.7900667779632722</v>
+        <v>0.9451959764134582</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2687,55 +2609,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>894</v>
+        <v>513.6</v>
       </c>
       <c r="V18">
-        <v>0.101010101010101</v>
+        <v>0.1071406220664622</v>
       </c>
       <c r="W18">
-        <v>0.1167641325536062</v>
+        <v>0.07800957869956977</v>
       </c>
       <c r="X18">
-        <v>0.03947243299297234</v>
+        <v>0.1101750222964535</v>
       </c>
       <c r="Y18">
-        <v>0.07729169956063389</v>
+        <v>-0.03216544359688368</v>
       </c>
       <c r="Z18">
-        <v>0.2519093632642728</v>
+        <v>0.06695736783307507</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.03667551053014014</v>
+        <v>0.06828220654179795</v>
       </c>
       <c r="AC18">
-        <v>-0.03667551053014014</v>
+        <v>-0.06828220654179795</v>
       </c>
       <c r="AD18">
-        <v>1686.8</v>
+        <v>7625.4</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>1686.8</v>
+        <v>7625.4</v>
       </c>
       <c r="AG18">
-        <v>792.8</v>
+        <v>7111.799999999999</v>
       </c>
       <c r="AH18">
-        <v>0.1600774384573045</v>
+        <v>0.6140058458342392</v>
       </c>
       <c r="AI18">
-        <v>0.3204468169988032</v>
+        <v>0.6244697403980017</v>
       </c>
       <c r="AJ18">
-        <v>0.08221166808387083</v>
+        <v>0.5973541640418294</v>
       </c>
       <c r="AK18">
-        <v>0.1814229158561981</v>
+        <v>0.6079812607929966</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2752,7 +2674,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Huaan Securities Co., Ltd. (SHSE:600909)</t>
+          <t>Soochow Securities Co., Ltd. (SHSE:601555)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2761,10 +2683,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0669</v>
+        <v>0.206</v>
       </c>
       <c r="E19">
-        <v>0.0616</v>
+        <v>0.103</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2773,103 +2695,97 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0.008800119880258462</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>0.006660339693606404</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>191.5</v>
+        <v>242.1</v>
       </c>
       <c r="L19">
-        <v>0.4035827186512118</v>
+        <v>0.1502513498417427</v>
       </c>
       <c r="M19">
-        <v>137.3</v>
+        <v>410.8</v>
       </c>
       <c r="N19">
-        <v>0.03431985202219667</v>
+        <v>0.08665021409437028</v>
       </c>
       <c r="O19">
-        <v>0.7169712793733682</v>
+        <v>1.696819496076002</v>
       </c>
       <c r="P19">
-        <v>137.3</v>
+        <v>361.5</v>
       </c>
       <c r="Q19">
-        <v>0.03431985202219667</v>
+        <v>0.07625134468138961</v>
       </c>
       <c r="R19">
-        <v>0.7169712793733682</v>
+        <v>1.493184634448575</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>49.30000000000001</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.1200097370983447</v>
       </c>
       <c r="U19">
-        <v>315.8</v>
+        <v>600</v>
       </c>
       <c r="V19">
-        <v>0.07893815927610859</v>
+        <v>0.1265582484338417</v>
       </c>
       <c r="W19">
-        <v>0.09100845927193234</v>
+        <v>0.0542946849069298</v>
       </c>
       <c r="X19">
-        <v>0.0548023236636408</v>
+        <v>0.1056667292992553</v>
       </c>
       <c r="Y19">
-        <v>0.03620613560829154</v>
+        <v>-0.05137204439232548</v>
       </c>
       <c r="Z19">
-        <v>0.08785804233187737</v>
+        <v>0.143623706423981</v>
       </c>
       <c r="AA19">
-        <v>0.0005851644067455546</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.03726329306389253</v>
+        <v>0.06843006700303009</v>
       </c>
       <c r="AC19">
-        <v>-0.03667812865714698</v>
+        <v>-0.06843006700303009</v>
       </c>
       <c r="AD19">
-        <v>4556</v>
+        <v>6665.8</v>
       </c>
       <c r="AE19">
-        <v>41.1217155840868</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>4597.121715584087</v>
+        <v>6665.8</v>
       </c>
       <c r="AG19">
-        <v>4281.321715584087</v>
+        <v>6065.8</v>
       </c>
       <c r="AH19">
-        <v>0.5346906852371625</v>
+        <v>0.5843758492815626</v>
       </c>
       <c r="AI19">
-        <v>0.6005916508871602</v>
+        <v>0.5533758934723594</v>
       </c>
       <c r="AJ19">
-        <v>0.516947860969022</v>
+        <v>0.5612999343000176</v>
       </c>
       <c r="AK19">
-        <v>0.5834038354744213</v>
+        <v>0.5299632176275807</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
         <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>367.4193548387097</v>
-      </c>
-      <c r="AP19">
-        <v>345.2678802890392</v>
       </c>
     </row>
     <row r="20">
@@ -2880,7 +2796,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HUAXI Securities Co., Ltd. (SZSE:002926)</t>
+          <t>Huaan Securities Co., Ltd. (SHSE:600909)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2888,6 +2804,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.132</v>
+      </c>
+      <c r="E20">
+        <v>0.154</v>
+      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2895,34 +2817,34 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0.007603091240665018</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0.005942361826037376</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>280.6</v>
+        <v>198.7</v>
       </c>
       <c r="L20">
-        <v>0.3468479604449938</v>
+        <v>0.3966067864271457</v>
       </c>
       <c r="M20">
-        <v>161.4</v>
+        <v>133</v>
       </c>
       <c r="N20">
-        <v>0.03965407105301951</v>
+        <v>0.04254366323331841</v>
       </c>
       <c r="O20">
-        <v>0.5751960085531005</v>
+        <v>0.669350780070458</v>
       </c>
       <c r="P20">
-        <v>161.4</v>
+        <v>133</v>
       </c>
       <c r="Q20">
-        <v>0.03965407105301951</v>
+        <v>0.04254366323331841</v>
       </c>
       <c r="R20">
-        <v>0.5751960085531005</v>
+        <v>0.669350780070458</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2931,67 +2853,61 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>524.4</v>
+        <v>227.2</v>
       </c>
       <c r="V20">
-        <v>0.1288388776964277</v>
+        <v>0.07267609238052587</v>
       </c>
       <c r="W20">
-        <v>0.09096213692946058</v>
+        <v>0.06728294731139103</v>
       </c>
       <c r="X20">
-        <v>0.05981360918045969</v>
+        <v>0.1050561392839482</v>
       </c>
       <c r="Y20">
-        <v>0.03114852774900089</v>
+        <v>-0.03777319197255717</v>
       </c>
       <c r="Z20">
-        <v>0.1015104160682323</v>
+        <v>0.06965292821744393</v>
       </c>
       <c r="AA20">
-        <v>0.0006032116213890348</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.03735619417315464</v>
+        <v>0.06845185656300484</v>
       </c>
       <c r="AC20">
-        <v>-0.0367529825517656</v>
+        <v>-0.06845185656300484</v>
       </c>
       <c r="AD20">
-        <v>5919.7</v>
+        <v>4317.3</v>
       </c>
       <c r="AE20">
-        <v>32.74549593151</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>5952.44549593151</v>
+        <v>4317.3</v>
       </c>
       <c r="AG20">
-        <v>5428.04549593151</v>
+        <v>4090.1</v>
       </c>
       <c r="AH20">
-        <v>0.593899634417658</v>
+        <v>0.5800094041781421</v>
       </c>
       <c r="AI20">
-        <v>0.6307597620965121</v>
+        <v>0.6054439894541987</v>
       </c>
       <c r="AJ20">
-        <v>0.5714787534452089</v>
+        <v>0.5667863032301873</v>
       </c>
       <c r="AK20">
-        <v>0.6090342538402032</v>
+        <v>0.5924590068949533</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>466.1181102362205</v>
-      </c>
-      <c r="AP20">
-        <v>427.4051571599614</v>
       </c>
     </row>
     <row r="21">
@@ -3002,7 +2918,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Holly Futures Co., Ltd. (SEHK:3678)</t>
+          <t>Central China Securities Co., Ltd. (SEHK:1375)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3011,10 +2927,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.433</v>
+        <v>0.00603</v>
       </c>
       <c r="E21">
-        <v>0.0622</v>
+        <v>-0.236</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3029,28 +2945,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>10.5</v>
+        <v>16.7</v>
       </c>
       <c r="L21">
-        <v>0.03977272727272727</v>
+        <v>0.05024067388688327</v>
       </c>
       <c r="M21">
-        <v>8.69</v>
+        <v>104.1</v>
       </c>
       <c r="N21">
-        <v>0.07047850770478507</v>
+        <v>0.052240678476439</v>
       </c>
       <c r="O21">
-        <v>0.8276190476190476</v>
+        <v>6.233532934131737</v>
       </c>
       <c r="P21">
-        <v>8.69</v>
+        <v>104.1</v>
       </c>
       <c r="Q21">
-        <v>0.07047850770478507</v>
+        <v>0.052240678476439</v>
       </c>
       <c r="R21">
-        <v>0.8276190476190476</v>
+        <v>6.233532934131737</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3059,55 +2975,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>472</v>
+        <v>236.8</v>
       </c>
       <c r="V21">
-        <v>3.828061638280616</v>
+        <v>0.1188337431625433</v>
       </c>
       <c r="W21">
-        <v>0.04531722054380665</v>
+        <v>0.007809942477669175</v>
       </c>
       <c r="X21">
-        <v>0.04139224029994179</v>
+        <v>0.1045474149322008</v>
       </c>
       <c r="Y21">
-        <v>0.00392498024386486</v>
+        <v>-0.09673747245453163</v>
       </c>
       <c r="Z21">
-        <v>-1.914430746918056</v>
+        <v>0.05790506982926365</v>
       </c>
       <c r="AA21">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.03679621274323455</v>
+        <v>0.06847036365660483</v>
       </c>
       <c r="AC21">
-        <v>-0.03679621274323455</v>
+        <v>-0.06847036365660483</v>
       </c>
       <c r="AD21">
-        <v>38.3</v>
+        <v>2710.4</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>38.3</v>
+        <v>2710.4</v>
       </c>
       <c r="AG21">
-        <v>-433.7</v>
+        <v>2473.6</v>
       </c>
       <c r="AH21">
-        <v>0.2370049504950495</v>
+        <v>0.5763007378112308</v>
       </c>
       <c r="AI21">
-        <v>0.130716723549488</v>
+        <v>0.5761169918802873</v>
       </c>
       <c r="AJ21">
-        <v>1.397229381443299</v>
+        <v>0.553836508967154</v>
       </c>
       <c r="AK21">
-        <v>2.422905027932961</v>
+        <v>0.5536505662742289</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3124,7 +3040,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LUZHENG FUTURES Company Limited (SEHK:1461)</t>
+          <t>Zheshang Securities Co., Ltd. (SHSE:601878)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3133,10 +3049,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0102</v>
+        <v>0.285</v>
       </c>
       <c r="E22">
-        <v>0.0141</v>
+        <v>0.104</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3151,28 +3067,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>15.4</v>
+        <v>247.9</v>
       </c>
       <c r="L22">
-        <v>0.1500974658869396</v>
+        <v>0.1112756979980249</v>
       </c>
       <c r="M22">
-        <v>4.0076</v>
+        <v>201.3</v>
       </c>
       <c r="N22">
-        <v>0.04953770086526576</v>
+        <v>0.03605330085610919</v>
       </c>
       <c r="O22">
-        <v>0.2602337662337662</v>
+        <v>0.8120209762000807</v>
       </c>
       <c r="P22">
-        <v>4.0076</v>
+        <v>201.3</v>
       </c>
       <c r="Q22">
-        <v>0.04953770086526576</v>
+        <v>0.03605330085610919</v>
       </c>
       <c r="R22">
-        <v>0.2602337662337662</v>
+        <v>0.8120209762000807</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3181,55 +3097,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>146.6</v>
+        <v>1140.4</v>
       </c>
       <c r="V22">
-        <v>1.812113720642769</v>
+        <v>0.2042483074828958</v>
       </c>
       <c r="W22">
-        <v>0.04885786802030457</v>
+        <v>0.06876178852768224</v>
       </c>
       <c r="X22">
-        <v>0.04160386499798846</v>
+        <v>0.102410713349996</v>
       </c>
       <c r="Y22">
-        <v>0.007254003022316109</v>
+        <v>-0.03364892482231373</v>
       </c>
       <c r="Z22">
-        <v>0.4174125305126119</v>
+        <v>0.2165557545040448</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.03680817859856287</v>
+        <v>0.06855180245267847</v>
       </c>
       <c r="AC22">
-        <v>-0.03680817859856287</v>
+        <v>-0.06855180245267847</v>
       </c>
       <c r="AD22">
-        <v>26.2</v>
+        <v>7105.6</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>26.2</v>
+        <v>7105.6</v>
       </c>
       <c r="AG22">
-        <v>-120.4</v>
+        <v>5965.200000000001</v>
       </c>
       <c r="AH22">
-        <v>0.2446311858076564</v>
+        <v>0.5599810859799826</v>
       </c>
       <c r="AI22">
-        <v>0.06851464435146444</v>
+        <v>0.6536770252617247</v>
       </c>
       <c r="AJ22">
-        <v>3.048101265822786</v>
+        <v>0.5165301421817363</v>
       </c>
       <c r="AK22">
-        <v>-0.5106022052586937</v>
+        <v>0.6130855721597567</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3246,7 +3162,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nanhua Futures Co., Ltd. (SHSE:603093)</t>
+          <t>Founder Securities Co., Ltd. (SHSE:601901)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3254,8 +3170,14 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D23">
+        <v>0.0493</v>
+      </c>
+      <c r="E23">
+        <v>0.0824</v>
+      </c>
       <c r="G23">
-        <v>0.003888652783680408</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3267,28 +3189,28 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>30.7</v>
+        <v>257.9</v>
       </c>
       <c r="L23">
-        <v>0.02174528970109081</v>
+        <v>0.2318827549001978</v>
       </c>
       <c r="M23">
-        <v>4.5</v>
+        <v>136.7</v>
       </c>
       <c r="N23">
-        <v>0.003450655624568668</v>
+        <v>0.01795188317486999</v>
       </c>
       <c r="O23">
-        <v>0.1465798045602606</v>
+        <v>0.5300504071345483</v>
       </c>
       <c r="P23">
-        <v>4.5</v>
+        <v>136.7</v>
       </c>
       <c r="Q23">
-        <v>0.003450655624568668</v>
+        <v>0.01795188317486999</v>
       </c>
       <c r="R23">
-        <v>0.1465798045602606</v>
+        <v>0.5300504071345483</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3297,55 +3219,55 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>331.3</v>
+        <v>735.9</v>
       </c>
       <c r="V23">
-        <v>0.2540449352043555</v>
+        <v>0.09664075221936229</v>
       </c>
       <c r="W23">
-        <v>0.08464295561069754</v>
+        <v>0.04014632627646326</v>
       </c>
       <c r="X23">
-        <v>0.03784572048072001</v>
+        <v>0.101098615533687</v>
       </c>
       <c r="Y23">
-        <v>0.04679723512997753</v>
+        <v>-0.06095228925722373</v>
       </c>
       <c r="Z23">
-        <v>5.046865281084443</v>
+        <v>0.0843086719223772</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.03683508642797079</v>
+        <v>0.06860499647943402</v>
       </c>
       <c r="AC23">
-        <v>-0.03683508642797079</v>
+        <v>-0.06860499647943402</v>
       </c>
       <c r="AD23">
-        <v>115.9</v>
+        <v>9281.5</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>115.9</v>
+        <v>9281.5</v>
       </c>
       <c r="AG23">
-        <v>-215.4</v>
+        <v>8545.6</v>
       </c>
       <c r="AH23">
-        <v>0.08161971830985916</v>
+        <v>0.5493214490746495</v>
       </c>
       <c r="AI23">
-        <v>0.1995523415977962</v>
+        <v>0.6011256330876543</v>
       </c>
       <c r="AJ23">
-        <v>-0.1978506475613117</v>
+        <v>0.5287987921091062</v>
       </c>
       <c r="AK23">
-        <v>-0.8633266533066134</v>
+        <v>0.5811633331746496</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3362,7 +3284,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Soochow Securities Co., Ltd. (SHSE:601555)</t>
+          <t>Guolian Securities Co., Ltd. (SEHK:1456)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3371,10 +3293,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.09880000000000001</v>
+        <v>0.153</v>
       </c>
       <c r="E24">
-        <v>0.0614</v>
+        <v>0.149</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3383,103 +3305,97 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0.003718468990637197</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>0.002803607572305823</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>311.8</v>
+        <v>123</v>
       </c>
       <c r="L24">
-        <v>0.2681689171755397</v>
+        <v>0.266695576756288</v>
       </c>
       <c r="M24">
-        <v>261.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="N24">
-        <v>0.03742840778923253</v>
+        <v>0.0160654230480753</v>
       </c>
       <c r="O24">
-        <v>0.838357921744708</v>
+        <v>0.5398373983739838</v>
       </c>
       <c r="P24">
-        <v>207</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Q24">
-        <v>0.02963917525773196</v>
+        <v>0.0160654230480753</v>
       </c>
       <c r="R24">
-        <v>0.6638871071199487</v>
+        <v>0.5398373983739838</v>
       </c>
       <c r="S24">
-        <v>54.39999999999998</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>0.2081101759755164</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>423.7</v>
+        <v>442.6</v>
       </c>
       <c r="V24">
-        <v>0.06066723940435281</v>
+        <v>0.1070866903776826</v>
       </c>
       <c r="W24">
-        <v>0.08112397554312475</v>
+        <v>0.0493718139124152</v>
       </c>
       <c r="X24">
-        <v>0.05429397434496577</v>
+        <v>0.09975597968399728</v>
       </c>
       <c r="Y24">
-        <v>0.02683000119815898</v>
+        <v>-0.05038416577158208</v>
       </c>
       <c r="Z24">
-        <v>0.1282627933198574</v>
+        <v>0.06726562044221457</v>
       </c>
       <c r="AA24">
-        <v>0.000359598538596649</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.03725233298863279</v>
+        <v>0.06866216434146502</v>
       </c>
       <c r="AC24">
-        <v>-0.03689273445003614</v>
+        <v>-0.06866216434146502</v>
       </c>
       <c r="AD24">
-        <v>7767.5</v>
+        <v>4810.4</v>
       </c>
       <c r="AE24">
-        <v>35.88268052293066</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>7803.382680522931</v>
+        <v>4810.4</v>
       </c>
       <c r="AG24">
-        <v>7379.682680522931</v>
+        <v>4367.799999999999</v>
       </c>
       <c r="AH24">
-        <v>0.5277054668234891</v>
+        <v>0.5378654889025549</v>
       </c>
       <c r="AI24">
-        <v>0.6387062609029155</v>
+        <v>0.6722942754919499</v>
       </c>
       <c r="AJ24">
-        <v>0.513773719780773</v>
+        <v>0.5138044207083955</v>
       </c>
       <c r="AK24">
-        <v>0.625726527309194</v>
+        <v>0.6506867681673271</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
         <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>675.4347826086956</v>
-      </c>
-      <c r="AP24">
-        <v>641.7115374367767</v>
       </c>
     </row>
     <row r="25">
@@ -3490,7 +3406,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BOC International (China) CO., LTD (SHSE:601696)</t>
+          <t>Nanjing Securities Co., Ltd. (SHSE:601990)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3498,6 +3414,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D25">
+        <v>0.118</v>
+      </c>
+      <c r="E25">
+        <v>0.138</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3505,34 +3427,34 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0.01971253410147801</v>
+        <v>0.008769631162784897</v>
       </c>
       <c r="J25">
-        <v>0.01589754208289929</v>
+        <v>0.007135290809720438</v>
       </c>
       <c r="K25">
-        <v>151.8</v>
+        <v>88.5</v>
       </c>
       <c r="L25">
-        <v>0.3561708118254341</v>
+        <v>0.3012253233492171</v>
       </c>
       <c r="M25">
-        <v>95.09999999999999</v>
+        <v>121.1</v>
       </c>
       <c r="N25">
-        <v>0.01616879473621572</v>
+        <v>0.0285721026802567</v>
       </c>
       <c r="O25">
-        <v>0.6264822134387351</v>
+        <v>1.368361581920904</v>
       </c>
       <c r="P25">
-        <v>95.09999999999999</v>
+        <v>121.1</v>
       </c>
       <c r="Q25">
-        <v>0.01616879473621572</v>
+        <v>0.0285721026802567</v>
       </c>
       <c r="R25">
-        <v>0.6264822134387351</v>
+        <v>1.368361581920904</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3541,55 +3463,55 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>408.2</v>
+        <v>318.3</v>
       </c>
       <c r="V25">
-        <v>0.06940170358909839</v>
+        <v>0.075099093997735</v>
       </c>
       <c r="W25">
-        <v>0.06888102368635993</v>
+        <v>0.03494018713727348</v>
       </c>
       <c r="X25">
-        <v>0.04355503625104543</v>
+        <v>0.08981657889063055</v>
       </c>
       <c r="Y25">
-        <v>0.02532598743531449</v>
+        <v>-0.05487639175335707</v>
       </c>
       <c r="Z25">
-        <v>0.1124095563692339</v>
+        <v>0.04892092224658184</v>
       </c>
       <c r="AA25">
-        <v>0.001787035652899935</v>
+        <v>0.0003490650069090836</v>
       </c>
       <c r="AB25">
-        <v>0.03868081169917646</v>
+        <v>0.06919672141787392</v>
       </c>
       <c r="AC25">
-        <v>-0.03689377604627652</v>
+        <v>-0.06884765641096484</v>
       </c>
       <c r="AD25">
-        <v>2587.4</v>
+        <v>3195.1</v>
       </c>
       <c r="AE25">
-        <v>34.99258982975037</v>
+        <v>12.01741182186899</v>
       </c>
       <c r="AF25">
-        <v>2622.39258982975</v>
+        <v>3207.117411821869</v>
       </c>
       <c r="AG25">
-        <v>2214.19258982975</v>
+        <v>2888.817411821869</v>
       </c>
       <c r="AH25">
-        <v>0.308368301747553</v>
+        <v>0.4307447332981401</v>
       </c>
       <c r="AI25">
-        <v>0.5184958443506398</v>
+        <v>0.5731890605440466</v>
       </c>
       <c r="AJ25">
-        <v>0.2734957962030364</v>
+        <v>0.4053219152582895</v>
       </c>
       <c r="AK25">
-        <v>0.4762224150379444</v>
+        <v>0.5474441205674464</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3598,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="AN25">
-        <v>168.012987012987</v>
+        <v>641.586345381526</v>
       </c>
       <c r="AP25">
-        <v>143.7787395993344</v>
+        <v>580.0838176349133</v>
       </c>
     </row>
     <row r="26">
@@ -3612,7 +3534,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yongan Futures Co.,Ltd. (SHSE:600927)</t>
+          <t>Sinolink Securities Co., Ltd. (SHSE:600109)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3621,13 +3543,13 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.459</v>
+        <v>0.0694</v>
       </c>
       <c r="E26">
-        <v>0.248</v>
+        <v>0.066</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>0.0151497629235573</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3639,28 +3561,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>228.5</v>
+        <v>225.1</v>
       </c>
       <c r="L26">
-        <v>0.04753880081554529</v>
+        <v>0.260321498785706</v>
       </c>
       <c r="M26">
-        <v>33.8</v>
+        <v>126.6</v>
       </c>
       <c r="N26">
-        <v>0.003931649780734916</v>
+        <v>0.02694878453744306</v>
       </c>
       <c r="O26">
-        <v>0.1479212253829321</v>
+        <v>0.5624167036872501</v>
       </c>
       <c r="P26">
-        <v>33.8</v>
+        <v>126.6</v>
       </c>
       <c r="Q26">
-        <v>0.003931649780734916</v>
+        <v>0.02694878453744306</v>
       </c>
       <c r="R26">
-        <v>0.1479212253829321</v>
+        <v>0.5624167036872501</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3669,55 +3591,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>602.3</v>
+        <v>723.8</v>
       </c>
       <c r="V26">
-        <v>0.07006013795670532</v>
+        <v>0.1540721188641491</v>
       </c>
       <c r="W26">
-        <v>0.2214361856769066</v>
+        <v>0.06132512395793603</v>
       </c>
       <c r="X26">
-        <v>0.03760027118078335</v>
+        <v>0.09414671815492817</v>
       </c>
       <c r="Y26">
-        <v>0.1838359144961233</v>
+        <v>-0.03282159419699214</v>
       </c>
       <c r="Z26">
-        <v>5.455845629965948</v>
+        <v>0.1109339258704279</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.03692551945480892</v>
+        <v>0.06893616971669901</v>
       </c>
       <c r="AC26">
-        <v>-0.03692551945480892</v>
+        <v>-0.06893616971669901</v>
       </c>
       <c r="AD26">
-        <v>632.1</v>
+        <v>4388.1</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>632.1</v>
+        <v>4388.1</v>
       </c>
       <c r="AG26">
-        <v>29.80000000000007</v>
+        <v>3664.3</v>
       </c>
       <c r="AH26">
-        <v>0.06849062737024597</v>
+        <v>0.4829571093672613</v>
       </c>
       <c r="AI26">
-        <v>0.3237222165318038</v>
+        <v>0.5028476479688306</v>
       </c>
       <c r="AJ26">
-        <v>0.003454391598177759</v>
+        <v>0.4382033221320004</v>
       </c>
       <c r="AK26">
-        <v>0.02206916981411543</v>
+        <v>0.4578829644994815</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3734,7 +3656,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guosen Securities Co., Ltd. (SZSE:002736)</t>
+          <t>Guangdong Golden Dragon Development Inc. (SZSE:000712)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3743,115 +3665,106 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.0527</v>
-      </c>
-      <c r="E27">
-        <v>0.0635</v>
+        <v>-0.367</v>
       </c>
       <c r="G27">
-        <v>0.0348476718535742</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0.002574837497444433</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>0.002035290470441068</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>1387.5</v>
+        <v>-55.4</v>
       </c>
       <c r="L27">
-        <v>0.4136111607941335</v>
+        <v>-2.78391959798995</v>
       </c>
       <c r="M27">
-        <v>1486</v>
+        <v>73.8</v>
       </c>
       <c r="N27">
-        <v>0.08554487363997466</v>
+        <v>0.04390243902439024</v>
       </c>
       <c r="O27">
-        <v>1.070990990990991</v>
+        <v>-1.332129963898917</v>
       </c>
       <c r="P27">
-        <v>710.1</v>
+        <v>73.8</v>
       </c>
       <c r="Q27">
-        <v>0.04087847562028669</v>
+        <v>0.04390243902439024</v>
       </c>
       <c r="R27">
-        <v>0.5117837837837838</v>
+        <v>-1.332129963898917</v>
       </c>
       <c r="S27">
-        <v>775.9</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>0.5221399730820996</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1035.1</v>
+        <v>169.6</v>
       </c>
       <c r="V27">
-        <v>0.05958781877842381</v>
+        <v>0.1008923259964307</v>
       </c>
       <c r="W27">
-        <v>0.1187399445452367</v>
+        <v>-0.103319656844461</v>
       </c>
       <c r="X27">
-        <v>0.06128189554369119</v>
+        <v>0.09356034925321166</v>
       </c>
       <c r="Y27">
-        <v>0.05745804900154551</v>
+        <v>-0.1968800060976727</v>
       </c>
       <c r="Z27">
-        <v>0.1203085620865138</v>
+        <v>0.01139291234900097</v>
       </c>
       <c r="AA27">
-        <v>0.0002448628699271491</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.03737909636358951</v>
+        <v>0.06896861939382543</v>
       </c>
       <c r="AC27">
-        <v>-0.03713423349366236</v>
+        <v>-0.06896861939382543</v>
       </c>
       <c r="AD27">
-        <v>26937.1</v>
+        <v>1529.8</v>
       </c>
       <c r="AE27">
-        <v>61.81225065536453</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>26998.91225065536</v>
+        <v>1529.8</v>
       </c>
       <c r="AG27">
-        <v>25963.81225065536</v>
+        <v>1360.2</v>
       </c>
       <c r="AH27">
-        <v>0.6084959577592263</v>
+        <v>0.4764544661766538</v>
       </c>
       <c r="AI27">
-        <v>0.6478581256456345</v>
+        <v>0.6747827621190067</v>
       </c>
       <c r="AJ27">
-        <v>0.5991444499742284</v>
+        <v>0.4472576614494279</v>
       </c>
       <c r="AK27">
-        <v>0.6388888610410717</v>
+        <v>0.6484862932061979</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
         <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>1282.719047619048</v>
-      </c>
-      <c r="AP27">
-        <v>1236.37201193597</v>
       </c>
     </row>
     <row r="28">
@@ -3862,7 +3775,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caitong Securities Co.,Ltd. (SHSE:601108)</t>
+          <t>First Capital Securities Co., Ltd. (SZSE:002797)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3871,10 +3784,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>-0.0198</v>
+        <v>0.0643</v>
       </c>
       <c r="E28">
-        <v>-0.0314</v>
+        <v>0.011</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3883,34 +3796,34 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0.001851158539762447</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>0.001554027757274357</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>368.1</v>
+        <v>64.8</v>
       </c>
       <c r="L28">
-        <v>0.3980750513680112</v>
+        <v>0.1741467347487234</v>
       </c>
       <c r="M28">
-        <v>270.6</v>
+        <v>71.5</v>
       </c>
       <c r="N28">
-        <v>0.04307271106583472</v>
+        <v>0.02084365798909716</v>
       </c>
       <c r="O28">
-        <v>0.7351263243683782</v>
+        <v>1.103395061728395</v>
       </c>
       <c r="P28">
-        <v>270.6</v>
+        <v>71.5</v>
       </c>
       <c r="Q28">
-        <v>0.04307271106583472</v>
+        <v>0.02084365798909716</v>
       </c>
       <c r="R28">
-        <v>0.7351263243683782</v>
+        <v>1.103395061728395</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3919,67 +3832,61 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>572.1</v>
+        <v>1190.1</v>
       </c>
       <c r="V28">
-        <v>0.0910639246147969</v>
+        <v>0.3469375856339095</v>
       </c>
       <c r="W28">
-        <v>0.1122838056309673</v>
+        <v>0.02913800080938891</v>
       </c>
       <c r="X28">
-        <v>0.05698346107239022</v>
+        <v>0.09090998434705272</v>
       </c>
       <c r="Y28">
-        <v>0.05530034455857704</v>
+        <v>-0.06177198353766381</v>
       </c>
       <c r="Z28">
-        <v>0.09870688147933923</v>
+        <v>0.08119153652964549</v>
       </c>
       <c r="AA28">
-        <v>0.0001533932336528833</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.03730685856505267</v>
+        <v>0.06912608666117273</v>
       </c>
       <c r="AC28">
-        <v>-0.03715346533139979</v>
+        <v>-0.06912608666117273</v>
       </c>
       <c r="AD28">
-        <v>7976</v>
+        <v>2749.3</v>
       </c>
       <c r="AE28">
-        <v>99.94116849140832</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>8075.941168491408</v>
+        <v>2749.3</v>
       </c>
       <c r="AG28">
-        <v>7503.841168491408</v>
+        <v>1559.2</v>
       </c>
       <c r="AH28">
-        <v>0.5624564198414241</v>
+        <v>0.4448993462360024</v>
       </c>
       <c r="AI28">
-        <v>0.6859631641982805</v>
+        <v>0.5634157837571981</v>
       </c>
       <c r="AJ28">
-        <v>0.5442992819276593</v>
+        <v>0.3124962421084277</v>
       </c>
       <c r="AK28">
-        <v>0.6699235415364562</v>
+        <v>0.4225932350390287</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
         <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>367.557603686636</v>
-      </c>
-      <c r="AP28">
-        <v>345.7991321885441</v>
       </c>
     </row>
     <row r="29">
@@ -3990,7 +3897,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Western Securities Co., Ltd. (SZSE:002673)</t>
+          <t>Nanhua Futures Co., Ltd. (SHSE:603093)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3998,47 +3905,41 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D29">
-        <v>0.0888</v>
-      </c>
-      <c r="E29">
-        <v>0.00021</v>
-      </c>
       <c r="G29">
-        <v>0</v>
+        <v>0.004540705617616331</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>-0.0003330801525218429</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>-0.0002508247777317209</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>183.3</v>
+        <v>28.8</v>
       </c>
       <c r="L29">
-        <v>0.1876919926274831</v>
+        <v>0.02314554367917705</v>
       </c>
       <c r="M29">
-        <v>83.59999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="N29">
-        <v>0.01472375350041388</v>
+        <v>0.008203028046661703</v>
       </c>
       <c r="O29">
-        <v>0.4560829241680305</v>
+        <v>0.2295138888888889</v>
       </c>
       <c r="P29">
-        <v>83.59999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="Q29">
-        <v>0.01472375350041388</v>
+        <v>0.008203028046661703</v>
       </c>
       <c r="R29">
-        <v>0.4560829241680305</v>
+        <v>0.2295138888888889</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4047,67 +3948,61 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>694.5</v>
+        <v>270.7</v>
       </c>
       <c r="V29">
-        <v>0.1223163493545149</v>
+        <v>0.3359394390667659</v>
       </c>
       <c r="W29">
-        <v>0.06774837374334713</v>
+        <v>0.06233766233766234</v>
       </c>
       <c r="X29">
-        <v>0.04899728807535285</v>
+        <v>0.0822394105357013</v>
       </c>
       <c r="Y29">
-        <v>0.01875108566799429</v>
+        <v>-0.01990174819803896</v>
       </c>
       <c r="Z29">
-        <v>0.1808583014469485</v>
+        <v>5.045823195458232</v>
       </c>
       <c r="AA29">
-        <v>-4.536374326136743e-05</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.03711492935860633</v>
+        <v>0.06980643330756872</v>
       </c>
       <c r="AC29">
-        <v>-0.0371602931018677</v>
+        <v>-0.06980643330756872</v>
       </c>
       <c r="AD29">
-        <v>4363.5</v>
+        <v>359.6</v>
       </c>
       <c r="AE29">
-        <v>100.1264303847641</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>4463.626430384764</v>
+        <v>359.6</v>
       </c>
       <c r="AG29">
-        <v>3769.126430384764</v>
+        <v>88.90000000000003</v>
       </c>
       <c r="AH29">
-        <v>0.4401335894576391</v>
+        <v>0.3085635833190321</v>
       </c>
       <c r="AI29">
-        <v>0.5179466854865546</v>
+        <v>0.4426935861135049</v>
       </c>
       <c r="AJ29">
-        <v>0.3989749005318759</v>
+        <v>0.09936291494355654</v>
       </c>
       <c r="AK29">
-        <v>0.4756940022729199</v>
+        <v>0.1641432791728213</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
         <v>0</v>
-      </c>
-      <c r="AN29">
-        <v>221.497461928934</v>
-      </c>
-      <c r="AP29">
-        <v>191.3262147403433</v>
       </c>
     </row>
     <row r="30">
@@ -4118,7 +4013,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>First Capital Securities Co., Ltd. (SZSE:002797)</t>
+          <t>Ruida Futures Co., Ltd. (SZSE:002961)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4126,47 +4021,41 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D30">
-        <v>0.0788</v>
-      </c>
-      <c r="E30">
-        <v>0.0487</v>
-      </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.002447593740773546</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0.009866604566361953</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>0.008204119603753215</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>136.2</v>
+        <v>52.2</v>
       </c>
       <c r="L30">
-        <v>0.2536785248649656</v>
+        <v>0.154118689105403</v>
       </c>
       <c r="M30">
-        <v>82.2</v>
+        <v>24.2</v>
       </c>
       <c r="N30">
-        <v>0.01697505369238394</v>
+        <v>0.02813626322520637</v>
       </c>
       <c r="O30">
-        <v>0.6035242290748899</v>
+        <v>0.4636015325670498</v>
       </c>
       <c r="P30">
-        <v>82.2</v>
+        <v>24.2</v>
       </c>
       <c r="Q30">
-        <v>0.01697505369238394</v>
+        <v>0.02813626322520637</v>
       </c>
       <c r="R30">
-        <v>0.6035242290748899</v>
+        <v>0.4636015325670498</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -4175,67 +4064,61 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>275.2</v>
+        <v>84.3</v>
       </c>
       <c r="V30">
-        <v>0.056831323310755</v>
+        <v>0.09801185908615277</v>
       </c>
       <c r="W30">
-        <v>0.0676366886825247</v>
+        <v>0.150736355760901</v>
       </c>
       <c r="X30">
-        <v>0.04524373083350221</v>
+        <v>0.07438290104660228</v>
       </c>
       <c r="Y30">
-        <v>0.02239295784902249</v>
+        <v>0.07635345471429869</v>
       </c>
       <c r="Z30">
-        <v>0.1214383576148484</v>
+        <v>0.842440914721201</v>
       </c>
       <c r="AA30">
-        <v>0.0009962948103555715</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.03821305737634074</v>
+        <v>0.07079411697821544</v>
       </c>
       <c r="AC30">
-        <v>-0.03721676256598518</v>
+        <v>-0.07079411697821544</v>
       </c>
       <c r="AD30">
-        <v>2635.8</v>
+        <v>107</v>
       </c>
       <c r="AE30">
-        <v>34.51310004160133</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>2670.313100041602</v>
+        <v>107</v>
       </c>
       <c r="AG30">
-        <v>2395.113100041602</v>
+        <v>22.7</v>
       </c>
       <c r="AH30">
-        <v>0.3554392487085411</v>
+        <v>0.110640057905077</v>
       </c>
       <c r="AI30">
-        <v>0.5360123004251811</v>
+        <v>0.2333696837513631</v>
       </c>
       <c r="AJ30">
-        <v>0.3309303992869919</v>
+        <v>0.02571363842319891</v>
       </c>
       <c r="AK30">
-        <v>0.5088825125694805</v>
+        <v>0.06066274719401391</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
         <v>0</v>
-      </c>
-      <c r="AN30">
-        <v>216.0491803278689</v>
-      </c>
-      <c r="AP30">
-        <v>196.3207459050493</v>
       </c>
     </row>
     <row r="31">
@@ -4246,7 +4129,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Southwest Securities Co., Ltd. (SHSE:600369)</t>
+          <t>The Pacific Securities Co., Ltd (SHSE:601099)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4255,10 +4138,7 @@
         </is>
       </c>
       <c r="D31">
-        <v>-0.0576</v>
-      </c>
-      <c r="E31">
-        <v>-0.03700000000000001</v>
+        <v>0.0136</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4273,28 +4153,28 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>192.9</v>
+        <v>-14.1</v>
       </c>
       <c r="L31">
-        <v>0.3686222052360023</v>
+        <v>-0.05579738820736051</v>
       </c>
       <c r="M31">
-        <v>230.7</v>
+        <v>11.8</v>
       </c>
       <c r="N31">
-        <v>0.0416907618909932</v>
+        <v>0.004645852198905469</v>
       </c>
       <c r="O31">
-        <v>1.195956454121306</v>
+        <v>-0.8368794326241136</v>
       </c>
       <c r="P31">
-        <v>230.7</v>
+        <v>11.8</v>
       </c>
       <c r="Q31">
-        <v>0.0416907618909932</v>
+        <v>0.004645852198905469</v>
       </c>
       <c r="R31">
-        <v>1.195956454121306</v>
+        <v>-0.8368794326241136</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -4303,55 +4183,55 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>723.1</v>
+        <v>112.9</v>
       </c>
       <c r="V31">
-        <v>0.1306744253288998</v>
+        <v>0.04445056892003622</v>
       </c>
       <c r="W31">
-        <v>0.05291600373072914</v>
+        <v>-0.009361306599389191</v>
       </c>
       <c r="X31">
-        <v>0.0545508628866645</v>
+        <v>0.07350571271348344</v>
       </c>
       <c r="Y31">
-        <v>-0.001634859155935357</v>
+        <v>-0.08286701931287263</v>
       </c>
       <c r="Z31">
-        <v>0.06519491198126254</v>
+        <v>0.1080699653594492</v>
       </c>
       <c r="AA31">
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.03725791235669441</v>
+        <v>0.07094064245598662</v>
       </c>
       <c r="AC31">
-        <v>-0.03725791235669441</v>
+        <v>-0.07094064245598662</v>
       </c>
       <c r="AD31">
-        <v>6271.7</v>
+        <v>224.7</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>6271.7</v>
+        <v>224.7</v>
       </c>
       <c r="AG31">
-        <v>5548.599999999999</v>
+        <v>111.8</v>
       </c>
       <c r="AH31">
-        <v>0.531261382599341</v>
+        <v>0.08127758084352167</v>
       </c>
       <c r="AI31">
-        <v>0.616092654079648</v>
+        <v>0.1347930413917217</v>
       </c>
       <c r="AJ31">
-        <v>0.5006767609319448</v>
+        <v>0.0421616321605008</v>
       </c>
       <c r="AK31">
-        <v>0.586737445409075</v>
+        <v>0.07193874268065117</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -4368,7 +4248,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Central China Securities Co., Ltd. (SEHK:1375)</t>
+          <t>Yongan Futures Co.,Ltd. (SHSE:600927)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4377,10 +4257,10 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.0902</v>
+        <v>0.312</v>
       </c>
       <c r="E32">
-        <v>-0.0596</v>
+        <v>-0.00769</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4395,28 +4275,28 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>79.8</v>
+        <v>127</v>
       </c>
       <c r="L32">
-        <v>0.1175430844012373</v>
+        <v>0.02309426825720105</v>
       </c>
       <c r="M32">
-        <v>65.5</v>
+        <v>69.3</v>
       </c>
       <c r="N32">
-        <v>0.02274937482634065</v>
+        <v>0.02037096916429054</v>
       </c>
       <c r="O32">
-        <v>0.8208020050125313</v>
+        <v>0.5456692913385827</v>
       </c>
       <c r="P32">
-        <v>65.5</v>
+        <v>69.3</v>
       </c>
       <c r="Q32">
-        <v>0.02274937482634065</v>
+        <v>0.02037096916429054</v>
       </c>
       <c r="R32">
-        <v>0.8208020050125313</v>
+        <v>0.5456692913385827</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -4425,55 +4305,55 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>258.1</v>
+        <v>462.6</v>
       </c>
       <c r="V32">
-        <v>0.08964295637677133</v>
+        <v>0.1359828331226667</v>
       </c>
       <c r="W32">
-        <v>0.04048295454545454</v>
+        <v>0.09617569102612647</v>
       </c>
       <c r="X32">
-        <v>0.05788403671403532</v>
+        <v>0.07300157952009118</v>
       </c>
       <c r="Y32">
-        <v>-0.01740108216858078</v>
+        <v>0.02317411150603529</v>
       </c>
       <c r="Z32">
-        <v>0.1458055925432756</v>
+        <v>4.072576464489373</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.03732336635811877</v>
+        <v>0.07139607561082795</v>
       </c>
       <c r="AC32">
-        <v>-0.03732336635811877</v>
+        <v>-0.07139607561082795</v>
       </c>
       <c r="AD32">
-        <v>3863.3</v>
+        <v>230.7</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>3863.3</v>
+        <v>230.7</v>
       </c>
       <c r="AG32">
-        <v>3605.2</v>
+        <v>-231.9</v>
       </c>
       <c r="AH32">
-        <v>0.5729773822766037</v>
+        <v>0.06350823101910477</v>
       </c>
       <c r="AI32">
-        <v>0.6306193072377656</v>
+        <v>0.1224002546689304</v>
       </c>
       <c r="AJ32">
-        <v>0.5559805070631054</v>
+        <v>-0.07315457413249213</v>
       </c>
       <c r="AK32">
-        <v>0.6143726248700602</v>
+        <v>-0.1630572352693011</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -4490,7 +4370,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guoyuan Securities Company Limited (SZSE:000728)</t>
+          <t>ChinaLin Securities Co., Ltd (SZSE:002945)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4498,12 +4378,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D33">
-        <v>0.0509</v>
-      </c>
-      <c r="E33">
-        <v>0.0149</v>
-      </c>
       <c r="G33">
         <v>0</v>
       </c>
@@ -4517,28 +4391,28 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>250.7</v>
+        <v>61.8</v>
       </c>
       <c r="L33">
-        <v>0.3464142600525079</v>
+        <v>0.3384446878422782</v>
       </c>
       <c r="M33">
-        <v>186.8</v>
+        <v>30.9</v>
       </c>
       <c r="N33">
-        <v>0.03531658253455089</v>
+        <v>0.005988952417869948</v>
       </c>
       <c r="O33">
-        <v>0.7451136816912646</v>
+        <v>0.5</v>
       </c>
       <c r="P33">
-        <v>186.8</v>
+        <v>30.9</v>
       </c>
       <c r="Q33">
-        <v>0.03531658253455089</v>
+        <v>0.005988952417869948</v>
       </c>
       <c r="R33">
-        <v>0.7451136816912646</v>
+        <v>0.5</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -4547,55 +4421,55 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>445</v>
+        <v>203</v>
       </c>
       <c r="V33">
-        <v>0.08413211578091619</v>
+        <v>0.03934489776141099</v>
       </c>
       <c r="W33">
-        <v>0.06760874841563065</v>
+        <v>0.06358024691358025</v>
       </c>
       <c r="X33">
-        <v>0.05913323809093391</v>
+        <v>0.08092843601666917</v>
       </c>
       <c r="Y33">
-        <v>0.00847551032469674</v>
+        <v>-0.01734818910308893</v>
       </c>
       <c r="Z33">
-        <v>0.08184151899306773</v>
+        <v>0.09048114563203014</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.03734499263507925</v>
+        <v>0.07156746064210415</v>
       </c>
       <c r="AC33">
-        <v>-0.03734499263507925</v>
+        <v>-0.07156746064210415</v>
       </c>
       <c r="AD33">
-        <v>7510.3</v>
+        <v>2025.4</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>7510.3</v>
+        <v>2025.4</v>
       </c>
       <c r="AG33">
-        <v>7065.3</v>
+        <v>1822.4</v>
       </c>
       <c r="AH33">
-        <v>0.5867605237663677</v>
+        <v>0.2818967556959735</v>
       </c>
       <c r="AI33">
-        <v>0.6019170814198586</v>
+        <v>0.6964445361391927</v>
       </c>
       <c r="AJ33">
-        <v>0.5718760623573406</v>
+        <v>0.261017774531288</v>
       </c>
       <c r="AK33">
-        <v>0.587194468223033</v>
+        <v>0.6736655330474642</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -4612,7 +4486,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GF Securities Co., Ltd. (SZSE:000776)</t>
+          <t>BOC International (China) CO., LTD (SHSE:601696)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4620,15 +4494,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D34">
-        <v>0.083</v>
-      </c>
-      <c r="E34">
-        <v>0.0321</v>
-      </c>
-      <c r="F34">
-        <v>0.195</v>
-      </c>
       <c r="G34">
         <v>0</v>
       </c>
@@ -4642,28 +4507,28 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>1635.4</v>
+        <v>110.3</v>
       </c>
       <c r="L34">
-        <v>0.3185058232384217</v>
+        <v>0.2770660638030645</v>
       </c>
       <c r="M34">
-        <v>1239</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="N34">
-        <v>0.04736999059482027</v>
+        <v>0.01700608366805252</v>
       </c>
       <c r="O34">
-        <v>0.7576128164363458</v>
+        <v>0.6563916591115141</v>
       </c>
       <c r="P34">
-        <v>1239</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Q34">
-        <v>0.04736999059482027</v>
+        <v>0.01700608366805252</v>
       </c>
       <c r="R34">
-        <v>0.7576128164363458</v>
+        <v>0.6563916591115141</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -4672,55 +4537,55 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>3895.1</v>
+        <v>326.9</v>
       </c>
       <c r="V34">
-        <v>0.1489191689797291</v>
+        <v>0.07678575623047471</v>
       </c>
       <c r="W34">
-        <v>0.1154992443182621</v>
+        <v>0.04531262837893353</v>
       </c>
       <c r="X34">
-        <v>0.05947802039511125</v>
+        <v>0.08166385861544337</v>
       </c>
       <c r="Y34">
-        <v>0.05602122392315084</v>
+        <v>-0.03635123023650984</v>
       </c>
       <c r="Z34">
-        <v>0.1201355243642125</v>
+        <v>0.08629210560541033</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.03735071787077663</v>
+        <v>0.07157939491378323</v>
       </c>
       <c r="AC34">
-        <v>-0.03735071787077663</v>
+        <v>-0.07157939491378323</v>
       </c>
       <c r="AD34">
-        <v>37702.6</v>
+        <v>1799.5</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>37702.6</v>
+        <v>1799.5</v>
       </c>
       <c r="AG34">
-        <v>33807.5</v>
+        <v>1472.6</v>
       </c>
       <c r="AH34">
-        <v>0.5904094058103554</v>
+        <v>0.297104081363096</v>
       </c>
       <c r="AI34">
-        <v>0.6913709288487175</v>
+        <v>0.438731226838307</v>
       </c>
       <c r="AJ34">
-        <v>0.5638031929530229</v>
+        <v>0.2570027400129147</v>
       </c>
       <c r="AK34">
-        <v>0.6676310280816778</v>
+        <v>0.3901237184412006</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -4737,7 +4602,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Polaris Bay Group Co.,Ltd. (SHSE:600155)</t>
+          <t>ZHONGTAI FUTURES Company Limited (SEHK:1461)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4746,7 +4611,10 @@
         </is>
       </c>
       <c r="D35">
-        <v>0.329</v>
+        <v>0.19</v>
+      </c>
+      <c r="E35">
+        <v>0.0721</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4761,28 +4629,28 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>113</v>
+        <v>32.7</v>
       </c>
       <c r="L35">
-        <v>0.3351126927639383</v>
+        <v>0.1966325917017439</v>
       </c>
       <c r="M35">
-        <v>104.9</v>
+        <v>3.53</v>
       </c>
       <c r="N35">
-        <v>0.03904708728829332</v>
+        <v>0.04294403892944038</v>
       </c>
       <c r="O35">
-        <v>0.9283185840707965</v>
+        <v>0.1079510703363914</v>
       </c>
       <c r="P35">
-        <v>104.9</v>
+        <v>3.53</v>
       </c>
       <c r="Q35">
-        <v>0.03904708728829332</v>
+        <v>0.04294403892944038</v>
       </c>
       <c r="R35">
-        <v>0.9283185840707965</v>
+        <v>0.1079510703363914</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -4791,64 +4659,61 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>1208.6</v>
+        <v>183.6</v>
       </c>
       <c r="V35">
-        <v>0.4498790247533966</v>
+        <v>2.233576642335766</v>
       </c>
       <c r="W35">
-        <v>0.05120768568450628</v>
+        <v>0.0918023582257159</v>
       </c>
       <c r="X35">
-        <v>0.06229573579628675</v>
+        <v>0.08565945318359502</v>
       </c>
       <c r="Y35">
-        <v>-0.01108805011178047</v>
+        <v>0.00614290504212088</v>
       </c>
       <c r="Z35">
-        <v>0.07579572019420969</v>
+        <v>0.7052586938083122</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.03739397255854389</v>
+        <v>0.07163631266071754</v>
       </c>
       <c r="AC35">
-        <v>-0.03739397255854389</v>
+        <v>-0.07163631266071754</v>
       </c>
       <c r="AD35">
-        <v>4345.8</v>
+        <v>48.2</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>4345.8</v>
+        <v>48.2</v>
       </c>
       <c r="AG35">
-        <v>3137.2</v>
+        <v>-135.4</v>
       </c>
       <c r="AH35">
-        <v>0.6179770487607185</v>
+        <v>0.3696319018404908</v>
       </c>
       <c r="AI35">
-        <v>0.637186047534566</v>
+        <v>0.1205904428321241</v>
       </c>
       <c r="AJ35">
-        <v>0.5386953311468654</v>
+        <v>2.545112781954888</v>
       </c>
       <c r="AK35">
-        <v>0.5590462783113851</v>
+        <v>-0.6265617769551132</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-222.1</v>
-      </c>
-      <c r="AQ35">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4859,7 +4724,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tianfeng Securities Co., Ltd. (SHSE:601162)</t>
+          <t>Hongta Securities Co., Ltd. (SHSE:601236)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4868,7 +4733,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>0.003921232876712329</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -4880,28 +4745,28 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>60.1</v>
+        <v>172.5</v>
       </c>
       <c r="L36">
-        <v>0.1029109589041096</v>
+        <v>0.3372434017595308</v>
       </c>
       <c r="M36">
-        <v>195.2</v>
+        <v>145.8</v>
       </c>
       <c r="N36">
-        <v>0.03533223523449237</v>
+        <v>0.02881081294708137</v>
       </c>
       <c r="O36">
-        <v>3.247920133111481</v>
+        <v>0.8452173913043479</v>
       </c>
       <c r="P36">
-        <v>195.2</v>
+        <v>145.8</v>
       </c>
       <c r="Q36">
-        <v>0.03533223523449237</v>
+        <v>0.02881081294708137</v>
       </c>
       <c r="R36">
-        <v>3.247920133111481</v>
+        <v>0.8452173913043479</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -4910,55 +4775,55 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>1693</v>
+        <v>454.2</v>
       </c>
       <c r="V36">
-        <v>0.3064419787499774</v>
+        <v>0.08975220329605184</v>
       </c>
       <c r="W36">
-        <v>0.02259228629426359</v>
+        <v>0.07624646393210749</v>
       </c>
       <c r="X36">
-        <v>0.06277166145501421</v>
+        <v>0.08726322103640452</v>
       </c>
       <c r="Y36">
-        <v>-0.04017937516075062</v>
+        <v>-0.01101675710429703</v>
       </c>
       <c r="Z36">
-        <v>0.07591612827745788</v>
+        <v>0.1496401614885027</v>
       </c>
       <c r="AA36">
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>0.03740071016068466</v>
+        <v>0.07165598638263956</v>
       </c>
       <c r="AC36">
-        <v>-0.03740071016068466</v>
+        <v>-0.07165598638263956</v>
       </c>
       <c r="AD36">
-        <v>9101.4</v>
+        <v>3299.9</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>9101.4</v>
+        <v>3299.9</v>
       </c>
       <c r="AG36">
-        <v>7408.4</v>
+        <v>2845.7</v>
       </c>
       <c r="AH36">
-        <v>0.6222711454181225</v>
+        <v>0.3947012738472579</v>
       </c>
       <c r="AI36">
-        <v>0.6564961481866183</v>
+        <v>0.48542932376175</v>
       </c>
       <c r="AJ36">
-        <v>0.5728247674571448</v>
+        <v>0.3599281585571</v>
       </c>
       <c r="AK36">
-        <v>0.608712799697632</v>
+        <v>0.4485867868909312</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -4975,7 +4840,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Changjiang Securities Company Limited (SZSE:000783)</t>
+          <t>China Renaissance Holdings Limited (SEHK:1911)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4983,14 +4848,11 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D37">
-        <v>0.0825</v>
-      </c>
-      <c r="E37">
-        <v>0.0274</v>
+      <c r="F37">
+        <v>0.0518</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>0.0846969696969697</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -5002,91 +4864,94 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>365.1</v>
+        <v>36.1</v>
       </c>
       <c r="L37">
-        <v>0.2812572220938295</v>
+        <v>0.546969696969697</v>
       </c>
       <c r="M37">
-        <v>353.1</v>
+        <v>48.1</v>
       </c>
       <c r="N37">
-        <v>0.05379669693460905</v>
+        <v>0.08126372698090895</v>
       </c>
       <c r="O37">
-        <v>0.9671322925225966</v>
+        <v>1.332409972299169</v>
       </c>
       <c r="P37">
-        <v>353.1</v>
+        <v>29.5</v>
       </c>
       <c r="Q37">
-        <v>0.05379669693460905</v>
+        <v>0.04983949991552628</v>
       </c>
       <c r="R37">
-        <v>0.9671322925225966</v>
+        <v>0.817174515235457</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>0.3866943866943867</v>
       </c>
       <c r="U37">
-        <v>1523.1</v>
+        <v>381.4</v>
       </c>
       <c r="V37">
-        <v>0.2320525321469925</v>
+        <v>0.6443656022976854</v>
       </c>
       <c r="W37">
-        <v>0.08567003777835137</v>
+        <v>0.03383634829880963</v>
       </c>
       <c r="X37">
-        <v>0.06607921793148909</v>
+        <v>0.09022156853853754</v>
       </c>
       <c r="Y37">
-        <v>0.01959081984686228</v>
+        <v>-0.0563852202397279</v>
       </c>
       <c r="Z37">
-        <v>0.1003106454005935</v>
+        <v>0.05220692928334124</v>
       </c>
       <c r="AA37">
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>0.03744365371275865</v>
+        <v>0.07168845206262657</v>
       </c>
       <c r="AC37">
-        <v>-0.03744365371275865</v>
+        <v>-0.07168845206262657</v>
       </c>
       <c r="AD37">
-        <v>12170.3</v>
+        <v>457.7</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>12170.3</v>
+        <v>457.7</v>
       </c>
       <c r="AG37">
-        <v>10647.2</v>
+        <v>76.30000000000001</v>
       </c>
       <c r="AH37">
-        <v>0.6496404913018644</v>
+        <v>0.4360708841463415</v>
       </c>
       <c r="AI37">
-        <v>0.71921685892587</v>
+        <v>0.2844447206512957</v>
       </c>
       <c r="AJ37">
-        <v>0.6186348107002579</v>
+        <v>0.1141873690511823</v>
       </c>
       <c r="AK37">
-        <v>0.6914439718154365</v>
+        <v>0.06214873340392605</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>-19.8</v>
+      </c>
+      <c r="AQ37">
+        <v>-0</v>
       </c>
     </row>
     <row r="38">
@@ -5097,7 +4962,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Northeast Securities Co., Ltd. (SZSE:000686)</t>
+          <t>Hengtai Securities Co., Ltd (SEHK:1476)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5106,10 +4971,7 @@
         </is>
       </c>
       <c r="D38">
-        <v>0.0668</v>
-      </c>
-      <c r="E38">
-        <v>0.00245</v>
+        <v>-0.0141</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5118,97 +4980,100 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>0.0003529468116961285</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>0.0003529468116961285</v>
       </c>
       <c r="K38">
-        <v>244.6</v>
+        <v>-9.51</v>
       </c>
       <c r="L38">
-        <v>0.2378220709771512</v>
+        <v>-0.0218721251149954</v>
       </c>
       <c r="M38">
-        <v>184</v>
+        <v>-0</v>
       </c>
       <c r="N38">
-        <v>0.05688141461605044</v>
+        <v>-0</v>
       </c>
       <c r="O38">
-        <v>0.7522485690923958</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>184</v>
+        <v>-0</v>
       </c>
       <c r="Q38">
-        <v>0.05688141461605044</v>
+        <v>-0</v>
       </c>
       <c r="R38">
-        <v>0.7522485690923958</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
       <c r="U38">
-        <v>1163.8</v>
+        <v>317.6</v>
       </c>
       <c r="V38">
-        <v>0.3597749474465191</v>
+        <v>0.3018437559399354</v>
       </c>
       <c r="W38">
-        <v>0.1018106139438085</v>
+        <v>-0.006803061735460332</v>
       </c>
       <c r="X38">
-        <v>0.07144852795187026</v>
+        <v>0.1133724922170667</v>
       </c>
       <c r="Y38">
-        <v>0.03036208599193826</v>
+        <v>-0.120175553952527</v>
       </c>
       <c r="Z38">
-        <v>0.1632876625335387</v>
+        <v>0.1413382675927154</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>4.988489091750313e-05</v>
       </c>
       <c r="AB38">
-        <v>0.03750150955950149</v>
+        <v>0.07184266928447615</v>
       </c>
       <c r="AC38">
-        <v>-0.03750150955950149</v>
+        <v>-0.07179278439355864</v>
       </c>
       <c r="AD38">
-        <v>7084</v>
+        <v>1811.4</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>0.1776936313726167</v>
       </c>
       <c r="AF38">
-        <v>7084</v>
+        <v>1811.577693631373</v>
       </c>
       <c r="AG38">
-        <v>5920.2</v>
+        <v>1493.977693631373</v>
       </c>
       <c r="AH38">
-        <v>0.6865139357289608</v>
+        <v>0.6325832126076194</v>
       </c>
       <c r="AI38">
-        <v>0.7137028118923602</v>
+        <v>0.5655034518369999</v>
       </c>
       <c r="AJ38">
-        <v>0.6466630256690333</v>
+        <v>0.5867531152158724</v>
       </c>
       <c r="AK38">
-        <v>0.6756753672148735</v>
+        <v>0.5176857276135853</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
         <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>9584.126984126984</v>
+      </c>
+      <c r="AP38">
+        <v>7904.643881647476</v>
       </c>
     </row>
     <row r="39">
@@ -5219,7 +5084,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>China Merchants Securities Co., Ltd. (SHSE:600999)</t>
+          <t>Shanghai Chinafortune Co., Ltd. (SHSE:600621)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5228,16 +5093,13 @@
         </is>
       </c>
       <c r="D39">
-        <v>0.14</v>
+        <v>0.0373</v>
       </c>
       <c r="E39">
-        <v>0.121</v>
-      </c>
-      <c r="F39">
-        <v>0.193</v>
+        <v>0.0623</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>0.02322670375521558</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -5249,28 +5111,28 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>1663.7</v>
+        <v>35.4</v>
       </c>
       <c r="L39">
-        <v>0.3810232685965556</v>
+        <v>0.1230876216968011</v>
       </c>
       <c r="M39">
-        <v>1889.9</v>
+        <v>70.2</v>
       </c>
       <c r="N39">
-        <v>0.0837246597675078</v>
+        <v>0.04418150922021524</v>
       </c>
       <c r="O39">
-        <v>1.13596201238204</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="P39">
-        <v>1889.9</v>
+        <v>70.2</v>
       </c>
       <c r="Q39">
-        <v>0.0837246597675078</v>
+        <v>0.04418150922021524</v>
       </c>
       <c r="R39">
-        <v>1.13596201238204</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -5279,61 +5141,64 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>2171.1</v>
+        <v>1110</v>
       </c>
       <c r="V39">
-        <v>0.09618213070598242</v>
+        <v>0.6985965133110957</v>
       </c>
       <c r="W39">
-        <v>0.1058926116401039</v>
+        <v>0.03150026695141484</v>
       </c>
       <c r="X39">
-        <v>0.0731864168550702</v>
+        <v>0.104684671792635</v>
       </c>
       <c r="Y39">
-        <v>0.03270619478503367</v>
+        <v>-0.07318440484122016</v>
       </c>
       <c r="Z39">
-        <v>0.083838829144208</v>
+        <v>0.1562678287139419</v>
       </c>
       <c r="AA39">
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0.03751771300760254</v>
+        <v>0.07179929072668076</v>
       </c>
       <c r="AC39">
-        <v>-0.03751771300760254</v>
+        <v>-0.07179929072668076</v>
       </c>
       <c r="AD39">
-        <v>51885.8</v>
+        <v>2170.1</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>51885.8</v>
+        <v>2170.1</v>
       </c>
       <c r="AG39">
-        <v>49714.7</v>
+        <v>1060.1</v>
       </c>
       <c r="AH39">
-        <v>0.6968409290531919</v>
+        <v>0.5773077946262304</v>
       </c>
       <c r="AI39">
-        <v>0.7529502249310696</v>
+        <v>0.6744258321161077</v>
       </c>
       <c r="AJ39">
-        <v>0.6877357772782293</v>
+        <v>0.4001887504718761</v>
       </c>
       <c r="AK39">
-        <v>0.7449133863458942</v>
+        <v>0.5029653176448261</v>
       </c>
       <c r="AL39">
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>-37.2</v>
+      </c>
+      <c r="AQ39">
+        <v>-0</v>
       </c>
     </row>
     <row r="40">
@@ -5344,7 +5209,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shenwan Hongyuan Group Co., Ltd. (SZSE:000166)</t>
+          <t>Industrial Securities Co.,Ltd. (SHSE:601377)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5353,13 +5218,13 @@
         </is>
       </c>
       <c r="D40">
-        <v>0.117</v>
+        <v>0.169</v>
       </c>
       <c r="E40">
-        <v>0.0112</v>
+        <v>0.0862</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>0.003086867222423584</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -5371,28 +5236,28 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>1341.7</v>
+        <v>421.7</v>
       </c>
       <c r="L40">
-        <v>0.2645568372276447</v>
+        <v>0.254742056300592</v>
       </c>
       <c r="M40">
-        <v>1228.2</v>
+        <v>278.7</v>
       </c>
       <c r="N40">
-        <v>0.06542235290357633</v>
+        <v>0.03877834979824683</v>
       </c>
       <c r="O40">
-        <v>0.915405828426623</v>
+        <v>0.660896371828314</v>
       </c>
       <c r="P40">
-        <v>1228.2</v>
+        <v>278.7</v>
       </c>
       <c r="Q40">
-        <v>0.06542235290357633</v>
+        <v>0.03877834979824683</v>
       </c>
       <c r="R40">
-        <v>0.915405828426623</v>
+        <v>0.660896371828314</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -5401,55 +5266,55 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>4771.5</v>
+        <v>3928.2</v>
       </c>
       <c r="V40">
-        <v>0.2541628048195851</v>
+        <v>0.5465701961875609</v>
       </c>
       <c r="W40">
-        <v>0.1119632157818315</v>
+        <v>0.06800187057552448</v>
       </c>
       <c r="X40">
-        <v>0.07332629581960584</v>
+        <v>0.1218216581469897</v>
       </c>
       <c r="Y40">
-        <v>0.03863691996222569</v>
+        <v>-0.05381978757146523</v>
       </c>
       <c r="Z40">
-        <v>0.1296425531262222</v>
+        <v>0.09035286412138745</v>
       </c>
       <c r="AA40">
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>0.03751897089039446</v>
+        <v>0.07187520201376793</v>
       </c>
       <c r="AC40">
-        <v>-0.03751897089039446</v>
+        <v>-0.07187520201376793</v>
       </c>
       <c r="AD40">
-        <v>43316.7</v>
+        <v>14861.6</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>43316.7</v>
+        <v>14861.6</v>
       </c>
       <c r="AG40">
-        <v>38545.2</v>
+        <v>10933.4</v>
       </c>
       <c r="AH40">
-        <v>0.6976426193547763</v>
+        <v>0.6740382609326669</v>
       </c>
       <c r="AI40">
-        <v>0.7547094530553078</v>
+        <v>0.6456708649580968</v>
       </c>
       <c r="AJ40">
-        <v>0.6724728098732349</v>
+        <v>0.603375201430432</v>
       </c>
       <c r="AK40">
-        <v>0.7324684505270439</v>
+        <v>0.5727561802285074</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -5466,7 +5331,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>China Galaxy Securities Co., Ltd. (SEHK:6881)</t>
+          <t>Guangzhou Yuexiu Capital Holdings Group Co., Ltd. (SZSE:000987)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5475,16 +5340,13 @@
         </is>
       </c>
       <c r="D41">
-        <v>0.151</v>
+        <v>0.0641</v>
       </c>
       <c r="E41">
-        <v>0.0917</v>
-      </c>
-      <c r="F41">
-        <v>0.306</v>
+        <v>0.209</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>0.0006689890516138206</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -5496,28 +5358,28 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>1395.6</v>
+        <v>340.7</v>
       </c>
       <c r="L41">
-        <v>0.2766083957664407</v>
+        <v>0.2422152708659178</v>
       </c>
       <c r="M41">
-        <v>257.3</v>
+        <v>567.4</v>
       </c>
       <c r="N41">
-        <v>0.0190939111721272</v>
+        <v>0.1302212430000918</v>
       </c>
       <c r="O41">
-        <v>0.1843651476067641</v>
+        <v>1.665394775462284</v>
       </c>
       <c r="P41">
-        <v>257.3</v>
+        <v>567.4</v>
       </c>
       <c r="Q41">
-        <v>0.0190939111721272</v>
+        <v>0.1302212430000918</v>
       </c>
       <c r="R41">
-        <v>0.1843651476067641</v>
+        <v>1.665394775462284</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -5526,61 +5388,64 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>2540.3</v>
+        <v>3284.9</v>
       </c>
       <c r="V41">
-        <v>0.1885124856220549</v>
+        <v>0.7539015881758928</v>
       </c>
       <c r="W41">
-        <v>0.1273822562979189</v>
+        <v>0.08909285845035433</v>
       </c>
       <c r="X41">
-        <v>0.08416710254642618</v>
+        <v>0.1534311423641206</v>
       </c>
       <c r="Y41">
-        <v>0.04321515375149276</v>
+        <v>-0.06433828391376625</v>
       </c>
       <c r="Z41">
-        <v>0.1198156244285758</v>
+        <v>0.08774359358235397</v>
       </c>
       <c r="AA41">
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>0.03759966295052517</v>
+        <v>0.07195112959945063</v>
       </c>
       <c r="AC41">
-        <v>-0.03759966295052517</v>
+        <v>-0.07195112959945063</v>
       </c>
       <c r="AD41">
-        <v>40226.8</v>
+        <v>14652.4</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>40226.8</v>
+        <v>14652.4</v>
       </c>
       <c r="AG41">
-        <v>37686.5</v>
+        <v>11367.5</v>
       </c>
       <c r="AH41">
-        <v>0.7490703377695183</v>
+        <v>0.7707894958336841</v>
       </c>
       <c r="AI41">
-        <v>0.7276759549358552</v>
+        <v>0.7335442657748763</v>
       </c>
       <c r="AJ41">
-        <v>0.7366111567178766</v>
+        <v>0.7229072732707142</v>
       </c>
       <c r="AK41">
-        <v>0.7145592889010237</v>
+        <v>0.6811005458391002</v>
       </c>
       <c r="AL41">
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>0</v>
+        <v>-354.3</v>
+      </c>
+      <c r="AQ41">
+        <v>-0</v>
       </c>
     </row>
     <row r="42">
@@ -5591,7 +5456,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>China Renaissance Holdings Limited (SEHK:1911)</t>
+          <t>Capital Securities Corporation Limited (SHSE:601136)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5599,11 +5464,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="F42">
-        <v>0.165</v>
-      </c>
       <c r="G42">
-        <v>0.01162752504516341</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -5615,94 +5477,91 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>287.9</v>
+        <v>122.4</v>
       </c>
       <c r="L42">
-        <v>0.4728198390540319</v>
+        <v>0.3945841392649904</v>
       </c>
       <c r="M42">
-        <v>18.46</v>
+        <v>42.5</v>
       </c>
       <c r="N42">
-        <v>0.01769555214723926</v>
+        <v>0.006156297530238285</v>
       </c>
       <c r="O42">
-        <v>0.0641194859326155</v>
+        <v>0.3472222222222222</v>
       </c>
       <c r="P42">
-        <v>12.4</v>
+        <v>42.5</v>
       </c>
       <c r="Q42">
-        <v>0.01188650306748466</v>
+        <v>0.006156297530238285</v>
       </c>
       <c r="R42">
-        <v>0.04307051059395624</v>
+        <v>0.3472222222222222</v>
       </c>
       <c r="S42">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>0.3282773564463705</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>191.4</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="V42">
-        <v>0.1834739263803681</v>
+        <v>0.01200840153545303</v>
       </c>
       <c r="W42">
-        <v>0.3724932074006986</v>
+        <v>0.08669169204617891</v>
       </c>
       <c r="X42">
-        <v>0.04238348693805721</v>
+        <v>0.08137706301394554</v>
       </c>
       <c r="Y42">
-        <v>0.3301097204626414</v>
+        <v>0.00531462903223337</v>
       </c>
       <c r="Z42">
-        <v>0.9168799879536216</v>
+        <v>0.08265387689848121</v>
       </c>
       <c r="AA42">
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>0.03779042717092136</v>
+        <v>0.07240486647104545</v>
       </c>
       <c r="AC42">
-        <v>-0.03779042717092136</v>
+        <v>-0.07240486647104545</v>
       </c>
       <c r="AD42">
-        <v>388.7</v>
+        <v>2836.9</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>388.7</v>
+        <v>2836.9</v>
       </c>
       <c r="AG42">
-        <v>197.3</v>
+        <v>2754</v>
       </c>
       <c r="AH42">
-        <v>0.2714575040156435</v>
+        <v>0.2912508726541005</v>
       </c>
       <c r="AI42">
-        <v>0.2295924394565859</v>
+        <v>0.6561278534588432</v>
       </c>
       <c r="AJ42">
-        <v>0.1590487706569931</v>
+        <v>0.2851669686771939</v>
       </c>
       <c r="AK42">
-        <v>0.1313931806073522</v>
+        <v>0.6494057724957555</v>
       </c>
       <c r="AL42">
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-3.75</v>
-      </c>
-      <c r="AQ42">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5713,7 +5572,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>China Industrial Securities Co.,Ltd. (SHSE:601377)</t>
+          <t>CSC Financial Co., Ltd. (SEHK:6066)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5722,46 +5581,49 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.154</v>
+        <v>0.226</v>
       </c>
       <c r="E43">
-        <v>0.108</v>
+        <v>0.171</v>
+      </c>
+      <c r="F43">
+        <v>0.00433</v>
       </c>
       <c r="G43">
-        <v>0.002290561243554293</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0.008103924737319185</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>0.006108363690892239</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>697.9</v>
+        <v>1323.7</v>
       </c>
       <c r="L43">
-        <v>0.260780210746581</v>
+        <v>0.2798342599835106</v>
       </c>
       <c r="M43">
-        <v>519.7</v>
+        <v>535.5</v>
       </c>
       <c r="N43">
-        <v>0.04989870476519669</v>
+        <v>0.02281441717791411</v>
       </c>
       <c r="O43">
-        <v>0.7446625591058892</v>
+        <v>0.4045478582760444</v>
       </c>
       <c r="P43">
-        <v>519.7</v>
+        <v>535.5</v>
       </c>
       <c r="Q43">
-        <v>0.04989870476519669</v>
+        <v>0.02281441717791411</v>
       </c>
       <c r="R43">
-        <v>0.7446625591058892</v>
+        <v>0.4045478582760444</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -5770,67 +5632,61 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>2430.6</v>
+        <v>4820</v>
       </c>
       <c r="V43">
-        <v>0.2333726992539678</v>
+        <v>0.2053510565780504</v>
       </c>
       <c r="W43">
-        <v>0.1285645862500921</v>
+        <v>0.1110374794483777</v>
       </c>
       <c r="X43">
-        <v>0.05903698116966954</v>
+        <v>0.1056936635968614</v>
       </c>
       <c r="Y43">
-        <v>0.06952760508042258</v>
+        <v>0.005343815851516262</v>
       </c>
       <c r="Z43">
-        <v>0.177540409947468</v>
+        <v>0.1139652825461072</v>
       </c>
       <c r="AA43">
-        <v>0.001084481393789237</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>0.03937197478116522</v>
+        <v>0.07263799412877534</v>
       </c>
       <c r="AC43">
-        <v>-0.03828749338737598</v>
+        <v>-0.07263799412877534</v>
       </c>
       <c r="AD43">
-        <v>14552.7</v>
+        <v>33028</v>
       </c>
       <c r="AE43">
-        <v>173.061383089932</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>14725.76138308993</v>
+        <v>33028</v>
       </c>
       <c r="AG43">
-        <v>12295.16138308993</v>
+        <v>28208</v>
       </c>
       <c r="AH43">
-        <v>0.5857301847658517</v>
+        <v>0.5845663716814159</v>
       </c>
       <c r="AI43">
-        <v>0.6833565873540461</v>
+        <v>0.716451841021792</v>
       </c>
       <c r="AJ43">
-        <v>0.5413923325534646</v>
+        <v>0.5458204334365325</v>
       </c>
       <c r="AK43">
-        <v>0.6431007614393419</v>
+        <v>0.683343265648241</v>
       </c>
       <c r="AL43">
         <v>0</v>
       </c>
       <c r="AM43">
         <v>0</v>
-      </c>
-      <c r="AN43">
-        <v>258.4849023090587</v>
-      </c>
-      <c r="AP43">
-        <v>218.3865254545281</v>
       </c>
     </row>
     <row r="44">
@@ -5841,7 +5697,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zheshang Securities Co., Ltd. (SHSE:601878)</t>
+          <t>Guosheng Financial Holding Inc. (SZSE:002670)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5850,46 +5706,43 @@
         </is>
       </c>
       <c r="D44">
-        <v>0.265</v>
-      </c>
-      <c r="E44">
-        <v>0.0925</v>
+        <v>0.0866</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>0.1719512195121951</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>0.1720681590377547</v>
       </c>
       <c r="I44">
-        <v>0.0006084496667995409</v>
+        <v>-0.00407617774807885</v>
       </c>
       <c r="J44">
-        <v>0.0004584302305336088</v>
+        <v>-0.00407617774807885</v>
       </c>
       <c r="K44">
-        <v>339.5</v>
+        <v>-37.3</v>
       </c>
       <c r="L44">
-        <v>0.1402428949107733</v>
+        <v>-0.1246241229535583</v>
       </c>
       <c r="M44">
-        <v>155.3</v>
+        <v>48.6</v>
       </c>
       <c r="N44">
-        <v>0.01930103651413089</v>
+        <v>0.02337662337662338</v>
       </c>
       <c r="O44">
-        <v>0.4574374079528719</v>
+        <v>-1.302949061662199</v>
       </c>
       <c r="P44">
-        <v>155.3</v>
+        <v>48.6</v>
       </c>
       <c r="Q44">
-        <v>0.01930103651413089</v>
+        <v>0.02337662337662338</v>
       </c>
       <c r="R44">
-        <v>0.4574374079528719</v>
+        <v>-1.302949061662199</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -5898,67 +5751,73 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>930.3</v>
+        <v>1355.2</v>
       </c>
       <c r="V44">
-        <v>0.1156197956799483</v>
+        <v>0.6518518518518519</v>
       </c>
       <c r="W44">
-        <v>0.1229537882080255</v>
+        <v>-0.02091745177209511</v>
       </c>
       <c r="X44">
-        <v>0.05167030324324926</v>
+        <v>0.08374832466127449</v>
       </c>
       <c r="Y44">
-        <v>0.07128348496477624</v>
+        <v>-0.1046657764333696</v>
       </c>
       <c r="Z44">
-        <v>0.3267547164657044</v>
+        <v>0.2630052724077327</v>
       </c>
       <c r="AA44">
-        <v>0.0001497942399973169</v>
+        <v>-0.001072056239015817</v>
       </c>
       <c r="AB44">
-        <v>0.03888035373520184</v>
+        <v>0.07161062996858816</v>
       </c>
       <c r="AC44">
-        <v>-0.03873055949520453</v>
+        <v>-0.07268268620760399</v>
       </c>
       <c r="AD44">
-        <v>7615.6</v>
+        <v>1056.3</v>
       </c>
       <c r="AE44">
-        <v>54.63532523305836</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>7670.235325233059</v>
+        <v>1056.3</v>
       </c>
       <c r="AG44">
-        <v>6739.935325233058</v>
+        <v>-298.9000000000001</v>
       </c>
       <c r="AH44">
-        <v>0.4880391237902617</v>
+        <v>0.3369055592766242</v>
       </c>
       <c r="AI44">
-        <v>0.6802606820925132</v>
+        <v>0.4004777070063694</v>
       </c>
       <c r="AJ44">
-        <v>0.4558280562826394</v>
+        <v>-0.1679119150609517</v>
       </c>
       <c r="AK44">
-        <v>0.6515077003191564</v>
+        <v>-0.2330786026200874</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>55.9</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AN44">
-        <v>614.1612903225806</v>
+        <v>754.5</v>
+      </c>
+      <c r="AO44">
+        <v>-0.02182468694096601</v>
       </c>
       <c r="AP44">
-        <v>543.5431713897627</v>
+        <v>-213.5000000000001</v>
+      </c>
+      <c r="AQ44">
+        <v>-0.03485714285714286</v>
       </c>
     </row>
     <row r="45">
@@ -5969,7 +5828,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Guolian Securities Co., Ltd. (SEHK:1456)</t>
+          <t>CITIC Securities Company Limited (SHSE:600030)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5978,10 +5837,13 @@
         </is>
       </c>
       <c r="D45">
-        <v>0.0466</v>
+        <v>0.104</v>
       </c>
       <c r="E45">
-        <v>0.0149</v>
+        <v>0.163</v>
+      </c>
+      <c r="F45">
+        <v>0.0906</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5996,28 +5858,28 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>121.9</v>
+        <v>3095.5</v>
       </c>
       <c r="L45">
-        <v>0.2823720176048182</v>
+        <v>0.3414028895996471</v>
       </c>
       <c r="M45">
-        <v>51.7</v>
+        <v>2159.6</v>
       </c>
       <c r="N45">
-        <v>0.009408210802154609</v>
+        <v>0.05329555886795061</v>
       </c>
       <c r="O45">
-        <v>0.4241181296144381</v>
+        <v>0.6976578904861896</v>
       </c>
       <c r="P45">
-        <v>51.7</v>
+        <v>2159.6</v>
       </c>
       <c r="Q45">
-        <v>0.009408210802154609</v>
+        <v>0.05329555886795061</v>
       </c>
       <c r="R45">
-        <v>0.4241181296144381</v>
+        <v>0.6976578904861896</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -6026,55 +5888,55 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>608.1</v>
+        <v>20002.3</v>
       </c>
       <c r="V45">
-        <v>0.1106602125491338</v>
+        <v>0.4936255589666644</v>
       </c>
       <c r="W45">
-        <v>0.1026526315789474</v>
+        <v>0.0978476983427056</v>
       </c>
       <c r="X45">
-        <v>0.0508983686968889</v>
+        <v>0.1107024822446874</v>
       </c>
       <c r="Y45">
-        <v>0.05175426288205847</v>
+        <v>-0.01285478390198178</v>
       </c>
       <c r="Z45">
-        <v>0.1309650213876164</v>
+        <v>0.104703396191554</v>
       </c>
       <c r="AA45">
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>0.03881507688880285</v>
+        <v>0.0727101041493886</v>
       </c>
       <c r="AC45">
-        <v>-0.03881507688880285</v>
+        <v>-0.0727101041493886</v>
       </c>
       <c r="AD45">
-        <v>4973.2</v>
+        <v>65333.2</v>
       </c>
       <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45">
-        <v>4973.2</v>
+        <v>65333.2</v>
       </c>
       <c r="AG45">
-        <v>4365.099999999999</v>
+        <v>45330.89999999999</v>
       </c>
       <c r="AH45">
-        <v>0.4750678231630431</v>
+        <v>0.617198718239393</v>
       </c>
       <c r="AI45">
-        <v>0.6662469020028133</v>
+        <v>0.6468025284750444</v>
       </c>
       <c r="AJ45">
-        <v>0.442694441345598</v>
+        <v>0.5280115454368618</v>
       </c>
       <c r="AK45">
-        <v>0.6366460533224432</v>
+        <v>0.559590999318579</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -6091,7 +5953,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sinolink Securities Co., Ltd. (SHSE:600109)</t>
+          <t>China International Capital Corporation Limited (SEHK:3908)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6100,13 +5962,16 @@
         </is>
       </c>
       <c r="D46">
-        <v>0.0269</v>
+        <v>0.219</v>
       </c>
       <c r="E46">
-        <v>0.0167</v>
+        <v>0.286</v>
+      </c>
+      <c r="F46">
+        <v>0.3</v>
       </c>
       <c r="G46">
-        <v>0.01210052745888923</v>
+        <v>0</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -6118,28 +5983,28 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>284.8</v>
+        <v>1312.3</v>
       </c>
       <c r="L46">
-        <v>0.2945495914779191</v>
+        <v>0.3215239495283597</v>
       </c>
       <c r="M46">
-        <v>106.5</v>
+        <v>1115.8</v>
       </c>
       <c r="N46">
-        <v>0.01974416017797553</v>
+        <v>0.05635296613165523</v>
       </c>
       <c r="O46">
-        <v>0.3739466292134832</v>
+        <v>0.8502628972033833</v>
       </c>
       <c r="P46">
-        <v>106.5</v>
+        <v>1115.8</v>
       </c>
       <c r="Q46">
-        <v>0.01974416017797553</v>
+        <v>0.05635296613165523</v>
       </c>
       <c r="R46">
-        <v>0.3739466292134832</v>
+        <v>0.8502628972033833</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -6148,55 +6013,55 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>983.4</v>
+        <v>9286.6</v>
       </c>
       <c r="V46">
-        <v>0.1823136818687431</v>
+        <v>0.4690154644902577</v>
       </c>
       <c r="W46">
-        <v>0.08756072065424585</v>
+        <v>0.1039948014486207</v>
       </c>
       <c r="X46">
-        <v>0.05158828712440573</v>
+        <v>0.1207097481553939</v>
       </c>
       <c r="Y46">
-        <v>0.03597243352984011</v>
+        <v>-0.01671494670677322</v>
       </c>
       <c r="Z46">
-        <v>0.1602493983810983</v>
+        <v>0.08595255393751776</v>
       </c>
       <c r="AA46">
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0.03887357180702575</v>
+        <v>0.07282485015609622</v>
       </c>
       <c r="AC46">
-        <v>-0.03887357180702575</v>
+        <v>-0.07282485015609622</v>
       </c>
       <c r="AD46">
-        <v>5114.3</v>
+        <v>40041.8</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>5114.3</v>
+        <v>40041.8</v>
       </c>
       <c r="AG46">
-        <v>4130.900000000001</v>
+        <v>30755.2</v>
       </c>
       <c r="AH46">
-        <v>0.486691472455107</v>
+        <v>0.6691253634571037</v>
       </c>
       <c r="AI46">
-        <v>0.5813223910794867</v>
+        <v>0.7512476454210475</v>
       </c>
       <c r="AJ46">
-        <v>0.4336948419405978</v>
+        <v>0.6083464872199607</v>
       </c>
       <c r="AK46">
-        <v>0.5286334028639801</v>
+        <v>0.6987626608018395</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -6213,7 +6078,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dongxing Securities Corporation Limited (SHSE:601198)</t>
+          <t>Caida Securities Co., Ltd. (SHSE:600906)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6222,10 +6087,10 @@
         </is>
       </c>
       <c r="D47">
-        <v>0.08160000000000001</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="E47">
-        <v>0.0106</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6234,34 +6099,34 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0.0170018057688976</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>0.01509405672173564</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>224.6</v>
+        <v>71.5</v>
       </c>
       <c r="L47">
-        <v>0.2692077190459067</v>
+        <v>0.2521156558533145</v>
       </c>
       <c r="M47">
-        <v>287.8</v>
+        <v>98.8</v>
       </c>
       <c r="N47">
-        <v>0.04863293791611747</v>
+        <v>0.02774112031447424</v>
       </c>
       <c r="O47">
-        <v>1.281389136242209</v>
+        <v>1.381818181818182</v>
       </c>
       <c r="P47">
-        <v>287.8</v>
+        <v>98.8</v>
       </c>
       <c r="Q47">
-        <v>0.04863293791611747</v>
+        <v>0.02774112031447424</v>
       </c>
       <c r="R47">
-        <v>1.281389136242209</v>
+        <v>1.381818181818182</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -6270,67 +6135,61 @@
         <v>0</v>
       </c>
       <c r="U47">
-        <v>300</v>
+        <v>233.2</v>
       </c>
       <c r="V47">
-        <v>0.05069451485349285</v>
+        <v>0.06547802892039871</v>
       </c>
       <c r="W47">
-        <v>0.0728345818335117</v>
+        <v>0.04179331306990881</v>
       </c>
       <c r="X47">
-        <v>0.05719297555733287</v>
+        <v>0.09136470732014576</v>
       </c>
       <c r="Y47">
-        <v>0.01564160627617883</v>
+        <v>-0.04957139425023695</v>
       </c>
       <c r="Z47">
-        <v>0.08736009509217518</v>
+        <v>0.05964724836054196</v>
       </c>
       <c r="AA47">
-        <v>0.001318618230537512</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>0.04055833535510563</v>
+        <v>0.07298399435209556</v>
       </c>
       <c r="AC47">
-        <v>-0.03923971712456811</v>
+        <v>-0.07298399435209556</v>
       </c>
       <c r="AD47">
-        <v>7639.2</v>
+        <v>2920.8</v>
       </c>
       <c r="AE47">
-        <v>45.57696723504367</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>7684.776967235043</v>
+        <v>2920.8</v>
       </c>
       <c r="AG47">
-        <v>7384.776967235043</v>
+        <v>2687.6</v>
       </c>
       <c r="AH47">
-        <v>0.5649500815724556</v>
+        <v>0.4505808123659812</v>
       </c>
       <c r="AI47">
-        <v>0.6933168174446586</v>
+        <v>0.6494996664442962</v>
       </c>
       <c r="AJ47">
-        <v>0.5551388265164068</v>
+        <v>0.430077931222096</v>
       </c>
       <c r="AK47">
-        <v>0.6847852616104283</v>
+        <v>0.6303297528026643</v>
       </c>
       <c r="AL47">
         <v>0</v>
       </c>
       <c r="AM47">
         <v>0</v>
-      </c>
-      <c r="AN47">
-        <v>327.862660944206</v>
-      </c>
-      <c r="AP47">
-        <v>316.9432174778988</v>
       </c>
     </row>
     <row r="48">
@@ -6341,7 +6200,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CSC Financial Co., Ltd. (SEHK:6066)</t>
+          <t>Guotai Junan Securities Co., Ltd. (SHSE:601211)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6350,13 +6209,13 @@
         </is>
       </c>
       <c r="D48">
-        <v>0.129</v>
+        <v>0.104</v>
       </c>
       <c r="E48">
-        <v>0.08359999999999999</v>
+        <v>0.0505</v>
       </c>
       <c r="F48">
-        <v>0.00433</v>
+        <v>0.083</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6371,85 +6230,85 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>1439.4</v>
+        <v>1659.5</v>
       </c>
       <c r="L48">
-        <v>0.3094086541561875</v>
+        <v>0.3198111389477741</v>
       </c>
       <c r="M48">
-        <v>504.7</v>
+        <v>1683.17</v>
       </c>
       <c r="N48">
-        <v>0.01613073340982674</v>
+        <v>0.1038730938466191</v>
       </c>
       <c r="O48">
-        <v>0.3506322078643879</v>
+        <v>1.014263332329015</v>
       </c>
       <c r="P48">
-        <v>504.7</v>
+        <v>1681.4</v>
       </c>
       <c r="Q48">
-        <v>0.01613073340982674</v>
+        <v>0.103763862232398</v>
       </c>
       <c r="R48">
-        <v>0.3506322078643879</v>
+        <v>1.013196746007834</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.769999999999982</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>0.001051587183706923</v>
       </c>
       <c r="U48">
-        <v>5910.2</v>
+        <v>5541.2</v>
       </c>
       <c r="V48">
-        <v>0.1888960978774678</v>
+        <v>0.3419628365660543</v>
       </c>
       <c r="W48">
-        <v>0.1583428672005633</v>
+        <v>0.07440169292432952</v>
       </c>
       <c r="X48">
-        <v>0.05456825895456311</v>
+        <v>0.1425335080006312</v>
       </c>
       <c r="Y48">
-        <v>0.1037746082460002</v>
+        <v>-0.06813181507630167</v>
       </c>
       <c r="Z48">
-        <v>0.1355617591178768</v>
+        <v>0.07301862573008074</v>
       </c>
       <c r="AA48">
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>0.03955193154580033</v>
+        <v>0.07299176552806469</v>
       </c>
       <c r="AC48">
-        <v>-0.03955193154580033</v>
+        <v>-0.07299176552806469</v>
       </c>
       <c r="AD48">
-        <v>35495.5</v>
+        <v>47256.9</v>
       </c>
       <c r="AE48">
         <v>0</v>
       </c>
       <c r="AF48">
-        <v>35495.5</v>
+        <v>47256.9</v>
       </c>
       <c r="AG48">
-        <v>29585.3</v>
+        <v>41715.7</v>
       </c>
       <c r="AH48">
-        <v>0.5315002485640187</v>
+        <v>0.7446605001496983</v>
       </c>
       <c r="AI48">
-        <v>0.7480942254557104</v>
+        <v>0.679707962425189</v>
       </c>
       <c r="AJ48">
-        <v>0.4860135954292023</v>
+        <v>0.7202321140611674</v>
       </c>
       <c r="AK48">
-        <v>0.7122517616526673</v>
+        <v>0.65196978624377</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -6466,7 +6325,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CITIC Securities Company Limited (SHSE:600030)</t>
+          <t>Huatai Securities Co., Ltd. (SHSE:601688)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6475,13 +6334,13 @@
         </is>
       </c>
       <c r="D49">
-        <v>0.115</v>
+        <v>0.153</v>
       </c>
       <c r="E49">
-        <v>0.118</v>
+        <v>0.104</v>
       </c>
       <c r="F49">
-        <v>0.0906</v>
+        <v>0.0765</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -6496,85 +6355,85 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>3181.2</v>
+        <v>1422.3</v>
       </c>
       <c r="L49">
-        <v>0.2947793695213032</v>
+        <v>0.2852644457369783</v>
       </c>
       <c r="M49">
-        <v>1865.9</v>
+        <v>840.88</v>
       </c>
       <c r="N49">
-        <v>0.03715807165957719</v>
+        <v>0.05463985184703857</v>
       </c>
       <c r="O49">
-        <v>0.5865396705645669</v>
+        <v>0.5912114181255713</v>
       </c>
       <c r="P49">
-        <v>1865.9</v>
+        <v>834</v>
       </c>
       <c r="Q49">
-        <v>0.03715807165957719</v>
+        <v>0.05419279378797232</v>
       </c>
       <c r="R49">
-        <v>0.5865396705645669</v>
+        <v>0.5863741826618857</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>6.879999999999995</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>0.008181904671296732</v>
       </c>
       <c r="U49">
-        <v>11688.7</v>
+        <v>7401.3</v>
       </c>
       <c r="V49">
-        <v>0.2327721486721152</v>
+        <v>0.4809318041521817</v>
       </c>
       <c r="W49">
-        <v>0.1201858778193358</v>
+        <v>0.0658216249236408</v>
       </c>
       <c r="X49">
-        <v>0.05814715406840897</v>
+        <v>0.1559593655480293</v>
       </c>
       <c r="Y49">
-        <v>0.06203872375092685</v>
+        <v>-0.09013774062438848</v>
       </c>
       <c r="Z49">
-        <v>0.1296193981090015</v>
+        <v>0.07620798809016137</v>
       </c>
       <c r="AA49">
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>0.03981353174946203</v>
+        <v>0.07306125035749791</v>
       </c>
       <c r="AC49">
-        <v>-0.03981353174946203</v>
+        <v>-0.07306125035749791</v>
       </c>
       <c r="AD49">
-        <v>68204.7</v>
+        <v>53345.8</v>
       </c>
       <c r="AE49">
         <v>0</v>
       </c>
       <c r="AF49">
-        <v>68204.7</v>
+        <v>53345.8</v>
       </c>
       <c r="AG49">
-        <v>56516</v>
+        <v>45944.5</v>
       </c>
       <c r="AH49">
-        <v>0.5759564059756849</v>
+        <v>0.7761048544197814</v>
       </c>
       <c r="AI49">
-        <v>0.6784849539915444</v>
+        <v>0.7018205355568828</v>
       </c>
       <c r="AJ49">
-        <v>0.5295171421290119</v>
+        <v>0.7490869664460169</v>
       </c>
       <c r="AK49">
-        <v>0.6361813808094213</v>
+        <v>0.6696541139466515</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -6591,7 +6450,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>China International Capital Corporation Limited (SEHK:3908)</t>
+          <t>China Great Wall Securities Co.,Ltd. (SZSE:002939)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6600,13 +6459,10 @@
         </is>
       </c>
       <c r="D50">
-        <v>0.38</v>
+        <v>0.0793</v>
       </c>
       <c r="E50">
-        <v>0.449</v>
-      </c>
-      <c r="F50">
-        <v>0.3</v>
+        <v>0.0114</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -6621,28 +6477,28 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>1516</v>
+        <v>137.5</v>
       </c>
       <c r="L50">
-        <v>0.3037224025323557</v>
+        <v>0.2137084239975132</v>
       </c>
       <c r="M50">
-        <v>886.3</v>
+        <v>204.9</v>
       </c>
       <c r="N50">
-        <v>0.03186639341315212</v>
+        <v>0.0423058658352776</v>
       </c>
       <c r="O50">
-        <v>0.5846306068601583</v>
+        <v>1.490181818181818</v>
       </c>
       <c r="P50">
-        <v>886.3</v>
+        <v>204.9</v>
       </c>
       <c r="Q50">
-        <v>0.03186639341315212</v>
+        <v>0.0423058658352776</v>
       </c>
       <c r="R50">
-        <v>0.5846306068601583</v>
+        <v>1.490181818181818</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -6651,55 +6507,55 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>7713.6</v>
+        <v>164.4</v>
       </c>
       <c r="V50">
-        <v>0.2773379354977888</v>
+        <v>0.033943798649681</v>
       </c>
       <c r="W50">
-        <v>0.1817702213376178</v>
+        <v>0.04623869253791573</v>
       </c>
       <c r="X50">
-        <v>0.06105038226905384</v>
+        <v>0.1003689204517235</v>
       </c>
       <c r="Y50">
-        <v>0.1207198390685639</v>
+        <v>-0.05413022791380773</v>
       </c>
       <c r="Z50">
-        <v>0.1394530169559715</v>
+        <v>0.06723549666382773</v>
       </c>
       <c r="AA50">
         <v>0</v>
       </c>
       <c r="AB50">
-        <v>0.03999187859768746</v>
+        <v>0.07332052320308323</v>
       </c>
       <c r="AC50">
-        <v>-0.03999187859768746</v>
+        <v>-0.07332052320308323</v>
       </c>
       <c r="AD50">
-        <v>42825.8</v>
+        <v>5758.6</v>
       </c>
       <c r="AE50">
         <v>0</v>
       </c>
       <c r="AF50">
-        <v>42825.8</v>
+        <v>5758.6</v>
       </c>
       <c r="AG50">
-        <v>35112.2</v>
+        <v>5594.200000000001</v>
       </c>
       <c r="AH50">
-        <v>0.6062645458303368</v>
+        <v>0.5431667908582424</v>
       </c>
       <c r="AI50">
-        <v>0.772004650869334</v>
+        <v>0.5959679589344483</v>
       </c>
       <c r="AJ50">
-        <v>0.5579990210599252</v>
+        <v>0.5359712574850301</v>
       </c>
       <c r="AK50">
-        <v>0.7351816063266464</v>
+        <v>0.5889747531111158</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -6716,7 +6572,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Zhongtai Securities Co., Ltd. (SHSE:600918)</t>
+          <t>Guosen Securities Co., Ltd. (SZSE:002736)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6724,110 +6580,110 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D51">
+        <v>0.113</v>
+      </c>
+      <c r="E51">
+        <v>0.109</v>
+      </c>
       <c r="G51">
-        <v>0</v>
+        <v>0.04423308111166113</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0.01140411963176031</v>
+        <v>0</v>
       </c>
       <c r="J51">
-        <v>0.009072710449306007</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>430.6</v>
+        <v>994.8</v>
       </c>
       <c r="L51">
-        <v>0.2374676005073623</v>
+        <v>0.3517431581924899</v>
       </c>
       <c r="M51">
-        <v>1303.3</v>
+        <v>1118.8</v>
       </c>
       <c r="N51">
-        <v>0.1191664837978202</v>
+        <v>0.090402236623087</v>
       </c>
       <c r="O51">
-        <v>3.02670692057594</v>
+        <v>1.12464817048653</v>
       </c>
       <c r="P51">
-        <v>372.2</v>
+        <v>1118.8</v>
       </c>
       <c r="Q51">
-        <v>0.0340318923268232</v>
+        <v>0.090402236623087</v>
       </c>
       <c r="R51">
-        <v>0.8643752902926148</v>
+        <v>1.12464817048653</v>
       </c>
       <c r="S51">
-        <v>931.0999999999999</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>0.7144172485229801</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>1067.4</v>
+        <v>1813.3</v>
       </c>
       <c r="V51">
-        <v>0.09759710335747204</v>
+        <v>0.1465198209408685</v>
       </c>
       <c r="W51">
-        <v>0.08862817742101473</v>
+        <v>0.06780030669620037</v>
       </c>
       <c r="X51">
-        <v>0.05832426720647345</v>
+        <v>0.1254199885356819</v>
       </c>
       <c r="Y51">
-        <v>0.03030391021454128</v>
+        <v>-0.0576196818394815</v>
       </c>
       <c r="Z51">
-        <v>0.1166874392943918</v>
+        <v>0.06970660965654175</v>
       </c>
       <c r="AA51">
-        <v>0.001058671349788989</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>0.04134228291913627</v>
+        <v>0.07385053193437451</v>
       </c>
       <c r="AC51">
-        <v>-0.04028361156934728</v>
+        <v>-0.07385053193437451</v>
       </c>
       <c r="AD51">
-        <v>14898.4</v>
+        <v>27415.6</v>
       </c>
       <c r="AE51">
-        <v>77.60454935864513</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>14976.00454935864</v>
+        <v>27415.6</v>
       </c>
       <c r="AG51">
-        <v>13908.60454935864</v>
+        <v>25602.3</v>
       </c>
       <c r="AH51">
-        <v>0.5779383902978309</v>
+        <v>0.6889830465879563</v>
       </c>
       <c r="AI51">
-        <v>0.7263133994092158</v>
+        <v>0.648754815565042</v>
       </c>
       <c r="AJ51">
-        <v>0.5598059199127703</v>
+        <v>0.6741332504785653</v>
       </c>
       <c r="AK51">
-        <v>0.7113719101603277</v>
+        <v>0.6330073803018877</v>
       </c>
       <c r="AL51">
         <v>0</v>
       </c>
       <c r="AM51">
         <v>0</v>
-      </c>
-      <c r="AN51">
-        <v>411.5580110497237</v>
-      </c>
-      <c r="AP51">
-        <v>384.2155952861503</v>
       </c>
     </row>
     <row r="52">
@@ -6838,7 +6694,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Guotai Junan Securities Co., Ltd. (SHSE:601211)</t>
+          <t>Haitong Securities Co., Ltd. (SHSE:600837)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6847,13 +6703,13 @@
         </is>
       </c>
       <c r="D52">
-        <v>0.07049999999999999</v>
+        <v>0.00743</v>
       </c>
       <c r="E52">
-        <v>0.0393</v>
+        <v>-0.0199</v>
       </c>
       <c r="F52">
-        <v>0.083</v>
+        <v>-0.527</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -6868,28 +6724,28 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>2142.2</v>
+        <v>994.6</v>
       </c>
       <c r="L52">
-        <v>0.343455396652344</v>
+        <v>0.2570158664530466</v>
       </c>
       <c r="M52">
-        <v>1315</v>
+        <v>759.6</v>
       </c>
       <c r="N52">
-        <v>0.05698264954153883</v>
+        <v>0.05325630473038821</v>
       </c>
       <c r="O52">
-        <v>0.6138549155074223</v>
+        <v>0.7637241101950533</v>
       </c>
       <c r="P52">
-        <v>1315</v>
+        <v>759.6</v>
       </c>
       <c r="Q52">
-        <v>0.05698264954153883</v>
+        <v>0.05325630473038821</v>
       </c>
       <c r="R52">
-        <v>0.6138549155074223</v>
+        <v>0.7637241101950533</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -6898,55 +6754,55 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>4027</v>
+        <v>9644.799999999999</v>
       </c>
       <c r="V52">
-        <v>0.1745012393184615</v>
+        <v>0.6762064347862666</v>
       </c>
       <c r="W52">
-        <v>0.1076039019097658</v>
+        <v>0.03954624795728083</v>
       </c>
       <c r="X52">
-        <v>0.07300933796571249</v>
+        <v>0.1636276203374212</v>
       </c>
       <c r="Y52">
-        <v>0.03459456394405332</v>
+        <v>-0.1240813723801403</v>
       </c>
       <c r="Z52">
-        <v>0.1004069595229816</v>
+        <v>0.054558399537569</v>
       </c>
       <c r="AA52">
         <v>0</v>
       </c>
       <c r="AB52">
-        <v>0.04051886303562574</v>
+        <v>0.07422067845813221</v>
       </c>
       <c r="AC52">
-        <v>-0.04051886303562574</v>
+        <v>-0.07422067845813221</v>
       </c>
       <c r="AD52">
-        <v>52789.7</v>
+        <v>53922</v>
       </c>
       <c r="AE52">
         <v>0</v>
       </c>
       <c r="AF52">
-        <v>52789.7</v>
+        <v>53922</v>
       </c>
       <c r="AG52">
-        <v>48762.7</v>
+        <v>44277.2</v>
       </c>
       <c r="AH52">
-        <v>0.6958199161953369</v>
+        <v>0.7908179352967143</v>
       </c>
       <c r="AI52">
-        <v>0.6978075578843846</v>
+        <v>0.6825604180274329</v>
       </c>
       <c r="AJ52">
-        <v>0.6787690406027849</v>
+        <v>0.7563541696916484</v>
       </c>
       <c r="AK52">
-        <v>0.6808169910001983</v>
+        <v>0.6384157981855618</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -6963,7 +6819,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Huatai Securities Co., Ltd. (SHSE:601688)</t>
+          <t>China Galaxy Securities Co., Ltd. (SEHK:6881)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6972,16 +6828,16 @@
         </is>
       </c>
       <c r="D53">
-        <v>0.122</v>
+        <v>0.248</v>
       </c>
       <c r="E53">
-        <v>0.137</v>
+        <v>0.161</v>
       </c>
       <c r="F53">
-        <v>0.133</v>
+        <v>0.305</v>
       </c>
       <c r="G53">
-        <v>0.01810759073328906</v>
+        <v>0</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -6993,85 +6849,85 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>2022.2</v>
+        <v>1331.1</v>
       </c>
       <c r="L53">
-        <v>0.3950072274094621</v>
+        <v>0.2565481352992194</v>
       </c>
       <c r="M53">
-        <v>1380</v>
+        <v>1232.68</v>
       </c>
       <c r="N53">
-        <v>0.05954050264264912</v>
+        <v>0.1175525929316625</v>
       </c>
       <c r="O53">
-        <v>0.6824250815943033</v>
+        <v>0.9260611524303207</v>
       </c>
       <c r="P53">
-        <v>1127.6</v>
+        <v>1232.6</v>
       </c>
       <c r="Q53">
-        <v>0.04865063099989213</v>
+        <v>0.11754496385726</v>
       </c>
       <c r="R53">
-        <v>0.5576105231925625</v>
+        <v>0.9260010517617009</v>
       </c>
       <c r="S53">
-        <v>252.4000000000001</v>
+        <v>0.07999999999992724</v>
       </c>
       <c r="T53">
-        <v>0.1828985507246378</v>
+        <v>6.489924392374927e-05</v>
       </c>
       <c r="U53">
-        <v>9422.4</v>
+        <v>2475.3</v>
       </c>
       <c r="V53">
-        <v>0.4065321971739834</v>
+        <v>0.2360530983578417</v>
       </c>
       <c r="W53">
-        <v>0.1080506323703067</v>
+        <v>0.08922239575303809</v>
       </c>
       <c r="X53">
-        <v>0.07347549793707642</v>
+        <v>0.1784502065961737</v>
       </c>
       <c r="Y53">
-        <v>0.03457513443323024</v>
+        <v>-0.08922781084313564</v>
       </c>
       <c r="Z53">
-        <v>0.09017918166893316</v>
+        <v>0.09875427059640841</v>
       </c>
       <c r="AA53">
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>0.0405345931640565</v>
+        <v>0.07430637330172779</v>
       </c>
       <c r="AC53">
-        <v>-0.0405345931640565</v>
+        <v>-0.07430637330172779</v>
       </c>
       <c r="AD53">
-        <v>53694.7</v>
+        <v>46011</v>
       </c>
       <c r="AE53">
         <v>0</v>
       </c>
       <c r="AF53">
-        <v>53694.7</v>
+        <v>46011</v>
       </c>
       <c r="AG53">
-        <v>44272.3</v>
+        <v>43535.7</v>
       </c>
       <c r="AH53">
-        <v>0.6984930833253113</v>
+        <v>0.8143943416664897</v>
       </c>
       <c r="AI53">
-        <v>0.7078261396862056</v>
+        <v>0.7603465029117614</v>
       </c>
       <c r="AJ53">
-        <v>0.6563740737555931</v>
+        <v>0.8058898335674977</v>
       </c>
       <c r="AK53">
-        <v>0.6663882040213016</v>
+        <v>0.7501253491253129</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -7088,7 +6944,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hengtai Securities Co., Ltd (SEHK:1476)</t>
+          <t>Dongxing Securities Corporation Limited (SHSE:601198)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7097,10 +6953,10 @@
         </is>
       </c>
       <c r="D54">
-        <v>-0.025</v>
+        <v>0.107</v>
       </c>
       <c r="E54">
-        <v>-0.147</v>
+        <v>-0.0294</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7109,100 +6965,97 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>0.001760057069925775</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>0.001329292351610608</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>50</v>
+        <v>143.2</v>
       </c>
       <c r="L54">
-        <v>0.1028594939312898</v>
+        <v>0.2344082501227697</v>
       </c>
       <c r="M54">
-        <v>-0</v>
+        <v>255.4</v>
       </c>
       <c r="N54">
-        <v>-0</v>
+        <v>0.07058953594428015</v>
       </c>
       <c r="O54">
-        <v>-0</v>
+        <v>1.783519553072626</v>
       </c>
       <c r="P54">
-        <v>-0</v>
+        <v>255.4</v>
       </c>
       <c r="Q54">
-        <v>-0</v>
+        <v>0.07058953594428015</v>
       </c>
       <c r="R54">
-        <v>-0</v>
+        <v>1.783519553072626</v>
       </c>
       <c r="S54">
         <v>0</v>
       </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
       <c r="U54">
-        <v>191.6</v>
+        <v>591.5</v>
       </c>
       <c r="V54">
-        <v>0.1597865065465766</v>
+        <v>0.1634835963627318</v>
       </c>
       <c r="W54">
-        <v>0.04058112166220275</v>
+        <v>0.04219459013495196</v>
       </c>
       <c r="X54">
-        <v>0.06146753730930446</v>
+        <v>0.1162357275533082</v>
       </c>
       <c r="Y54">
-        <v>-0.02088641564710171</v>
+        <v>-0.07404113741835627</v>
       </c>
       <c r="Z54">
-        <v>0.21103291164728</v>
+        <v>0.05693436099124875</v>
       </c>
       <c r="AA54">
-        <v>0.0002805244353908464</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>0.0408899399127097</v>
+        <v>0.07472093728586207</v>
       </c>
       <c r="AC54">
-        <v>-0.04060941547731885</v>
+        <v>-0.07472093728586207</v>
       </c>
       <c r="AD54">
-        <v>1876.6</v>
+        <v>6653.7</v>
       </c>
       <c r="AE54">
-        <v>1.022181291545404</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>1877.622181291545</v>
+        <v>6653.7</v>
       </c>
       <c r="AG54">
-        <v>1686.022181291545</v>
+        <v>6062.2</v>
       </c>
       <c r="AH54">
-        <v>0.6102670539149421</v>
+        <v>0.6477637804474387</v>
       </c>
       <c r="AI54">
-        <v>0.5626471190709778</v>
+        <v>0.6407646379044684</v>
       </c>
       <c r="AJ54">
-        <v>0.5843850191941561</v>
+        <v>0.6262409222854664</v>
       </c>
       <c r="AK54">
-        <v>0.5360070869375552</v>
+        <v>0.6190656114373244</v>
       </c>
       <c r="AL54">
         <v>0</v>
       </c>
       <c r="AM54">
         <v>0</v>
-      </c>
-      <c r="AN54">
-        <v>1770.377358490566</v>
-      </c>
-      <c r="AP54">
-        <v>1590.58696348259</v>
       </c>
     </row>
     <row r="55">
@@ -7222,16 +7075,16 @@
         </is>
       </c>
       <c r="D55">
-        <v>0.257</v>
+        <v>0.144</v>
       </c>
       <c r="E55">
-        <v>0.0395</v>
+        <v>-0.0009299999999999999</v>
       </c>
       <c r="F55">
         <v>0.123</v>
       </c>
       <c r="G55">
-        <v>0.01488274203247144</v>
+        <v>0</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -7243,28 +7096,28 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>619.6</v>
+        <v>429.1</v>
       </c>
       <c r="L55">
-        <v>0.1552415313690118</v>
+        <v>0.1720115449370641</v>
       </c>
       <c r="M55">
-        <v>838.2</v>
+        <v>702.2</v>
       </c>
       <c r="N55">
-        <v>0.05693713276500357</v>
+        <v>0.06901635477276302</v>
       </c>
       <c r="O55">
-        <v>1.352808263395739</v>
+        <v>1.636448380330925</v>
       </c>
       <c r="P55">
-        <v>838.2</v>
+        <v>702.2</v>
       </c>
       <c r="Q55">
-        <v>0.05693713276500357</v>
+        <v>0.06901635477276302</v>
       </c>
       <c r="R55">
-        <v>1.352808263395739</v>
+        <v>1.636448380330925</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -7273,55 +7126,55 @@
         <v>0</v>
       </c>
       <c r="U55">
-        <v>2893.3</v>
+        <v>3992.5</v>
       </c>
       <c r="V55">
-        <v>0.1965356791087865</v>
+        <v>0.3924064318289039</v>
       </c>
       <c r="W55">
-        <v>0.06958201379062506</v>
+        <v>0.04372280698179151</v>
       </c>
       <c r="X55">
-        <v>0.06188014595939949</v>
+        <v>0.1210698213890453</v>
       </c>
       <c r="Y55">
-        <v>0.007701867831225576</v>
+        <v>-0.07734701440725383</v>
       </c>
       <c r="Z55">
-        <v>0.1386157251329911</v>
+        <v>0.08220141356379343</v>
       </c>
       <c r="AA55">
         <v>0</v>
       </c>
       <c r="AB55">
-        <v>0.04165039575456532</v>
+        <v>0.0748405988370919</v>
       </c>
       <c r="AC55">
-        <v>-0.04165039575456532</v>
+        <v>-0.0748405988370919</v>
       </c>
       <c r="AD55">
-        <v>23431.6</v>
+        <v>20725.7</v>
       </c>
       <c r="AE55">
         <v>0</v>
       </c>
       <c r="AF55">
-        <v>23431.6</v>
+        <v>20725.7</v>
       </c>
       <c r="AG55">
-        <v>20538.3</v>
+        <v>16733.2</v>
       </c>
       <c r="AH55">
-        <v>0.6141466879493409</v>
+        <v>0.6707324571765141</v>
       </c>
       <c r="AI55">
-        <v>0.7047203717349133</v>
+        <v>0.6560135977767508</v>
       </c>
       <c r="AJ55">
-        <v>0.5824848694547331</v>
+        <v>0.6218763472030208</v>
       </c>
       <c r="AK55">
-        <v>0.6765767783846464</v>
+        <v>0.6062555931147172</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -7338,7 +7191,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Haitong Securities Co., Ltd. (SHSE:600837)</t>
+          <t>Zhongtai Securities Co., Ltd. (SHSE:600918)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7346,15 +7199,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D56">
-        <v>0.07049999999999999</v>
-      </c>
-      <c r="E56">
-        <v>0.0498</v>
-      </c>
-      <c r="F56">
-        <v>-0.527</v>
-      </c>
       <c r="G56">
         <v>0</v>
       </c>
@@ -7368,28 +7212,28 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>2203.4</v>
+        <v>222.6</v>
       </c>
       <c r="L56">
-        <v>0.3308805862566074</v>
+        <v>0.1391771914467925</v>
       </c>
       <c r="M56">
-        <v>2398.1</v>
+        <v>399.7</v>
       </c>
       <c r="N56">
-        <v>0.1107457710087235</v>
+        <v>0.06171638564634674</v>
       </c>
       <c r="O56">
-        <v>1.088363438322592</v>
+        <v>1.795597484276729</v>
       </c>
       <c r="P56">
-        <v>2398.1</v>
+        <v>399.7</v>
       </c>
       <c r="Q56">
-        <v>0.1107457710087235</v>
+        <v>0.06171638564634674</v>
       </c>
       <c r="R56">
-        <v>1.088363438322592</v>
+        <v>1.795597484276729</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -7398,55 +7242,55 @@
         <v>0</v>
       </c>
       <c r="U56">
-        <v>11499.7</v>
+        <v>1191.5</v>
       </c>
       <c r="V56">
-        <v>0.5310634013881899</v>
+        <v>0.1839756654931752</v>
       </c>
       <c r="W56">
-        <v>0.09687957544286989</v>
+        <v>0.04081408140814081</v>
       </c>
       <c r="X56">
-        <v>0.07917002869579219</v>
+        <v>0.1256513981578483</v>
       </c>
       <c r="Y56">
-        <v>0.0177095467470777</v>
+        <v>-0.0848373167497075</v>
       </c>
       <c r="Z56">
-        <v>0.08989455694613374</v>
+        <v>0.08293492351568577</v>
       </c>
       <c r="AA56">
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>0.04174941835780119</v>
+        <v>0.07494044374753173</v>
       </c>
       <c r="AC56">
-        <v>-0.04174941835780119</v>
+        <v>-0.07494044374753173</v>
       </c>
       <c r="AD56">
-        <v>57875.6</v>
+        <v>14408.3</v>
       </c>
       <c r="AE56">
         <v>0</v>
       </c>
       <c r="AF56">
-        <v>57875.6</v>
+        <v>14408.3</v>
       </c>
       <c r="AG56">
-        <v>46375.89999999999</v>
+        <v>13216.8</v>
       </c>
       <c r="AH56">
-        <v>0.7277231021869818</v>
+        <v>0.6898973889976874</v>
       </c>
       <c r="AI56">
-        <v>0.6773013084799</v>
+        <v>0.7342183041174072</v>
       </c>
       <c r="AJ56">
-        <v>0.6816977803910039</v>
+        <v>0.6711352141856073</v>
       </c>
       <c r="AK56">
-        <v>0.6271199963218689</v>
+        <v>0.7170378407703784</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/research/traditional_assets/database/data/china/china_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/china/china_brokerage_investment_banking.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.104</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0505</v>
+        <v>0.129</v>
       </c>
       <c r="F2">
-        <v>0.083</v>
+        <v>0.128</v>
       </c>
       <c r="G2">
-        <v>0.002668168370168764</v>
+        <v>0.002725305963015473</v>
       </c>
       <c r="H2">
-        <v>0.0005921725142265136</v>
+        <v>0.0008326343698355309</v>
       </c>
       <c r="I2">
-        <v>1.736248557630665e-05</v>
+        <v>-0.0004838158171055896</v>
       </c>
       <c r="J2">
-        <v>1.468566889174114e-05</v>
+        <v>-0.000425285178713277</v>
       </c>
       <c r="K2">
-        <v>21262.185</v>
+        <v>19151.36</v>
       </c>
       <c r="L2">
-        <v>0.2444831368815391</v>
+        <v>0.2521318770668574</v>
       </c>
       <c r="M2">
-        <v>21098.6339</v>
+        <v>18434.7911</v>
       </c>
       <c r="N2">
-        <v>0.05882254153251843</v>
+        <v>0.0510502488572064</v>
       </c>
       <c r="O2">
-        <v>0.9923078883943489</v>
+        <v>0.9625839157114692</v>
       </c>
       <c r="P2">
-        <v>20919.1039</v>
+        <v>16341.8341</v>
       </c>
       <c r="Q2">
-        <v>0.058322015719739</v>
+        <v>0.04525436133573444</v>
       </c>
       <c r="R2">
-        <v>0.9838642594822685</v>
+        <v>0.8532988832124716</v>
       </c>
       <c r="S2">
-        <v>179.5299999999999</v>
+        <v>2092.957</v>
       </c>
       <c r="T2">
-        <v>0.008509081718319206</v>
+        <v>0.1135329925165249</v>
       </c>
       <c r="U2">
-        <v>122316.1</v>
+        <v>120659.59</v>
       </c>
       <c r="V2">
-        <v>0.3410146792653565</v>
+        <v>0.3341346296301937</v>
       </c>
       <c r="W2">
-        <v>0.04898971057045419</v>
+        <v>0.05089764737947835</v>
       </c>
       <c r="X2">
-        <v>0.1109174792403322</v>
+        <v>0.08792910336160735</v>
       </c>
       <c r="Y2">
-        <v>-0.06192776866987802</v>
+        <v>-0.037031455982129</v>
       </c>
       <c r="Z2">
-        <v>0.08740600019080309</v>
+        <v>0.08221715920036574</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07030027514289208</v>
+        <v>0.05887059239903851</v>
       </c>
       <c r="AC2">
-        <v>-0.07030027514289208</v>
+        <v>-0.05887059239903851</v>
       </c>
       <c r="AD2">
-        <v>747936</v>
+        <v>736222.6</v>
       </c>
       <c r="AE2">
-        <v>12.1951054532416</v>
+        <v>11.02270764559706</v>
       </c>
       <c r="AF2">
-        <v>747948.1951054533</v>
+        <v>736233.6227076456</v>
       </c>
       <c r="AG2">
-        <v>625632.0951054533</v>
+        <v>615574.0327076457</v>
       </c>
       <c r="AH2">
-        <v>0.6758785886294281</v>
+        <v>0.6709230707924234</v>
       </c>
       <c r="AI2">
-        <v>0.678995277414043</v>
+        <v>0.6728395529027557</v>
       </c>
       <c r="AJ2">
-        <v>0.6356015724403186</v>
+        <v>0.6302689210684196</v>
       </c>
       <c r="AK2">
-        <v>0.6388986367552032</v>
+        <v>0.632292404922</v>
       </c>
       <c r="AL2">
-        <v>55.9</v>
+        <v>22</v>
       </c>
       <c r="AM2">
-        <v>-638.8000000000001</v>
+        <v>-864</v>
       </c>
       <c r="AN2">
-        <v>113858.4259400213</v>
+        <v>-33671.28287217014</v>
       </c>
       <c r="AO2">
-        <v>-0.02182468694096601</v>
+        <v>-1.783636363636364</v>
       </c>
       <c r="AP2">
-        <v>95240.08145919521</v>
+        <v>-28153.39733398791</v>
       </c>
       <c r="AQ2">
-        <v>0.001909830932999374</v>
+        <v>0.04541666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shenwan Hongyuan Group Co., Ltd. (SZSE:000166)</t>
+          <t>Guangzhou Yuexiu Capital Holdings Group Co., Ltd. (SZSE:000987)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.135</v>
+        <v>0.106</v>
       </c>
       <c r="E3">
-        <v>0.0403</v>
+        <v>0.424</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.0007657082801591473</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -743,28 +743,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>881</v>
+        <v>359.2</v>
       </c>
       <c r="L3">
-        <v>0.2336188380048262</v>
+        <v>0.2696494257187899</v>
       </c>
       <c r="M3">
-        <v>1248.5</v>
+        <v>406</v>
       </c>
       <c r="N3">
-        <v>0.09268814170855018</v>
+        <v>0.0953185894726957</v>
       </c>
       <c r="O3">
-        <v>1.417139614074915</v>
+        <v>1.130289532293987</v>
       </c>
       <c r="P3">
-        <v>1248.5</v>
+        <v>406</v>
       </c>
       <c r="Q3">
-        <v>0.09268814170855018</v>
+        <v>0.0953185894726957</v>
       </c>
       <c r="R3">
-        <v>1.417139614074915</v>
+        <v>1.130289532293987</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,61 +773,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5761.6</v>
+        <v>2753.7</v>
       </c>
       <c r="V3">
-        <v>0.4277388844757571</v>
+        <v>0.6464995069728131</v>
       </c>
       <c r="W3">
-        <v>0.05760391261989917</v>
+        <v>0.09657731293522974</v>
       </c>
       <c r="X3">
-        <v>0.1588223251413954</v>
+        <v>0.1251693964504726</v>
       </c>
       <c r="Y3">
-        <v>-0.1012184125214963</v>
+        <v>-0.02859208351524285</v>
       </c>
       <c r="Z3">
-        <v>0.06210240119623411</v>
+        <v>0.08829572871649388</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06744470597468225</v>
+        <v>0.05684598494967933</v>
       </c>
       <c r="AC3">
-        <v>-0.06744470597468225</v>
+        <v>-0.05684598494967933</v>
       </c>
       <c r="AD3">
-        <v>48271.6</v>
+        <v>16820.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>48271.6</v>
+        <v>16820.1</v>
       </c>
       <c r="AG3">
-        <v>42510</v>
+        <v>14066.4</v>
       </c>
       <c r="AH3">
-        <v>0.781833936655248</v>
+        <v>0.7979363836903152</v>
       </c>
       <c r="AI3">
-        <v>0.7432071242055477</v>
+        <v>0.750877208646197</v>
       </c>
       <c r="AJ3">
-        <v>0.7593797059301642</v>
+        <v>0.7675735847821106</v>
       </c>
       <c r="AK3">
-        <v>0.7182102019300949</v>
+        <v>0.715960278720816</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-381.3</v>
+      </c>
+      <c r="AQ3">
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -847,13 +850,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.109</v>
+        <v>0.106</v>
       </c>
       <c r="E4">
-        <v>0.028</v>
+        <v>0.129</v>
       </c>
       <c r="G4">
-        <v>0.006799390774586597</v>
+        <v>0.01663019693654267</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -865,28 +868,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>421.7</v>
+        <v>442.4</v>
       </c>
       <c r="L4">
-        <v>0.2293842471714534</v>
+        <v>0.2420131291028446</v>
       </c>
       <c r="M4">
-        <v>494.4</v>
+        <v>432.8</v>
       </c>
       <c r="N4">
-        <v>0.0830533530439457</v>
+        <v>0.07086485247404788</v>
       </c>
       <c r="O4">
-        <v>1.172397438937633</v>
+        <v>0.9783001808318265</v>
       </c>
       <c r="P4">
-        <v>494.4</v>
+        <v>432.8</v>
       </c>
       <c r="Q4">
-        <v>0.0830533530439457</v>
+        <v>0.07086485247404788</v>
       </c>
       <c r="R4">
-        <v>1.172397438937633</v>
+        <v>0.9783001808318265</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,61 +898,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>13095.9</v>
+        <v>8248.1</v>
       </c>
       <c r="V4">
-        <v>2.199956323074856</v>
+        <v>1.35050921832531</v>
       </c>
       <c r="W4">
-        <v>0.05598109625774934</v>
+        <v>0.06204246486971643</v>
       </c>
       <c r="X4">
-        <v>0.1563442190543497</v>
+        <v>0.1188633961124013</v>
       </c>
       <c r="Y4">
-        <v>-0.1003631227966004</v>
+        <v>-0.05682093124268485</v>
       </c>
       <c r="Z4">
-        <v>0.117032925059204</v>
+        <v>0.1294911027995013</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06746936522196537</v>
+        <v>0.05692635231553504</v>
       </c>
       <c r="AC4">
-        <v>-0.06746936522196537</v>
+        <v>-0.05692635231553504</v>
       </c>
       <c r="AD4">
-        <v>20728.5</v>
+        <v>21762.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>20728.5</v>
+        <v>21762.3</v>
       </c>
       <c r="AG4">
-        <v>7632.6</v>
+        <v>13514.2</v>
       </c>
       <c r="AH4">
-        <v>0.7768924302788844</v>
+        <v>0.7808587821182145</v>
       </c>
       <c r="AI4">
-        <v>0.7240840878604963</v>
+        <v>0.7291358843691262</v>
       </c>
       <c r="AJ4">
-        <v>0.5618237225256525</v>
+        <v>0.6887409793289029</v>
       </c>
       <c r="AK4">
-        <v>0.491433427980916</v>
+        <v>0.6256979619049383</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-190</v>
+        <v>-110.3</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -963,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Changjiang Securities Company Limited (SZSE:000783)</t>
+          <t>Minmetals Capital Company Limited (SHSE:600390)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,13 +975,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00164</v>
+        <v>-0.0466</v>
       </c>
       <c r="E5">
-        <v>-0.09759999999999999</v>
+        <v>0.0382</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.007561400116031715</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -990,28 +993,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>163.9</v>
+        <v>340.7</v>
       </c>
       <c r="L5">
-        <v>0.1939185991481306</v>
+        <v>0.3294333784567782</v>
       </c>
       <c r="M5">
-        <v>459.7</v>
+        <v>58.4753</v>
       </c>
       <c r="N5">
-        <v>0.1075724247671643</v>
+        <v>0.01969727490147203</v>
       </c>
       <c r="O5">
-        <v>2.804758999389872</v>
+        <v>0.1716328147930731</v>
       </c>
       <c r="P5">
-        <v>459.7</v>
+        <v>58.4753</v>
       </c>
       <c r="Q5">
-        <v>0.1075724247671643</v>
+        <v>0.01969727490147203</v>
       </c>
       <c r="R5">
-        <v>2.804758999389872</v>
+        <v>0.1716328147930731</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1020,61 +1023,64 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1184.6</v>
+        <v>3224</v>
       </c>
       <c r="V5">
-        <v>0.2772031637571957</v>
+        <v>1.085997237848217</v>
       </c>
       <c r="W5">
-        <v>0.03465629162878228</v>
+        <v>0.05976249364135488</v>
       </c>
       <c r="X5">
-        <v>0.1412428845493386</v>
+        <v>0.1111538222176254</v>
       </c>
       <c r="Y5">
-        <v>-0.1065865929205563</v>
+        <v>-0.0513913285762705</v>
       </c>
       <c r="Z5">
-        <v>0.05500670337251228</v>
+        <v>0.08098795595858981</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06764764794763661</v>
+        <v>0.05704519108026608</v>
       </c>
       <c r="AC5">
-        <v>-0.06764764794763661</v>
+        <v>-0.05704519108026608</v>
       </c>
       <c r="AD5">
-        <v>12236.8</v>
+        <v>9178.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>12236.8</v>
+        <v>9178.5</v>
       </c>
       <c r="AG5">
-        <v>11052.2</v>
+        <v>5954.5</v>
       </c>
       <c r="AH5">
-        <v>0.7411660670373467</v>
+        <v>0.7556062302423603</v>
       </c>
       <c r="AI5">
-        <v>0.7372010362070004</v>
+        <v>0.4952704197536194</v>
       </c>
       <c r="AJ5">
-        <v>0.7211593673330897</v>
+        <v>0.6673054509592971</v>
       </c>
       <c r="AK5">
-        <v>0.7170048785551173</v>
+        <v>0.3889719955840949</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-82.5</v>
+      </c>
+      <c r="AQ5">
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -1085,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Minmetals Capital Company Limited (SHSE:600390)</t>
+          <t>China Merchants Securities Co., Ltd. (SHSE:600999)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,13 +1100,16 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0258</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="E6">
-        <v>-0.0174</v>
+        <v>0.118</v>
+      </c>
+      <c r="F6">
+        <v>0.132</v>
       </c>
       <c r="G6">
-        <v>0.003976516634050881</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1112,94 +1121,91 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>299.2</v>
+        <v>1122.6</v>
       </c>
       <c r="L6">
-        <v>0.2342074363992172</v>
+        <v>0.4465216180740623</v>
       </c>
       <c r="M6">
-        <v>85.46390000000001</v>
+        <v>3216.1</v>
       </c>
       <c r="N6">
-        <v>0.02579652882583761</v>
+        <v>0.2099350500995464</v>
       </c>
       <c r="O6">
-        <v>0.2856413770053476</v>
+        <v>2.86486727240335</v>
       </c>
       <c r="P6">
-        <v>85.46390000000001</v>
+        <v>1160.3</v>
       </c>
       <c r="Q6">
-        <v>0.02579652882583761</v>
+        <v>0.07574006984562159</v>
       </c>
       <c r="R6">
-        <v>0.2856413770053476</v>
+        <v>1.033582754320328</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2055.8</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.6392214172444887</v>
       </c>
       <c r="U6">
-        <v>2885</v>
+        <v>1662.7</v>
       </c>
       <c r="V6">
-        <v>0.8708119529127679</v>
+        <v>0.1085348738535853</v>
       </c>
       <c r="W6">
-        <v>0.04863300932999577</v>
+        <v>0.07028637974429933</v>
       </c>
       <c r="X6">
-        <v>0.1378771578652744</v>
+        <v>0.1053640623530228</v>
       </c>
       <c r="Y6">
-        <v>-0.08924414853527861</v>
+        <v>-0.03507768260872343</v>
       </c>
       <c r="Z6">
-        <v>0.08927074016100178</v>
+        <v>0.04495063850968635</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06769545177875115</v>
+        <v>0.05715415038098901</v>
       </c>
       <c r="AC6">
-        <v>-0.06769545177875115</v>
+        <v>-0.05715415038098901</v>
       </c>
       <c r="AD6">
-        <v>9029.9</v>
+        <v>41939.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>9029.9</v>
+        <v>41939.6</v>
       </c>
       <c r="AG6">
-        <v>6144.9</v>
+        <v>40276.9</v>
       </c>
       <c r="AH6">
-        <v>0.7315865801391893</v>
+        <v>0.7324530074695551</v>
       </c>
       <c r="AI6">
-        <v>0.5228056970819823</v>
+        <v>0.7189378680220448</v>
       </c>
       <c r="AJ6">
-        <v>0.649710823755802</v>
+        <v>0.7244515831960343</v>
       </c>
       <c r="AK6">
-        <v>0.427114756377285</v>
+        <v>0.7106919015824169</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-72.5</v>
-      </c>
-      <c r="AQ6">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1210,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>China Merchants Securities Co., Ltd. (SHSE:600999)</t>
+          <t>Changjiang Securities Company Limited (SZSE:000783)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,13 +1225,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.13</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="E7">
-        <v>0.11</v>
-      </c>
-      <c r="F7">
-        <v>0.193</v>
+        <v>0.227</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1240,28 +1243,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1324.7</v>
+        <v>240.2</v>
       </c>
       <c r="L7">
-        <v>0.4073743772679747</v>
+        <v>0.239076341196377</v>
       </c>
       <c r="M7">
-        <v>1589.6</v>
+        <v>295.4</v>
       </c>
       <c r="N7">
-        <v>0.1021436282321493</v>
+        <v>0.07040541506780751</v>
       </c>
       <c r="O7">
-        <v>1.199969804484034</v>
+        <v>1.229808492922565</v>
       </c>
       <c r="P7">
-        <v>1589.6</v>
+        <v>295.4</v>
       </c>
       <c r="Q7">
-        <v>0.1021436282321493</v>
+        <v>0.07040541506780751</v>
       </c>
       <c r="R7">
-        <v>1.199969804484034</v>
+        <v>1.229808492922565</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1270,55 +1273,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2020.4</v>
+        <v>885.9</v>
       </c>
       <c r="V7">
-        <v>0.1298257338199764</v>
+        <v>0.2111447434277951</v>
       </c>
       <c r="W7">
-        <v>0.07787359869260298</v>
+        <v>0.05529847825586481</v>
       </c>
       <c r="X7">
-        <v>0.1371923221293815</v>
+        <v>0.1015168852870356</v>
       </c>
       <c r="Y7">
-        <v>-0.05931872343677848</v>
+        <v>-0.04621840703117081</v>
       </c>
       <c r="Z7">
-        <v>0.04873501478476293</v>
+        <v>0.06529682205234924</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06770561511169933</v>
+        <v>0.05723873542771321</v>
       </c>
       <c r="AC7">
-        <v>-0.06770561511169933</v>
+        <v>-0.05723873542771321</v>
       </c>
       <c r="AD7">
-        <v>41980.2</v>
+        <v>10499.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>41980.2</v>
+        <v>10499.2</v>
       </c>
       <c r="AG7">
-        <v>39959.8</v>
+        <v>9613.300000000001</v>
       </c>
       <c r="AH7">
-        <v>0.7295499334406161</v>
+        <v>0.714479173046431</v>
       </c>
       <c r="AI7">
-        <v>0.7242273421259197</v>
+        <v>0.6918793534059532</v>
       </c>
       <c r="AJ7">
-        <v>0.7197085129911999</v>
+        <v>0.6961619233833009</v>
       </c>
       <c r="AK7">
-        <v>0.7142680949716776</v>
+        <v>0.6727762614598644</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1335,7 +1338,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GF Securities Co., Ltd. (SZSE:000776)</t>
+          <t>Northeast Securities Co., Ltd. (SZSE:000686)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1344,13 +1347,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0277</v>
+        <v>0.0201</v>
       </c>
       <c r="E8">
-        <v>-0.0194</v>
-      </c>
-      <c r="F8">
-        <v>0.07539999999999999</v>
+        <v>0.124</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1365,85 +1365,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>1046.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="L8">
-        <v>0.3124216558228377</v>
+        <v>0.08764125991824959</v>
       </c>
       <c r="M8">
-        <v>1357.6</v>
+        <v>133.9</v>
       </c>
       <c r="N8">
-        <v>0.08642564758758109</v>
+        <v>0.05713676125453382</v>
       </c>
       <c r="O8">
-        <v>1.296904852884983</v>
+        <v>1.836762688614541</v>
       </c>
       <c r="P8">
-        <v>1324.8</v>
+        <v>133.9</v>
       </c>
       <c r="Q8">
-        <v>0.08433757949618992</v>
+        <v>0.05713676125453382</v>
       </c>
       <c r="R8">
-        <v>1.265571264807031</v>
+        <v>1.836762688614541</v>
       </c>
       <c r="S8">
-        <v>32.79999999999995</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.0241602828520919</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>2998.7</v>
+        <v>585.1</v>
       </c>
       <c r="V8">
-        <v>0.1908990788309365</v>
+        <v>0.2496692980584596</v>
       </c>
       <c r="W8">
-        <v>0.06480329340390627</v>
+        <v>0.02867482201156433</v>
       </c>
       <c r="X8">
-        <v>0.1353837420642991</v>
+        <v>0.1014512479399823</v>
       </c>
       <c r="Y8">
-        <v>-0.07058044866039283</v>
+        <v>-0.07277642592841796</v>
       </c>
       <c r="Z8">
-        <v>0.0670647598465713</v>
+        <v>0.1145951009836607</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06773321207413101</v>
+        <v>0.05724027726384341</v>
       </c>
       <c r="AC8">
-        <v>-0.06773321207413101</v>
+        <v>-0.05724027726384341</v>
       </c>
       <c r="AD8">
-        <v>41209.9</v>
+        <v>5854.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>41209.9</v>
+        <v>5854.9</v>
       </c>
       <c r="AG8">
-        <v>38211.2</v>
+        <v>5269.799999999999</v>
       </c>
       <c r="AH8">
-        <v>0.72401973358258</v>
+        <v>0.7141515417642467</v>
       </c>
       <c r="AI8">
-        <v>0.7053808312593501</v>
+        <v>0.6942020393644771</v>
       </c>
       <c r="AJ8">
-        <v>0.7086712599337903</v>
+        <v>0.6921834158643426</v>
       </c>
       <c r="AK8">
-        <v>0.689440399830397</v>
+        <v>0.671406184306081</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Northeast Securities Co., Ltd. (SZSE:000686)</t>
+          <t>Guoyuan Securities Company Limited (SZSE:000728)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0545</v>
+        <v>0.201</v>
       </c>
       <c r="E9">
-        <v>-0.0299</v>
+        <v>0.255</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1487,28 +1487,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>96.2</v>
+        <v>274</v>
       </c>
       <c r="L9">
-        <v>0.1066637099456703</v>
+        <v>0.3116469517743403</v>
       </c>
       <c r="M9">
-        <v>185.3</v>
+        <v>220.8</v>
       </c>
       <c r="N9">
-        <v>0.08400961146121413</v>
+        <v>0.0525314046440807</v>
       </c>
       <c r="O9">
-        <v>1.926195426195426</v>
+        <v>0.8058394160583942</v>
       </c>
       <c r="P9">
-        <v>185.3</v>
+        <v>220.8</v>
       </c>
       <c r="Q9">
-        <v>0.08400961146121413</v>
+        <v>0.0525314046440807</v>
       </c>
       <c r="R9">
-        <v>1.926195426195426</v>
+        <v>0.8058394160583942</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1517,55 +1517,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>971.9</v>
+        <v>470.8</v>
       </c>
       <c r="V9">
-        <v>0.4406310921702861</v>
+        <v>0.1120098972211648</v>
       </c>
       <c r="W9">
-        <v>0.0351248722068059</v>
+        <v>0.05910904972494876</v>
       </c>
       <c r="X9">
-        <v>0.1344138831914123</v>
+        <v>0.09906703417539156</v>
       </c>
       <c r="Y9">
-        <v>-0.09928901098460638</v>
+        <v>-0.0399579844504428</v>
       </c>
       <c r="Z9">
-        <v>0.1042996576926635</v>
+        <v>0.06368706990220935</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06774848110730494</v>
+        <v>0.05729878597205659</v>
       </c>
       <c r="AC9">
-        <v>-0.06774848110730494</v>
+        <v>-0.05729878597205659</v>
       </c>
       <c r="AD9">
-        <v>5698.9</v>
+        <v>9888.200000000001</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>5698.9</v>
+        <v>9888.200000000001</v>
       </c>
       <c r="AG9">
-        <v>4727</v>
+        <v>9417.400000000001</v>
       </c>
       <c r="AH9">
-        <v>0.7209599473724161</v>
+        <v>0.7017187788296407</v>
       </c>
       <c r="AI9">
-        <v>0.6840184840664946</v>
+        <v>0.679111294255005</v>
       </c>
       <c r="AJ9">
-        <v>0.6818411297185801</v>
+        <v>0.6914086016768718</v>
       </c>
       <c r="AK9">
-        <v>0.6422903418664058</v>
+        <v>0.6683889649886088</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guoyuan Securities Company Limited (SZSE:000728)</t>
+          <t>Industrial Securities Co.,Ltd. (SHSE:601377)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1591,13 +1591,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.123</v>
+        <v>0.05</v>
       </c>
       <c r="E10">
-        <v>0.0536</v>
+        <v>0.188</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.004755210561701608</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1609,85 +1609,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>245</v>
+        <v>334.1</v>
       </c>
       <c r="L10">
-        <v>0.2794889345197353</v>
+        <v>0.204205121936312</v>
       </c>
       <c r="M10">
-        <v>292.9</v>
+        <v>662.71</v>
       </c>
       <c r="N10">
-        <v>0.07313540912382331</v>
+        <v>0.09269838161446896</v>
       </c>
       <c r="O10">
-        <v>1.195510204081633</v>
+        <v>1.983567794073631</v>
       </c>
       <c r="P10">
-        <v>292.9</v>
+        <v>655.2</v>
       </c>
       <c r="Q10">
-        <v>0.07313540912382331</v>
+        <v>0.09164789973563106</v>
       </c>
       <c r="R10">
-        <v>1.195510204081633</v>
+        <v>1.961089494163424</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>7.509999999999991</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.01133225694496837</v>
       </c>
       <c r="U10">
-        <v>554.9</v>
+        <v>1760.1</v>
       </c>
       <c r="V10">
-        <v>0.1385552697945017</v>
+        <v>0.2461988222293715</v>
       </c>
       <c r="W10">
-        <v>0.04934641181091261</v>
+        <v>0.0446192473089559</v>
       </c>
       <c r="X10">
-        <v>0.1307196110015128</v>
+        <v>0.09729692111814281</v>
       </c>
       <c r="Y10">
-        <v>-0.0813731991906002</v>
+        <v>-0.05267767380918691</v>
       </c>
       <c r="Z10">
-        <v>0.07298066836505319</v>
+        <v>0.08882444021221012</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06780987988353795</v>
+        <v>0.0573456265027296</v>
       </c>
       <c r="AC10">
-        <v>-0.06780987988353795</v>
+        <v>-0.0573456265027296</v>
       </c>
       <c r="AD10">
-        <v>9741.4</v>
+        <v>16044.6</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>9741.4</v>
+        <v>16044.6</v>
       </c>
       <c r="AG10">
-        <v>9186.5</v>
+        <v>14284.5</v>
       </c>
       <c r="AH10">
-        <v>0.7086561474724108</v>
+        <v>0.6917654363038239</v>
       </c>
       <c r="AI10">
-        <v>0.6774740941651018</v>
+        <v>0.6710750853242321</v>
       </c>
       <c r="AJ10">
-        <v>0.6964006852949649</v>
+        <v>0.6664536055538968</v>
       </c>
       <c r="AK10">
-        <v>0.664527889699872</v>
+        <v>0.6449362716547697</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shanxi Securities Co., Ltd. (SZSE:002500)</t>
+          <t>Tianfeng Securities Co., Ltd. (SHSE:601162)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1713,10 +1713,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.00101</v>
-      </c>
-      <c r="E11">
-        <v>0.0154</v>
+        <v>-0.0228</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1731,28 +1728,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>79.3</v>
+        <v>-155.8</v>
       </c>
       <c r="L11">
-        <v>0.1368657231618916</v>
+        <v>-0.4540950160303119</v>
       </c>
       <c r="M11">
-        <v>149</v>
+        <v>302.5</v>
       </c>
       <c r="N11">
-        <v>0.05401486315026283</v>
+        <v>0.0801048645499563</v>
       </c>
       <c r="O11">
-        <v>1.878940731399748</v>
+        <v>-1.941591784338896</v>
       </c>
       <c r="P11">
-        <v>149</v>
+        <v>302.5</v>
       </c>
       <c r="Q11">
-        <v>0.05401486315026283</v>
+        <v>0.0801048645499563</v>
       </c>
       <c r="R11">
-        <v>1.878940731399748</v>
+        <v>-1.941591784338896</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1761,55 +1758,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1507.4</v>
+        <v>1608.1</v>
       </c>
       <c r="V11">
-        <v>0.5464564074678268</v>
+        <v>0.4258401080422635</v>
       </c>
       <c r="W11">
-        <v>0.02989519716504561</v>
+        <v>-0.04442923546354122</v>
       </c>
       <c r="X11">
-        <v>0.1305913586524849</v>
+        <v>0.09628250664946797</v>
       </c>
       <c r="Y11">
-        <v>-0.1006961614874392</v>
+        <v>-0.1407117421130092</v>
       </c>
       <c r="Z11">
-        <v>0.07618872291184516</v>
+        <v>0.034299127176685</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06781210883586269</v>
+        <v>0.05737390635503545</v>
       </c>
       <c r="AC11">
-        <v>-0.06781210883586269</v>
+        <v>-0.05737390635503545</v>
       </c>
       <c r="AD11">
-        <v>6695.2</v>
+        <v>8240.799999999999</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>6695.2</v>
+        <v>8240.799999999999</v>
       </c>
       <c r="AG11">
-        <v>5187.799999999999</v>
+        <v>6632.699999999999</v>
       </c>
       <c r="AH11">
-        <v>0.7082094841173296</v>
+        <v>0.6857561308468766</v>
       </c>
       <c r="AI11">
-        <v>0.7291737004323724</v>
+        <v>0.7083802532385479</v>
       </c>
       <c r="AJ11">
-        <v>0.6528573046575136</v>
+        <v>0.637208185224325</v>
       </c>
       <c r="AK11">
-        <v>0.6759788911329728</v>
+        <v>0.6616027610421736</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1826,7 +1823,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sealand Securities Co., Ltd. (SZSE:000750)</t>
+          <t>Soochow Securities Co., Ltd. (SHSE:601555)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1835,10 +1832,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.05980000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="E12">
-        <v>-0.137</v>
+        <v>0.67</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1853,28 +1850,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>40.2</v>
+        <v>307.7</v>
       </c>
       <c r="L12">
-        <v>0.06702234078026009</v>
+        <v>0.2300732765066547</v>
       </c>
       <c r="M12">
-        <v>109.3</v>
+        <v>256.4</v>
       </c>
       <c r="N12">
-        <v>0.04158106977098075</v>
+        <v>0.04966874588353802</v>
       </c>
       <c r="O12">
-        <v>2.718905472636816</v>
+        <v>0.8332791680207995</v>
       </c>
       <c r="P12">
-        <v>109.3</v>
+        <v>256.4</v>
       </c>
       <c r="Q12">
-        <v>0.04158106977098075</v>
+        <v>0.04966874588353802</v>
       </c>
       <c r="R12">
-        <v>2.718905472636816</v>
+        <v>0.8332791680207995</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1883,55 +1880,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1803</v>
+        <v>565.1</v>
       </c>
       <c r="V12">
-        <v>0.6859164574298106</v>
+        <v>0.1094688311185154</v>
       </c>
       <c r="W12">
-        <v>0.01395687949171961</v>
+        <v>0.05806536835748792</v>
       </c>
       <c r="X12">
-        <v>0.1240091441873045</v>
+        <v>0.09504383017781379</v>
       </c>
       <c r="Y12">
-        <v>-0.1100522646955849</v>
+        <v>-0.03697846182032587</v>
       </c>
       <c r="Z12">
-        <v>0.1265569052426799</v>
+        <v>0.1181521825554584</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.06793646397274622</v>
+        <v>0.05740996994098132</v>
       </c>
       <c r="AC12">
-        <v>-0.06793646397274622</v>
+        <v>-0.05740996994098132</v>
       </c>
       <c r="AD12">
-        <v>5671.1</v>
+        <v>10874.1</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>5671.1</v>
+        <v>10874.1</v>
       </c>
       <c r="AG12">
-        <v>3868.1</v>
+        <v>10309</v>
       </c>
       <c r="AH12">
-        <v>0.6832897574611131</v>
+        <v>0.678092826898973</v>
       </c>
       <c r="AI12">
-        <v>0.6757825998879872</v>
+        <v>0.6648223325426132</v>
       </c>
       <c r="AJ12">
-        <v>0.5953945849431249</v>
+        <v>0.6663348673664615</v>
       </c>
       <c r="AK12">
-        <v>0.5870630909560017</v>
+        <v>0.6528278229151495</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1948,7 +1945,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tianfeng Securities Co., Ltd. (SHSE:601162)</t>
+          <t>Shanxi Securities Co., Ltd. (SZSE:002500)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1956,6 +1953,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D13">
+        <v>-0.0461</v>
+      </c>
+      <c r="E13">
+        <v>0.184</v>
+      </c>
       <c r="G13">
         <v>0</v>
       </c>
@@ -1969,28 +1972,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.495</v>
+        <v>90.5</v>
       </c>
       <c r="L13">
-        <v>0.001070964950237992</v>
+        <v>0.1590230188016166</v>
       </c>
       <c r="M13">
-        <v>283.1</v>
+        <v>121.5</v>
       </c>
       <c r="N13">
-        <v>0.07851021936271112</v>
+        <v>0.04452669769487302</v>
       </c>
       <c r="O13">
-        <v>571.9191919191919</v>
+        <v>1.342541436464088</v>
       </c>
       <c r="P13">
-        <v>283.1</v>
+        <v>121.5</v>
       </c>
       <c r="Q13">
-        <v>0.07851021936271112</v>
+        <v>0.04452669769487302</v>
       </c>
       <c r="R13">
-        <v>571.9191919191919</v>
+        <v>1.342541436464088</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1999,55 +2002,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1241.7</v>
+        <v>897.3</v>
       </c>
       <c r="V13">
-        <v>0.3443523114895033</v>
+        <v>0.3288379081613955</v>
       </c>
       <c r="W13">
-        <v>0.0001220865704772475</v>
+        <v>0.03533361964627337</v>
       </c>
       <c r="X13">
-        <v>0.1237777271433114</v>
+        <v>0.0942680413464124</v>
       </c>
       <c r="Y13">
-        <v>-0.1236556405728342</v>
+        <v>-0.05893442170013902</v>
       </c>
       <c r="Z13">
-        <v>0.04035764804498541</v>
+        <v>0.07490819106787937</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.06794122372061598</v>
+        <v>0.05743346641531527</v>
       </c>
       <c r="AC13">
-        <v>-0.06794122372061598</v>
+        <v>-0.05743346641531527</v>
       </c>
       <c r="AD13">
-        <v>7745.4</v>
+        <v>5618.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>7745.4</v>
+        <v>5618.5</v>
       </c>
       <c r="AG13">
-        <v>6503.7</v>
+        <v>4721.2</v>
       </c>
       <c r="AH13">
-        <v>0.6823359439006986</v>
+        <v>0.6730999616637914</v>
       </c>
       <c r="AI13">
-        <v>0.6817353647910011</v>
+        <v>0.694362054476247</v>
       </c>
       <c r="AJ13">
-        <v>0.6433192213341774</v>
+        <v>0.6337266272030497</v>
       </c>
       <c r="AK13">
-        <v>0.6426835052768883</v>
+        <v>0.6562417469385486</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2064,7 +2067,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Polaris Bay Group Co.,Ltd. (SHSE:600155)</t>
+          <t>HUAXI Securities Co., Ltd. (SZSE:002926)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2073,10 +2076,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.13</v>
+        <v>0.0542</v>
       </c>
       <c r="E14">
-        <v>0.468</v>
+        <v>-0.149</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2091,85 +2094,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>88.7</v>
+        <v>59.8</v>
       </c>
       <c r="L14">
-        <v>0.2164998779594826</v>
+        <v>0.1295774647887324</v>
       </c>
       <c r="M14">
-        <v>162</v>
+        <v>128.8</v>
       </c>
       <c r="N14">
-        <v>0.09944140936713523</v>
+        <v>0.04483586869495597</v>
       </c>
       <c r="O14">
-        <v>1.826381059751973</v>
+        <v>2.153846153846154</v>
       </c>
       <c r="P14">
-        <v>91.90000000000001</v>
+        <v>128.8</v>
       </c>
       <c r="Q14">
-        <v>0.05641151556073906</v>
+        <v>0.04483586869495597</v>
       </c>
       <c r="R14">
-        <v>1.036076662908681</v>
+        <v>2.153846153846154</v>
       </c>
       <c r="S14">
-        <v>70.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>0.432716049382716</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>389.9</v>
+        <v>267.3</v>
       </c>
       <c r="V14">
-        <v>0.2393346019274446</v>
+        <v>0.09304835172485816</v>
       </c>
       <c r="W14">
-        <v>0.03600860634108716</v>
+        <v>0.01910604172657273</v>
       </c>
       <c r="X14">
-        <v>0.1219995751494549</v>
+        <v>0.09031849750899508</v>
       </c>
       <c r="Y14">
-        <v>-0.08599096880836778</v>
+        <v>-0.07121245578242234</v>
       </c>
       <c r="Z14">
-        <v>0.08136071173246484</v>
+        <v>0.05829839429926341</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.06797877557626553</v>
+        <v>0.05756535684039214</v>
       </c>
       <c r="AC14">
-        <v>-0.06797877557626553</v>
+        <v>-0.05756535684039214</v>
       </c>
       <c r="AD14">
-        <v>3380.6</v>
+        <v>5221.1</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>3380.6</v>
+        <v>5221.1</v>
       </c>
       <c r="AG14">
-        <v>2990.7</v>
+        <v>4953.8</v>
       </c>
       <c r="AH14">
-        <v>0.6748108669181787</v>
+        <v>0.64507400726482</v>
       </c>
       <c r="AI14">
-        <v>0.5943076138740925</v>
+        <v>0.626173828570058</v>
       </c>
       <c r="AJ14">
-        <v>0.6473656868262696</v>
+        <v>0.6329521497476522</v>
       </c>
       <c r="AK14">
-        <v>0.5644534199003473</v>
+        <v>0.6137929325469594</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2186,7 +2189,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HUAXI Securities Co., Ltd. (SZSE:002926)</t>
+          <t>Caitong Securities Co.,Ltd. (SHSE:601108)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2195,10 +2198,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0578</v>
+        <v>0.103</v>
       </c>
       <c r="E15">
-        <v>-0.138</v>
+        <v>0.0867</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2213,28 +2216,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>79.40000000000001</v>
+        <v>264.9</v>
       </c>
       <c r="L15">
-        <v>0.1538759689922481</v>
+        <v>0.3265935149796572</v>
       </c>
       <c r="M15">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="N15">
-        <v>0.04431572335822458</v>
+        <v>0.03620693047875795</v>
       </c>
       <c r="O15">
-        <v>1.599496221662468</v>
+        <v>0.6946017365043413</v>
       </c>
       <c r="P15">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="Q15">
-        <v>0.04431572335822458</v>
+        <v>0.03620693047875795</v>
       </c>
       <c r="R15">
-        <v>1.599496221662468</v>
+        <v>0.6946017365043413</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2243,55 +2246,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>501.6</v>
+        <v>535.3</v>
       </c>
       <c r="V15">
-        <v>0.1750296601298067</v>
+        <v>0.1053346189417344</v>
       </c>
       <c r="W15">
-        <v>0.02278989667049369</v>
+        <v>0.05526809931149593</v>
       </c>
       <c r="X15">
-        <v>0.1164025241611963</v>
+        <v>0.09011838371208714</v>
       </c>
       <c r="Y15">
-        <v>-0.09361262749070259</v>
+        <v>-0.03485028440059121</v>
       </c>
       <c r="Z15">
-        <v>0.05812663269938504</v>
+        <v>0.07086380275906656</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.06810952616987892</v>
+        <v>0.05757264397544351</v>
       </c>
       <c r="AC15">
-        <v>-0.06810952616987892</v>
+        <v>-0.05757264397544351</v>
       </c>
       <c r="AD15">
-        <v>5289.8</v>
+        <v>9174.1</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>5289.8</v>
+        <v>9174.1</v>
       </c>
       <c r="AG15">
-        <v>4788.2</v>
+        <v>8638.800000000001</v>
       </c>
       <c r="AH15">
-        <v>0.648609544362156</v>
+        <v>0.6435255331088665</v>
       </c>
       <c r="AI15">
-        <v>0.6280483461164011</v>
+        <v>0.6637605452414371</v>
       </c>
       <c r="AJ15">
-        <v>0.6255813953488372</v>
+        <v>0.6296180224041048</v>
       </c>
       <c r="AK15">
-        <v>0.6044943820224719</v>
+        <v>0.6502133809018448</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2308,7 +2311,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Western Securities Co., Ltd. (SZSE:002673)</t>
+          <t>China Great Wall Securities Co.,Ltd. (SZSE:002939)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2317,10 +2320,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.154</v>
+        <v>0.0556</v>
       </c>
       <c r="E16">
-        <v>0.00387</v>
+        <v>0.173</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2335,28 +2338,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>128.9</v>
+        <v>211.7</v>
       </c>
       <c r="L16">
-        <v>0.1455674760022586</v>
+        <v>0.4369453044375645</v>
       </c>
       <c r="M16">
-        <v>139.5</v>
+        <v>161.7</v>
       </c>
       <c r="N16">
-        <v>0.03534777651083238</v>
+        <v>0.03552518839115056</v>
       </c>
       <c r="O16">
-        <v>1.082234290147401</v>
+        <v>0.7638167217760983</v>
       </c>
       <c r="P16">
-        <v>139.5</v>
+        <v>161.7</v>
       </c>
       <c r="Q16">
-        <v>0.03534777651083238</v>
+        <v>0.03552518839115056</v>
       </c>
       <c r="R16">
-        <v>1.082234290147401</v>
+        <v>0.7638167217760983</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2365,55 +2368,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>699.9</v>
+        <v>211.8</v>
       </c>
       <c r="V16">
-        <v>0.1773470163435956</v>
+        <v>0.04653206494276864</v>
       </c>
       <c r="W16">
-        <v>0.03114880866077039</v>
+        <v>0.05530591984952191</v>
       </c>
       <c r="X16">
-        <v>0.1160425723846438</v>
+        <v>0.08970866526808911</v>
       </c>
       <c r="Y16">
-        <v>-0.08489376372387339</v>
+        <v>-0.0344027454185672</v>
       </c>
       <c r="Z16">
-        <v>0.1134350238930926</v>
+        <v>0.05143088251997523</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.0681186597049033</v>
+        <v>0.05758776400719628</v>
       </c>
       <c r="AC16">
-        <v>-0.0681186597049033</v>
+        <v>-0.05758776400719628</v>
       </c>
       <c r="AD16">
-        <v>7226.4</v>
+        <v>8102.9</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>7226.4</v>
+        <v>8102.9</v>
       </c>
       <c r="AG16">
-        <v>6526.5</v>
+        <v>7891.099999999999</v>
       </c>
       <c r="AH16">
-        <v>0.6467792605321805</v>
+        <v>0.6403126135950564</v>
       </c>
       <c r="AI16">
-        <v>0.6537539466423007</v>
+        <v>0.6716817533737857</v>
       </c>
       <c r="AJ16">
-        <v>0.6231738756803208</v>
+        <v>0.6341900536856656</v>
       </c>
       <c r="AK16">
-        <v>0.6303482779269447</v>
+        <v>0.6658144754383301</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2430,7 +2433,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southwest Securities Co., Ltd. (SHSE:600369)</t>
+          <t>Dongxing Securities Corporation Limited (SHSE:601198)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2439,10 +2442,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.108</v>
+        <v>-0.0401</v>
       </c>
       <c r="E17">
-        <v>-0.044</v>
+        <v>-0.176</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2457,28 +2460,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>50.7</v>
+        <v>60.3</v>
       </c>
       <c r="L17">
-        <v>0.213743676222597</v>
+        <v>0.1217443973349485</v>
       </c>
       <c r="M17">
-        <v>170.4</v>
+        <v>120.9</v>
       </c>
       <c r="N17">
-        <v>0.0471643278252927</v>
+        <v>0.03222539115600928</v>
       </c>
       <c r="O17">
-        <v>3.36094674556213</v>
+        <v>2.00497512437811</v>
       </c>
       <c r="P17">
-        <v>170.4</v>
+        <v>120.9</v>
       </c>
       <c r="Q17">
-        <v>0.0471643278252927</v>
+        <v>0.03222539115600928</v>
       </c>
       <c r="R17">
-        <v>3.36094674556213</v>
+        <v>2.00497512437811</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2487,55 +2490,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>685</v>
+        <v>189.3</v>
       </c>
       <c r="V17">
-        <v>0.1895983835699853</v>
+        <v>0.05045712610283339</v>
       </c>
       <c r="W17">
-        <v>0.01293499336667007</v>
+        <v>0.01618835404977315</v>
       </c>
       <c r="X17">
-        <v>0.111132476235977</v>
+        <v>0.08970192574121222</v>
       </c>
       <c r="Y17">
-        <v>-0.09819748286930696</v>
+        <v>-0.07351357169143907</v>
       </c>
       <c r="Z17">
-        <v>0.02510106033990138</v>
+        <v>0.05062196643803485</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.06825347812683331</v>
+        <v>0.05758801499797733</v>
       </c>
       <c r="AC17">
-        <v>-0.06825347812683331</v>
+        <v>-0.05758801499797733</v>
       </c>
       <c r="AD17">
-        <v>5888.8</v>
+        <v>6677.2</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>5888.8</v>
+        <v>6677.2</v>
       </c>
       <c r="AG17">
-        <v>5203.8</v>
+        <v>6487.9</v>
       </c>
       <c r="AH17">
-        <v>0.6197627792921266</v>
+        <v>0.6402592795021527</v>
       </c>
       <c r="AI17">
-        <v>0.6273223112323163</v>
+        <v>0.6460514348743155</v>
       </c>
       <c r="AJ17">
-        <v>0.5902208309231345</v>
+        <v>0.6336087347161999</v>
       </c>
       <c r="AK17">
-        <v>0.5979867160028498</v>
+        <v>0.6394476695479052</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2552,7 +2555,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caitong Securities Co.,Ltd. (SHSE:601108)</t>
+          <t>Southwest Securities Co., Ltd. (SHSE:600369)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2561,10 +2564,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.06179999999999999</v>
+        <v>-0.0305</v>
       </c>
       <c r="E18">
-        <v>0.0482</v>
+        <v>0.117</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2579,28 +2582,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>288.3</v>
+        <v>89.5</v>
       </c>
       <c r="L18">
-        <v>0.3879171151776103</v>
+        <v>0.2649496743635287</v>
       </c>
       <c r="M18">
-        <v>272.5</v>
+        <v>103.1</v>
       </c>
       <c r="N18">
-        <v>0.05684544297724096</v>
+        <v>0.02689869289571864</v>
       </c>
       <c r="O18">
-        <v>0.9451959764134582</v>
+        <v>1.15195530726257</v>
       </c>
       <c r="P18">
-        <v>272.5</v>
+        <v>103.1</v>
       </c>
       <c r="Q18">
-        <v>0.05684544297724096</v>
+        <v>0.02689869289571864</v>
       </c>
       <c r="R18">
-        <v>0.9451959764134582</v>
+        <v>1.15195530726257</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2609,55 +2612,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>513.6</v>
+        <v>415</v>
       </c>
       <c r="V18">
-        <v>0.1071406220664622</v>
+        <v>0.108273109134076</v>
       </c>
       <c r="W18">
-        <v>0.07800957869956977</v>
+        <v>0.02544276089490292</v>
       </c>
       <c r="X18">
-        <v>0.1101750222964535</v>
+        <v>0.08809232011724497</v>
       </c>
       <c r="Y18">
-        <v>-0.03216544359688368</v>
+        <v>-0.06264955922234204</v>
       </c>
       <c r="Z18">
-        <v>0.06695736783307507</v>
+        <v>0.03873875423597612</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.06828220654179795</v>
+        <v>0.05765016928482689</v>
       </c>
       <c r="AC18">
-        <v>-0.06828220654179795</v>
+        <v>-0.05765016928482689</v>
       </c>
       <c r="AD18">
-        <v>7625.4</v>
+        <v>6444.4</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>7625.4</v>
+        <v>6444.4</v>
       </c>
       <c r="AG18">
-        <v>7111.799999999999</v>
+        <v>6029.4</v>
       </c>
       <c r="AH18">
-        <v>0.6140058458342392</v>
+        <v>0.6270518521401536</v>
       </c>
       <c r="AI18">
-        <v>0.6244697403980017</v>
+        <v>0.6500368169943211</v>
       </c>
       <c r="AJ18">
-        <v>0.5973541640418294</v>
+        <v>0.6113584052401569</v>
       </c>
       <c r="AK18">
-        <v>0.6079812607929966</v>
+        <v>0.634747181252566</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2674,7 +2677,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Soochow Securities Co., Ltd. (SHSE:601555)</t>
+          <t>Guolian Securities Co., Ltd. (SEHK:1456)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2683,10 +2686,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.206</v>
+        <v>0.203</v>
       </c>
       <c r="E19">
-        <v>0.103</v>
+        <v>0.408</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2701,85 +2704,85 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>242.1</v>
+        <v>116.6</v>
       </c>
       <c r="L19">
-        <v>0.1502513498417427</v>
+        <v>0.2651808050943825</v>
       </c>
       <c r="M19">
-        <v>410.8</v>
+        <v>28.3</v>
       </c>
       <c r="N19">
-        <v>0.08665021409437028</v>
+        <v>0.007356955312345648</v>
       </c>
       <c r="O19">
-        <v>1.696819496076002</v>
+        <v>0.2427101200686106</v>
       </c>
       <c r="P19">
-        <v>361.5</v>
+        <v>28.3</v>
       </c>
       <c r="Q19">
-        <v>0.07625134468138961</v>
+        <v>0.007356955312345648</v>
       </c>
       <c r="R19">
-        <v>1.493184634448575</v>
+        <v>0.2427101200686106</v>
       </c>
       <c r="S19">
-        <v>49.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>0.1200097370983447</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>600</v>
+        <v>605.2</v>
       </c>
       <c r="V19">
-        <v>0.1265582484338417</v>
+        <v>0.1573296591883953</v>
       </c>
       <c r="W19">
-        <v>0.0542946849069298</v>
+        <v>0.04972705561241896</v>
       </c>
       <c r="X19">
-        <v>0.1056667292992553</v>
+        <v>0.08800177171224116</v>
       </c>
       <c r="Y19">
-        <v>-0.05137204439232548</v>
+        <v>-0.0382747160998222</v>
       </c>
       <c r="Z19">
-        <v>0.143623706423981</v>
+        <v>0.06550367964723058</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.06843006700303009</v>
+        <v>0.05765380164709923</v>
       </c>
       <c r="AC19">
-        <v>-0.06843006700303009</v>
+        <v>-0.05765380164709923</v>
       </c>
       <c r="AD19">
-        <v>6665.8</v>
+        <v>6446.3</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>6665.8</v>
+        <v>6446.3</v>
       </c>
       <c r="AG19">
-        <v>6065.8</v>
+        <v>5841.1</v>
       </c>
       <c r="AH19">
-        <v>0.5843758492815626</v>
+        <v>0.6262799961138638</v>
       </c>
       <c r="AI19">
-        <v>0.5533758934723594</v>
+        <v>0.7206354174818062</v>
       </c>
       <c r="AJ19">
-        <v>0.5612999343000176</v>
+        <v>0.6029335865728029</v>
       </c>
       <c r="AK19">
-        <v>0.5299632176275807</v>
+        <v>0.700363304996343</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2796,7 +2799,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Huaan Securities Co., Ltd. (SHSE:600909)</t>
+          <t>Central China Securities Co., Ltd. (SEHK:1375)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2805,10 +2808,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.132</v>
+        <v>0.00709</v>
       </c>
       <c r="E20">
-        <v>0.154</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2823,28 +2826,28 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>198.7</v>
+        <v>29.1</v>
       </c>
       <c r="L20">
-        <v>0.3966067864271457</v>
+        <v>0.1043758967001435</v>
       </c>
       <c r="M20">
-        <v>133</v>
+        <v>54.3</v>
       </c>
       <c r="N20">
-        <v>0.04254366323331841</v>
+        <v>0.02672244094488189</v>
       </c>
       <c r="O20">
-        <v>0.669350780070458</v>
+        <v>1.865979381443299</v>
       </c>
       <c r="P20">
-        <v>133</v>
+        <v>54.3</v>
       </c>
       <c r="Q20">
-        <v>0.04254366323331841</v>
+        <v>0.02672244094488189</v>
       </c>
       <c r="R20">
-        <v>0.669350780070458</v>
+        <v>1.865979381443299</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2853,55 +2856,55 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>227.2</v>
+        <v>170.6</v>
       </c>
       <c r="V20">
-        <v>0.07267609238052587</v>
+        <v>0.08395669291338582</v>
       </c>
       <c r="W20">
-        <v>0.06728294731139103</v>
+        <v>0.01506133222918069</v>
       </c>
       <c r="X20">
-        <v>0.1050561392839482</v>
+        <v>0.0862924547356184</v>
       </c>
       <c r="Y20">
-        <v>-0.03777319197255717</v>
+        <v>-0.07123112250643772</v>
       </c>
       <c r="Z20">
-        <v>0.06965292821744393</v>
+        <v>0.06332377117133078</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.06845185656300484</v>
+        <v>0.05772530666762919</v>
       </c>
       <c r="AC20">
-        <v>-0.06845185656300484</v>
+        <v>-0.05772530666762919</v>
       </c>
       <c r="AD20">
-        <v>4317.3</v>
+        <v>3192.8</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>4317.3</v>
+        <v>3192.8</v>
       </c>
       <c r="AG20">
-        <v>4090.1</v>
+        <v>3022.2</v>
       </c>
       <c r="AH20">
-        <v>0.5800094041781421</v>
+        <v>0.6110855917929873</v>
       </c>
       <c r="AI20">
-        <v>0.6054439894541987</v>
+        <v>0.6219780647926285</v>
       </c>
       <c r="AJ20">
-        <v>0.5667863032301873</v>
+        <v>0.5979581338292904</v>
       </c>
       <c r="AK20">
-        <v>0.5924590068949533</v>
+        <v>0.6089830132790618</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2918,7 +2921,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Central China Securities Co., Ltd. (SEHK:1375)</t>
+          <t>Huaan Securities Co., Ltd. (SHSE:600909)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2927,10 +2930,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.00603</v>
+        <v>0.167</v>
       </c>
       <c r="E21">
-        <v>-0.236</v>
+        <v>0.24</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2945,28 +2948,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>16.7</v>
+        <v>162.2</v>
       </c>
       <c r="L21">
-        <v>0.05024067388688327</v>
+        <v>0.3421940928270042</v>
       </c>
       <c r="M21">
-        <v>104.1</v>
+        <v>127.2</v>
       </c>
       <c r="N21">
-        <v>0.052240678476439</v>
+        <v>0.03934426229508197</v>
       </c>
       <c r="O21">
-        <v>6.233532934131737</v>
+        <v>0.7842170160295932</v>
       </c>
       <c r="P21">
-        <v>104.1</v>
+        <v>127.2</v>
       </c>
       <c r="Q21">
-        <v>0.052240678476439</v>
+        <v>0.03934426229508197</v>
       </c>
       <c r="R21">
-        <v>6.233532934131737</v>
+        <v>0.7842170160295932</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -2975,55 +2978,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>236.8</v>
+        <v>147.2</v>
       </c>
       <c r="V21">
-        <v>0.1188337431625433</v>
+        <v>0.04553046705845963</v>
       </c>
       <c r="W21">
-        <v>0.007809942477669175</v>
+        <v>0.05792029710041422</v>
       </c>
       <c r="X21">
-        <v>0.1045474149322008</v>
+        <v>0.08609529889487291</v>
       </c>
       <c r="Y21">
-        <v>-0.09673747245453163</v>
+        <v>-0.02817500179445869</v>
       </c>
       <c r="Z21">
-        <v>0.05790506982926365</v>
+        <v>0.06879573501276202</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.06847036365660483</v>
+        <v>0.05773392995123491</v>
       </c>
       <c r="AC21">
-        <v>-0.06847036365660483</v>
+        <v>-0.05773392995123491</v>
       </c>
       <c r="AD21">
-        <v>2710.4</v>
+        <v>5040.9</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>2710.4</v>
+        <v>5040.9</v>
       </c>
       <c r="AG21">
-        <v>2473.6</v>
+        <v>4893.7</v>
       </c>
       <c r="AH21">
-        <v>0.5763007378112308</v>
+        <v>0.6092531937780249</v>
       </c>
       <c r="AI21">
-        <v>0.5761169918802873</v>
+        <v>0.6387111488412757</v>
       </c>
       <c r="AJ21">
-        <v>0.553836508967154</v>
+        <v>0.6021755448090861</v>
       </c>
       <c r="AK21">
-        <v>0.5536505662742289</v>
+        <v>0.6318446501659113</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3040,7 +3043,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zheshang Securities Co., Ltd. (SHSE:601878)</t>
+          <t>Western Securities Co., Ltd. (SZSE:002673)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3049,10 +3052,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.285</v>
+        <v>0.211</v>
       </c>
       <c r="E22">
-        <v>0.104</v>
+        <v>0.159</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3067,28 +3070,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>247.9</v>
+        <v>110.6</v>
       </c>
       <c r="L22">
-        <v>0.1112756979980249</v>
+        <v>0.1215919085312225</v>
       </c>
       <c r="M22">
-        <v>201.3</v>
+        <v>113.1</v>
       </c>
       <c r="N22">
-        <v>0.03605330085610919</v>
+        <v>0.0281679617453676</v>
       </c>
       <c r="O22">
-        <v>0.8120209762000807</v>
+        <v>1.022603978300181</v>
       </c>
       <c r="P22">
-        <v>201.3</v>
+        <v>113.1</v>
       </c>
       <c r="Q22">
-        <v>0.03605330085610919</v>
+        <v>0.0281679617453676</v>
       </c>
       <c r="R22">
-        <v>0.8120209762000807</v>
+        <v>1.022603978300181</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3097,55 +3100,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>1140.4</v>
+        <v>413.6</v>
       </c>
       <c r="V22">
-        <v>0.2042483074828958</v>
+        <v>0.1030085674437139</v>
       </c>
       <c r="W22">
-        <v>0.06876178852768224</v>
+        <v>0.02904869464726585</v>
       </c>
       <c r="X22">
-        <v>0.102410713349996</v>
+        <v>0.08521729474821765</v>
       </c>
       <c r="Y22">
-        <v>-0.03364892482231373</v>
+        <v>-0.0561686001009518</v>
       </c>
       <c r="Z22">
-        <v>0.2165557545040448</v>
+        <v>0.08802845866388363</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.06855180245267847</v>
+        <v>0.05777334031477908</v>
       </c>
       <c r="AC22">
-        <v>-0.06855180245267847</v>
+        <v>-0.05777334031477908</v>
       </c>
       <c r="AD22">
-        <v>7105.6</v>
+        <v>6044.9</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>7105.6</v>
+        <v>6044.9</v>
       </c>
       <c r="AG22">
-        <v>5965.200000000001</v>
+        <v>5631.299999999999</v>
       </c>
       <c r="AH22">
-        <v>0.5599810859799826</v>
+        <v>0.6008787188994146</v>
       </c>
       <c r="AI22">
-        <v>0.6536770252617247</v>
+        <v>0.6130357179076324</v>
       </c>
       <c r="AJ22">
-        <v>0.5165301421817363</v>
+        <v>0.5837661327942777</v>
       </c>
       <c r="AK22">
-        <v>0.6130855721597567</v>
+        <v>0.5960939980946331</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3162,7 +3165,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Founder Securities Co., Ltd. (SHSE:601901)</t>
+          <t>Zheshang Securities Co., Ltd. (SHSE:601878)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3171,13 +3174,16 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.0493</v>
+        <v>0.354</v>
       </c>
       <c r="E23">
-        <v>0.0824</v>
+        <v>0.176</v>
+      </c>
+      <c r="F23">
+        <v>0.23</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>0.00152985688435598</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3189,28 +3195,28 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>257.9</v>
+        <v>250.6</v>
       </c>
       <c r="L23">
-        <v>0.2318827549001978</v>
+        <v>0.103059713768712</v>
       </c>
       <c r="M23">
-        <v>136.7</v>
+        <v>255.6</v>
       </c>
       <c r="N23">
-        <v>0.01795188317486999</v>
+        <v>0.04523653611312673</v>
       </c>
       <c r="O23">
-        <v>0.5300504071345483</v>
+        <v>1.019952114924182</v>
       </c>
       <c r="P23">
-        <v>136.7</v>
+        <v>255.6</v>
       </c>
       <c r="Q23">
-        <v>0.01795188317486999</v>
+        <v>0.04523653611312673</v>
       </c>
       <c r="R23">
-        <v>0.5300504071345483</v>
+        <v>1.019952114924182</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3219,55 +3225,55 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>735.9</v>
+        <v>1353.8</v>
       </c>
       <c r="V23">
-        <v>0.09664075221936229</v>
+        <v>0.2395978974567722</v>
       </c>
       <c r="W23">
-        <v>0.04014632627646326</v>
+        <v>0.06954542931675639</v>
       </c>
       <c r="X23">
-        <v>0.101098615533687</v>
+        <v>0.08248830193414772</v>
       </c>
       <c r="Y23">
-        <v>-0.06095228925722373</v>
+        <v>-0.01294287261739133</v>
       </c>
       <c r="Z23">
-        <v>0.0843086719223772</v>
+        <v>0.2541969786144613</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.06860499647943402</v>
+        <v>0.05790738963225842</v>
       </c>
       <c r="AC23">
-        <v>-0.06860499647943402</v>
+        <v>-0.05790738963225842</v>
       </c>
       <c r="AD23">
-        <v>9281.5</v>
+        <v>7563.5</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>9281.5</v>
+        <v>7563.5</v>
       </c>
       <c r="AG23">
-        <v>8545.6</v>
+        <v>6209.7</v>
       </c>
       <c r="AH23">
-        <v>0.5493214490746495</v>
+        <v>0.5723940123204528</v>
       </c>
       <c r="AI23">
-        <v>0.6011256330876543</v>
+        <v>0.6648938508197442</v>
       </c>
       <c r="AJ23">
-        <v>0.5287987921091062</v>
+        <v>0.5235834738617201</v>
       </c>
       <c r="AK23">
-        <v>0.5811633331746496</v>
+        <v>0.6196254128541065</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3284,7 +3290,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guolian Securities Co., Ltd. (SEHK:1456)</t>
+          <t>Founder Securities Co., Ltd. (SHSE:601901)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3293,10 +3299,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.153</v>
+        <v>0.0877</v>
       </c>
       <c r="E24">
-        <v>0.149</v>
+        <v>0.3</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3311,28 +3317,28 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>123</v>
+        <v>293.8</v>
       </c>
       <c r="L24">
-        <v>0.266695576756288</v>
+        <v>0.286942084187909</v>
       </c>
       <c r="M24">
-        <v>66.40000000000001</v>
+        <v>111.6</v>
       </c>
       <c r="N24">
-        <v>0.0160654230480753</v>
+        <v>0.01192664472278032</v>
       </c>
       <c r="O24">
-        <v>0.5398373983739838</v>
+        <v>0.3798502382573179</v>
       </c>
       <c r="P24">
-        <v>66.40000000000001</v>
+        <v>111.6</v>
       </c>
       <c r="Q24">
-        <v>0.0160654230480753</v>
+        <v>0.01192664472278032</v>
       </c>
       <c r="R24">
-        <v>0.5398373983739838</v>
+        <v>0.3798502382573179</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3341,55 +3347,55 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>442.6</v>
+        <v>709.5</v>
       </c>
       <c r="V24">
-        <v>0.1070866903776826</v>
+        <v>0.07582396443380497</v>
       </c>
       <c r="W24">
-        <v>0.0493718139124152</v>
+        <v>0.04867623181682627</v>
       </c>
       <c r="X24">
-        <v>0.09975597968399728</v>
+        <v>0.08225980809468023</v>
       </c>
       <c r="Y24">
-        <v>-0.05038416577158208</v>
+        <v>-0.03358357627785395</v>
       </c>
       <c r="Z24">
-        <v>0.06726562044221457</v>
+        <v>0.07328595048420691</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.06866216434146502</v>
+        <v>0.05791948665627783</v>
       </c>
       <c r="AC24">
-        <v>-0.06866216434146502</v>
+        <v>-0.05791948665627783</v>
       </c>
       <c r="AD24">
-        <v>4810.4</v>
+        <v>12394.8</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>4810.4</v>
+        <v>12394.8</v>
       </c>
       <c r="AG24">
-        <v>4367.799999999999</v>
+        <v>11685.3</v>
       </c>
       <c r="AH24">
-        <v>0.5378654889025549</v>
+        <v>0.5698234645090107</v>
       </c>
       <c r="AI24">
-        <v>0.6722942754919499</v>
+        <v>0.6643511818620357</v>
       </c>
       <c r="AJ24">
-        <v>0.5138044207083955</v>
+        <v>0.5553189972674349</v>
       </c>
       <c r="AK24">
-        <v>0.6506867681673271</v>
+        <v>0.6510823234433765</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3406,7 +3412,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nanjing Securities Co., Ltd. (SHSE:601990)</t>
+          <t>Sinolink Securities Co., Ltd. (SHSE:600109)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3415,115 +3421,112 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.118</v>
+        <v>0.119</v>
       </c>
       <c r="E25">
-        <v>0.138</v>
+        <v>0.0931</v>
+      </c>
+      <c r="F25">
+        <v>0.379</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>0.02129090094128194</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0.008769631162784897</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>0.007135290809720438</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>88.5</v>
+        <v>220.9</v>
       </c>
       <c r="L25">
-        <v>0.3012253233492171</v>
+        <v>0.2475347377857463</v>
       </c>
       <c r="M25">
-        <v>121.1</v>
+        <v>106.897</v>
       </c>
       <c r="N25">
-        <v>0.0285721026802567</v>
+        <v>0.02241450168794951</v>
       </c>
       <c r="O25">
-        <v>1.368361581920904</v>
+        <v>0.4839157990040743</v>
       </c>
       <c r="P25">
-        <v>121.1</v>
+        <v>105.9</v>
       </c>
       <c r="Q25">
-        <v>0.0285721026802567</v>
+        <v>0.02220544756872366</v>
       </c>
       <c r="R25">
-        <v>1.368361581920904</v>
+        <v>0.479402444545043</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>0.9969999999999999</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>0.009326735081433528</v>
       </c>
       <c r="U25">
-        <v>318.3</v>
+        <v>678.3</v>
       </c>
       <c r="V25">
-        <v>0.075099093997735</v>
+        <v>0.1422280933509467</v>
       </c>
       <c r="W25">
-        <v>0.03494018713727348</v>
+        <v>0.05107160196980556</v>
       </c>
       <c r="X25">
-        <v>0.08981657889063055</v>
+        <v>0.08146241421119654</v>
       </c>
       <c r="Y25">
-        <v>-0.05487639175335707</v>
+        <v>-0.03039081224139098</v>
       </c>
       <c r="Z25">
-        <v>0.04892092224658184</v>
+        <v>0.1117864282958457</v>
       </c>
       <c r="AA25">
-        <v>0.0003490650069090836</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.06919672141787392</v>
+        <v>0.05796286648011104</v>
       </c>
       <c r="AC25">
-        <v>-0.06884765641096484</v>
+        <v>-0.05796286648011104</v>
       </c>
       <c r="AD25">
-        <v>3195.1</v>
+        <v>6084.7</v>
       </c>
       <c r="AE25">
-        <v>12.01741182186899</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>3207.117411821869</v>
+        <v>6084.7</v>
       </c>
       <c r="AG25">
-        <v>2888.817411821869</v>
+        <v>5406.4</v>
       </c>
       <c r="AH25">
-        <v>0.4307447332981401</v>
+        <v>0.5606055022204205</v>
       </c>
       <c r="AI25">
-        <v>0.5731890605440466</v>
+        <v>0.578014420199679</v>
       </c>
       <c r="AJ25">
-        <v>0.4053219152582895</v>
+        <v>0.5313154144759471</v>
       </c>
       <c r="AK25">
-        <v>0.5474441205674464</v>
+        <v>0.548951119956136</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
         <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>641.586345381526</v>
-      </c>
-      <c r="AP25">
-        <v>580.0838176349133</v>
       </c>
     </row>
     <row r="26">
@@ -3534,7 +3537,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sinolink Securities Co., Ltd. (SHSE:600109)</t>
+          <t>Sealand Securities Co., Ltd. (SZSE:000750)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3543,13 +3546,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.0694</v>
-      </c>
-      <c r="E26">
-        <v>0.066</v>
+        <v>0.162</v>
       </c>
       <c r="G26">
-        <v>0.0151497629235573</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3561,28 +3561,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>225.1</v>
+        <v>46.6</v>
       </c>
       <c r="L26">
-        <v>0.260321498785706</v>
+        <v>0.08759398496240602</v>
       </c>
       <c r="M26">
-        <v>126.6</v>
+        <v>101.6</v>
       </c>
       <c r="N26">
-        <v>0.02694878453744306</v>
+        <v>0.03186751144846622</v>
       </c>
       <c r="O26">
-        <v>0.5624167036872501</v>
+        <v>2.180257510729613</v>
       </c>
       <c r="P26">
-        <v>126.6</v>
+        <v>101.6</v>
       </c>
       <c r="Q26">
-        <v>0.02694878453744306</v>
+        <v>0.03186751144846622</v>
       </c>
       <c r="R26">
-        <v>0.5624167036872501</v>
+        <v>2.180257510729613</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3591,55 +3591,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>723.8</v>
+        <v>1374.6</v>
       </c>
       <c r="V26">
-        <v>0.1540721188641491</v>
+        <v>0.4311523743805282</v>
       </c>
       <c r="W26">
-        <v>0.06132512395793603</v>
+        <v>0.01776659422776316</v>
       </c>
       <c r="X26">
-        <v>0.09414671815492817</v>
+        <v>0.08042545302758727</v>
       </c>
       <c r="Y26">
-        <v>-0.03282159419699214</v>
+        <v>-0.06265885879982411</v>
       </c>
       <c r="Z26">
-        <v>0.1109339258704279</v>
+        <v>0.08199879776198771</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.06893616971669901</v>
+        <v>0.05802213979811459</v>
       </c>
       <c r="AC26">
-        <v>-0.06893616971669901</v>
+        <v>-0.05802213979811459</v>
       </c>
       <c r="AD26">
-        <v>4388.1</v>
+        <v>3865.5</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>4388.1</v>
+        <v>3865.5</v>
       </c>
       <c r="AG26">
-        <v>3664.3</v>
+        <v>2490.9</v>
       </c>
       <c r="AH26">
-        <v>0.4829571093672613</v>
+        <v>0.5480102641167047</v>
       </c>
       <c r="AI26">
-        <v>0.5028476479688306</v>
+        <v>0.590594490534904</v>
       </c>
       <c r="AJ26">
-        <v>0.4382033221320004</v>
+        <v>0.4386082301773168</v>
       </c>
       <c r="AK26">
-        <v>0.4578829644994815</v>
+        <v>0.4817522483318828</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guangdong Golden Dragon Development Inc. (SZSE:000712)</t>
+          <t>Nanjing Securities Co., Ltd. (SHSE:601990)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3665,7 +3665,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>-0.367</v>
+        <v>0.0974</v>
+      </c>
+      <c r="E27">
+        <v>0.164</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3674,34 +3677,34 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>0.007307610778209402</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>0.005943777169429002</v>
       </c>
       <c r="K27">
-        <v>-55.4</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L27">
-        <v>-2.78391959798995</v>
+        <v>0.300939423388403</v>
       </c>
       <c r="M27">
-        <v>73.8</v>
+        <v>108.1</v>
       </c>
       <c r="N27">
-        <v>0.04390243902439024</v>
+        <v>0.02605698307862893</v>
       </c>
       <c r="O27">
-        <v>-1.332129963898917</v>
+        <v>1.163616792249731</v>
       </c>
       <c r="P27">
-        <v>73.8</v>
+        <v>108.1</v>
       </c>
       <c r="Q27">
-        <v>0.04390243902439024</v>
+        <v>0.02605698307862893</v>
       </c>
       <c r="R27">
-        <v>-1.332129963898917</v>
+        <v>1.163616792249731</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3710,61 +3713,67 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>169.6</v>
+        <v>159</v>
       </c>
       <c r="V27">
-        <v>0.1008923259964307</v>
+        <v>0.038326182326568</v>
       </c>
       <c r="W27">
-        <v>-0.103319656844461</v>
+        <v>0.03971952627303434</v>
       </c>
       <c r="X27">
-        <v>0.09356034925321166</v>
+        <v>0.07465026456233931</v>
       </c>
       <c r="Y27">
-        <v>-0.1968800060976727</v>
+        <v>-0.03493073828930497</v>
       </c>
       <c r="Z27">
-        <v>0.01139291234900097</v>
+        <v>0.05907909298008423</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>0.0003511529640455979</v>
       </c>
       <c r="AB27">
-        <v>0.06896861939382543</v>
+        <v>0.05842622606499984</v>
       </c>
       <c r="AC27">
-        <v>-0.06896861939382543</v>
+        <v>-0.05807507310095424</v>
       </c>
       <c r="AD27">
-        <v>1529.8</v>
+        <v>3554.3</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>10.32070276383379</v>
       </c>
       <c r="AF27">
-        <v>1529.8</v>
+        <v>3564.620702763834</v>
       </c>
       <c r="AG27">
-        <v>1360.2</v>
+        <v>3405.620702763834</v>
       </c>
       <c r="AH27">
-        <v>0.4764544661766538</v>
+        <v>0.4621442637427117</v>
       </c>
       <c r="AI27">
-        <v>0.6747827621190067</v>
+        <v>0.6008104271578378</v>
       </c>
       <c r="AJ27">
-        <v>0.4472576614494279</v>
+        <v>0.450823564304632</v>
       </c>
       <c r="AK27">
-        <v>0.6484862932061979</v>
+        <v>0.5898178891415605</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
         <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>822.7546296296296</v>
+      </c>
+      <c r="AP27">
+        <v>788.3381256397763</v>
       </c>
     </row>
     <row r="28">
@@ -3784,10 +3793,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.0643</v>
+        <v>0.06570000000000001</v>
       </c>
       <c r="E28">
-        <v>0.011</v>
+        <v>0.09269999999999999</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3802,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>64.8</v>
+        <v>53.2</v>
       </c>
       <c r="L28">
-        <v>0.1741467347487234</v>
+        <v>0.15326995102276</v>
       </c>
       <c r="M28">
-        <v>71.5</v>
+        <v>68.2</v>
       </c>
       <c r="N28">
-        <v>0.02084365798909716</v>
+        <v>0.01980658089623327</v>
       </c>
       <c r="O28">
-        <v>1.103395061728395</v>
+        <v>1.281954887218045</v>
       </c>
       <c r="P28">
-        <v>71.5</v>
+        <v>68.2</v>
       </c>
       <c r="Q28">
-        <v>0.02084365798909716</v>
+        <v>0.01980658089623327</v>
       </c>
       <c r="R28">
-        <v>1.103395061728395</v>
+        <v>1.281954887218045</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3832,55 +3841,55 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>1190.1</v>
+        <v>346</v>
       </c>
       <c r="V28">
-        <v>0.3469375856339095</v>
+        <v>0.1004849998547905</v>
       </c>
       <c r="W28">
-        <v>0.02913800080938891</v>
+        <v>0.0259778309487768</v>
       </c>
       <c r="X28">
-        <v>0.09090998434705272</v>
+        <v>0.07634359882897135</v>
       </c>
       <c r="Y28">
-        <v>-0.06177198353766381</v>
+        <v>-0.05036576788019455</v>
       </c>
       <c r="Z28">
-        <v>0.08119153652964549</v>
+        <v>0.09626344734630711</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.06912608666117273</v>
+        <v>0.05829267523290058</v>
       </c>
       <c r="AC28">
-        <v>-0.06912608666117273</v>
+        <v>-0.05829267523290058</v>
       </c>
       <c r="AD28">
-        <v>2749.3</v>
+        <v>3315.2</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>2749.3</v>
+        <v>3315.2</v>
       </c>
       <c r="AG28">
-        <v>1559.2</v>
+        <v>2969.2</v>
       </c>
       <c r="AH28">
-        <v>0.4448993462360024</v>
+        <v>0.4905230450543759</v>
       </c>
       <c r="AI28">
-        <v>0.5634157837571981</v>
+        <v>0.6100397467981746</v>
       </c>
       <c r="AJ28">
-        <v>0.3124962421084277</v>
+        <v>0.4630331384015594</v>
       </c>
       <c r="AK28">
-        <v>0.4225932350390287</v>
+        <v>0.5835233079160443</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3897,7 +3906,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nanhua Futures Co., Ltd. (SHSE:603093)</t>
+          <t>ZHONGTAI FUTURES Company Limited (SEHK:1461)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3905,8 +3914,14 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D29">
+        <v>0.246</v>
+      </c>
+      <c r="E29">
+        <v>-0.0264</v>
+      </c>
       <c r="G29">
-        <v>0.004540705617616331</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -3918,28 +3933,28 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>28.8</v>
+        <v>19.8</v>
       </c>
       <c r="L29">
-        <v>0.02314554367917705</v>
+        <v>0.07468879668049792</v>
       </c>
       <c r="M29">
-        <v>6.61</v>
+        <v>4.2</v>
       </c>
       <c r="N29">
-        <v>0.008203028046661703</v>
+        <v>0.05548216644649934</v>
       </c>
       <c r="O29">
-        <v>0.2295138888888889</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="P29">
-        <v>6.61</v>
+        <v>4.2</v>
       </c>
       <c r="Q29">
-        <v>0.008203028046661703</v>
+        <v>0.05548216644649934</v>
       </c>
       <c r="R29">
-        <v>0.2295138888888889</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3948,55 +3963,55 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>270.7</v>
+        <v>2327</v>
       </c>
       <c r="V29">
-        <v>0.3359394390667659</v>
+        <v>30.73976221928666</v>
       </c>
       <c r="W29">
-        <v>0.06233766233766234</v>
+        <v>0.05633001422475107</v>
       </c>
       <c r="X29">
-        <v>0.0822394105357013</v>
+        <v>0.07060164387019695</v>
       </c>
       <c r="Y29">
-        <v>-0.01990174819803896</v>
+        <v>-0.01427162964544588</v>
       </c>
       <c r="Z29">
-        <v>5.045823195458232</v>
+        <v>1.22674687644609</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.06980643330756872</v>
+        <v>0.05881511223283481</v>
       </c>
       <c r="AC29">
-        <v>-0.06980643330756872</v>
+        <v>-0.05881511223283481</v>
       </c>
       <c r="AD29">
-        <v>359.6</v>
+        <v>46.3</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>359.6</v>
+        <v>46.3</v>
       </c>
       <c r="AG29">
-        <v>88.90000000000003</v>
+        <v>-2280.7</v>
       </c>
       <c r="AH29">
-        <v>0.3085635833190321</v>
+        <v>0.3795081967213115</v>
       </c>
       <c r="AI29">
-        <v>0.4426935861135049</v>
+        <v>0.118626697412247</v>
       </c>
       <c r="AJ29">
-        <v>0.09936291494355654</v>
+        <v>1.034331065759637</v>
       </c>
       <c r="AK29">
-        <v>0.1641432791728213</v>
+        <v>1.177621727681107</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -4013,7 +4028,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ruida Futures Co., Ltd. (SZSE:002961)</t>
+          <t>BOC International (China) CO., LTD (SHSE:601696)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4021,8 +4036,11 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="F30">
+        <v>0.172</v>
+      </c>
       <c r="G30">
-        <v>0.002447593740773546</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -4034,28 +4052,28 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>52.2</v>
+        <v>116.7</v>
       </c>
       <c r="L30">
-        <v>0.154118689105403</v>
+        <v>0.3057374901755305</v>
       </c>
       <c r="M30">
-        <v>24.2</v>
+        <v>36.6</v>
       </c>
       <c r="N30">
-        <v>0.02813626322520637</v>
+        <v>0.009078957160221269</v>
       </c>
       <c r="O30">
-        <v>0.4636015325670498</v>
+        <v>0.3136246786632391</v>
       </c>
       <c r="P30">
-        <v>24.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q30">
-        <v>0.02813626322520637</v>
+        <v>0.009078957160221269</v>
       </c>
       <c r="R30">
-        <v>0.4636015325670498</v>
+        <v>0.3136246786632391</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -4064,55 +4082,55 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>84.3</v>
+        <v>277.1</v>
       </c>
       <c r="V30">
-        <v>0.09801185908615277</v>
+        <v>0.06873713194254956</v>
       </c>
       <c r="W30">
-        <v>0.150736355760901</v>
+        <v>0.05072369278915113</v>
       </c>
       <c r="X30">
-        <v>0.07438290104660228</v>
+        <v>0.06963696021601171</v>
       </c>
       <c r="Y30">
-        <v>0.07635345471429869</v>
+        <v>-0.01891326742686057</v>
       </c>
       <c r="Z30">
-        <v>0.842440914721201</v>
+        <v>0.1011581374393767</v>
       </c>
       <c r="AA30">
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.07079411697821544</v>
+        <v>0.05892607256524221</v>
       </c>
       <c r="AC30">
-        <v>-0.07079411697821544</v>
+        <v>-0.05892607256524221</v>
       </c>
       <c r="AD30">
-        <v>107</v>
+        <v>2227.8</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>107</v>
+        <v>2227.8</v>
       </c>
       <c r="AG30">
-        <v>22.7</v>
+        <v>1950.7</v>
       </c>
       <c r="AH30">
-        <v>0.110640057905077</v>
+        <v>0.355929766260325</v>
       </c>
       <c r="AI30">
-        <v>0.2333696837513631</v>
+        <v>0.4868763249338899</v>
       </c>
       <c r="AJ30">
-        <v>0.02571363842319891</v>
+        <v>0.3260949515212304</v>
       </c>
       <c r="AK30">
-        <v>0.06066274719401391</v>
+        <v>0.4537989112734379</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -4129,7 +4147,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Pacific Securities Co., Ltd (SHSE:601099)</t>
+          <t>Hongta Securities Co., Ltd. (SHSE:601236)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4137,9 +4155,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D31">
-        <v>0.0136</v>
-      </c>
       <c r="G31">
         <v>0</v>
       </c>
@@ -4153,28 +4168,28 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>-14.1</v>
+        <v>31.2</v>
       </c>
       <c r="L31">
-        <v>-0.05579738820736051</v>
+        <v>0.2275711159737418</v>
       </c>
       <c r="M31">
-        <v>11.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="N31">
-        <v>0.004645852198905469</v>
+        <v>0.01507288860719379</v>
       </c>
       <c r="O31">
-        <v>-0.8368794326241136</v>
+        <v>2.439102564102564</v>
       </c>
       <c r="P31">
-        <v>11.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Q31">
-        <v>0.004645852198905469</v>
+        <v>0.01507288860719379</v>
       </c>
       <c r="R31">
-        <v>-0.8368794326241136</v>
+        <v>2.439102564102564</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -4183,55 +4198,55 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>112.9</v>
+        <v>377.3</v>
       </c>
       <c r="V31">
-        <v>0.04445056892003622</v>
+        <v>0.07473062906037078</v>
       </c>
       <c r="W31">
-        <v>-0.009361306599389191</v>
+        <v>0.009703302855010263</v>
       </c>
       <c r="X31">
-        <v>0.07350571271348344</v>
+        <v>0.06588445857916023</v>
       </c>
       <c r="Y31">
-        <v>-0.08286701931287263</v>
+        <v>-0.05618115572414997</v>
       </c>
       <c r="Z31">
-        <v>0.1080699653594492</v>
+        <v>0.02851023124272167</v>
       </c>
       <c r="AA31">
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.07094064245598662</v>
+        <v>0.0594518069386761</v>
       </c>
       <c r="AC31">
-        <v>-0.07094064245598662</v>
+        <v>-0.0594518069386761</v>
       </c>
       <c r="AD31">
-        <v>224.7</v>
+        <v>1631.4</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>224.7</v>
+        <v>1631.4</v>
       </c>
       <c r="AG31">
-        <v>111.8</v>
+        <v>1254.1</v>
       </c>
       <c r="AH31">
-        <v>0.08127758084352167</v>
+        <v>0.2442142450824825</v>
       </c>
       <c r="AI31">
-        <v>0.1347930413917217</v>
+        <v>0.3395283980936128</v>
       </c>
       <c r="AJ31">
-        <v>0.0421616321605008</v>
+        <v>0.1989719018229704</v>
       </c>
       <c r="AK31">
-        <v>0.07193874268065117</v>
+        <v>0.2832460023489023</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -4248,7 +4263,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yongan Futures Co.,Ltd. (SHSE:600927)</t>
+          <t>ChinaLin Securities Co., Ltd (SZSE:002945)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4257,10 +4272,10 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.312</v>
+        <v>-0.00222</v>
       </c>
       <c r="E32">
-        <v>-0.00769</v>
+        <v>-0.13</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4275,28 +4290,28 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>127</v>
+        <v>29.4</v>
       </c>
       <c r="L32">
-        <v>0.02309426825720105</v>
+        <v>0.194831013916501</v>
       </c>
       <c r="M32">
-        <v>69.3</v>
+        <v>34</v>
       </c>
       <c r="N32">
-        <v>0.02037096916429054</v>
+        <v>0.005913454849032976</v>
       </c>
       <c r="O32">
-        <v>0.5456692913385827</v>
+        <v>1.156462585034014</v>
       </c>
       <c r="P32">
-        <v>69.3</v>
+        <v>34</v>
       </c>
       <c r="Q32">
-        <v>0.02037096916429054</v>
+        <v>0.005913454849032976</v>
       </c>
       <c r="R32">
-        <v>0.5456692913385827</v>
+        <v>1.156462585034014</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -4305,55 +4320,55 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>462.6</v>
+        <v>1180.4</v>
       </c>
       <c r="V32">
-        <v>0.1359828331226667</v>
+        <v>0.2053012383470154</v>
       </c>
       <c r="W32">
-        <v>0.09617569102612647</v>
+        <v>0.03077245132928616</v>
       </c>
       <c r="X32">
-        <v>0.07300157952009118</v>
+        <v>0.06458413198484811</v>
       </c>
       <c r="Y32">
-        <v>0.02317411150603529</v>
+        <v>-0.03381168065556195</v>
       </c>
       <c r="Z32">
-        <v>4.072576464489373</v>
+        <v>0.04902056329792417</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.07139607561082795</v>
+        <v>0.05967925599597299</v>
       </c>
       <c r="AC32">
-        <v>-0.07139607561082795</v>
+        <v>-0.05967925599597299</v>
       </c>
       <c r="AD32">
-        <v>230.7</v>
+        <v>1400.6</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>230.7</v>
+        <v>1400.6</v>
       </c>
       <c r="AG32">
-        <v>-231.9</v>
+        <v>220.1999999999998</v>
       </c>
       <c r="AH32">
-        <v>0.06350823101910477</v>
+        <v>0.195882632653632</v>
       </c>
       <c r="AI32">
-        <v>0.1224002546689304</v>
+        <v>0.6072140813318304</v>
       </c>
       <c r="AJ32">
-        <v>-0.07315457413249213</v>
+        <v>0.03688565781098191</v>
       </c>
       <c r="AK32">
-        <v>-0.1630572352693011</v>
+        <v>0.1955247735748534</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -4370,7 +4385,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ChinaLin Securities Co., Ltd (SZSE:002945)</t>
+          <t>Ruida Futures Co.,Ltd. (SZSE:002961)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4379,7 +4394,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>0.007101123595505618</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -4391,28 +4406,28 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>61.8</v>
+        <v>32.3</v>
       </c>
       <c r="L33">
-        <v>0.3384446878422782</v>
+        <v>0.2419475655430711</v>
       </c>
       <c r="M33">
-        <v>30.9</v>
+        <v>15.5</v>
       </c>
       <c r="N33">
-        <v>0.005988952417869948</v>
+        <v>0.01657576729761523</v>
       </c>
       <c r="O33">
-        <v>0.5</v>
+        <v>0.4798761609907121</v>
       </c>
       <c r="P33">
-        <v>30.9</v>
+        <v>15.5</v>
       </c>
       <c r="Q33">
-        <v>0.005988952417869948</v>
+        <v>0.01657576729761523</v>
       </c>
       <c r="R33">
-        <v>0.5</v>
+        <v>0.4798761609907121</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -4421,55 +4436,55 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>203</v>
+        <v>61.3</v>
       </c>
       <c r="V33">
-        <v>0.03934489776141099</v>
+        <v>0.06555448615121377</v>
       </c>
       <c r="W33">
-        <v>0.06358024691358025</v>
+        <v>0.09335260115606936</v>
       </c>
       <c r="X33">
-        <v>0.08092843601666917</v>
+        <v>0.06271334557404909</v>
       </c>
       <c r="Y33">
-        <v>-0.01734818910308893</v>
+        <v>0.03063925558202027</v>
       </c>
       <c r="Z33">
-        <v>0.09048114563203014</v>
+        <v>0.3624457349503572</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.07156746064210415</v>
+        <v>0.0600626916273683</v>
       </c>
       <c r="AC33">
-        <v>-0.07156746064210415</v>
+        <v>-0.0600626916273683</v>
       </c>
       <c r="AD33">
-        <v>2025.4</v>
+        <v>120.8</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>2025.4</v>
+        <v>120.8</v>
       </c>
       <c r="AG33">
-        <v>1822.4</v>
+        <v>59.5</v>
       </c>
       <c r="AH33">
-        <v>0.2818967556959735</v>
+        <v>0.1144047731792783</v>
       </c>
       <c r="AI33">
-        <v>0.6964445361391927</v>
+        <v>0.2505184570717545</v>
       </c>
       <c r="AJ33">
-        <v>0.261017774531288</v>
+        <v>0.05982304443997587</v>
       </c>
       <c r="AK33">
-        <v>0.6736655330474642</v>
+        <v>0.1413637443573295</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -4486,7 +4501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BOC International (China) CO., LTD (SHSE:601696)</t>
+          <t>Hengtai Securities Co., Ltd. (SEHK:1476)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4494,6 +4509,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D34">
+        <v>-0.0178</v>
+      </c>
       <c r="G34">
         <v>0</v>
       </c>
@@ -4501,97 +4519,100 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>0.0004287103188851202</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>0.0004287103188851202</v>
       </c>
       <c r="K34">
-        <v>110.3</v>
+        <v>-101.7</v>
       </c>
       <c r="L34">
-        <v>0.2770660638030645</v>
+        <v>-0.3125384142593731</v>
       </c>
       <c r="M34">
-        <v>72.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N34">
-        <v>0.01700608366805252</v>
+        <v>-0</v>
       </c>
       <c r="O34">
-        <v>0.6563916591115141</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>72.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q34">
-        <v>0.01700608366805252</v>
+        <v>-0</v>
       </c>
       <c r="R34">
-        <v>0.6563916591115141</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
       <c r="U34">
-        <v>326.9</v>
+        <v>288.1</v>
       </c>
       <c r="V34">
-        <v>0.07678575623047471</v>
+        <v>0.360034991252187</v>
       </c>
       <c r="W34">
-        <v>0.04531262837893353</v>
+        <v>-0.07621974068800121</v>
       </c>
       <c r="X34">
-        <v>0.08166385861544337</v>
+        <v>0.08785643501097354</v>
       </c>
       <c r="Y34">
-        <v>-0.03635123023650984</v>
+        <v>-0.1640761756989748</v>
       </c>
       <c r="Z34">
-        <v>0.08629210560541033</v>
+        <v>0.1153192236854296</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>4.943854115976501e-05</v>
       </c>
       <c r="AB34">
-        <v>0.07157939491378323</v>
+        <v>0.06038418838114445</v>
       </c>
       <c r="AC34">
-        <v>-0.07157939491378323</v>
+        <v>-0.06033474983998469</v>
       </c>
       <c r="AD34">
-        <v>1799.5</v>
+        <v>1333.7</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>0.1624883111739094</v>
       </c>
       <c r="AF34">
-        <v>1799.5</v>
+        <v>1333.862488311174</v>
       </c>
       <c r="AG34">
-        <v>1472.6</v>
+        <v>1045.762488311174</v>
       </c>
       <c r="AH34">
-        <v>0.297104081363096</v>
+        <v>0.6250344100124023</v>
       </c>
       <c r="AI34">
-        <v>0.438731226838307</v>
+        <v>0.536083352505055</v>
       </c>
       <c r="AJ34">
-        <v>0.2570027400129147</v>
+        <v>0.5665134015089963</v>
       </c>
       <c r="AK34">
-        <v>0.3901237184412006</v>
+        <v>0.4753330843406765</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
         <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>7754.069767441862</v>
+      </c>
+      <c r="AP34">
+        <v>6080.01446692543</v>
       </c>
     </row>
     <row r="35">
@@ -4602,7 +4623,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ZHONGTAI FUTURES Company Limited (SEHK:1461)</t>
+          <t>Everbright Securities Company Limited (SHSE:601788)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4611,13 +4632,13 @@
         </is>
       </c>
       <c r="D35">
-        <v>0.19</v>
+        <v>0.0139</v>
       </c>
       <c r="E35">
-        <v>0.0721</v>
+        <v>0.166</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.05384250474383302</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -4629,28 +4650,28 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>32.7</v>
+        <v>567.5</v>
       </c>
       <c r="L35">
-        <v>0.1966325917017439</v>
+        <v>0.4486875395319418</v>
       </c>
       <c r="M35">
-        <v>3.53</v>
+        <v>449.4</v>
       </c>
       <c r="N35">
-        <v>0.04294403892944038</v>
+        <v>0.05014729512587038</v>
       </c>
       <c r="O35">
-        <v>0.1079510703363914</v>
+        <v>0.7918942731277533</v>
       </c>
       <c r="P35">
-        <v>3.53</v>
+        <v>449.4</v>
       </c>
       <c r="Q35">
-        <v>0.04294403892944038</v>
+        <v>0.05014729512587038</v>
       </c>
       <c r="R35">
-        <v>0.1079510703363914</v>
+        <v>0.7918942731277533</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -4659,55 +4680,55 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>183.6</v>
+        <v>1943.8</v>
       </c>
       <c r="V35">
-        <v>2.233576642335766</v>
+        <v>0.2169032315657918</v>
       </c>
       <c r="W35">
-        <v>0.0918023582257159</v>
+        <v>0.0627758542493999</v>
       </c>
       <c r="X35">
-        <v>0.08565945318359502</v>
+        <v>0.0848736872313656</v>
       </c>
       <c r="Y35">
-        <v>0.00614290504212088</v>
+        <v>-0.0220978329819657</v>
       </c>
       <c r="Z35">
-        <v>0.7052586938083122</v>
+        <v>0.06207089469835644</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.07163631266071754</v>
+        <v>0.06039374212602787</v>
       </c>
       <c r="AC35">
-        <v>-0.07163631266071754</v>
+        <v>-0.06039374212602787</v>
       </c>
       <c r="AD35">
-        <v>48.2</v>
+        <v>13303.4</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>48.2</v>
+        <v>13303.4</v>
       </c>
       <c r="AG35">
-        <v>-135.4</v>
+        <v>11359.6</v>
       </c>
       <c r="AH35">
-        <v>0.3696319018404908</v>
+        <v>0.5975028070963395</v>
       </c>
       <c r="AI35">
-        <v>0.1205904428321241</v>
+        <v>0.5880449628919114</v>
       </c>
       <c r="AJ35">
-        <v>2.545112781954888</v>
+        <v>0.5590024211168632</v>
       </c>
       <c r="AK35">
-        <v>-0.6265617769551132</v>
+        <v>0.5493222691290324</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -4724,7 +4745,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hongta Securities Co., Ltd. (SHSE:601236)</t>
+          <t>Huachuang Yunxin Digital Technology Co., Ltd. (SHSE:600155)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4732,6 +4753,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D36">
+        <v>0.193</v>
+      </c>
+      <c r="E36">
+        <v>0.28</v>
+      </c>
       <c r="G36">
         <v>0</v>
       </c>
@@ -4745,85 +4772,85 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>172.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L36">
-        <v>0.3372434017595308</v>
+        <v>0.1856846473029045</v>
       </c>
       <c r="M36">
-        <v>145.8</v>
+        <v>89.7</v>
       </c>
       <c r="N36">
-        <v>0.02881081294708137</v>
+        <v>0.03493262715164732</v>
       </c>
       <c r="O36">
-        <v>0.8452173913043479</v>
+        <v>1.252793296089386</v>
       </c>
       <c r="P36">
-        <v>145.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Q36">
-        <v>0.02881081294708137</v>
+        <v>0.03053197289508529</v>
       </c>
       <c r="R36">
-        <v>0.8452173913043479</v>
+        <v>1.094972067039106</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>0.1259754738015607</v>
       </c>
       <c r="U36">
-        <v>454.2</v>
+        <v>252.9</v>
       </c>
       <c r="V36">
-        <v>0.08975220329605184</v>
+        <v>0.0984889788924371</v>
       </c>
       <c r="W36">
-        <v>0.07624646393210749</v>
+        <v>0.031173807035876</v>
       </c>
       <c r="X36">
-        <v>0.08726322103640452</v>
+        <v>0.0792990028697112</v>
       </c>
       <c r="Y36">
-        <v>-0.01101675710429703</v>
+        <v>-0.0481251958338352</v>
       </c>
       <c r="Z36">
-        <v>0.1496401614885027</v>
+        <v>0.08074039951421752</v>
       </c>
       <c r="AA36">
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>0.07165598638263956</v>
+        <v>0.06041595746606473</v>
       </c>
       <c r="AC36">
-        <v>-0.07165598638263956</v>
+        <v>-0.06041595746606473</v>
       </c>
       <c r="AD36">
-        <v>3299.9</v>
+        <v>2936.4</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>3299.9</v>
+        <v>2936.4</v>
       </c>
       <c r="AG36">
-        <v>2845.7</v>
+        <v>2683.5</v>
       </c>
       <c r="AH36">
-        <v>0.3947012738472579</v>
+        <v>0.5334835216743578</v>
       </c>
       <c r="AI36">
-        <v>0.48542932376175</v>
+        <v>0.5209061396817513</v>
       </c>
       <c r="AJ36">
-        <v>0.3599281585571</v>
+        <v>0.5110163197684383</v>
       </c>
       <c r="AK36">
-        <v>0.4485867868909312</v>
+        <v>0.4984027339251885</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -4840,7 +4867,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>China Renaissance Holdings Limited (SEHK:1911)</t>
+          <t>Shanghai Chinafortune Co., Ltd. (SHSE:600621)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4848,11 +4875,14 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="F37">
-        <v>0.0518</v>
+      <c r="D37">
+        <v>-0.121</v>
+      </c>
+      <c r="E37">
+        <v>-0.05690000000000001</v>
       </c>
       <c r="G37">
-        <v>0.0846969696969697</v>
+        <v>0.02188491164476665</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -4864,91 +4894,91 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>36.1</v>
+        <v>71.7</v>
       </c>
       <c r="L37">
-        <v>0.546969696969697</v>
+        <v>0.3248753964657907</v>
       </c>
       <c r="M37">
-        <v>48.1</v>
+        <v>60.6</v>
       </c>
       <c r="N37">
-        <v>0.08126372698090895</v>
+        <v>0.02878723101040331</v>
       </c>
       <c r="O37">
-        <v>1.332409972299169</v>
+        <v>0.8451882845188284</v>
       </c>
       <c r="P37">
-        <v>29.5</v>
+        <v>60.6</v>
       </c>
       <c r="Q37">
-        <v>0.04983949991552628</v>
+        <v>0.02878723101040331</v>
       </c>
       <c r="R37">
-        <v>0.817174515235457</v>
+        <v>0.8451882845188284</v>
       </c>
       <c r="S37">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>0.3866943866943867</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>381.4</v>
+        <v>952.5</v>
       </c>
       <c r="V37">
-        <v>0.6443656022976854</v>
+        <v>0.4524725666239134</v>
       </c>
       <c r="W37">
-        <v>0.03383634829880963</v>
+        <v>0.06956437372659358</v>
       </c>
       <c r="X37">
-        <v>0.09022156853853754</v>
+        <v>0.07862883941652879</v>
       </c>
       <c r="Y37">
-        <v>-0.0563852202397279</v>
+        <v>-0.009064465689935214</v>
       </c>
       <c r="Z37">
-        <v>0.05220692928334124</v>
+        <v>0.1059743203142256</v>
       </c>
       <c r="AA37">
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>0.07168845206262657</v>
+        <v>0.06041911321232513</v>
       </c>
       <c r="AC37">
-        <v>-0.07168845206262657</v>
+        <v>-0.06041911321232513</v>
       </c>
       <c r="AD37">
-        <v>457.7</v>
+        <v>2321</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>457.7</v>
+        <v>2321</v>
       </c>
       <c r="AG37">
-        <v>76.30000000000001</v>
+        <v>1368.5</v>
       </c>
       <c r="AH37">
-        <v>0.4360708841463415</v>
+        <v>0.5243894173199882</v>
       </c>
       <c r="AI37">
-        <v>0.2844447206512957</v>
+        <v>0.6830890576255224</v>
       </c>
       <c r="AJ37">
-        <v>0.1141873690511823</v>
+        <v>0.3939716720405343</v>
       </c>
       <c r="AK37">
-        <v>0.06214873340392605</v>
+        <v>0.5596450333292439</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-19.8</v>
+        <v>-114.6</v>
       </c>
       <c r="AQ37">
         <v>-0</v>
@@ -4962,7 +4992,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hengtai Securities Co., Ltd (SEHK:1476)</t>
+          <t>Yongan Futures Co.,Ltd. (SHSE:600927)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4971,7 +5001,10 @@
         </is>
       </c>
       <c r="D38">
-        <v>-0.0141</v>
+        <v>0.133</v>
+      </c>
+      <c r="E38">
+        <v>-0.0382</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4980,100 +5013,97 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0.0003529468116961285</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>0.0003529468116961285</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>-9.51</v>
+        <v>104</v>
       </c>
       <c r="L38">
-        <v>-0.0218721251149954</v>
+        <v>0.03047976319568594</v>
       </c>
       <c r="M38">
-        <v>-0</v>
+        <v>33.2</v>
       </c>
       <c r="N38">
-        <v>-0</v>
+        <v>0.01029521210617713</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>0.3192307692307693</v>
       </c>
       <c r="P38">
-        <v>-0</v>
+        <v>33.2</v>
       </c>
       <c r="Q38">
-        <v>-0</v>
+        <v>0.01029521210617713</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>0.3192307692307693</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
       <c r="U38">
-        <v>317.6</v>
+        <v>555.8</v>
       </c>
       <c r="V38">
-        <v>0.3018437559399354</v>
+        <v>0.172351773753411</v>
       </c>
       <c r="W38">
-        <v>-0.006803061735460332</v>
+        <v>0.06287407049150597</v>
       </c>
       <c r="X38">
-        <v>0.1133724922170667</v>
+        <v>0.06124754915990611</v>
       </c>
       <c r="Y38">
-        <v>-0.120175553952527</v>
+        <v>0.001626521331599858</v>
       </c>
       <c r="Z38">
-        <v>0.1413382675927154</v>
+        <v>2.399170299535931</v>
       </c>
       <c r="AA38">
-        <v>4.988489091750313e-05</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>0.07184266928447615</v>
+        <v>0.06042209519370397</v>
       </c>
       <c r="AC38">
-        <v>-0.07179278439355864</v>
+        <v>-0.06042209519370397</v>
       </c>
       <c r="AD38">
-        <v>1811.4</v>
+        <v>127.5</v>
       </c>
       <c r="AE38">
-        <v>0.1776936313726167</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1811.577693631373</v>
+        <v>127.5</v>
       </c>
       <c r="AG38">
-        <v>1493.977693631373</v>
+        <v>-428.3</v>
       </c>
       <c r="AH38">
-        <v>0.6325832126076194</v>
+        <v>0.03803358887927692</v>
       </c>
       <c r="AI38">
-        <v>0.5655034518369999</v>
+        <v>0.07008960474960145</v>
       </c>
       <c r="AJ38">
-        <v>0.5867531152158724</v>
+        <v>-0.1531557303772573</v>
       </c>
       <c r="AK38">
-        <v>0.5176857276135853</v>
+        <v>-0.3390326921554658</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
         <v>0</v>
-      </c>
-      <c r="AN38">
-        <v>9584.126984126984</v>
-      </c>
-      <c r="AP38">
-        <v>7904.643881647476</v>
       </c>
     </row>
     <row r="39">
@@ -5084,7 +5114,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shanghai Chinafortune Co., Ltd. (SHSE:600621)</t>
+          <t>Caida Securities Co., Ltd. (SHSE:600906)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5093,13 +5123,13 @@
         </is>
       </c>
       <c r="D39">
-        <v>0.0373</v>
+        <v>0.0634</v>
       </c>
       <c r="E39">
-        <v>0.0623</v>
+        <v>0.338</v>
       </c>
       <c r="G39">
-        <v>0.02322670375521558</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -5111,28 +5141,28 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>35.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L39">
-        <v>0.1230876216968011</v>
+        <v>0.2458162885831164</v>
       </c>
       <c r="M39">
-        <v>70.2</v>
+        <v>82.8</v>
       </c>
       <c r="N39">
-        <v>0.04418150922021524</v>
+        <v>0.02412446827107977</v>
       </c>
       <c r="O39">
-        <v>1.983050847457627</v>
+        <v>1.252647503782148</v>
       </c>
       <c r="P39">
-        <v>70.2</v>
+        <v>82.8</v>
       </c>
       <c r="Q39">
-        <v>0.04418150922021524</v>
+        <v>0.02412446827107977</v>
       </c>
       <c r="R39">
-        <v>1.983050847457627</v>
+        <v>1.252647503782148</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -5141,64 +5171,61 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>1110</v>
+        <v>260.7</v>
       </c>
       <c r="V39">
-        <v>0.6985965133110957</v>
+        <v>0.07595711205640697</v>
       </c>
       <c r="W39">
-        <v>0.03150026695141484</v>
+        <v>0.04195227215029195</v>
       </c>
       <c r="X39">
-        <v>0.104684671792635</v>
+        <v>0.07355329468573532</v>
       </c>
       <c r="Y39">
-        <v>-0.07318440484122016</v>
+        <v>-0.03160102253544337</v>
       </c>
       <c r="Z39">
-        <v>0.1562678287139419</v>
+        <v>0.06311199151309181</v>
       </c>
       <c r="AA39">
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0.07179929072668076</v>
+        <v>0.0604476999019871</v>
       </c>
       <c r="AC39">
-        <v>-0.07179929072668076</v>
+        <v>-0.0604476999019871</v>
       </c>
       <c r="AD39">
-        <v>2170.1</v>
+        <v>2718.8</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>2170.1</v>
+        <v>2718.8</v>
       </c>
       <c r="AG39">
-        <v>1060.1</v>
+        <v>2458.1</v>
       </c>
       <c r="AH39">
-        <v>0.5773077946262304</v>
+        <v>0.4420094293610795</v>
       </c>
       <c r="AI39">
-        <v>0.6744258321161077</v>
+        <v>0.6323378918969206</v>
       </c>
       <c r="AJ39">
-        <v>0.4001887504718761</v>
+        <v>0.417313209853488</v>
       </c>
       <c r="AK39">
-        <v>0.5029653176448261</v>
+        <v>0.608606303696551</v>
       </c>
       <c r="AL39">
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-37.2</v>
-      </c>
-      <c r="AQ39">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -5209,7 +5236,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Industrial Securities Co.,Ltd. (SHSE:601377)</t>
+          <t>Guosheng Financial Holding Inc. (SZSE:002670)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5220,11 +5247,8 @@
       <c r="D40">
         <v>0.169</v>
       </c>
-      <c r="E40">
-        <v>0.0862</v>
-      </c>
       <c r="G40">
-        <v>0.003086867222423584</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -5236,28 +5260,28 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>421.7</v>
+        <v>-33.3</v>
       </c>
       <c r="L40">
-        <v>0.254742056300592</v>
+        <v>-0.1660019940179462</v>
       </c>
       <c r="M40">
-        <v>278.7</v>
+        <v>21.8</v>
       </c>
       <c r="N40">
-        <v>0.03877834979824683</v>
+        <v>0.008571203900290949</v>
       </c>
       <c r="O40">
-        <v>0.660896371828314</v>
+        <v>-0.6546546546546548</v>
       </c>
       <c r="P40">
-        <v>278.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q40">
-        <v>0.03877834979824683</v>
+        <v>0.008571203900290949</v>
       </c>
       <c r="R40">
-        <v>0.660896371828314</v>
+        <v>-0.6546546546546548</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -5266,61 +5290,64 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>3928.2</v>
+        <v>1269.9</v>
       </c>
       <c r="V40">
-        <v>0.5465701961875609</v>
+        <v>0.4992922859164898</v>
       </c>
       <c r="W40">
-        <v>0.06800187057552448</v>
+        <v>-0.02106128644614509</v>
       </c>
       <c r="X40">
-        <v>0.1218216581469897</v>
+        <v>0.06859648305320912</v>
       </c>
       <c r="Y40">
-        <v>-0.05381978757146523</v>
+        <v>-0.08965776949935421</v>
       </c>
       <c r="Z40">
-        <v>0.09035286412138745</v>
+        <v>0.1774750066354066</v>
       </c>
       <c r="AA40">
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>0.07187520201376793</v>
+        <v>0.06048712202485746</v>
       </c>
       <c r="AC40">
-        <v>-0.07187520201376793</v>
+        <v>-0.06048712202485746</v>
       </c>
       <c r="AD40">
-        <v>14861.6</v>
+        <v>1243.7</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>14861.6</v>
+        <v>1243.7</v>
       </c>
       <c r="AG40">
-        <v>10933.4</v>
+        <v>-26.20000000000005</v>
       </c>
       <c r="AH40">
-        <v>0.6740382609326669</v>
+        <v>0.3284043199281772</v>
       </c>
       <c r="AI40">
-        <v>0.6456708649580968</v>
+        <v>0.4516960848405608</v>
       </c>
       <c r="AJ40">
-        <v>0.603375201430432</v>
+        <v>-0.01040839027490865</v>
       </c>
       <c r="AK40">
-        <v>0.5727561802285074</v>
+        <v>-0.01766093697337381</v>
       </c>
       <c r="AL40">
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>-45</v>
+      </c>
+      <c r="AQ40">
+        <v>-0</v>
       </c>
     </row>
     <row r="41">
@@ -5331,7 +5358,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Guangzhou Yuexiu Capital Holdings Group Co., Ltd. (SZSE:000987)</t>
+          <t>The Pacific Securities Co., Ltd (SHSE:601099)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5340,13 +5367,10 @@
         </is>
       </c>
       <c r="D41">
-        <v>0.0641</v>
-      </c>
-      <c r="E41">
-        <v>0.209</v>
+        <v>0.0262</v>
       </c>
       <c r="G41">
-        <v>0.0006689890516138206</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -5358,28 +5382,28 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>340.7</v>
+        <v>-19.8</v>
       </c>
       <c r="L41">
-        <v>0.2422152708659178</v>
+        <v>-0.1200727713765919</v>
       </c>
       <c r="M41">
-        <v>567.4</v>
+        <v>4.7</v>
       </c>
       <c r="N41">
-        <v>0.1302212430000918</v>
+        <v>0.001321449658391205</v>
       </c>
       <c r="O41">
-        <v>1.665394775462284</v>
+        <v>-0.2373737373737374</v>
       </c>
       <c r="P41">
-        <v>567.4</v>
+        <v>4.7</v>
       </c>
       <c r="Q41">
-        <v>0.1302212430000918</v>
+        <v>0.001321449658391205</v>
       </c>
       <c r="R41">
-        <v>1.665394775462284</v>
+        <v>-0.2373737373737374</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -5388,64 +5412,61 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>3284.9</v>
+        <v>154.4</v>
       </c>
       <c r="V41">
-        <v>0.7539015881758928</v>
+        <v>0.04341102707566002</v>
       </c>
       <c r="W41">
-        <v>0.08909285845035433</v>
+        <v>-0.01462765957446809</v>
       </c>
       <c r="X41">
-        <v>0.1534311423641206</v>
+        <v>0.06105758221187138</v>
       </c>
       <c r="Y41">
-        <v>-0.06433828391376625</v>
+        <v>-0.07568524178633947</v>
       </c>
       <c r="Z41">
-        <v>0.08774359358235397</v>
+        <v>0.1164712530018364</v>
       </c>
       <c r="AA41">
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>0.07195112959945063</v>
+        <v>0.06059165656448866</v>
       </c>
       <c r="AC41">
-        <v>-0.07195112959945063</v>
+        <v>-0.06059165656448866</v>
       </c>
       <c r="AD41">
-        <v>14652.4</v>
+        <v>99.3</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>14652.4</v>
+        <v>99.3</v>
       </c>
       <c r="AG41">
-        <v>11367.5</v>
+        <v>-55.10000000000001</v>
       </c>
       <c r="AH41">
-        <v>0.7707894958336841</v>
+        <v>0.02716083150984683</v>
       </c>
       <c r="AI41">
-        <v>0.7335442657748763</v>
+        <v>0.0709589824210376</v>
       </c>
       <c r="AJ41">
-        <v>0.7229072732707142</v>
+        <v>-0.01573566369659584</v>
       </c>
       <c r="AK41">
-        <v>0.6811005458391002</v>
+        <v>-0.0442570281124498</v>
       </c>
       <c r="AL41">
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-354.3</v>
-      </c>
-      <c r="AQ41">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -5456,7 +5477,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capital Securities Corporation Limited (SHSE:601136)</t>
+          <t>CSC Financial Co., Ltd. (SEHK:6066)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5464,6 +5485,15 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D42">
+        <v>0.173</v>
+      </c>
+      <c r="E42">
+        <v>0.164</v>
+      </c>
+      <c r="F42">
+        <v>0.00433</v>
+      </c>
       <c r="G42">
         <v>0</v>
       </c>
@@ -5477,28 +5507,28 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>122.4</v>
+        <v>926.8</v>
       </c>
       <c r="L42">
-        <v>0.3945841392649904</v>
+        <v>0.2730620783123656</v>
       </c>
       <c r="M42">
-        <v>42.5</v>
+        <v>432</v>
       </c>
       <c r="N42">
-        <v>0.006156297530238285</v>
+        <v>0.01895751235310122</v>
       </c>
       <c r="O42">
-        <v>0.3472222222222222</v>
+        <v>0.466119982736297</v>
       </c>
       <c r="P42">
-        <v>42.5</v>
+        <v>432</v>
       </c>
       <c r="Q42">
-        <v>0.006156297530238285</v>
+        <v>0.01895751235310122</v>
       </c>
       <c r="R42">
-        <v>0.3472222222222222</v>
+        <v>0.466119982736297</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -5507,55 +5537,55 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>82.90000000000001</v>
+        <v>3737.9</v>
       </c>
       <c r="V42">
-        <v>0.01200840153545303</v>
+        <v>0.1640307532978173</v>
       </c>
       <c r="W42">
-        <v>0.08669169204617891</v>
+        <v>0.070937619594336</v>
       </c>
       <c r="X42">
-        <v>0.08137706301394554</v>
+        <v>0.08662075458392419</v>
       </c>
       <c r="Y42">
-        <v>0.00531462903223337</v>
+        <v>-0.01568313498958819</v>
       </c>
       <c r="Z42">
-        <v>0.08265387689848121</v>
+        <v>0.08223535967824001</v>
       </c>
       <c r="AA42">
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>0.07240486647104545</v>
+        <v>0.06100238914366611</v>
       </c>
       <c r="AC42">
-        <v>-0.07240486647104545</v>
+        <v>-0.06100238914366611</v>
       </c>
       <c r="AD42">
-        <v>2836.9</v>
+        <v>36263.1</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>2836.9</v>
+        <v>36263.1</v>
       </c>
       <c r="AG42">
-        <v>2754</v>
+        <v>32525.2</v>
       </c>
       <c r="AH42">
-        <v>0.2912508726541005</v>
+        <v>0.6140990230462194</v>
       </c>
       <c r="AI42">
-        <v>0.6561278534588432</v>
+        <v>0.7327832876645892</v>
       </c>
       <c r="AJ42">
-        <v>0.2851669686771939</v>
+        <v>0.5880208992461085</v>
       </c>
       <c r="AK42">
-        <v>0.6494057724957555</v>
+        <v>0.7109504272233869</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -5572,7 +5602,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CSC Financial Co., Ltd. (SEHK:6066)</t>
+          <t>CITIC Securities Company Limited (SHSE:600030)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5581,13 +5611,13 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.226</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="E43">
-        <v>0.171</v>
+        <v>0.144</v>
       </c>
       <c r="F43">
-        <v>0.00433</v>
+        <v>0.0906</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -5602,28 +5632,28 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>1323.7</v>
+        <v>2900.5</v>
       </c>
       <c r="L43">
-        <v>0.2798342599835106</v>
+        <v>0.3675520186532175</v>
       </c>
       <c r="M43">
-        <v>535.5</v>
+        <v>2030.7</v>
       </c>
       <c r="N43">
-        <v>0.02281441717791411</v>
+        <v>0.05027169540407729</v>
       </c>
       <c r="O43">
-        <v>0.4045478582760444</v>
+        <v>0.7001206688501983</v>
       </c>
       <c r="P43">
-        <v>535.5</v>
+        <v>2030.7</v>
       </c>
       <c r="Q43">
-        <v>0.02281441717791411</v>
+        <v>0.05027169540407729</v>
       </c>
       <c r="R43">
-        <v>0.4045478582760444</v>
+        <v>0.7001206688501983</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -5632,55 +5662,55 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>4820</v>
+        <v>39346.4</v>
       </c>
       <c r="V43">
-        <v>0.2053510565780504</v>
+        <v>0.9740533983586874</v>
       </c>
       <c r="W43">
-        <v>0.1110374794483777</v>
+        <v>0.08294015041034</v>
       </c>
       <c r="X43">
-        <v>0.1056936635968614</v>
+        <v>0.08992499231652443</v>
       </c>
       <c r="Y43">
-        <v>0.005343815851516262</v>
+        <v>-0.006984841906184425</v>
       </c>
       <c r="Z43">
-        <v>0.1139652825461072</v>
+        <v>0.0998013180542575</v>
       </c>
       <c r="AA43">
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>0.07263799412877534</v>
+        <v>0.06102063272586357</v>
       </c>
       <c r="AC43">
-        <v>-0.07263799412877534</v>
+        <v>-0.06102063272586357</v>
       </c>
       <c r="AD43">
-        <v>33028</v>
+        <v>72444.39999999999</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>33028</v>
+        <v>72444.39999999999</v>
       </c>
       <c r="AG43">
-        <v>28208</v>
+        <v>33097.99999999999</v>
       </c>
       <c r="AH43">
-        <v>0.5845663716814159</v>
+        <v>0.6420161841350811</v>
       </c>
       <c r="AI43">
-        <v>0.716451841021792</v>
+        <v>0.6638528249602299</v>
       </c>
       <c r="AJ43">
-        <v>0.5458204334365325</v>
+        <v>0.4503588801578391</v>
       </c>
       <c r="AK43">
-        <v>0.683343265648241</v>
+        <v>0.4743138513745901</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -5697,7 +5727,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Guosheng Financial Holding Inc. (SZSE:002670)</t>
+          <t>China International Capital Corporation Limited (SEHK:3908)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5706,43 +5736,49 @@
         </is>
       </c>
       <c r="D44">
-        <v>0.0866</v>
+        <v>0.121</v>
+      </c>
+      <c r="E44">
+        <v>0.119</v>
+      </c>
+      <c r="F44">
+        <v>0.3</v>
       </c>
       <c r="G44">
-        <v>0.1719512195121951</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>0.1720681590377547</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>-0.00407617774807885</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>-0.00407617774807885</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>-37.3</v>
+        <v>848.8</v>
       </c>
       <c r="L44">
-        <v>-0.1246241229535583</v>
+        <v>0.2489368566149515</v>
       </c>
       <c r="M44">
-        <v>48.6</v>
+        <v>200</v>
       </c>
       <c r="N44">
-        <v>0.02337662337662338</v>
+        <v>0.01082215945369739</v>
       </c>
       <c r="O44">
-        <v>-1.302949061662199</v>
+        <v>0.235626767200754</v>
       </c>
       <c r="P44">
-        <v>48.6</v>
+        <v>200</v>
       </c>
       <c r="Q44">
-        <v>0.02337662337662338</v>
+        <v>0.01082215945369739</v>
       </c>
       <c r="R44">
-        <v>-1.302949061662199</v>
+        <v>0.235626767200754</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -5751,73 +5787,61 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>1355.2</v>
+        <v>7045.5</v>
       </c>
       <c r="V44">
-        <v>0.6518518518518519</v>
+        <v>0.3812376221551249</v>
       </c>
       <c r="W44">
-        <v>-0.02091745177209511</v>
+        <v>0.06422178002073134</v>
       </c>
       <c r="X44">
-        <v>0.08374832466127449</v>
+        <v>0.09413676306556562</v>
       </c>
       <c r="Y44">
-        <v>-0.1046657764333696</v>
+        <v>-0.02991498304483428</v>
       </c>
       <c r="Z44">
-        <v>0.2630052724077327</v>
+        <v>0.07794704620997718</v>
       </c>
       <c r="AA44">
-        <v>-0.001072056239015817</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>0.07161062996858816</v>
+        <v>0.06104038349492616</v>
       </c>
       <c r="AC44">
-        <v>-0.07268268620760399</v>
+        <v>-0.06104038349492616</v>
       </c>
       <c r="AD44">
-        <v>1056.3</v>
+        <v>37903.9</v>
       </c>
       <c r="AE44">
         <v>0</v>
       </c>
       <c r="AF44">
-        <v>1056.3</v>
+        <v>37903.9</v>
       </c>
       <c r="AG44">
-        <v>-298.9000000000001</v>
+        <v>30858.4</v>
       </c>
       <c r="AH44">
-        <v>0.3369055592766242</v>
+        <v>0.6722397112681677</v>
       </c>
       <c r="AI44">
-        <v>0.4004777070063694</v>
+        <v>0.7276561516133491</v>
       </c>
       <c r="AJ44">
-        <v>-0.1679119150609517</v>
+        <v>0.6254362674557652</v>
       </c>
       <c r="AK44">
-        <v>-0.2330786026200874</v>
+        <v>0.6850586858889686</v>
       </c>
       <c r="AL44">
-        <v>55.9</v>
+        <v>0</v>
       </c>
       <c r="AM44">
-        <v>35</v>
-      </c>
-      <c r="AN44">
-        <v>754.5</v>
-      </c>
-      <c r="AO44">
-        <v>-0.02182468694096601</v>
-      </c>
-      <c r="AP44">
-        <v>-213.5000000000001</v>
-      </c>
-      <c r="AQ44">
-        <v>-0.03485714285714286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5828,7 +5852,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CITIC Securities Company Limited (SHSE:600030)</t>
+          <t>Guotai Junan Securities Co., Ltd. (SHSE:601211)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5837,13 +5861,13 @@
         </is>
       </c>
       <c r="D45">
-        <v>0.104</v>
+        <v>0.0955</v>
       </c>
       <c r="E45">
-        <v>0.163</v>
+        <v>0.0697</v>
       </c>
       <c r="F45">
-        <v>0.0906</v>
+        <v>0.0965</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5858,85 +5882,85 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>3095.5</v>
+        <v>1604.6</v>
       </c>
       <c r="L45">
-        <v>0.3414028895996471</v>
+        <v>0.3388305847076462</v>
       </c>
       <c r="M45">
-        <v>2159.6</v>
+        <v>1619.65</v>
       </c>
       <c r="N45">
-        <v>0.05329555886795061</v>
+        <v>0.09413723757933648</v>
       </c>
       <c r="O45">
-        <v>0.6976578904861896</v>
+        <v>1.009379284556899</v>
       </c>
       <c r="P45">
-        <v>2159.6</v>
+        <v>1611</v>
       </c>
       <c r="Q45">
-        <v>0.05329555886795061</v>
+        <v>0.09363448259828423</v>
       </c>
       <c r="R45">
-        <v>0.6976578904861896</v>
+        <v>1.003988532967718</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>8.650000000000091</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>0.005340660019139993</v>
       </c>
       <c r="U45">
-        <v>20002.3</v>
+        <v>4405.4</v>
       </c>
       <c r="V45">
-        <v>0.4936255589666644</v>
+        <v>0.2560504963615651</v>
       </c>
       <c r="W45">
-        <v>0.0978476983427056</v>
+        <v>0.07380830814945653</v>
       </c>
       <c r="X45">
-        <v>0.1107024822446874</v>
+        <v>0.1070453038013323</v>
       </c>
       <c r="Y45">
-        <v>-0.01285478390198178</v>
+        <v>-0.03323699565187581</v>
       </c>
       <c r="Z45">
-        <v>0.104703396191554</v>
+        <v>0.07463335773990329</v>
       </c>
       <c r="AA45">
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>0.0727101041493886</v>
+        <v>0.06108441332938608</v>
       </c>
       <c r="AC45">
-        <v>-0.0727101041493886</v>
+        <v>-0.06108441332938608</v>
       </c>
       <c r="AD45">
-        <v>65333.2</v>
+        <v>48871.1</v>
       </c>
       <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45">
-        <v>65333.2</v>
+        <v>48871.1</v>
       </c>
       <c r="AG45">
-        <v>45330.89999999999</v>
+        <v>44465.7</v>
       </c>
       <c r="AH45">
-        <v>0.617198718239393</v>
+        <v>0.7396161710023109</v>
       </c>
       <c r="AI45">
-        <v>0.6468025284750444</v>
+        <v>0.6742375851055757</v>
       </c>
       <c r="AJ45">
-        <v>0.5280115454368618</v>
+        <v>0.7210159086376233</v>
       </c>
       <c r="AK45">
-        <v>0.559590999318579</v>
+        <v>0.6531571827063328</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -5953,7 +5977,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>China International Capital Corporation Limited (SEHK:3908)</t>
+          <t>Huatai Securities Co., Ltd. (SHSE:601688)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5962,13 +5986,13 @@
         </is>
       </c>
       <c r="D46">
-        <v>0.219</v>
+        <v>0.122</v>
       </c>
       <c r="E46">
-        <v>0.286</v>
+        <v>0.0721</v>
       </c>
       <c r="F46">
-        <v>0.3</v>
+        <v>0.0765</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5983,85 +6007,85 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>1312.3</v>
+        <v>1756.5</v>
       </c>
       <c r="L46">
-        <v>0.3215239495283597</v>
+        <v>0.3514194826240922</v>
       </c>
       <c r="M46">
-        <v>1115.8</v>
+        <v>799.16</v>
       </c>
       <c r="N46">
-        <v>0.05635296613165523</v>
+        <v>0.0485457417081764</v>
       </c>
       <c r="O46">
-        <v>0.8502628972033833</v>
+        <v>0.4549729575861087</v>
       </c>
       <c r="P46">
-        <v>1115.8</v>
+        <v>797.9</v>
       </c>
       <c r="Q46">
-        <v>0.05635296613165523</v>
+        <v>0.04846920179808042</v>
       </c>
       <c r="R46">
-        <v>0.8502628972033833</v>
+        <v>0.4542556219755195</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.259999999999991</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>0.001576655488262664</v>
       </c>
       <c r="U46">
-        <v>9286.6</v>
+        <v>7188.5</v>
       </c>
       <c r="V46">
-        <v>0.4690154644902577</v>
+        <v>0.4366723362896368</v>
       </c>
       <c r="W46">
-        <v>0.1039948014486207</v>
+        <v>0.07883363029652934</v>
       </c>
       <c r="X46">
-        <v>0.1207097481553939</v>
+        <v>0.1111632488680586</v>
       </c>
       <c r="Y46">
-        <v>-0.01671494670677322</v>
+        <v>-0.03232961857152922</v>
       </c>
       <c r="Z46">
-        <v>0.08595255393751776</v>
+        <v>0.07374070735489165</v>
       </c>
       <c r="AA46">
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0.07282485015609622</v>
+        <v>0.06109488517091419</v>
       </c>
       <c r="AC46">
-        <v>-0.07282485015609622</v>
+        <v>-0.06109488517091419</v>
       </c>
       <c r="AD46">
-        <v>40041.8</v>
+        <v>50906</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>40041.8</v>
+        <v>50906</v>
       </c>
       <c r="AG46">
-        <v>30755.2</v>
+        <v>43717.5</v>
       </c>
       <c r="AH46">
-        <v>0.6691253634571037</v>
+        <v>0.7556406602541266</v>
       </c>
       <c r="AI46">
-        <v>0.7512476454210475</v>
+        <v>0.6795331129894331</v>
       </c>
       <c r="AJ46">
-        <v>0.6083464872199607</v>
+        <v>0.7264516986681511</v>
       </c>
       <c r="AK46">
-        <v>0.6987626608018395</v>
+        <v>0.6455178096027003</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -6078,7 +6102,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Caida Securities Co., Ltd. (SHSE:600906)</t>
+          <t>Capital Securities Corporation Limited (SHSE:601136)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6086,12 +6110,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D47">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="E47">
-        <v>0.04219999999999999</v>
-      </c>
       <c r="G47">
         <v>0</v>
       </c>
@@ -6105,28 +6123,28 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>71.5</v>
+        <v>77.2</v>
       </c>
       <c r="L47">
-        <v>0.2521156558533145</v>
+        <v>0.3349240780911063</v>
       </c>
       <c r="M47">
-        <v>98.8</v>
+        <v>114.6</v>
       </c>
       <c r="N47">
-        <v>0.02774112031447424</v>
+        <v>0.01752936857562408</v>
       </c>
       <c r="O47">
-        <v>1.381818181818182</v>
+        <v>1.484455958549223</v>
       </c>
       <c r="P47">
-        <v>98.8</v>
+        <v>114.6</v>
       </c>
       <c r="Q47">
-        <v>0.02774112031447424</v>
+        <v>0.01752936857562408</v>
       </c>
       <c r="R47">
-        <v>1.381818181818182</v>
+        <v>1.484455958549223</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -6135,55 +6153,55 @@
         <v>0</v>
       </c>
       <c r="U47">
-        <v>233.2</v>
+        <v>53.6</v>
       </c>
       <c r="V47">
-        <v>0.06547802892039871</v>
+        <v>0.008198727361722957</v>
       </c>
       <c r="W47">
-        <v>0.04179331306990881</v>
+        <v>0.05200404176490401</v>
       </c>
       <c r="X47">
-        <v>0.09136470732014576</v>
+        <v>0.06831904671050797</v>
       </c>
       <c r="Y47">
-        <v>-0.04957139425023695</v>
+        <v>-0.01631500494560396</v>
       </c>
       <c r="Z47">
-        <v>0.05964724836054196</v>
+        <v>0.05462473635566509</v>
       </c>
       <c r="AA47">
         <v>0</v>
       </c>
       <c r="AB47">
-        <v>0.07298399435209556</v>
+        <v>0.06113169543605308</v>
       </c>
       <c r="AC47">
-        <v>-0.07298399435209556</v>
+        <v>-0.06113169543605308</v>
       </c>
       <c r="AD47">
-        <v>2920.8</v>
+        <v>3085.9</v>
       </c>
       <c r="AE47">
         <v>0</v>
       </c>
       <c r="AF47">
-        <v>2920.8</v>
+        <v>3085.9</v>
       </c>
       <c r="AG47">
-        <v>2687.6</v>
+        <v>3032.3</v>
       </c>
       <c r="AH47">
-        <v>0.4505808123659812</v>
+        <v>0.3206629604613706</v>
       </c>
       <c r="AI47">
-        <v>0.6494996664442962</v>
+        <v>0.6503888549328725</v>
       </c>
       <c r="AJ47">
-        <v>0.430077931222096</v>
+        <v>0.3168580653925328</v>
       </c>
       <c r="AK47">
-        <v>0.6303297528026643</v>
+        <v>0.6463942358935004</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -6200,7 +6218,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Guotai Junan Securities Co., Ltd. (SHSE:601211)</t>
+          <t>Guangdong Golden Dragon Development Inc. (SZSE:000712)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6209,13 +6227,7 @@
         </is>
       </c>
       <c r="D48">
-        <v>0.104</v>
-      </c>
-      <c r="E48">
-        <v>0.0505</v>
-      </c>
-      <c r="F48">
-        <v>0.083</v>
+        <v>-0.289</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6230,85 +6242,85 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>1659.5</v>
+        <v>-58.3</v>
       </c>
       <c r="L48">
-        <v>0.3198111389477741</v>
+        <v>-2.208333333333333</v>
       </c>
       <c r="M48">
-        <v>1683.17</v>
+        <v>53.4</v>
       </c>
       <c r="N48">
-        <v>0.1038730938466191</v>
+        <v>0.02880725036413659</v>
       </c>
       <c r="O48">
-        <v>1.014263332329015</v>
+        <v>-0.9159519725557461</v>
       </c>
       <c r="P48">
-        <v>1681.4</v>
+        <v>53.4</v>
       </c>
       <c r="Q48">
-        <v>0.103763862232398</v>
+        <v>0.02880725036413659</v>
       </c>
       <c r="R48">
-        <v>1.013196746007834</v>
+        <v>-0.9159519725557461</v>
       </c>
       <c r="S48">
-        <v>1.769999999999982</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>0.001051587183706923</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>5541.2</v>
+        <v>187.4</v>
       </c>
       <c r="V48">
-        <v>0.3419628365660543</v>
+        <v>0.101095107083131</v>
       </c>
       <c r="W48">
-        <v>0.07440169292432952</v>
+        <v>-0.1365339578454332</v>
       </c>
       <c r="X48">
-        <v>0.1425335080006312</v>
+        <v>0.07214288264176347</v>
       </c>
       <c r="Y48">
-        <v>-0.06813181507630167</v>
+        <v>-0.2086768404871967</v>
       </c>
       <c r="Z48">
-        <v>0.07301862573008074</v>
+        <v>0.01524953789279113</v>
       </c>
       <c r="AA48">
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>0.07299176552806469</v>
+        <v>0.06128580340194847</v>
       </c>
       <c r="AC48">
-        <v>-0.07299176552806469</v>
+        <v>-0.06128580340194847</v>
       </c>
       <c r="AD48">
-        <v>47256.9</v>
+        <v>1308.5</v>
       </c>
       <c r="AE48">
         <v>0</v>
       </c>
       <c r="AF48">
-        <v>47256.9</v>
+        <v>1308.5</v>
       </c>
       <c r="AG48">
-        <v>41715.7</v>
+        <v>1121.1</v>
       </c>
       <c r="AH48">
-        <v>0.7446605001496983</v>
+        <v>0.4137941939156284</v>
       </c>
       <c r="AI48">
-        <v>0.679707962425189</v>
+        <v>0.6711288916243524</v>
       </c>
       <c r="AJ48">
-        <v>0.7202321140611674</v>
+        <v>0.376865671641791</v>
       </c>
       <c r="AK48">
-        <v>0.65196978624377</v>
+        <v>0.6361572944447597</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -6325,7 +6337,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Huatai Securities Co., Ltd. (SHSE:601688)</t>
+          <t>Guosen Securities Co., Ltd. (SZSE:002736)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6334,13 +6346,10 @@
         </is>
       </c>
       <c r="D49">
-        <v>0.153</v>
+        <v>0.09630000000000001</v>
       </c>
       <c r="E49">
-        <v>0.104</v>
-      </c>
-      <c r="F49">
-        <v>0.0765</v>
+        <v>0.145</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -6355,85 +6364,85 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>1422.3</v>
+        <v>849.7</v>
       </c>
       <c r="L49">
-        <v>0.2852644457369783</v>
+        <v>0.4125157782308962</v>
       </c>
       <c r="M49">
-        <v>840.88</v>
+        <v>358.4288</v>
       </c>
       <c r="N49">
-        <v>0.05463985184703857</v>
+        <v>0.03096095639554972</v>
       </c>
       <c r="O49">
-        <v>0.5912114181255713</v>
+        <v>0.42182982229022</v>
       </c>
       <c r="P49">
-        <v>834</v>
+        <v>355.6588</v>
       </c>
       <c r="Q49">
-        <v>0.05419279378797232</v>
+        <v>0.03072168474880796</v>
       </c>
       <c r="R49">
-        <v>0.5863741826618857</v>
+        <v>0.4185698481817112</v>
       </c>
       <c r="S49">
-        <v>6.879999999999995</v>
+        <v>2.769999999999982</v>
       </c>
       <c r="T49">
-        <v>0.008181904671296732</v>
+        <v>0.00772817362890477</v>
       </c>
       <c r="U49">
-        <v>7401.3</v>
+        <v>689.8</v>
       </c>
       <c r="V49">
-        <v>0.4809318041521817</v>
+        <v>0.05958468661460853</v>
       </c>
       <c r="W49">
-        <v>0.0658216249236408</v>
+        <v>0.057245068448852</v>
       </c>
       <c r="X49">
-        <v>0.1559593655480293</v>
+        <v>0.1007969200948294</v>
       </c>
       <c r="Y49">
-        <v>-0.09013774062438848</v>
+        <v>-0.04355185164597735</v>
       </c>
       <c r="Z49">
-        <v>0.07620798809016137</v>
+        <v>0.05092960499020129</v>
       </c>
       <c r="AA49">
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>0.07306125035749791</v>
+        <v>0.06177734332189797</v>
       </c>
       <c r="AC49">
-        <v>-0.07306125035749791</v>
+        <v>-0.06177734332189797</v>
       </c>
       <c r="AD49">
-        <v>53345.8</v>
+        <v>28459.7</v>
       </c>
       <c r="AE49">
         <v>0</v>
       </c>
       <c r="AF49">
-        <v>53345.8</v>
+        <v>28459.7</v>
       </c>
       <c r="AG49">
-        <v>45944.5</v>
+        <v>27769.9</v>
       </c>
       <c r="AH49">
-        <v>0.7761048544197814</v>
+        <v>0.7108438549823286</v>
       </c>
       <c r="AI49">
-        <v>0.7018205355568828</v>
+        <v>0.6554710297636733</v>
       </c>
       <c r="AJ49">
-        <v>0.7490869664460169</v>
+        <v>0.705774563051031</v>
       </c>
       <c r="AK49">
-        <v>0.6696541139466515</v>
+        <v>0.6499090779308618</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -6450,7 +6459,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>China Great Wall Securities Co.,Ltd. (SZSE:002939)</t>
+          <t>China Galaxy Securities Co., Ltd. (SEHK:6881)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6459,10 +6468,13 @@
         </is>
       </c>
       <c r="D50">
-        <v>0.0793</v>
+        <v>0.279</v>
       </c>
       <c r="E50">
-        <v>0.0114</v>
+        <v>0.231</v>
+      </c>
+      <c r="F50">
+        <v>0.305</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -6477,28 +6489,28 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>137.5</v>
+        <v>1085.9</v>
       </c>
       <c r="L50">
-        <v>0.2137084239975132</v>
+        <v>0.2501266872437463</v>
       </c>
       <c r="M50">
-        <v>204.9</v>
+        <v>993.2</v>
       </c>
       <c r="N50">
-        <v>0.0423058658352776</v>
+        <v>0.06964643843877537</v>
       </c>
       <c r="O50">
-        <v>1.490181818181818</v>
+        <v>0.9146330232986463</v>
       </c>
       <c r="P50">
-        <v>204.9</v>
+        <v>993.2</v>
       </c>
       <c r="Q50">
-        <v>0.0423058658352776</v>
+        <v>0.06964643843877537</v>
       </c>
       <c r="R50">
-        <v>1.490181818181818</v>
+        <v>0.9146330232986463</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -6507,55 +6519,55 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>164.4</v>
+        <v>2355</v>
       </c>
       <c r="V50">
-        <v>0.033943798649681</v>
+        <v>0.1651403166767177</v>
       </c>
       <c r="W50">
-        <v>0.04623869253791573</v>
+        <v>0.07489482033243673</v>
       </c>
       <c r="X50">
-        <v>0.1003689204517235</v>
+        <v>0.1123342017694006</v>
       </c>
       <c r="Y50">
-        <v>-0.05413022791380773</v>
+        <v>-0.03743938143696386</v>
       </c>
       <c r="Z50">
-        <v>0.06723549666382773</v>
+        <v>0.07499434268963218</v>
       </c>
       <c r="AA50">
         <v>0</v>
       </c>
       <c r="AB50">
-        <v>0.07332052320308323</v>
+        <v>0.0618584246828965</v>
       </c>
       <c r="AC50">
-        <v>-0.07332052320308323</v>
+        <v>-0.0618584246828965</v>
       </c>
       <c r="AD50">
-        <v>5758.6</v>
+        <v>45119.8</v>
       </c>
       <c r="AE50">
         <v>0</v>
       </c>
       <c r="AF50">
-        <v>5758.6</v>
+        <v>45119.8</v>
       </c>
       <c r="AG50">
-        <v>5594.200000000001</v>
+        <v>42764.8</v>
       </c>
       <c r="AH50">
-        <v>0.5431667908582424</v>
+        <v>0.7598433153026924</v>
       </c>
       <c r="AI50">
-        <v>0.5959679589344483</v>
+        <v>0.7318987276065897</v>
       </c>
       <c r="AJ50">
-        <v>0.5359712574850301</v>
+        <v>0.7499254718073</v>
       </c>
       <c r="AK50">
-        <v>0.5889747531111158</v>
+        <v>0.7212502066025103</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -6572,7 +6584,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Guosen Securities Co., Ltd. (SZSE:002736)</t>
+          <t>GF Securities Co., Ltd. (SZSE:000776)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6581,13 +6593,16 @@
         </is>
       </c>
       <c r="D51">
-        <v>0.113</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="E51">
-        <v>0.109</v>
+        <v>0.0605</v>
+      </c>
+      <c r="F51">
+        <v>0.128</v>
       </c>
       <c r="G51">
-        <v>0.04423308111166113</v>
+        <v>0</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -6599,28 +6614,28 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>994.8</v>
+        <v>1165.6</v>
       </c>
       <c r="L51">
-        <v>0.3517431581924899</v>
+        <v>0.3488462574447071</v>
       </c>
       <c r="M51">
-        <v>1118.8</v>
+        <v>1114.1</v>
       </c>
       <c r="N51">
-        <v>0.090402236623087</v>
+        <v>0.07996181699430843</v>
       </c>
       <c r="O51">
-        <v>1.12464817048653</v>
+        <v>0.9558167467398765</v>
       </c>
       <c r="P51">
-        <v>1118.8</v>
+        <v>1114.1</v>
       </c>
       <c r="Q51">
-        <v>0.090402236623087</v>
+        <v>0.07996181699430843</v>
       </c>
       <c r="R51">
-        <v>1.12464817048653</v>
+        <v>0.9558167467398765</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -6629,55 +6644,55 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>1813.3</v>
+        <v>3088.8</v>
       </c>
       <c r="V51">
-        <v>0.1465198209408685</v>
+        <v>0.2216911052257606</v>
       </c>
       <c r="W51">
-        <v>0.06780030669620037</v>
+        <v>0.07020713997458183</v>
       </c>
       <c r="X51">
-        <v>0.1254199885356819</v>
+        <v>0.1133021676258827</v>
       </c>
       <c r="Y51">
-        <v>-0.0576196818394815</v>
+        <v>-0.04309502765130088</v>
       </c>
       <c r="Z51">
-        <v>0.06970660965654175</v>
+        <v>0.06095797779986088</v>
       </c>
       <c r="AA51">
         <v>0</v>
       </c>
       <c r="AB51">
-        <v>0.07385053193437451</v>
+        <v>0.06186399537090334</v>
       </c>
       <c r="AC51">
-        <v>-0.07385053193437451</v>
+        <v>-0.06186399537090334</v>
       </c>
       <c r="AD51">
-        <v>27415.6</v>
+        <v>44907.8</v>
       </c>
       <c r="AE51">
         <v>0</v>
       </c>
       <c r="AF51">
-        <v>27415.6</v>
+        <v>44907.8</v>
       </c>
       <c r="AG51">
-        <v>25602.3</v>
+        <v>41819</v>
       </c>
       <c r="AH51">
-        <v>0.6889830465879563</v>
+        <v>0.7632098190538181</v>
       </c>
       <c r="AI51">
-        <v>0.648754815565042</v>
+        <v>0.7017194609730487</v>
       </c>
       <c r="AJ51">
-        <v>0.6741332504785653</v>
+        <v>0.7500910282878251</v>
       </c>
       <c r="AK51">
-        <v>0.6330073803018877</v>
+        <v>0.6865928942010902</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -6703,10 +6718,10 @@
         </is>
       </c>
       <c r="D52">
-        <v>0.00743</v>
+        <v>0.0391</v>
       </c>
       <c r="E52">
-        <v>-0.0199</v>
+        <v>-0.0443</v>
       </c>
       <c r="F52">
         <v>-0.527</v>
@@ -6724,85 +6739,85 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>994.6</v>
+        <v>662.2</v>
       </c>
       <c r="L52">
-        <v>0.2570158664530466</v>
+        <v>0.1745341451200548</v>
       </c>
       <c r="M52">
-        <v>759.6</v>
+        <v>899.59</v>
       </c>
       <c r="N52">
-        <v>0.05325630473038821</v>
+        <v>0.06194243613578462</v>
       </c>
       <c r="O52">
-        <v>0.7637241101950533</v>
+        <v>1.358486861975234</v>
       </c>
       <c r="P52">
-        <v>759.6</v>
+        <v>897.5</v>
       </c>
       <c r="Q52">
-        <v>0.05325630473038821</v>
+        <v>0.06179852647524616</v>
       </c>
       <c r="R52">
-        <v>0.7637241101950533</v>
+        <v>1.355330715795832</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>2.090000000000032</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>0.002323280605609257</v>
       </c>
       <c r="U52">
-        <v>9644.799999999999</v>
+        <v>7151.6</v>
       </c>
       <c r="V52">
-        <v>0.6762064347862666</v>
+        <v>0.4924326929697721</v>
       </c>
       <c r="W52">
-        <v>0.03954624795728083</v>
+        <v>0.02868429943948228</v>
       </c>
       <c r="X52">
-        <v>0.1636276203374212</v>
+        <v>0.1203095201885622</v>
       </c>
       <c r="Y52">
-        <v>-0.1240813723801403</v>
+        <v>-0.09162522074907994</v>
       </c>
       <c r="Z52">
-        <v>0.054558399537569</v>
+        <v>0.05676408367469681</v>
       </c>
       <c r="AA52">
         <v>0</v>
       </c>
       <c r="AB52">
-        <v>0.07422067845813221</v>
+        <v>0.06190009438608617</v>
       </c>
       <c r="AC52">
-        <v>-0.07422067845813221</v>
+        <v>-0.06190009438608617</v>
       </c>
       <c r="AD52">
-        <v>53922</v>
+        <v>53033.8</v>
       </c>
       <c r="AE52">
         <v>0</v>
       </c>
       <c r="AF52">
-        <v>53922</v>
+        <v>53033.8</v>
       </c>
       <c r="AG52">
-        <v>44277.2</v>
+        <v>45882.2</v>
       </c>
       <c r="AH52">
-        <v>0.7908179352967143</v>
+        <v>0.7850253416384435</v>
       </c>
       <c r="AI52">
-        <v>0.6825604180274329</v>
+        <v>0.6822366186746801</v>
       </c>
       <c r="AJ52">
-        <v>0.7563541696916484</v>
+        <v>0.7595736790872309</v>
       </c>
       <c r="AK52">
-        <v>0.6384157981855618</v>
+        <v>0.6500405193274359</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -6819,7 +6834,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>China Galaxy Securities Co., Ltd. (SEHK:6881)</t>
+          <t>Zhongtai Securities Co., Ltd. (SHSE:600918)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6828,13 +6843,10 @@
         </is>
       </c>
       <c r="D53">
-        <v>0.248</v>
+        <v>0.0895</v>
       </c>
       <c r="E53">
-        <v>0.161</v>
-      </c>
-      <c r="F53">
-        <v>0.305</v>
+        <v>0.0858</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -6849,85 +6861,85 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>1331.1</v>
+        <v>213.2</v>
       </c>
       <c r="L53">
-        <v>0.2565481352992194</v>
+        <v>0.1413418191461151</v>
       </c>
       <c r="M53">
-        <v>1232.68</v>
+        <v>429.93</v>
       </c>
       <c r="N53">
-        <v>0.1175525929316625</v>
+        <v>0.06377174896539449</v>
       </c>
       <c r="O53">
-        <v>0.9260611524303207</v>
+        <v>2.01655722326454</v>
       </c>
       <c r="P53">
-        <v>1232.6</v>
+        <v>428.7</v>
       </c>
       <c r="Q53">
-        <v>0.11754496385726</v>
+        <v>0.06358930240147144</v>
       </c>
       <c r="R53">
-        <v>0.9260010517617009</v>
+        <v>2.01078799249531</v>
       </c>
       <c r="S53">
-        <v>0.07999999999992724</v>
+        <v>1.230000000000018</v>
       </c>
       <c r="T53">
-        <v>6.489924392374927e-05</v>
+        <v>0.002860930849208053</v>
       </c>
       <c r="U53">
-        <v>2475.3</v>
+        <v>1520.6</v>
       </c>
       <c r="V53">
-        <v>0.2360530983578417</v>
+        <v>0.2255514187816129</v>
       </c>
       <c r="W53">
-        <v>0.08922239575303809</v>
+        <v>0.04253790901835594</v>
       </c>
       <c r="X53">
-        <v>0.1784502065961737</v>
+        <v>0.09049345057036141</v>
       </c>
       <c r="Y53">
-        <v>-0.08922781084313564</v>
+        <v>-0.04795554155200547</v>
       </c>
       <c r="Z53">
-        <v>0.09875427059640841</v>
+        <v>0.08274817870622313</v>
       </c>
       <c r="AA53">
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>0.07430637330172779</v>
+        <v>0.0623242607116453</v>
       </c>
       <c r="AC53">
-        <v>-0.07430637330172779</v>
+        <v>-0.0623242607116453</v>
       </c>
       <c r="AD53">
-        <v>46011</v>
+        <v>12325.1</v>
       </c>
       <c r="AE53">
         <v>0</v>
       </c>
       <c r="AF53">
-        <v>46011</v>
+        <v>12325.1</v>
       </c>
       <c r="AG53">
-        <v>43535.7</v>
+        <v>10804.5</v>
       </c>
       <c r="AH53">
-        <v>0.8143943416664897</v>
+        <v>0.6464168082740681</v>
       </c>
       <c r="AI53">
-        <v>0.7603465029117614</v>
+        <v>0.6798329803194776</v>
       </c>
       <c r="AJ53">
-        <v>0.8058898335674977</v>
+        <v>0.6157743557009495</v>
       </c>
       <c r="AK53">
-        <v>0.7501253491253129</v>
+        <v>0.650520801974833</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -6944,7 +6956,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dongxing Securities Corporation Limited (SHSE:601198)</t>
+          <t>Orient Securities Company Limited (SHSE:600958)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6953,10 +6965,13 @@
         </is>
       </c>
       <c r="D54">
-        <v>0.107</v>
+        <v>0.153</v>
       </c>
       <c r="E54">
-        <v>-0.0294</v>
+        <v>0.162</v>
+      </c>
+      <c r="F54">
+        <v>0.123</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -6971,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>143.2</v>
+        <v>529.8</v>
       </c>
       <c r="L54">
-        <v>0.2344082501227697</v>
+        <v>0.1900150634818162</v>
       </c>
       <c r="M54">
-        <v>255.4</v>
+        <v>541.4</v>
       </c>
       <c r="N54">
-        <v>0.07058953594428015</v>
+        <v>0.0565218299125133</v>
       </c>
       <c r="O54">
-        <v>1.783519553072626</v>
+        <v>1.021895054737637</v>
       </c>
       <c r="P54">
-        <v>255.4</v>
+        <v>541.4</v>
       </c>
       <c r="Q54">
-        <v>0.07058953594428015</v>
+        <v>0.0565218299125133</v>
       </c>
       <c r="R54">
-        <v>1.783519553072626</v>
+        <v>1.021895054737637</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -7001,55 +7016,55 @@
         <v>0</v>
       </c>
       <c r="U54">
-        <v>591.5</v>
+        <v>2932.1</v>
       </c>
       <c r="V54">
-        <v>0.1634835963627318</v>
+        <v>0.3061094523207984</v>
       </c>
       <c r="W54">
-        <v>0.04219459013495196</v>
+        <v>0.04875804121149652</v>
       </c>
       <c r="X54">
-        <v>0.1162357275533082</v>
+        <v>0.09731709064644331</v>
       </c>
       <c r="Y54">
-        <v>-0.07404113741835627</v>
+        <v>-0.04855904943494679</v>
       </c>
       <c r="Z54">
-        <v>0.05693436099124875</v>
+        <v>0.1010415813540195</v>
       </c>
       <c r="AA54">
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>0.07472093728586207</v>
+        <v>0.06244546065765649</v>
       </c>
       <c r="AC54">
-        <v>-0.07472093728586207</v>
+        <v>-0.06244546065765649</v>
       </c>
       <c r="AD54">
-        <v>6653.7</v>
+        <v>21508.9</v>
       </c>
       <c r="AE54">
         <v>0</v>
       </c>
       <c r="AF54">
-        <v>6653.7</v>
+        <v>21508.9</v>
       </c>
       <c r="AG54">
-        <v>6062.2</v>
+        <v>18576.8</v>
       </c>
       <c r="AH54">
-        <v>0.6477637804474387</v>
+        <v>0.6918825894652192</v>
       </c>
       <c r="AI54">
-        <v>0.6407646379044684</v>
+        <v>0.6660360006069258</v>
       </c>
       <c r="AJ54">
-        <v>0.6262409222854664</v>
+        <v>0.659795279058369</v>
       </c>
       <c r="AK54">
-        <v>0.6190656114373244</v>
+        <v>0.6326860069886724</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -7066,7 +7081,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Orient Securities Company Limited (SHSE:600958)</t>
+          <t>Zhejiang Orient Financial Holdings Group Co., Ltd. (SHSE:600120)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7075,112 +7090,121 @@
         </is>
       </c>
       <c r="D55">
-        <v>0.144</v>
+        <v>0.151</v>
       </c>
       <c r="E55">
-        <v>-0.0009299999999999999</v>
-      </c>
-      <c r="F55">
-        <v>0.123</v>
+        <v>0.0861</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>0.02485203667169548</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>0.02479594599822057</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>-0.01431279254187459</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>-0.0121577413921037</v>
       </c>
       <c r="K55">
-        <v>429.1</v>
+        <v>144.4</v>
       </c>
       <c r="L55">
-        <v>0.1720115449370641</v>
+        <v>0.05585857413639705</v>
       </c>
       <c r="M55">
-        <v>702.2</v>
+        <v>60.05</v>
       </c>
       <c r="N55">
-        <v>0.06901635477276302</v>
+        <v>0.03472704140643072</v>
       </c>
       <c r="O55">
-        <v>1.636448380330925</v>
+        <v>0.4158587257617729</v>
       </c>
       <c r="P55">
-        <v>702.2</v>
+        <v>58.7</v>
       </c>
       <c r="Q55">
-        <v>0.06901635477276302</v>
+        <v>0.03394633356465417</v>
       </c>
       <c r="R55">
-        <v>1.636448380330925</v>
+        <v>0.4065096952908587</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.350000000000001</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>0.02248126561199003</v>
       </c>
       <c r="U55">
-        <v>3992.5</v>
+        <v>813.5</v>
       </c>
       <c r="V55">
-        <v>0.3924064318289039</v>
+        <v>0.4704487624334953</v>
       </c>
       <c r="W55">
-        <v>0.04372280698179151</v>
+        <v>0.07629312622179955</v>
       </c>
       <c r="X55">
-        <v>0.1210698213890453</v>
+        <v>0.06750847674848817</v>
       </c>
       <c r="Y55">
-        <v>-0.07734701440725383</v>
+        <v>0.008784649473311382</v>
       </c>
       <c r="Z55">
-        <v>0.08220141356379343</v>
+        <v>1.234173589229447</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>-0.01500476333081604</v>
       </c>
       <c r="AB55">
-        <v>0.0748405988370919</v>
+        <v>0.05920345576103128</v>
       </c>
       <c r="AC55">
-        <v>-0.0748405988370919</v>
+        <v>-0.07420821909184733</v>
       </c>
       <c r="AD55">
-        <v>20725.7</v>
+        <v>730.5</v>
       </c>
       <c r="AE55">
         <v>0</v>
       </c>
       <c r="AF55">
-        <v>20725.7</v>
+        <v>730.5</v>
       </c>
       <c r="AG55">
-        <v>16733.2</v>
+        <v>-83</v>
       </c>
       <c r="AH55">
-        <v>0.6707324571765141</v>
+        <v>0.2969874374923772</v>
       </c>
       <c r="AI55">
-        <v>0.6560135977767508</v>
+        <v>0.2308567455677401</v>
       </c>
       <c r="AJ55">
-        <v>0.6218763472030208</v>
+        <v>-0.05041914712671607</v>
       </c>
       <c r="AK55">
-        <v>0.6062555931147172</v>
+        <v>-0.03530712948783393</v>
       </c>
       <c r="AL55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AM55">
-        <v>0</v>
+        <v>-130.3</v>
+      </c>
+      <c r="AN55">
+        <v>-29.93852459016394</v>
+      </c>
+      <c r="AO55">
+        <v>-1.681818181818182</v>
+      </c>
+      <c r="AP55">
+        <v>3.401639344262295</v>
+      </c>
+      <c r="AQ55">
+        <v>0.283960092095165</v>
       </c>
     </row>
     <row r="56">
@@ -7191,7 +7215,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zhongtai Securities Co., Ltd. (SHSE:600918)</t>
+          <t>Top KingWin Ltd (NasdaqCM:TCJH)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7200,103 +7224,100 @@
         </is>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>-0.2030878859857482</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>-0.2030878859857482</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>-0.5094782218807299</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>-0.5094782218807299</v>
       </c>
       <c r="K56">
-        <v>222.6</v>
+        <v>-2.24</v>
       </c>
       <c r="L56">
-        <v>0.1391771914467925</v>
+        <v>-0.5320665083135393</v>
       </c>
       <c r="M56">
-        <v>399.7</v>
+        <v>-0</v>
       </c>
       <c r="N56">
-        <v>0.06171638564634674</v>
+        <v>-0</v>
       </c>
       <c r="O56">
-        <v>1.795597484276729</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>399.7</v>
+        <v>-0</v>
       </c>
       <c r="Q56">
-        <v>0.06171638564634674</v>
+        <v>-0</v>
       </c>
       <c r="R56">
-        <v>1.795597484276729</v>
+        <v>0</v>
       </c>
       <c r="S56">
         <v>0</v>
       </c>
-      <c r="T56">
-        <v>0</v>
-      </c>
       <c r="U56">
-        <v>1191.5</v>
+        <v>4.89</v>
       </c>
       <c r="V56">
-        <v>0.1839756654931752</v>
-      </c>
-      <c r="W56">
-        <v>0.04081408140814081</v>
+        <v>0.1880769230769231</v>
       </c>
       <c r="X56">
-        <v>0.1256513981578483</v>
-      </c>
-      <c r="Y56">
-        <v>-0.0848373167497075</v>
+        <v>0.06094037140195572</v>
       </c>
       <c r="Z56">
-        <v>0.08293492351568577</v>
+        <v>7.803282103830536</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>-3.975602291093302</v>
       </c>
       <c r="AB56">
-        <v>0.07494044374753173</v>
+        <v>0.06063472052685173</v>
       </c>
       <c r="AC56">
-        <v>-0.07494044374753173</v>
+        <v>-4.036237011620154</v>
       </c>
       <c r="AD56">
-        <v>14408.3</v>
+        <v>0</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>0.539516570589363</v>
       </c>
       <c r="AF56">
-        <v>14408.3</v>
+        <v>0.539516570589363</v>
       </c>
       <c r="AG56">
-        <v>13216.8</v>
+        <v>-4.350483429410636</v>
       </c>
       <c r="AH56">
-        <v>0.6898973889976874</v>
+        <v>0.02032880173813136</v>
       </c>
       <c r="AI56">
-        <v>0.7342183041174072</v>
+        <v>0.05789104686953137</v>
       </c>
       <c r="AJ56">
-        <v>0.6711352141856073</v>
+        <v>-0.2009506039188294</v>
       </c>
       <c r="AK56">
-        <v>0.7170378407703784</v>
+        <v>-0.9821576147375806</v>
       </c>
       <c r="AL56">
         <v>0</v>
       </c>
       <c r="AM56">
         <v>0</v>
+      </c>
+      <c r="AN56">
+        <v>-0</v>
+      </c>
+      <c r="AP56">
+        <v>2.223037010429553</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/china/china_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06005000000000001</v>
+        <v>0.0383</v>
       </c>
       <c r="E2">
-        <v>0.0581</v>
+        <v>0.06115</v>
       </c>
       <c r="F2">
-        <v>0.1505</v>
+        <v>0.126</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.001639819298230363</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>-0.0003767034966777649</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-0.0006533967555858819</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-0.0005733229843491533</v>
       </c>
       <c r="K2">
-        <v>8927.299999999999</v>
+        <v>15620.951</v>
       </c>
       <c r="L2">
-        <v>0.2419401172937873</v>
+        <v>0.215548236744763</v>
       </c>
       <c r="M2">
-        <v>7093.791999999999</v>
+        <v>15191.0792</v>
       </c>
       <c r="N2">
-        <v>0.03508872107408072</v>
+        <v>0.03697618868540854</v>
       </c>
       <c r="O2">
-        <v>0.7946178575829198</v>
+        <v>0.9724810736555028</v>
       </c>
       <c r="P2">
-        <v>6991.2</v>
+        <v>14399.8872</v>
       </c>
       <c r="Q2">
-        <v>0.03458126017412311</v>
+        <v>0.03505036996685523</v>
       </c>
       <c r="R2">
-        <v>0.7831259171305994</v>
+        <v>0.9218316605691933</v>
       </c>
       <c r="S2">
-        <v>102.592</v>
+        <v>791.192</v>
       </c>
       <c r="T2">
-        <v>0.01446222274349177</v>
+        <v>0.05208267230941696</v>
       </c>
       <c r="U2">
-        <v>85809.89999999999</v>
+        <v>134923.2</v>
       </c>
       <c r="V2">
-        <v>0.4244499481370132</v>
+        <v>0.3284128557001476</v>
       </c>
       <c r="W2">
-        <v>0.06106914139799205</v>
+        <v>0.044414592760181</v>
       </c>
       <c r="X2">
-        <v>0.1013511596167442</v>
+        <v>0.09032460094220733</v>
       </c>
       <c r="Y2">
-        <v>-0.04028201821875219</v>
+        <v>-0.04591000818202633</v>
       </c>
       <c r="Z2">
-        <v>0.07365275978560434</v>
+        <v>0.08070443120900819</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06446006584058689</v>
+        <v>0.06385599289370902</v>
       </c>
       <c r="AC2">
-        <v>-0.06446006584058689</v>
+        <v>-0.06393409502403108</v>
       </c>
       <c r="AD2">
-        <v>445981.9</v>
+        <v>749881.8</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>10.91089530372885</v>
       </c>
       <c r="AF2">
-        <v>445981.9</v>
+        <v>749892.7108953038</v>
       </c>
       <c r="AG2">
-        <v>360172</v>
+        <v>614969.5108953038</v>
       </c>
       <c r="AH2">
-        <v>0.6880852433359479</v>
+        <v>0.6460544409385088</v>
       </c>
       <c r="AI2">
-        <v>0.6954656760504804</v>
+        <v>0.6727948296241539</v>
       </c>
       <c r="AJ2">
-        <v>0.6404887582994822</v>
+        <v>0.5995002399714395</v>
       </c>
       <c r="AK2">
-        <v>0.6484199610773753</v>
+        <v>0.6277311272168301</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-1013.9</v>
+      </c>
+      <c r="AN2">
+        <v>-30999.66101694916</v>
+      </c>
+      <c r="AO2">
+        <v>-1.780357142857143</v>
+      </c>
+      <c r="AP2">
+        <v>-25422.46841237304</v>
+      </c>
+      <c r="AQ2">
+        <v>0.04916658447578658</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>China International Capital Corporation Limited (SEHK:3908)</t>
+          <t>SDIC Capital Co.,Ltd (SHSE:600061)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,16 +725,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0898</v>
+        <v>0.0805</v>
       </c>
       <c r="E3">
-        <v>0.0242</v>
-      </c>
-      <c r="F3">
-        <v>0.16</v>
+        <v>-0.0793</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.003183210002551672</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -734,91 +743,94 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>628.2</v>
+        <v>286.5</v>
       </c>
       <c r="L3">
-        <v>0.2069374444115031</v>
+        <v>0.1827634600663435</v>
       </c>
       <c r="M3">
-        <v>221.2</v>
+        <v>496.2</v>
       </c>
       <c r="N3">
-        <v>0.01329638557113747</v>
+        <v>0.07538512959192975</v>
       </c>
       <c r="O3">
-        <v>0.3521171601400827</v>
+        <v>1.731937172774869</v>
       </c>
       <c r="P3">
-        <v>221.2</v>
+        <v>491.2</v>
       </c>
       <c r="Q3">
-        <v>0.01329638557113747</v>
+        <v>0.07462550515025372</v>
       </c>
       <c r="R3">
-        <v>0.3521171601400827</v>
+        <v>1.714485165794066</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.01007658202337767</v>
       </c>
       <c r="U3">
-        <v>7826.7</v>
+        <v>10465.4</v>
       </c>
       <c r="V3">
-        <v>0.4704648325028102</v>
+        <v>1.589954726383276</v>
       </c>
       <c r="W3">
-        <v>0.044414592760181</v>
+        <v>0.03929933335162273</v>
       </c>
       <c r="X3">
-        <v>0.1050886792535654</v>
+        <v>0.1047337815461891</v>
       </c>
       <c r="Y3">
-        <v>-0.06067408649338438</v>
+        <v>-0.0654344481945664</v>
       </c>
       <c r="Z3">
-        <v>0.06779142474318892</v>
+        <v>0.07770359024690071</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06380245954346846</v>
+        <v>0.061331820838932</v>
       </c>
       <c r="AC3">
-        <v>-0.06380245954346846</v>
+        <v>-0.061331820838932</v>
       </c>
       <c r="AD3">
-        <v>42230.1</v>
+        <v>16567.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>42230.1</v>
+        <v>16567.3</v>
       </c>
       <c r="AG3">
-        <v>34403.4</v>
+        <v>6101.9</v>
       </c>
       <c r="AH3">
-        <v>0.7173913043478261</v>
+        <v>0.7156655651309963</v>
       </c>
       <c r="AI3">
-        <v>0.7308268724906548</v>
+        <v>0.6587709950375366</v>
       </c>
       <c r="AJ3">
-        <v>0.6740544088402121</v>
+        <v>0.4810668474704551</v>
       </c>
       <c r="AK3">
-        <v>0.6886561123199212</v>
+        <v>0.4155645150305787</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-190.5</v>
+      </c>
+      <c r="AQ3">
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Guotai Junan Securities Co., Ltd. (SHSE:601211)</t>
+          <t>Industrial Securities Co.,Ltd. (SHSE:601377)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,16 +850,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0809</v>
+        <v>-0.0308</v>
       </c>
       <c r="E4">
-        <v>0.0581</v>
-      </c>
-      <c r="F4">
-        <v>0.169</v>
+        <v>0.0796</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.00178867174561113</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -859,85 +868,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1464.1</v>
+        <v>242.8</v>
       </c>
       <c r="L4">
-        <v>0.2731020332027607</v>
+        <v>0.1608479629016231</v>
       </c>
       <c r="M4">
-        <v>1449.892</v>
+        <v>385.8</v>
       </c>
       <c r="N4">
-        <v>0.06867392612029725</v>
+        <v>0.05208867766586558</v>
       </c>
       <c r="O4">
-        <v>0.990295744826173</v>
+        <v>1.588962108731466</v>
       </c>
       <c r="P4">
-        <v>1449.1</v>
+        <v>385.8</v>
       </c>
       <c r="Q4">
-        <v>0.06863641315416787</v>
+        <v>0.05208867766586558</v>
       </c>
       <c r="R4">
-        <v>0.9897547981695239</v>
+        <v>1.588962108731466</v>
       </c>
       <c r="S4">
-        <v>0.7919999999999163</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.0005462475825785068</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>3471.3</v>
+        <v>1966.5</v>
       </c>
       <c r="V4">
-        <v>0.1644176254102981</v>
+        <v>0.265506440201982</v>
       </c>
       <c r="W4">
-        <v>0.06439029109988169</v>
+        <v>0.03346795870263416</v>
       </c>
       <c r="X4">
-        <v>0.1025862775619267</v>
+        <v>0.1026386940779198</v>
       </c>
       <c r="Y4">
-        <v>-0.03819598646204499</v>
+        <v>-0.06917073537528567</v>
       </c>
       <c r="Z4">
-        <v>0.08044029847387002</v>
+        <v>0.07008699237423807</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06384852069466584</v>
+        <v>0.06141027715677798</v>
       </c>
       <c r="AC4">
-        <v>-0.06384852069466584</v>
+        <v>-0.06141027715677798</v>
       </c>
       <c r="AD4">
-        <v>50143.6</v>
+        <v>17628.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>50143.6</v>
+        <v>17628.5</v>
       </c>
       <c r="AG4">
-        <v>46672.3</v>
+        <v>15662</v>
       </c>
       <c r="AH4">
-        <v>0.7037076019944902</v>
+        <v>0.7041513714744499</v>
       </c>
       <c r="AI4">
-        <v>0.6703456831714405</v>
+        <v>0.6666351535319921</v>
       </c>
       <c r="AJ4">
-        <v>0.6885343365051264</v>
+        <v>0.6789315346401602</v>
       </c>
       <c r="AK4">
-        <v>0.6543032301388031</v>
+        <v>0.6398529261566746</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CITIC Securities Company Limited (SHSE:600030)</t>
+          <t>China Merchants Securities Co., Ltd. (SHSE:600999)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +972,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.07200000000000001</v>
+        <v>0.0305</v>
       </c>
       <c r="E5">
-        <v>0.098</v>
+        <v>0.0902</v>
       </c>
       <c r="F5">
-        <v>0.141</v>
+        <v>0.0842</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,28 +993,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2866.3</v>
+        <v>1356</v>
       </c>
       <c r="L5">
-        <v>0.3277569409504643</v>
+        <v>0.5004059340172706</v>
       </c>
       <c r="M5">
-        <v>1886.8</v>
+        <v>1216.8</v>
       </c>
       <c r="N5">
-        <v>0.03371736244020207</v>
+        <v>0.05503914890152389</v>
       </c>
       <c r="O5">
-        <v>0.6582702438684017</v>
+        <v>0.8973451327433628</v>
       </c>
       <c r="P5">
-        <v>1886.8</v>
+        <v>1216.8</v>
       </c>
       <c r="Q5">
-        <v>0.03371736244020207</v>
+        <v>0.05503914890152389</v>
       </c>
       <c r="R5">
-        <v>0.6582702438684017</v>
+        <v>0.8973451327433628</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1014,55 +1023,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>49607.7</v>
+        <v>2349.7</v>
       </c>
       <c r="V5">
-        <v>0.8864960783998369</v>
+        <v>0.1062832743046603</v>
       </c>
       <c r="W5">
-        <v>0.07968584931887684</v>
+        <v>0.0827601359805184</v>
       </c>
       <c r="X5">
-        <v>0.09244234167733545</v>
+        <v>0.09737547078852775</v>
       </c>
       <c r="Y5">
-        <v>-0.0127564923584586</v>
+        <v>-0.01461533480800935</v>
       </c>
       <c r="Z5">
-        <v>0.1287757527208686</v>
+        <v>0.04782539864352923</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06409208430349284</v>
+        <v>0.0616385799849808</v>
       </c>
       <c r="AC5">
-        <v>-0.06409208430349284</v>
+        <v>-0.0616385799849808</v>
       </c>
       <c r="AD5">
-        <v>95836.10000000001</v>
+        <v>45017.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>95836.10000000001</v>
+        <v>45017.1</v>
       </c>
       <c r="AG5">
-        <v>46228.40000000001</v>
+        <v>42667.4</v>
       </c>
       <c r="AH5">
-        <v>0.6313504888817447</v>
+        <v>0.6706458100558659</v>
       </c>
       <c r="AI5">
-        <v>0.6971987242722911</v>
+        <v>0.7146989482040087</v>
       </c>
       <c r="AJ5">
-        <v>0.4523871268264185</v>
+        <v>0.6586986088833243</v>
       </c>
       <c r="AK5">
-        <v>0.5262131037630718</v>
+        <v>0.7036436018457134</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CSC Financial Co., Ltd. (SEHK:6066)</t>
+          <t>Caitong Securities Co.,Ltd. (SHSE:601108)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,13 +1097,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0992</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="E6">
-        <v>0.0362</v>
-      </c>
-      <c r="F6">
-        <v>0.115</v>
+        <v>0.143</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,28 +1115,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>804.1</v>
+        <v>316.9</v>
       </c>
       <c r="L6">
-        <v>0.2656601030791595</v>
+        <v>0.379611883085769</v>
       </c>
       <c r="M6">
-        <v>367</v>
+        <v>227.7</v>
       </c>
       <c r="N6">
-        <v>0.0149734802121583</v>
+        <v>0.04380699526722844</v>
       </c>
       <c r="O6">
-        <v>0.4564108941673921</v>
+        <v>0.7185231934364152</v>
       </c>
       <c r="P6">
-        <v>367</v>
+        <v>227.7</v>
       </c>
       <c r="Q6">
-        <v>0.0149734802121583</v>
+        <v>0.04380699526722844</v>
       </c>
       <c r="R6">
-        <v>0.4564108941673921</v>
+        <v>0.7185231934364152</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,55 +1145,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3802</v>
+        <v>885.6</v>
       </c>
       <c r="V6">
-        <v>0.1551203590371277</v>
+        <v>0.1703797760591019</v>
       </c>
       <c r="W6">
-        <v>0.06083739369911933</v>
+        <v>0.06830330200879385</v>
       </c>
       <c r="X6">
-        <v>0.09151187111071916</v>
+        <v>0.09405793556274078</v>
       </c>
       <c r="Y6">
-        <v>-0.03067447741159984</v>
+        <v>-0.02575463355394693</v>
       </c>
       <c r="Z6">
-        <v>0.06617055510860821</v>
+        <v>0.06843352160476115</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06412051848344977</v>
+        <v>0.06181109753984126</v>
       </c>
       <c r="AC6">
-        <v>-0.06412051848344977</v>
+        <v>-0.06181109753984126</v>
       </c>
       <c r="AD6">
-        <v>40486.6</v>
+        <v>9457.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>40486.6</v>
+        <v>9457.4</v>
       </c>
       <c r="AG6">
-        <v>36684.6</v>
+        <v>8571.799999999999</v>
       </c>
       <c r="AH6">
-        <v>0.6229033518676361</v>
+        <v>0.6453272558545772</v>
       </c>
       <c r="AI6">
-        <v>0.7372285236164196</v>
+        <v>0.6501405817126908</v>
       </c>
       <c r="AJ6">
-        <v>0.599474463433048</v>
+        <v>0.6225162677201952</v>
       </c>
       <c r="AK6">
-        <v>0.7176833550815509</v>
+        <v>0.6274604534041914</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GF Securities Co., Ltd. (SZSE:000776)</t>
+          <t>China Great Wall Securities Co.,Ltd. (SZSE:002939)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1213,13 +1219,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0254</v>
+        <v>0.0192</v>
       </c>
       <c r="E7">
-        <v>0.0645</v>
-      </c>
-      <c r="F7">
-        <v>0.137</v>
+        <v>0.0925</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,28 +1237,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1130.8</v>
+        <v>188.7</v>
       </c>
       <c r="L7">
-        <v>0.3393961222162195</v>
+        <v>0.3602520045819015</v>
       </c>
       <c r="M7">
-        <v>498.1</v>
+        <v>205.8</v>
       </c>
       <c r="N7">
-        <v>0.03230011023928409</v>
+        <v>0.04540640720148267</v>
       </c>
       <c r="O7">
-        <v>0.440484612663601</v>
+        <v>1.090620031796502</v>
       </c>
       <c r="P7">
-        <v>498.1</v>
+        <v>205.8</v>
       </c>
       <c r="Q7">
-        <v>0.03230011023928409</v>
+        <v>0.04540640720148267</v>
       </c>
       <c r="R7">
-        <v>0.440484612663601</v>
+        <v>1.090620031796502</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1264,55 +1267,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3733.8</v>
+        <v>343.4</v>
       </c>
       <c r="V7">
-        <v>0.2421243758511121</v>
+        <v>0.07576559879975289</v>
       </c>
       <c r="W7">
-        <v>0.06135315501058</v>
+        <v>0.04852895792613928</v>
       </c>
       <c r="X7">
-        <v>0.1209284177645273</v>
+        <v>0.09400051083949267</v>
       </c>
       <c r="Y7">
-        <v>-0.05957526275394728</v>
+        <v>-0.04547155291335338</v>
       </c>
       <c r="Z7">
-        <v>0.05529988427821203</v>
+        <v>0.04447293459388093</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06440765644869881</v>
+        <v>0.06181431756716432</v>
       </c>
       <c r="AC7">
-        <v>-0.06440765644869881</v>
+        <v>-0.06181431756716432</v>
       </c>
       <c r="AD7">
-        <v>55097.1</v>
+        <v>8229.700000000001</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>55097.1</v>
+        <v>8229.700000000001</v>
       </c>
       <c r="AG7">
-        <v>51363.3</v>
+        <v>7886.300000000001</v>
       </c>
       <c r="AH7">
-        <v>0.7813185550943658</v>
+        <v>0.6448546869245657</v>
       </c>
       <c r="AI7">
-        <v>0.72296607522917</v>
+        <v>0.6584076035649711</v>
       </c>
       <c r="AJ7">
-        <v>0.7690924363959794</v>
+        <v>0.6350342628455475</v>
       </c>
       <c r="AK7">
-        <v>0.7086939124675754</v>
+        <v>0.648757815070747</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1329,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Haitong Securities Co., Ltd. (SHSE:600837)</t>
+          <t>Zheshang Securities Co., Ltd. (SHSE:601878)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,13 +1341,16 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.168</v>
+        <v>0.266</v>
+      </c>
+      <c r="E8">
+        <v>0.138</v>
       </c>
       <c r="F8">
-        <v>0.878</v>
+        <v>0.105</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.003343414674566019</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1356,85 +1362,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>-572.1</v>
+        <v>240.7</v>
       </c>
       <c r="L8">
-        <v>-0.3231473113420696</v>
+        <v>0.09972241786468906</v>
       </c>
       <c r="M8">
-        <v>242.7</v>
+        <v>238.4</v>
       </c>
       <c r="N8">
-        <v>0.01379133992499148</v>
+        <v>0.03159122230467507</v>
       </c>
       <c r="O8">
-        <v>-0.4242265338227582</v>
+        <v>0.9904445367677607</v>
       </c>
       <c r="P8">
-        <v>183.6</v>
+        <v>180.6</v>
       </c>
       <c r="Q8">
-        <v>0.01043300375042618</v>
+        <v>0.02393194105798791</v>
       </c>
       <c r="R8">
-        <v>-0.3209229155742003</v>
+        <v>0.7503115911923557</v>
       </c>
       <c r="S8">
-        <v>59.09999999999999</v>
+        <v>57.79999999999998</v>
       </c>
       <c r="T8">
-        <v>0.2435105067985167</v>
+        <v>0.2424496644295301</v>
       </c>
       <c r="U8">
-        <v>8806</v>
+        <v>1031.7</v>
       </c>
       <c r="V8">
-        <v>0.5003977724741447</v>
+        <v>0.1367141948478745</v>
       </c>
       <c r="W8">
-        <v>-0.02499945377875855</v>
+        <v>0.06606285165362975</v>
       </c>
       <c r="X8">
-        <v>0.1089217544896107</v>
+        <v>0.08232255506812552</v>
       </c>
       <c r="Y8">
-        <v>-0.1339212082683692</v>
+        <v>-0.01625970341449577</v>
       </c>
       <c r="Z8">
-        <v>0.02593981271877193</v>
+        <v>0.2450337445484889</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06451247523247496</v>
+        <v>0.0627137207444198</v>
       </c>
       <c r="AC8">
-        <v>-0.06451247523247496</v>
+        <v>-0.0627137207444198</v>
       </c>
       <c r="AD8">
-        <v>49076.9</v>
+        <v>7944.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>49076.9</v>
+        <v>7944.8</v>
       </c>
       <c r="AG8">
-        <v>40270.9</v>
+        <v>6913.1</v>
       </c>
       <c r="AH8">
-        <v>0.7360625962693608</v>
+        <v>0.5128589134476348</v>
       </c>
       <c r="AI8">
-        <v>0.6700842027364866</v>
+        <v>0.655684669219596</v>
       </c>
       <c r="AJ8">
-        <v>0.695898833397559</v>
+        <v>0.4781009025208341</v>
       </c>
       <c r="AK8">
-        <v>0.6249955380630382</v>
+        <v>0.6236389387556269</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>China Galaxy Securities Co., Ltd. (SEHK:6881)</t>
+          <t>Guangzhou Yuexiu Capital Holdings Group Co., Ltd. (SZSE:000987)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1460,16 +1466,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.184</v>
+        <v>0.0803</v>
       </c>
       <c r="E9">
-        <v>0.111</v>
-      </c>
-      <c r="F9">
-        <v>0.113</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.0008111006837377664</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1481,28 +1484,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1174.6</v>
+        <v>294</v>
       </c>
       <c r="L9">
-        <v>0.2272525006287848</v>
+        <v>0.1970773562139697</v>
       </c>
       <c r="M9">
-        <v>581.6</v>
+        <v>574.1</v>
       </c>
       <c r="N9">
-        <v>0.03146692348062263</v>
+        <v>0.1189770584212381</v>
       </c>
       <c r="O9">
-        <v>0.4951472841818492</v>
+        <v>1.952721088435374</v>
       </c>
       <c r="P9">
-        <v>581.6</v>
+        <v>574.1</v>
       </c>
       <c r="Q9">
-        <v>0.03146692348062263</v>
+        <v>0.1189770584212381</v>
       </c>
       <c r="R9">
-        <v>0.4951472841818492</v>
+        <v>1.952721088435374</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1511,61 +1514,64 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>2215.6</v>
+        <v>2535.6</v>
       </c>
       <c r="V9">
-        <v>0.1198729636583004</v>
+        <v>0.5254802810187967</v>
       </c>
       <c r="W9">
-        <v>0.07108190213378841</v>
+        <v>0.07585922179791517</v>
       </c>
       <c r="X9">
-        <v>0.1033425199911188</v>
+        <v>0.1292167737833048</v>
       </c>
       <c r="Y9">
-        <v>-0.03226061785733041</v>
+        <v>-0.05335755198538962</v>
       </c>
       <c r="Z9">
-        <v>0.08738632271415456</v>
+        <v>0.08314569167316911</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06457751682313936</v>
+        <v>0.06283809546830847</v>
       </c>
       <c r="AC9">
-        <v>-0.06457751682313936</v>
+        <v>-0.06283809546830847</v>
       </c>
       <c r="AD9">
-        <v>44810.5</v>
+        <v>19863.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>44810.5</v>
+        <v>19863.5</v>
       </c>
       <c r="AG9">
-        <v>42594.9</v>
+        <v>17327.9</v>
       </c>
       <c r="AH9">
-        <v>0.7079806109325775</v>
+        <v>0.8045551019085577</v>
       </c>
       <c r="AI9">
-        <v>0.6969157815992024</v>
+        <v>0.7642041519828873</v>
       </c>
       <c r="AJ9">
-        <v>0.6973875941831565</v>
+        <v>0.7821849665059676</v>
       </c>
       <c r="AK9">
-        <v>0.6860993481275782</v>
+        <v>0.7387154258040312</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-486.9</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1576,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guosen Securities Co., Ltd. (SZSE:002736)</t>
+          <t>Nanjing Securities Co., Ltd. (SHSE:601990)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,10 +1591,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0481</v>
+        <v>0.0906</v>
       </c>
       <c r="E10">
-        <v>0.0424</v>
+        <v>0.0413</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1597,34 +1603,34 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.00494077259331875</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.003874852861517283</v>
       </c>
       <c r="K10">
-        <v>917</v>
+        <v>114.8</v>
       </c>
       <c r="L10">
-        <v>0.3751892312098523</v>
+        <v>0.2633631566873136</v>
       </c>
       <c r="M10">
-        <v>937</v>
+        <v>104.4</v>
       </c>
       <c r="N10">
-        <v>0.0635271464988881</v>
+        <v>0.0238699499279786</v>
       </c>
       <c r="O10">
-        <v>1.021810250817884</v>
+        <v>0.9094076655052266</v>
       </c>
       <c r="P10">
-        <v>937</v>
+        <v>104.4</v>
       </c>
       <c r="Q10">
-        <v>0.0635271464988881</v>
+        <v>0.0238699499279786</v>
       </c>
       <c r="R10">
-        <v>1.021810250817884</v>
+        <v>0.9094076655052266</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1633,61 +1639,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1450.9</v>
+        <v>139.1</v>
       </c>
       <c r="V10">
-        <v>0.09836876932255791</v>
+        <v>0.03180373596725884</v>
       </c>
       <c r="W10">
-        <v>0.06130088909686476</v>
+        <v>0.04945930808668304</v>
       </c>
       <c r="X10">
-        <v>0.1001160416715618</v>
+        <v>0.07715549473276374</v>
       </c>
       <c r="Y10">
-        <v>-0.03881515257469703</v>
+        <v>-0.02769618664608071</v>
       </c>
       <c r="Z10">
-        <v>0.05720204954702465</v>
+        <v>0.07612736365607867</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.0002949823329025232</v>
       </c>
       <c r="AB10">
-        <v>0.06462186086296243</v>
+        <v>0.06336701180743425</v>
       </c>
       <c r="AC10">
-        <v>-0.06462186086296243</v>
+        <v>-0.06307202947453172</v>
       </c>
       <c r="AD10">
-        <v>32651.6</v>
+        <v>3117.8</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>10.33158613286178</v>
       </c>
       <c r="AF10">
-        <v>32651.6</v>
+        <v>3128.131586132862</v>
       </c>
       <c r="AG10">
-        <v>31200.7</v>
+        <v>2989.031586132862</v>
       </c>
       <c r="AH10">
-        <v>0.688834881817338</v>
+        <v>0.4169823795984989</v>
       </c>
       <c r="AI10">
-        <v>0.6670643660032443</v>
+        <v>0.5524360936728259</v>
       </c>
       <c r="AJ10">
-        <v>0.6790097126678172</v>
+        <v>0.4059677513930391</v>
       </c>
       <c r="AK10">
-        <v>0.6568941813534664</v>
+        <v>0.5411646104386103</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>738.8151658767773</v>
+      </c>
+      <c r="AP10">
+        <v>708.3013237281665</v>
       </c>
     </row>
     <row r="11">
@@ -1698,7 +1710,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Orient Securities Company Limited (SHSE:600958)</t>
+          <t>Soochow Securities Co., Ltd. (SHSE:601555)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1707,13 +1719,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.00062</v>
+        <v>0.182</v>
       </c>
       <c r="E11">
-        <v>0.0911</v>
-      </c>
-      <c r="F11">
-        <v>0.26</v>
+        <v>0.138</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1728,85 +1737,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>456</v>
+        <v>297.7</v>
       </c>
       <c r="L11">
-        <v>0.1838709677419355</v>
+        <v>0.1789815427162869</v>
       </c>
       <c r="M11">
-        <v>586</v>
+        <v>286.9</v>
       </c>
       <c r="N11">
-        <v>0.05129013058852361</v>
+        <v>0.0540331845490329</v>
       </c>
       <c r="O11">
-        <v>1.285087719298246</v>
+        <v>0.9637218676519986</v>
       </c>
       <c r="P11">
-        <v>543.3</v>
+        <v>286.9</v>
       </c>
       <c r="Q11">
-        <v>0.0475527780695305</v>
+        <v>0.0540331845490329</v>
       </c>
       <c r="R11">
-        <v>1.191447368421052</v>
+        <v>0.9637218676519986</v>
       </c>
       <c r="S11">
-        <v>42.70000000000005</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>0.07286689419795229</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>3135.4</v>
+        <v>380.7</v>
       </c>
       <c r="V11">
-        <v>0.2744284563946364</v>
+        <v>0.07169896604327929</v>
       </c>
       <c r="W11">
-        <v>0.04228761139910788</v>
+        <v>0.05514188338149218</v>
       </c>
       <c r="X11">
-        <v>0.09809760209895126</v>
+        <v>0.1032908913927763</v>
       </c>
       <c r="Y11">
-        <v>-0.05580999069984337</v>
+        <v>-0.04814900801128417</v>
       </c>
       <c r="Z11">
-        <v>0.08448103775416699</v>
+        <v>0.1061936167631792</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06566597461610799</v>
+        <v>0.0632432465750494</v>
       </c>
       <c r="AC11">
-        <v>-0.06566597461610799</v>
+        <v>-0.0632432465750494</v>
       </c>
       <c r="AD11">
-        <v>23786.3</v>
+        <v>12863.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>23786.3</v>
+        <v>12863.9</v>
       </c>
       <c r="AG11">
-        <v>20650.9</v>
+        <v>12483.2</v>
       </c>
       <c r="AH11">
-        <v>0.6755264615253539</v>
+        <v>0.7078344411674077</v>
       </c>
       <c r="AI11">
-        <v>0.6724080418829222</v>
+        <v>0.6873099918253074</v>
       </c>
       <c r="AJ11">
-        <v>0.643809565377337</v>
+        <v>0.7015832157770796</v>
       </c>
       <c r="AK11">
-        <v>0.6405485213744673</v>
+        <v>0.6808176443639695</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1823,118 +1832,5632 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Minmetals Capital Company Limited (SHSE:600390)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>-0.108</v>
+      </c>
+      <c r="E12">
+        <v>-0.14</v>
+      </c>
+      <c r="G12">
+        <v>0.008007713386785751</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>215.1</v>
+      </c>
+      <c r="L12">
+        <v>0.2183091444230184</v>
+      </c>
+      <c r="M12">
+        <v>669.1582000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.168350155982691</v>
+      </c>
+      <c r="O12">
+        <v>3.110916782891679</v>
+      </c>
+      <c r="P12">
+        <v>98.95820000000001</v>
+      </c>
+      <c r="Q12">
+        <v>0.02489639730300896</v>
+      </c>
+      <c r="R12">
+        <v>0.4600567178056718</v>
+      </c>
+      <c r="S12">
+        <v>570.2</v>
+      </c>
+      <c r="T12">
+        <v>0.8521153891561069</v>
+      </c>
+      <c r="U12">
+        <v>3370.5</v>
+      </c>
+      <c r="V12">
+        <v>0.8479671933179027</v>
+      </c>
+      <c r="W12">
+        <v>0.03735023441569717</v>
+      </c>
+      <c r="X12">
+        <v>0.1022191517888391</v>
+      </c>
+      <c r="Y12">
+        <v>-0.06486891737314192</v>
+      </c>
+      <c r="Z12">
+        <v>0.07187249252315997</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.06326880617898015</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06326880617898015</v>
+      </c>
+      <c r="AD12">
+        <v>9351.5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>9351.5</v>
+      </c>
+      <c r="AG12">
+        <v>5981</v>
+      </c>
+      <c r="AH12">
+        <v>0.7017326639802496</v>
+      </c>
+      <c r="AI12">
+        <v>0.5117659935423849</v>
+      </c>
+      <c r="AJ12">
+        <v>0.600755338596597</v>
+      </c>
+      <c r="AK12">
+        <v>0.4013420567018957</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-81.09999999999999</v>
+      </c>
+      <c r="AQ12">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Guoyuan Securities Company Limited (SZSE:000728)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.156</v>
+      </c>
+      <c r="E13">
+        <v>0.141</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>286.7</v>
+      </c>
+      <c r="L13">
+        <v>0.3112582781456953</v>
+      </c>
+      <c r="M13">
+        <v>243.4</v>
+      </c>
+      <c r="N13">
+        <v>0.04869947979191677</v>
+      </c>
+      <c r="O13">
+        <v>0.8489710498779213</v>
+      </c>
+      <c r="P13">
+        <v>243.4</v>
+      </c>
+      <c r="Q13">
+        <v>0.04869947979191677</v>
+      </c>
+      <c r="R13">
+        <v>0.8489710498779213</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>440</v>
+      </c>
+      <c r="V13">
+        <v>0.08803521408563425</v>
+      </c>
+      <c r="W13">
+        <v>0.06139054838226161</v>
+      </c>
+      <c r="X13">
+        <v>0.1004720770409267</v>
+      </c>
+      <c r="Y13">
+        <v>-0.03908152865866506</v>
+      </c>
+      <c r="Z13">
+        <v>0.06546134220270203</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.06331284097350602</v>
+      </c>
+      <c r="AC13">
+        <v>-0.06331284097350602</v>
+      </c>
+      <c r="AD13">
+        <v>11188.3</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>11188.3</v>
+      </c>
+      <c r="AG13">
+        <v>10748.3</v>
+      </c>
+      <c r="AH13">
+        <v>0.6912203530145864</v>
+      </c>
+      <c r="AI13">
+        <v>0.6882481760805108</v>
+      </c>
+      <c r="AJ13">
+        <v>0.6825921010015051</v>
+      </c>
+      <c r="AK13">
+        <v>0.6795753720868477</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Northeast Securities Co., Ltd. (SZSE:000686)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>-0.0605</v>
+      </c>
+      <c r="E14">
+        <v>-0.0882</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>80.7</v>
+      </c>
+      <c r="L14">
+        <v>0.09013738411705574</v>
+      </c>
+      <c r="M14">
+        <v>150.4</v>
+      </c>
+      <c r="N14">
+        <v>0.05907305577376277</v>
+      </c>
+      <c r="O14">
+        <v>1.863692688971499</v>
+      </c>
+      <c r="P14">
+        <v>150.4</v>
+      </c>
+      <c r="Q14">
+        <v>0.05907305577376277</v>
+      </c>
+      <c r="R14">
+        <v>1.863692688971499</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>554.7</v>
+      </c>
+      <c r="V14">
+        <v>0.2178711704634721</v>
+      </c>
+      <c r="W14">
+        <v>0.03202889347515479</v>
+      </c>
+      <c r="X14">
+        <v>0.09909498649528091</v>
+      </c>
+      <c r="Y14">
+        <v>-0.06706609302012612</v>
+      </c>
+      <c r="Z14">
+        <v>0.1150919141277799</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.06334980044280845</v>
+      </c>
+      <c r="AC14">
+        <v>-0.06334980044280845</v>
+      </c>
+      <c r="AD14">
+        <v>5470.3</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>5470.3</v>
+      </c>
+      <c r="AG14">
+        <v>4915.6</v>
+      </c>
+      <c r="AH14">
+        <v>0.6823971158764018</v>
+      </c>
+      <c r="AI14">
+        <v>0.6667276073470084</v>
+      </c>
+      <c r="AJ14">
+        <v>0.6587863192880884</v>
+      </c>
+      <c r="AK14">
+        <v>0.642562091503268</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HUAXI Securities Co., Ltd. (SZSE:002926)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>-0.0342</v>
+      </c>
+      <c r="E15">
+        <v>-0.234</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>43.6</v>
+      </c>
+      <c r="L15">
+        <v>0.1089727568107973</v>
+      </c>
+      <c r="M15">
+        <v>118.8</v>
+      </c>
+      <c r="N15">
+        <v>0.03975238413920026</v>
+      </c>
+      <c r="O15">
+        <v>2.724770642201835</v>
+      </c>
+      <c r="P15">
+        <v>118.8</v>
+      </c>
+      <c r="Q15">
+        <v>0.03975238413920026</v>
+      </c>
+      <c r="R15">
+        <v>2.724770642201835</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>357.7</v>
+      </c>
+      <c r="V15">
+        <v>0.1196921532541409</v>
+      </c>
+      <c r="W15">
+        <v>0.01399948625738505</v>
+      </c>
+      <c r="X15">
+        <v>0.09252666203454296</v>
+      </c>
+      <c r="Y15">
+        <v>-0.07852717577715791</v>
+      </c>
+      <c r="Z15">
+        <v>0.04960130518005733</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.06355973639439727</v>
+      </c>
+      <c r="AC15">
+        <v>-0.06355973639439727</v>
+      </c>
+      <c r="AD15">
+        <v>5138.6</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>5138.6</v>
+      </c>
+      <c r="AG15">
+        <v>4780.900000000001</v>
+      </c>
+      <c r="AH15">
+        <v>0.6322796569502036</v>
+      </c>
+      <c r="AI15">
+        <v>0.6105460767073808</v>
+      </c>
+      <c r="AJ15">
+        <v>0.6153499626740804</v>
+      </c>
+      <c r="AK15">
+        <v>0.5932594587216301</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shanxi Securities Co., Ltd. (SZSE:002500)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>-0.146</v>
+      </c>
+      <c r="E16">
+        <v>0.0583</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>116.2</v>
+      </c>
+      <c r="L16">
+        <v>0.2621249718023911</v>
+      </c>
+      <c r="M16">
+        <v>135.3</v>
+      </c>
+      <c r="N16">
+        <v>0.04380625526128343</v>
+      </c>
+      <c r="O16">
+        <v>1.164371772805508</v>
+      </c>
+      <c r="P16">
+        <v>135.3</v>
+      </c>
+      <c r="Q16">
+        <v>0.04380625526128343</v>
+      </c>
+      <c r="R16">
+        <v>1.164371772805508</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>894.5</v>
+      </c>
+      <c r="V16">
+        <v>0.2896134170821731</v>
+      </c>
+      <c r="W16">
+        <v>0.04847726324572382</v>
+      </c>
+      <c r="X16">
+        <v>0.0912807083564183</v>
+      </c>
+      <c r="Y16">
+        <v>-0.04280344511069448</v>
+      </c>
+      <c r="Z16">
+        <v>0.06670177550406259</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.06360726615818837</v>
+      </c>
+      <c r="AC16">
+        <v>-0.06360726615818837</v>
+      </c>
+      <c r="AD16">
+        <v>5059.3</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>5059.3</v>
+      </c>
+      <c r="AG16">
+        <v>4164.8</v>
+      </c>
+      <c r="AH16">
+        <v>0.6209330011413985</v>
+      </c>
+      <c r="AI16">
+        <v>0.6601641504756188</v>
+      </c>
+      <c r="AJ16">
+        <v>0.5741858990266634</v>
+      </c>
+      <c r="AK16">
+        <v>0.6152573420788275</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Founder Securities Co., Ltd. (SHSE:601901)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>-0.00269</v>
+      </c>
+      <c r="E17">
+        <v>0.112</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>311</v>
+      </c>
+      <c r="L17">
+        <v>0.3188435513635431</v>
+      </c>
+      <c r="M17">
+        <v>169.3</v>
+      </c>
+      <c r="N17">
+        <v>0.01802060714437774</v>
+      </c>
+      <c r="O17">
+        <v>0.5443729903536978</v>
+      </c>
+      <c r="P17">
+        <v>169.3</v>
+      </c>
+      <c r="Q17">
+        <v>0.01802060714437774</v>
+      </c>
+      <c r="R17">
+        <v>0.5443729903536978</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>1373</v>
+      </c>
+      <c r="V17">
+        <v>0.14614467577809</v>
+      </c>
+      <c r="W17">
+        <v>0.05056006242785843</v>
+      </c>
+      <c r="X17">
+        <v>0.09106563608557366</v>
+      </c>
+      <c r="Y17">
+        <v>-0.04050557365771523</v>
+      </c>
+      <c r="Z17">
+        <v>0.05657247587230883</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.06361576903532212</v>
+      </c>
+      <c r="AC17">
+        <v>-0.06361576903532212</v>
+      </c>
+      <c r="AD17">
+        <v>15257.2</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>15257.2</v>
+      </c>
+      <c r="AG17">
+        <v>13884.2</v>
+      </c>
+      <c r="AH17">
+        <v>0.6189031315917572</v>
+      </c>
+      <c r="AI17">
+        <v>0.6911341028103427</v>
+      </c>
+      <c r="AJ17">
+        <v>0.5964259633145754</v>
+      </c>
+      <c r="AK17">
+        <v>0.6706500632770764</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Changjiang Securities Company Limited (SZSE:000783)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0228</v>
+      </c>
+      <c r="E18">
+        <v>0.0919</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>254.1</v>
+      </c>
+      <c r="L18">
+        <v>0.2741691842900302</v>
+      </c>
+      <c r="M18">
+        <v>302.2</v>
+      </c>
+      <c r="N18">
+        <v>0.05848541735209305</v>
+      </c>
+      <c r="O18">
+        <v>1.189295552931916</v>
+      </c>
+      <c r="P18">
+        <v>302.2</v>
+      </c>
+      <c r="Q18">
+        <v>0.05848541735209305</v>
+      </c>
+      <c r="R18">
+        <v>1.189295552931916</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>1065.9</v>
+      </c>
+      <c r="V18">
+        <v>0.2062859244063401</v>
+      </c>
+      <c r="W18">
+        <v>0.05452321689125397</v>
+      </c>
+      <c r="X18">
+        <v>0.09068885338218358</v>
+      </c>
+      <c r="Y18">
+        <v>-0.0361656364909296</v>
+      </c>
+      <c r="Z18">
+        <v>0.0649676108280286</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.06363088671994033</v>
+      </c>
+      <c r="AC18">
+        <v>-0.06363088671994033</v>
+      </c>
+      <c r="AD18">
+        <v>8264.200000000001</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>8264.200000000001</v>
+      </c>
+      <c r="AG18">
+        <v>7198.300000000001</v>
+      </c>
+      <c r="AH18">
+        <v>0.6152941264062303</v>
+      </c>
+      <c r="AI18">
+        <v>0.6045633773967242</v>
+      </c>
+      <c r="AJ18">
+        <v>0.582132401701522</v>
+      </c>
+      <c r="AK18">
+        <v>0.5711214078293848</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Huaan Securities Co., Ltd. (SHSE:600909)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.0842</v>
+      </c>
+      <c r="E19">
+        <v>0.064</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>207.9</v>
+      </c>
+      <c r="L19">
+        <v>0.3580161873600826</v>
+      </c>
+      <c r="M19">
+        <v>151.6</v>
+      </c>
+      <c r="N19">
+        <v>0.03886980154863853</v>
+      </c>
+      <c r="O19">
+        <v>0.7291967291967292</v>
+      </c>
+      <c r="P19">
+        <v>151.6</v>
+      </c>
+      <c r="Q19">
+        <v>0.03886980154863853</v>
+      </c>
+      <c r="R19">
+        <v>0.7291967291967292</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>251.8</v>
+      </c>
+      <c r="V19">
+        <v>0.06456079175426901</v>
+      </c>
+      <c r="W19">
+        <v>0.07314241486068111</v>
+      </c>
+      <c r="X19">
+        <v>0.0905647036774159</v>
+      </c>
+      <c r="Y19">
+        <v>-0.01742228881673479</v>
+      </c>
+      <c r="Z19">
+        <v>0.07506875700901355</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.06363593090175197</v>
+      </c>
+      <c r="AC19">
+        <v>-0.06363593090175197</v>
+      </c>
+      <c r="AD19">
+        <v>6206.3</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>6206.3</v>
+      </c>
+      <c r="AG19">
+        <v>5954.5</v>
+      </c>
+      <c r="AH19">
+        <v>0.6140899421164597</v>
+      </c>
+      <c r="AI19">
+        <v>0.6635624933176522</v>
+      </c>
+      <c r="AJ19">
+        <v>0.6042294539661278</v>
+      </c>
+      <c r="AK19">
+        <v>0.6542543840372698</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sinolink Securities Co., Ltd. (SHSE:600109)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.0692</v>
+      </c>
+      <c r="E20">
+        <v>0.0317</v>
+      </c>
+      <c r="F20">
+        <v>0.0915</v>
+      </c>
+      <c r="G20">
+        <v>0.02180946674655482</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>196.2</v>
+      </c>
+      <c r="L20">
+        <v>0.2351108448172558</v>
+      </c>
+      <c r="M20">
+        <v>205</v>
+      </c>
+      <c r="N20">
+        <v>0.04644418767982963</v>
+      </c>
+      <c r="O20">
+        <v>1.044852191641183</v>
+      </c>
+      <c r="P20">
+        <v>181.1</v>
+      </c>
+      <c r="Q20">
+        <v>0.04102947506740071</v>
+      </c>
+      <c r="R20">
+        <v>0.9230377166156983</v>
+      </c>
+      <c r="S20">
+        <v>23.90000000000001</v>
+      </c>
+      <c r="T20">
+        <v>0.1165853658536586</v>
+      </c>
+      <c r="U20">
+        <v>3512.8</v>
+      </c>
+      <c r="V20">
+        <v>0.7958494755205149</v>
+      </c>
+      <c r="W20">
+        <v>0.04459597681554722</v>
+      </c>
+      <c r="X20">
+        <v>0.09032460094220733</v>
+      </c>
+      <c r="Y20">
+        <v>-0.04572862412666012</v>
+      </c>
+      <c r="Z20">
+        <v>0.0864792827970996</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.06364577637224365</v>
+      </c>
+      <c r="AC20">
+        <v>-0.06364577637224365</v>
+      </c>
+      <c r="AD20">
+        <v>6954.5</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>6954.5</v>
+      </c>
+      <c r="AG20">
+        <v>3441.7</v>
+      </c>
+      <c r="AH20">
+        <v>0.6117395587769607</v>
+      </c>
+      <c r="AI20">
+        <v>0.6074488806589394</v>
+      </c>
+      <c r="AJ20">
+        <v>0.4381205764040939</v>
+      </c>
+      <c r="AK20">
+        <v>0.433687420456407</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Huachuang Yunxin Digital Technology Co., Ltd. (SHSE:600155)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.154</v>
+      </c>
+      <c r="E21">
+        <v>0.009809999999999999</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>33.8</v>
+      </c>
+      <c r="L21">
+        <v>0.07657453556864521</v>
+      </c>
+      <c r="M21">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="N21">
+        <v>0.0451341827053402</v>
+      </c>
+      <c r="O21">
+        <v>2.955621301775148</v>
+      </c>
+      <c r="P21">
+        <v>68.2</v>
+      </c>
+      <c r="Q21">
+        <v>0.03081232492997199</v>
+      </c>
+      <c r="R21">
+        <v>2.017751479289941</v>
+      </c>
+      <c r="S21">
+        <v>31.7</v>
+      </c>
+      <c r="T21">
+        <v>0.3173173173173173</v>
+      </c>
+      <c r="U21">
+        <v>386</v>
+      </c>
+      <c r="V21">
+        <v>0.1743923375801934</v>
+      </c>
+      <c r="W21">
+        <v>0.01256832633027182</v>
+      </c>
+      <c r="X21">
+        <v>0.08988401280358065</v>
+      </c>
+      <c r="Y21">
+        <v>-0.07731568647330883</v>
+      </c>
+      <c r="Z21">
+        <v>0.09056402470300988</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.06366415826539243</v>
+      </c>
+      <c r="AC21">
+        <v>-0.06366415826539243</v>
+      </c>
+      <c r="AD21">
+        <v>3423.7</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>3423.7</v>
+      </c>
+      <c r="AG21">
+        <v>3037.7</v>
+      </c>
+      <c r="AH21">
+        <v>0.6073512976530485</v>
+      </c>
+      <c r="AI21">
+        <v>0.5327555085273248</v>
+      </c>
+      <c r="AJ21">
+        <v>0.5784883167336367</v>
+      </c>
+      <c r="AK21">
+        <v>0.5028971591285345</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Everbright Securities Company Limited (SHSE:601788)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>-0.0336</v>
+      </c>
+      <c r="E22">
+        <v>0.09789999999999999</v>
+      </c>
+      <c r="G22">
+        <v>0.06888888888888889</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>271.4</v>
+      </c>
+      <c r="L22">
+        <v>0.2233744855967078</v>
+      </c>
+      <c r="M22">
+        <v>477.8</v>
+      </c>
+      <c r="N22">
+        <v>0.04586204910637154</v>
+      </c>
+      <c r="O22">
+        <v>1.760501105379514</v>
+      </c>
+      <c r="P22">
+        <v>477.8</v>
+      </c>
+      <c r="Q22">
+        <v>0.04586204910637154</v>
+      </c>
+      <c r="R22">
+        <v>1.760501105379514</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>2408.1</v>
+      </c>
+      <c r="V22">
+        <v>0.231143575665662</v>
+      </c>
+      <c r="W22">
+        <v>0.02947084948583466</v>
+      </c>
+      <c r="X22">
+        <v>0.08931039741777611</v>
+      </c>
+      <c r="Y22">
+        <v>-0.05983954793194145</v>
+      </c>
+      <c r="Z22">
+        <v>0.05940971678923486</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.06368872216622419</v>
+      </c>
+      <c r="AC22">
+        <v>-0.06368872216622419</v>
+      </c>
+      <c r="AD22">
+        <v>15724.5</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>15724.5</v>
+      </c>
+      <c r="AG22">
+        <v>13316.4</v>
+      </c>
+      <c r="AH22">
+        <v>0.6014872220543402</v>
+      </c>
+      <c r="AI22">
+        <v>0.6177032101946858</v>
+      </c>
+      <c r="AJ22">
+        <v>0.5610543257522773</v>
+      </c>
+      <c r="AK22">
+        <v>0.5777606157504024</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tianfeng Securities Co., Ltd. (SHSE:601162)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>-0.106</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>-93.2</v>
+      </c>
+      <c r="L23">
+        <v>-0.3049738219895288</v>
+      </c>
+      <c r="M23">
+        <v>326.4</v>
+      </c>
+      <c r="N23">
+        <v>0.06185098158114151</v>
+      </c>
+      <c r="O23">
+        <v>-3.502145922746781</v>
+      </c>
+      <c r="P23">
+        <v>326.4</v>
+      </c>
+      <c r="Q23">
+        <v>0.06185098158114151</v>
+      </c>
+      <c r="R23">
+        <v>-3.502145922746781</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>1720.1</v>
+      </c>
+      <c r="V23">
+        <v>0.3259493670886076</v>
+      </c>
+      <c r="W23">
+        <v>-0.02861001964636542</v>
+      </c>
+      <c r="X23">
+        <v>0.08857445287216095</v>
+      </c>
+      <c r="Y23">
+        <v>-0.1171844725185264</v>
+      </c>
+      <c r="Z23">
+        <v>0.03092100270659955</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.06372133300904392</v>
+      </c>
+      <c r="AC23">
+        <v>-0.06372133300904392</v>
+      </c>
+      <c r="AD23">
+        <v>7711.3</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>7711.3</v>
+      </c>
+      <c r="AG23">
+        <v>5991.200000000001</v>
+      </c>
+      <c r="AH23">
+        <v>0.5937021211071333</v>
+      </c>
+      <c r="AI23">
+        <v>0.6935495476049143</v>
+      </c>
+      <c r="AJ23">
+        <v>0.53168151645309</v>
+      </c>
+      <c r="AK23">
+        <v>0.63746342501463</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hongta Securities Co., Ltd. (SHSE:601236)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.0273</v>
+      </c>
+      <c r="E24">
+        <v>0.0199</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>106.9</v>
+      </c>
+      <c r="L24">
+        <v>0.3871785584932995</v>
+      </c>
+      <c r="M24">
+        <v>89</v>
+      </c>
+      <c r="N24">
+        <v>0.01622193059200933</v>
+      </c>
+      <c r="O24">
+        <v>0.8325537885874649</v>
+      </c>
+      <c r="P24">
+        <v>89</v>
+      </c>
+      <c r="Q24">
+        <v>0.01622193059200933</v>
+      </c>
+      <c r="R24">
+        <v>0.8325537885874649</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>349.4</v>
+      </c>
+      <c r="V24">
+        <v>0.06368474773986585</v>
+      </c>
+      <c r="W24">
+        <v>0.03405651661410048</v>
+      </c>
+      <c r="X24">
+        <v>0.07488665208281334</v>
+      </c>
+      <c r="Y24">
+        <v>-0.04083013546871286</v>
+      </c>
+      <c r="Z24">
+        <v>0.06284998861825632</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.06374280446527915</v>
+      </c>
+      <c r="AC24">
+        <v>-0.06374280446527915</v>
+      </c>
+      <c r="AD24">
+        <v>3110.7</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>3110.7</v>
+      </c>
+      <c r="AG24">
+        <v>2761.3</v>
+      </c>
+      <c r="AH24">
+        <v>0.3618313152109432</v>
+      </c>
+      <c r="AI24">
+        <v>0.4764070755800597</v>
+      </c>
+      <c r="AJ24">
+        <v>0.3347963674721438</v>
+      </c>
+      <c r="AK24">
+        <v>0.4468050678791605</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dongxing Securities Corporation Limited (SHSE:601198)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.201</v>
+      </c>
+      <c r="E25">
+        <v>-0.006690000000000001</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>184.3</v>
+      </c>
+      <c r="L25">
+        <v>0.132886293171822</v>
+      </c>
+      <c r="M25">
+        <v>136.3</v>
+      </c>
+      <c r="N25">
+        <v>0.02795438697239427</v>
+      </c>
+      <c r="O25">
+        <v>0.7395550732501357</v>
+      </c>
+      <c r="P25">
+        <v>136.3</v>
+      </c>
+      <c r="Q25">
+        <v>0.02795438697239427</v>
+      </c>
+      <c r="R25">
+        <v>0.7395550732501357</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>225.5</v>
+      </c>
+      <c r="V25">
+        <v>0.04624882070634562</v>
+      </c>
+      <c r="W25">
+        <v>0.05045444590451161</v>
+      </c>
+      <c r="X25">
+        <v>0.08744227777332833</v>
+      </c>
+      <c r="Y25">
+        <v>-0.03698783186881673</v>
+      </c>
+      <c r="Z25">
+        <v>0.1368026703597173</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.06377406630463273</v>
+      </c>
+      <c r="AC25">
+        <v>-0.06377406630463273</v>
+      </c>
+      <c r="AD25">
+        <v>6764.1</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>6764.1</v>
+      </c>
+      <c r="AG25">
+        <v>6538.6</v>
+      </c>
+      <c r="AH25">
+        <v>0.5811132398044656</v>
+      </c>
+      <c r="AI25">
+        <v>0.6319580693985088</v>
+      </c>
+      <c r="AJ25">
+        <v>0.5728378188954303</v>
+      </c>
+      <c r="AK25">
+        <v>0.6240372593744929</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>China International Capital Corporation Limited (SEHK:3908)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.0898</v>
+      </c>
+      <c r="E26">
+        <v>0.0242</v>
+      </c>
+      <c r="F26">
+        <v>0.16</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>628.2</v>
+      </c>
+      <c r="L26">
+        <v>0.2069374444115031</v>
+      </c>
+      <c r="M26">
+        <v>221.2</v>
+      </c>
+      <c r="N26">
+        <v>0.01329638557113747</v>
+      </c>
+      <c r="O26">
+        <v>0.3521171601400827</v>
+      </c>
+      <c r="P26">
+        <v>221.2</v>
+      </c>
+      <c r="Q26">
+        <v>0.01329638557113747</v>
+      </c>
+      <c r="R26">
+        <v>0.3521171601400827</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>7826.7</v>
+      </c>
+      <c r="V26">
+        <v>0.4704648325028102</v>
+      </c>
+      <c r="W26">
+        <v>0.044414592760181</v>
+      </c>
+      <c r="X26">
+        <v>0.1050625028400898</v>
+      </c>
+      <c r="Y26">
+        <v>-0.06064791007990884</v>
+      </c>
+      <c r="Z26">
+        <v>0.06779142474318892</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.06379506186139929</v>
+      </c>
+      <c r="AC26">
+        <v>-0.06379506186139929</v>
+      </c>
+      <c r="AD26">
+        <v>42230.1</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>42230.1</v>
+      </c>
+      <c r="AG26">
+        <v>34403.4</v>
+      </c>
+      <c r="AH26">
+        <v>0.7173913043478261</v>
+      </c>
+      <c r="AI26">
+        <v>0.7308268724906548</v>
+      </c>
+      <c r="AJ26">
+        <v>0.6740544088402121</v>
+      </c>
+      <c r="AK26">
+        <v>0.6886561123199212</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Guotai Junan Securities Co., Ltd. (SHSE:601211)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0.0809</v>
+      </c>
+      <c r="E27">
+        <v>0.0581</v>
+      </c>
+      <c r="F27">
+        <v>0.169</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>1464.1</v>
+      </c>
+      <c r="L27">
+        <v>0.2731020332027607</v>
+      </c>
+      <c r="M27">
+        <v>1449.892</v>
+      </c>
+      <c r="N27">
+        <v>0.06867392612029725</v>
+      </c>
+      <c r="O27">
+        <v>0.990295744826173</v>
+      </c>
+      <c r="P27">
+        <v>1449.1</v>
+      </c>
+      <c r="Q27">
+        <v>0.06863641315416787</v>
+      </c>
+      <c r="R27">
+        <v>0.9897547981695239</v>
+      </c>
+      <c r="S27">
+        <v>0.7919999999999163</v>
+      </c>
+      <c r="T27">
+        <v>0.0005462475825785068</v>
+      </c>
+      <c r="U27">
+        <v>3471.3</v>
+      </c>
+      <c r="V27">
+        <v>0.1644176254102981</v>
+      </c>
+      <c r="W27">
+        <v>0.06439029109988169</v>
+      </c>
+      <c r="X27">
+        <v>0.1025612059782801</v>
+      </c>
+      <c r="Y27">
+        <v>-0.03817091487839845</v>
+      </c>
+      <c r="Z27">
+        <v>0.08044029847387002</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.06384109217502541</v>
+      </c>
+      <c r="AC27">
+        <v>-0.06384109217502541</v>
+      </c>
+      <c r="AD27">
+        <v>50143.6</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>50143.6</v>
+      </c>
+      <c r="AG27">
+        <v>46672.3</v>
+      </c>
+      <c r="AH27">
+        <v>0.7037076019944902</v>
+      </c>
+      <c r="AI27">
+        <v>0.6703456831714405</v>
+      </c>
+      <c r="AJ27">
+        <v>0.6885343365051264</v>
+      </c>
+      <c r="AK27">
+        <v>0.6543032301388031</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Shanghai Chinafortune Co., Ltd. (SHSE:600621)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.115</v>
+      </c>
+      <c r="E28">
+        <v>0.331</v>
+      </c>
+      <c r="G28">
+        <v>0.02549837737598517</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>40.8</v>
+      </c>
+      <c r="L28">
+        <v>0.1891515994436718</v>
+      </c>
+      <c r="M28">
+        <v>56.3</v>
+      </c>
+      <c r="N28">
+        <v>0.02350436271030768</v>
+      </c>
+      <c r="O28">
+        <v>1.379901960784314</v>
+      </c>
+      <c r="P28">
+        <v>56.3</v>
+      </c>
+      <c r="Q28">
+        <v>0.02350436271030768</v>
+      </c>
+      <c r="R28">
+        <v>1.379901960784314</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>1550.1</v>
+      </c>
+      <c r="V28">
+        <v>0.6471423203774057</v>
+      </c>
+      <c r="W28">
+        <v>0.03849419756580809</v>
+      </c>
+      <c r="X28">
+        <v>0.08601503672360482</v>
+      </c>
+      <c r="Y28">
+        <v>-0.04752083915779673</v>
+      </c>
+      <c r="Z28">
+        <v>0.08911786943426472</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.06384538841895876</v>
+      </c>
+      <c r="AC28">
+        <v>-0.06384538841895876</v>
+      </c>
+      <c r="AD28">
+        <v>3099.6</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>3099.6</v>
+      </c>
+      <c r="AG28">
+        <v>1549.5</v>
+      </c>
+      <c r="AH28">
+        <v>0.5640866985750423</v>
+      </c>
+      <c r="AI28">
+        <v>0.7284092778417502</v>
+      </c>
+      <c r="AJ28">
+        <v>0.3927955789900628</v>
+      </c>
+      <c r="AK28">
+        <v>0.5727857459707231</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-116.3</v>
+      </c>
+      <c r="AQ28">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Southwest Securities Co., Ltd. (SHSE:600369)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>-0.0608</v>
+      </c>
+      <c r="E29">
+        <v>-0.0307</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="L29">
+        <v>0.2340561224489796</v>
+      </c>
+      <c r="M29">
+        <v>110.4</v>
+      </c>
+      <c r="N29">
+        <v>0.02596669489133503</v>
+      </c>
+      <c r="O29">
+        <v>1.50408719346049</v>
+      </c>
+      <c r="P29">
+        <v>110.4</v>
+      </c>
+      <c r="Q29">
+        <v>0.02596669489133503</v>
+      </c>
+      <c r="R29">
+        <v>1.50408719346049</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>247.1</v>
+      </c>
+      <c r="V29">
+        <v>0.05811929626493555</v>
+      </c>
+      <c r="W29">
+        <v>0.02114908085057339</v>
+      </c>
+      <c r="X29">
+        <v>0.08581229463679543</v>
+      </c>
+      <c r="Y29">
+        <v>-0.06466321378622204</v>
+      </c>
+      <c r="Z29">
+        <v>0.03301577408619686</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.06385599289370902</v>
+      </c>
+      <c r="AC29">
+        <v>-0.06385599289370902</v>
+      </c>
+      <c r="AD29">
+        <v>5445.4</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>5445.4</v>
+      </c>
+      <c r="AG29">
+        <v>5198.299999999999</v>
+      </c>
+      <c r="AH29">
+        <v>0.5615551201402496</v>
+      </c>
+      <c r="AI29">
+        <v>0.5985271488239173</v>
+      </c>
+      <c r="AJ29">
+        <v>0.5500904771479063</v>
+      </c>
+      <c r="AK29">
+        <v>0.5873188037374729</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Western Securities Co.,Ltd. (SZSE:002673)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="E30">
+        <v>0.219</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>145.2</v>
+      </c>
+      <c r="L30">
+        <v>0.1820233170364799</v>
+      </c>
+      <c r="M30">
+        <v>135.2</v>
+      </c>
+      <c r="N30">
+        <v>0.02709093095018635</v>
+      </c>
+      <c r="O30">
+        <v>0.931129476584022</v>
+      </c>
+      <c r="P30">
+        <v>135.2</v>
+      </c>
+      <c r="Q30">
+        <v>0.02709093095018635</v>
+      </c>
+      <c r="R30">
+        <v>0.931129476584022</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>1165.7</v>
+      </c>
+      <c r="V30">
+        <v>0.2335791287620727</v>
+      </c>
+      <c r="W30">
+        <v>0.03829113924050633</v>
+      </c>
+      <c r="X30">
+        <v>0.08438827481572224</v>
+      </c>
+      <c r="Y30">
+        <v>-0.04609713557521591</v>
+      </c>
+      <c r="Z30">
+        <v>0.08465956390932119</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.06393409502403108</v>
+      </c>
+      <c r="AC30">
+        <v>-0.06393409502403108</v>
+      </c>
+      <c r="AD30">
+        <v>5927.6</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>5927.6</v>
+      </c>
+      <c r="AG30">
+        <v>4761.900000000001</v>
+      </c>
+      <c r="AH30">
+        <v>0.5429100034804272</v>
+      </c>
+      <c r="AI30">
+        <v>0.5936504757135704</v>
+      </c>
+      <c r="AJ30">
+        <v>0.4882748013329916</v>
+      </c>
+      <c r="AK30">
+        <v>0.5399408116290408</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CITIC Securities Company Limited (SHSE:600030)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.07200000000000001</v>
+      </c>
+      <c r="E31">
+        <v>0.098</v>
+      </c>
+      <c r="F31">
+        <v>0.141</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>2866.3</v>
+      </c>
+      <c r="L31">
+        <v>0.3277569409504643</v>
+      </c>
+      <c r="M31">
+        <v>1886.8</v>
+      </c>
+      <c r="N31">
+        <v>0.03371736244020207</v>
+      </c>
+      <c r="O31">
+        <v>0.6582702438684017</v>
+      </c>
+      <c r="P31">
+        <v>1886.8</v>
+      </c>
+      <c r="Q31">
+        <v>0.03371736244020207</v>
+      </c>
+      <c r="R31">
+        <v>0.6582702438684017</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>49607.7</v>
+      </c>
+      <c r="V31">
+        <v>0.8864960783998369</v>
+      </c>
+      <c r="W31">
+        <v>0.07968584931887684</v>
+      </c>
+      <c r="X31">
+        <v>0.09242174872035638</v>
+      </c>
+      <c r="Y31">
+        <v>-0.01273589940147954</v>
+      </c>
+      <c r="Z31">
+        <v>0.1287757527208686</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.06408449271997002</v>
+      </c>
+      <c r="AC31">
+        <v>-0.06408449271997002</v>
+      </c>
+      <c r="AD31">
+        <v>95836.10000000001</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>95836.10000000001</v>
+      </c>
+      <c r="AG31">
+        <v>46228.40000000001</v>
+      </c>
+      <c r="AH31">
+        <v>0.6313504888817447</v>
+      </c>
+      <c r="AI31">
+        <v>0.6971987242722911</v>
+      </c>
+      <c r="AJ31">
+        <v>0.4523871268264185</v>
+      </c>
+      <c r="AK31">
+        <v>0.5262131037630718</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CSC Financial Co., Ltd. (SEHK:6066)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.0992</v>
+      </c>
+      <c r="E32">
+        <v>0.0362</v>
+      </c>
+      <c r="F32">
+        <v>0.115</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>804.1</v>
+      </c>
+      <c r="L32">
+        <v>0.2656601030791595</v>
+      </c>
+      <c r="M32">
+        <v>367</v>
+      </c>
+      <c r="N32">
+        <v>0.0149734802121583</v>
+      </c>
+      <c r="O32">
+        <v>0.4564108941673921</v>
+      </c>
+      <c r="P32">
+        <v>367</v>
+      </c>
+      <c r="Q32">
+        <v>0.0149734802121583</v>
+      </c>
+      <c r="R32">
+        <v>0.4564108941673921</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>3802</v>
+      </c>
+      <c r="V32">
+        <v>0.1551203590371277</v>
+      </c>
+      <c r="W32">
+        <v>0.06083739369911933</v>
+      </c>
+      <c r="X32">
+        <v>0.09149168896373933</v>
+      </c>
+      <c r="Y32">
+        <v>-0.03065429526462</v>
+      </c>
+      <c r="Z32">
+        <v>0.06617055510860821</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.06411290786347157</v>
+      </c>
+      <c r="AC32">
+        <v>-0.06411290786347157</v>
+      </c>
+      <c r="AD32">
+        <v>40486.6</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>40486.6</v>
+      </c>
+      <c r="AG32">
+        <v>36684.6</v>
+      </c>
+      <c r="AH32">
+        <v>0.6229033518676361</v>
+      </c>
+      <c r="AI32">
+        <v>0.7372285236164196</v>
+      </c>
+      <c r="AJ32">
+        <v>0.599474463433048</v>
+      </c>
+      <c r="AK32">
+        <v>0.7176833550815509</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cinda Securities Co., Ltd. (SHSE:601059)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>180.5</v>
+      </c>
+      <c r="L33">
+        <v>0.4136113657195234</v>
+      </c>
+      <c r="M33">
+        <v>87.5</v>
+      </c>
+      <c r="N33">
+        <v>0.01314682372738746</v>
+      </c>
+      <c r="O33">
+        <v>0.4847645429362881</v>
+      </c>
+      <c r="P33">
+        <v>87.5</v>
+      </c>
+      <c r="Q33">
+        <v>0.01314682372738746</v>
+      </c>
+      <c r="R33">
+        <v>0.4847645429362881</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>998.9</v>
+      </c>
+      <c r="V33">
+        <v>0.1500841396718553</v>
+      </c>
+      <c r="W33">
+        <v>0.07608329118192547</v>
+      </c>
+      <c r="X33">
+        <v>0.07928005235297532</v>
+      </c>
+      <c r="Y33">
+        <v>-0.003196761171049847</v>
+      </c>
+      <c r="Z33">
+        <v>0.06614163585664785</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0.06427875255817006</v>
+      </c>
+      <c r="AC33">
+        <v>-0.06427875255817006</v>
+      </c>
+      <c r="AD33">
+        <v>5684</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>5684</v>
+      </c>
+      <c r="AG33">
+        <v>4685.1</v>
+      </c>
+      <c r="AH33">
+        <v>0.4606308146131155</v>
+      </c>
+      <c r="AI33">
+        <v>0.6555713181781484</v>
+      </c>
+      <c r="AJ33">
+        <v>0.4131226467502006</v>
+      </c>
+      <c r="AK33">
+        <v>0.6107229449644133</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Caida Securities Co., Ltd. (SHSE:600906)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.0451</v>
+      </c>
+      <c r="E34">
+        <v>-0.0406</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>60.1</v>
+      </c>
+      <c r="L34">
+        <v>0.1864143920595534</v>
+      </c>
+      <c r="M34">
+        <v>99.2</v>
+      </c>
+      <c r="N34">
+        <v>0.03142721368604467</v>
+      </c>
+      <c r="O34">
+        <v>1.650582362728785</v>
+      </c>
+      <c r="P34">
+        <v>99.2</v>
+      </c>
+      <c r="Q34">
+        <v>0.03142721368604467</v>
+      </c>
+      <c r="R34">
+        <v>1.650582362728785</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>196</v>
+      </c>
+      <c r="V34">
+        <v>0.06209409155710439</v>
+      </c>
+      <c r="W34">
+        <v>0.03803316035944817</v>
+      </c>
+      <c r="X34">
+        <v>0.07872964575291432</v>
+      </c>
+      <c r="Y34">
+        <v>-0.04069648539346615</v>
+      </c>
+      <c r="Z34">
+        <v>0.07988403929779352</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0.0643234406861381</v>
+      </c>
+      <c r="AC34">
+        <v>-0.0643234406861381</v>
+      </c>
+      <c r="AD34">
+        <v>2582.2</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>2582.2</v>
+      </c>
+      <c r="AG34">
+        <v>2386.2</v>
+      </c>
+      <c r="AH34">
+        <v>0.449962535068918</v>
+      </c>
+      <c r="AI34">
+        <v>0.6090094339622641</v>
+      </c>
+      <c r="AJ34">
+        <v>0.4305122052429321</v>
+      </c>
+      <c r="AK34">
+        <v>0.5900593471810088</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sealand Securities Co., Ltd. (SZSE:000750)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.0374</v>
+      </c>
+      <c r="E35">
+        <v>-0.258</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>17</v>
+      </c>
+      <c r="L35">
+        <v>0.03163379233345739</v>
+      </c>
+      <c r="M35">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="N35">
+        <v>0.02659759126231741</v>
+      </c>
+      <c r="O35">
+        <v>5.858823529411764</v>
+      </c>
+      <c r="P35">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="Q35">
+        <v>0.02659759126231741</v>
+      </c>
+      <c r="R35">
+        <v>5.858823529411764</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>1145.3</v>
+      </c>
+      <c r="V35">
+        <v>0.3058455951077523</v>
+      </c>
+      <c r="W35">
+        <v>0.006595026574077667</v>
+      </c>
+      <c r="X35">
+        <v>0.07828541661010291</v>
+      </c>
+      <c r="Y35">
+        <v>-0.07169039003602524</v>
+      </c>
+      <c r="Z35">
+        <v>0.1060887521048964</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0.06436081821330208</v>
+      </c>
+      <c r="AC35">
+        <v>-0.06436081821330208</v>
+      </c>
+      <c r="AD35">
+        <v>2954.7</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>2954.7</v>
+      </c>
+      <c r="AG35">
+        <v>1809.4</v>
+      </c>
+      <c r="AH35">
+        <v>0.4410394960742753</v>
+      </c>
+      <c r="AI35">
+        <v>0.478393212764924</v>
+      </c>
+      <c r="AJ35">
+        <v>0.3257773536666607</v>
+      </c>
+      <c r="AK35">
+        <v>0.3596501689524945</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GF Securities Co., Ltd. (SZSE:000776)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>0.0254</v>
+      </c>
+      <c r="E36">
+        <v>0.0645</v>
+      </c>
+      <c r="F36">
+        <v>0.137</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>1130.8</v>
+      </c>
+      <c r="L36">
+        <v>0.3393961222162195</v>
+      </c>
+      <c r="M36">
+        <v>498.1</v>
+      </c>
+      <c r="N36">
+        <v>0.03230011023928409</v>
+      </c>
+      <c r="O36">
+        <v>0.440484612663601</v>
+      </c>
+      <c r="P36">
+        <v>498.1</v>
+      </c>
+      <c r="Q36">
+        <v>0.03230011023928409</v>
+      </c>
+      <c r="R36">
+        <v>0.440484612663601</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>3733.8</v>
+      </c>
+      <c r="V36">
+        <v>0.2421243758511121</v>
+      </c>
+      <c r="W36">
+        <v>0.06135315501058</v>
+      </c>
+      <c r="X36">
+        <v>0.1208952479831807</v>
+      </c>
+      <c r="Y36">
+        <v>-0.05954209297260071</v>
+      </c>
+      <c r="Z36">
+        <v>0.05529988427821203</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0.06440040283298674</v>
+      </c>
+      <c r="AC36">
+        <v>-0.06440040283298674</v>
+      </c>
+      <c r="AD36">
+        <v>55097.1</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>55097.1</v>
+      </c>
+      <c r="AG36">
+        <v>51363.3</v>
+      </c>
+      <c r="AH36">
+        <v>0.7813185550943658</v>
+      </c>
+      <c r="AI36">
+        <v>0.72296607522917</v>
+      </c>
+      <c r="AJ36">
+        <v>0.7690924363959794</v>
+      </c>
+      <c r="AK36">
+        <v>0.7086939124675754</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hengtai Securities Co., Ltd. (SEHK:1476)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>-0.0824</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0.0008085530412484967</v>
+      </c>
+      <c r="J37">
+        <v>0.0008085530412484967</v>
+      </c>
+      <c r="K37">
+        <v>-10.3</v>
+      </c>
+      <c r="L37">
+        <v>-0.04168352893565359</v>
+      </c>
+      <c r="M37">
+        <v>-0</v>
+      </c>
+      <c r="N37">
+        <v>-0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>-0</v>
+      </c>
+      <c r="Q37">
+        <v>-0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>270.8</v>
+      </c>
+      <c r="V37">
+        <v>0.395906432748538</v>
+      </c>
+      <c r="W37">
+        <v>-0.009090909090909092</v>
+      </c>
+      <c r="X37">
+        <v>0.1063631578342655</v>
+      </c>
+      <c r="Y37">
+        <v>-0.1154540669251746</v>
+      </c>
+      <c r="Z37">
+        <v>0.113724172751773</v>
+      </c>
+      <c r="AA37">
+        <v>9.195202574191549E-05</v>
+      </c>
+      <c r="AB37">
+        <v>0.06453298716462361</v>
+      </c>
+      <c r="AC37">
+        <v>-0.06444103513888169</v>
+      </c>
+      <c r="AD37">
+        <v>1794.2</v>
+      </c>
+      <c r="AE37">
+        <v>0.2310327175374823</v>
+      </c>
+      <c r="AF37">
+        <v>1794.431032717538</v>
+      </c>
+      <c r="AG37">
+        <v>1523.631032717538</v>
+      </c>
+      <c r="AH37">
+        <v>0.7240189495004785</v>
+      </c>
+      <c r="AI37">
+        <v>0.6132435672407415</v>
+      </c>
+      <c r="AJ37">
+        <v>0.69016561650793</v>
+      </c>
+      <c r="AK37">
+        <v>0.5738007856437441</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>7293.49593495935</v>
+      </c>
+      <c r="AP37">
+        <v>6193.622084217633</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Haitong Securities Co., Ltd. (SHSE:600837)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>-0.168</v>
+      </c>
+      <c r="F38">
+        <v>0.878</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-572.1</v>
+      </c>
+      <c r="L38">
+        <v>-0.3231473113420696</v>
+      </c>
+      <c r="M38">
+        <v>242.7</v>
+      </c>
+      <c r="N38">
+        <v>0.01379133992499148</v>
+      </c>
+      <c r="O38">
+        <v>-0.4242265338227582</v>
+      </c>
+      <c r="P38">
+        <v>183.6</v>
+      </c>
+      <c r="Q38">
+        <v>0.01043300375042618</v>
+      </c>
+      <c r="R38">
+        <v>-0.3209229155742003</v>
+      </c>
+      <c r="S38">
+        <v>59.09999999999999</v>
+      </c>
+      <c r="T38">
+        <v>0.2435105067985167</v>
+      </c>
+      <c r="U38">
+        <v>8806</v>
+      </c>
+      <c r="V38">
+        <v>0.5003977724741447</v>
+      </c>
+      <c r="W38">
+        <v>-0.02499945377875855</v>
+      </c>
+      <c r="X38">
+        <v>0.1088938857435764</v>
+      </c>
+      <c r="Y38">
+        <v>-0.133893339522335</v>
+      </c>
+      <c r="Z38">
+        <v>0.02593981271877193</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0.06450511962800146</v>
+      </c>
+      <c r="AC38">
+        <v>-0.06450511962800146</v>
+      </c>
+      <c r="AD38">
+        <v>49076.9</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>49076.9</v>
+      </c>
+      <c r="AG38">
+        <v>40270.9</v>
+      </c>
+      <c r="AH38">
+        <v>0.7360625962693608</v>
+      </c>
+      <c r="AI38">
+        <v>0.6700842027364866</v>
+      </c>
+      <c r="AJ38">
+        <v>0.695898833397559</v>
+      </c>
+      <c r="AK38">
+        <v>0.6249955380630382</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>China Galaxy Securities Co., Ltd. (SEHK:6881)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>0.184</v>
+      </c>
+      <c r="E39">
+        <v>0.111</v>
+      </c>
+      <c r="F39">
+        <v>0.113</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>1174.6</v>
+      </c>
+      <c r="L39">
+        <v>0.2272525006287848</v>
+      </c>
+      <c r="M39">
+        <v>581.6</v>
+      </c>
+      <c r="N39">
+        <v>0.03146692348062263</v>
+      </c>
+      <c r="O39">
+        <v>0.4951472841818492</v>
+      </c>
+      <c r="P39">
+        <v>581.6</v>
+      </c>
+      <c r="Q39">
+        <v>0.03146692348062263</v>
+      </c>
+      <c r="R39">
+        <v>0.4951472841818492</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>2215.6</v>
+      </c>
+      <c r="V39">
+        <v>0.1198729636583004</v>
+      </c>
+      <c r="W39">
+        <v>0.07108190213378841</v>
+      </c>
+      <c r="X39">
+        <v>0.1033171145205522</v>
+      </c>
+      <c r="Y39">
+        <v>-0.03223521238676375</v>
+      </c>
+      <c r="Z39">
+        <v>0.08738632271415456</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0.06457009793314551</v>
+      </c>
+      <c r="AC39">
+        <v>-0.06457009793314551</v>
+      </c>
+      <c r="AD39">
+        <v>44810.5</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>44810.5</v>
+      </c>
+      <c r="AG39">
+        <v>42594.9</v>
+      </c>
+      <c r="AH39">
+        <v>0.7079806109325775</v>
+      </c>
+      <c r="AI39">
+        <v>0.6969157815992024</v>
+      </c>
+      <c r="AJ39">
+        <v>0.6973875941831565</v>
+      </c>
+      <c r="AK39">
+        <v>0.6860993481275782</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Guosen Securities Co., Ltd. (SZSE:002736)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>0.0481</v>
+      </c>
+      <c r="E40">
+        <v>0.0424</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>917</v>
+      </c>
+      <c r="L40">
+        <v>0.3751892312098523</v>
+      </c>
+      <c r="M40">
+        <v>937</v>
+      </c>
+      <c r="N40">
+        <v>0.0635271464988881</v>
+      </c>
+      <c r="O40">
+        <v>1.021810250817884</v>
+      </c>
+      <c r="P40">
+        <v>937</v>
+      </c>
+      <c r="Q40">
+        <v>0.0635271464988881</v>
+      </c>
+      <c r="R40">
+        <v>1.021810250817884</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>1450.9</v>
+      </c>
+      <c r="V40">
+        <v>0.09836876932255791</v>
+      </c>
+      <c r="W40">
+        <v>0.06130088909686476</v>
+      </c>
+      <c r="X40">
+        <v>0.1000920607162926</v>
+      </c>
+      <c r="Y40">
+        <v>-0.03879117161942783</v>
+      </c>
+      <c r="Z40">
+        <v>0.05720204954702465</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0.06461439882618195</v>
+      </c>
+      <c r="AC40">
+        <v>-0.06461439882618195</v>
+      </c>
+      <c r="AD40">
+        <v>32651.6</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>32651.6</v>
+      </c>
+      <c r="AG40">
+        <v>31200.7</v>
+      </c>
+      <c r="AH40">
+        <v>0.688834881817338</v>
+      </c>
+      <c r="AI40">
+        <v>0.6670643660032443</v>
+      </c>
+      <c r="AJ40">
+        <v>0.6790097126678172</v>
+      </c>
+      <c r="AK40">
+        <v>0.6568941813534664</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>First Capital Securities Co., Ltd. (SZSE:002797)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>0.0533</v>
+      </c>
+      <c r="E41">
+        <v>0.133</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>91.8</v>
+      </c>
+      <c r="L41">
+        <v>0.217123935666982</v>
+      </c>
+      <c r="M41">
+        <v>59.7</v>
+      </c>
+      <c r="N41">
+        <v>0.01241835503598619</v>
+      </c>
+      <c r="O41">
+        <v>0.6503267973856209</v>
+      </c>
+      <c r="P41">
+        <v>59.7</v>
+      </c>
+      <c r="Q41">
+        <v>0.01241835503598619</v>
+      </c>
+      <c r="R41">
+        <v>0.6503267973856209</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>381.1</v>
+      </c>
+      <c r="V41">
+        <v>0.07927361983608605</v>
+      </c>
+      <c r="W41">
+        <v>0.04530648504589872</v>
+      </c>
+      <c r="X41">
+        <v>0.07447905750910454</v>
+      </c>
+      <c r="Y41">
+        <v>-0.02917257246320581</v>
+      </c>
+      <c r="Z41">
+        <v>0.08466040724299019</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0.06473882564434168</v>
+      </c>
+      <c r="AC41">
+        <v>-0.06473882564434168</v>
+      </c>
+      <c r="AD41">
+        <v>2597.7</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>2597.7</v>
+      </c>
+      <c r="AG41">
+        <v>2216.6</v>
+      </c>
+      <c r="AH41">
+        <v>0.3507987738180443</v>
+      </c>
+      <c r="AI41">
+        <v>0.530586817541208</v>
+      </c>
+      <c r="AJ41">
+        <v>0.3155751708428246</v>
+      </c>
+      <c r="AK41">
+        <v>0.4909630548418535</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Guolian Securities Co., Ltd. (SEHK:1456)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>0.116</v>
+      </c>
+      <c r="E42">
+        <v>-0.0305</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>48.5</v>
+      </c>
+      <c r="L42">
+        <v>0.1253229974160207</v>
+      </c>
+      <c r="M42">
+        <v>47.6</v>
+      </c>
+      <c r="N42">
+        <v>0.0101533670356861</v>
+      </c>
+      <c r="O42">
+        <v>0.9814432989690722</v>
+      </c>
+      <c r="P42">
+        <v>47.6</v>
+      </c>
+      <c r="Q42">
+        <v>0.0101533670356861</v>
+      </c>
+      <c r="R42">
+        <v>0.9814432989690722</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>871.2</v>
+      </c>
+      <c r="V42">
+        <v>0.185832213476675</v>
+      </c>
+      <c r="W42">
+        <v>0.01978784169726642</v>
+      </c>
+      <c r="X42">
+        <v>0.09266218607966512</v>
+      </c>
+      <c r="Y42">
+        <v>-0.07287434438239869</v>
+      </c>
+      <c r="Z42">
+        <v>0.0475692950648393</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0.06474249945568512</v>
+      </c>
+      <c r="AC42">
+        <v>-0.06474249945568512</v>
+      </c>
+      <c r="AD42">
+        <v>8102.5</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>8102.5</v>
+      </c>
+      <c r="AG42">
+        <v>7231.3</v>
+      </c>
+      <c r="AH42">
+        <v>0.6334730192485106</v>
+      </c>
+      <c r="AI42">
+        <v>0.7521815818789455</v>
+      </c>
+      <c r="AJ42">
+        <v>0.6066832223098477</v>
+      </c>
+      <c r="AK42">
+        <v>0.7303753232062057</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BOC International (China) CO., LTD. (SHSE:601696)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>-0.008569999999999999</v>
+      </c>
+      <c r="E43">
+        <v>-0.0154</v>
+      </c>
+      <c r="F43">
+        <v>0.0459</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>107.1</v>
+      </c>
+      <c r="L43">
+        <v>0.2915872583719031</v>
+      </c>
+      <c r="M43">
+        <v>44.9</v>
+      </c>
+      <c r="N43">
+        <v>0.01057117295286528</v>
+      </c>
+      <c r="O43">
+        <v>0.419234360410831</v>
+      </c>
+      <c r="P43">
+        <v>44.9</v>
+      </c>
+      <c r="Q43">
+        <v>0.01057117295286528</v>
+      </c>
+      <c r="R43">
+        <v>0.419234360410831</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>317</v>
+      </c>
+      <c r="V43">
+        <v>0.07463389367613128</v>
+      </c>
+      <c r="W43">
+        <v>0.04563272262462718</v>
+      </c>
+      <c r="X43">
+        <v>0.07418787590006679</v>
+      </c>
+      <c r="Y43">
+        <v>-0.0285551532754396</v>
+      </c>
+      <c r="Z43">
+        <v>0.08546431812364753</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0.06477283119178054</v>
+      </c>
+      <c r="AC43">
+        <v>-0.06477283119178054</v>
+      </c>
+      <c r="AD43">
+        <v>2214.3</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>2214.3</v>
+      </c>
+      <c r="AG43">
+        <v>1897.3</v>
+      </c>
+      <c r="AH43">
+        <v>0.3426807186963183</v>
+      </c>
+      <c r="AI43">
+        <v>0.4664532030081524</v>
+      </c>
+      <c r="AJ43">
+        <v>0.3087701596497795</v>
+      </c>
+      <c r="AK43">
+        <v>0.4282747567774994</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Capital Securities Corporation Limited (SHSE:601136)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>0.146</v>
+      </c>
+      <c r="E44">
+        <v>0.201</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>141.3</v>
+      </c>
+      <c r="L44">
+        <v>0.4009648127128264</v>
+      </c>
+      <c r="M44">
+        <v>84</v>
+      </c>
+      <c r="N44">
+        <v>0.01019615459312488</v>
+      </c>
+      <c r="O44">
+        <v>0.5944798301486199</v>
+      </c>
+      <c r="P44">
+        <v>84</v>
+      </c>
+      <c r="Q44">
+        <v>0.01019615459312488</v>
+      </c>
+      <c r="R44">
+        <v>0.5944798301486199</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>144.5</v>
+      </c>
+      <c r="V44">
+        <v>0.0175398135560303</v>
+      </c>
+      <c r="W44">
+        <v>0.08529518290474467</v>
+      </c>
+      <c r="X44">
+        <v>0.07306582654608999</v>
+      </c>
+      <c r="Y44">
+        <v>0.01222935635865467</v>
+      </c>
+      <c r="Z44">
+        <v>0.07543292591561958</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0.0649122247586804</v>
+      </c>
+      <c r="AC44">
+        <v>-0.0649122247586804</v>
+      </c>
+      <c r="AD44">
+        <v>3691</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>3691</v>
+      </c>
+      <c r="AG44">
+        <v>3546.5</v>
+      </c>
+      <c r="AH44">
+        <v>0.3094036581890121</v>
+      </c>
+      <c r="AI44">
+        <v>0.6655247024882799</v>
+      </c>
+      <c r="AJ44">
+        <v>0.3009359434530628</v>
+      </c>
+      <c r="AK44">
+        <v>0.6565768767934833</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Central China Securities Co., Ltd. (SEHK:1375)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>-0.0563</v>
+      </c>
+      <c r="E45">
+        <v>0.374</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>23.8</v>
+      </c>
+      <c r="L45">
+        <v>0.09546730846369836</v>
+      </c>
+      <c r="M45">
+        <v>54</v>
+      </c>
+      <c r="N45">
+        <v>0.02342631556114702</v>
+      </c>
+      <c r="O45">
+        <v>2.26890756302521</v>
+      </c>
+      <c r="P45">
+        <v>54</v>
+      </c>
+      <c r="Q45">
+        <v>0.02342631556114702</v>
+      </c>
+      <c r="R45">
+        <v>2.26890756302521</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>465.2</v>
+      </c>
+      <c r="V45">
+        <v>0.2018133703526962</v>
+      </c>
+      <c r="W45">
+        <v>0.0124881939343058</v>
+      </c>
+      <c r="X45">
+        <v>0.08373429055031478</v>
+      </c>
+      <c r="Y45">
+        <v>-0.07124609661600897</v>
+      </c>
+      <c r="Z45">
+        <v>0.05061507569928189</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0.06497311860230212</v>
+      </c>
+      <c r="AC45">
+        <v>-0.06497311860230212</v>
+      </c>
+      <c r="AD45">
+        <v>2639.4</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>2639.4</v>
+      </c>
+      <c r="AG45">
+        <v>2174.2</v>
+      </c>
+      <c r="AH45">
+        <v>0.5338052381433916</v>
+      </c>
+      <c r="AI45">
+        <v>0.5659090909090909</v>
+      </c>
+      <c r="AJ45">
+        <v>0.4853883419284263</v>
+      </c>
+      <c r="AK45">
+        <v>0.5178146136991522</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Guangdong Golden Dragon Development Inc. (SZSE:000712)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>-0.187</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>-31.1</v>
+      </c>
+      <c r="L46">
+        <v>-0.4185733512786003</v>
+      </c>
+      <c r="M46">
+        <v>59.9</v>
+      </c>
+      <c r="N46">
+        <v>0.03227196810516675</v>
+      </c>
+      <c r="O46">
+        <v>-1.92604501607717</v>
+      </c>
+      <c r="P46">
+        <v>59.9</v>
+      </c>
+      <c r="Q46">
+        <v>0.03227196810516675</v>
+      </c>
+      <c r="R46">
+        <v>-1.92604501607717</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>140.6</v>
+      </c>
+      <c r="V46">
+        <v>0.07575022897473196</v>
+      </c>
+      <c r="W46">
+        <v>-0.08758096310898339</v>
+      </c>
+      <c r="X46">
+        <v>0.08065438522078452</v>
+      </c>
+      <c r="Y46">
+        <v>-0.1682353483297679</v>
+      </c>
+      <c r="Z46">
+        <v>0.05199076341753552</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0.06508478552755109</v>
+      </c>
+      <c r="AC46">
+        <v>-0.06508478552755109</v>
+      </c>
+      <c r="AD46">
+        <v>1751.8</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>1751.8</v>
+      </c>
+      <c r="AG46">
+        <v>1611.2</v>
+      </c>
+      <c r="AH46">
+        <v>0.4855456082485657</v>
+      </c>
+      <c r="AI46">
+        <v>0.7331547668870846</v>
+      </c>
+      <c r="AJ46">
+        <v>0.4646843365154443</v>
+      </c>
+      <c r="AK46">
+        <v>0.7164710067591604</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Guosheng Financial Holding Inc. (SZSE:002670)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>0.108</v>
+      </c>
+      <c r="G47">
+        <v>0.00958627648839556</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0.781</v>
+      </c>
+      <c r="L47">
+        <v>0.003940464177598386</v>
+      </c>
+      <c r="M47">
+        <v>23</v>
+      </c>
+      <c r="N47">
+        <v>0.006627669077601359</v>
+      </c>
+      <c r="O47">
+        <v>29.449423815621</v>
+      </c>
+      <c r="P47">
+        <v>23</v>
+      </c>
+      <c r="Q47">
+        <v>0.006627669077601359</v>
+      </c>
+      <c r="R47">
+        <v>29.449423815621</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>1957.2</v>
+      </c>
+      <c r="V47">
+        <v>0.5639858225513644</v>
+      </c>
+      <c r="W47">
+        <v>0.0005174241420431959</v>
+      </c>
+      <c r="X47">
+        <v>0.07639727552255607</v>
+      </c>
+      <c r="Y47">
+        <v>-0.07587985138051287</v>
+      </c>
+      <c r="Z47">
+        <v>0.1844064011909192</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0.06528355229296719</v>
+      </c>
+      <c r="AC47">
+        <v>-0.06528355229296719</v>
+      </c>
+      <c r="AD47">
+        <v>2310.1</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>2310.1</v>
+      </c>
+      <c r="AG47">
+        <v>352.8999999999999</v>
+      </c>
+      <c r="AH47">
+        <v>0.3996436232786659</v>
+      </c>
+      <c r="AI47">
+        <v>0.5955247351189709</v>
+      </c>
+      <c r="AJ47">
+        <v>0.09230487549696587</v>
+      </c>
+      <c r="AK47">
+        <v>0.1836203756699099</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-42.1</v>
+      </c>
+      <c r="AQ47">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nanhua Futures Co., Ltd. (SHSE:603093)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>-0.0911</v>
+      </c>
+      <c r="E48">
+        <v>0.281</v>
+      </c>
+      <c r="G48">
+        <v>0.006514697060587882</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>65.8</v>
+      </c>
+      <c r="L48">
+        <v>0.07894421115776844</v>
+      </c>
+      <c r="M48">
+        <v>7.2</v>
+      </c>
+      <c r="N48">
+        <v>0.007307419060184716</v>
+      </c>
+      <c r="O48">
+        <v>0.1094224924012158</v>
+      </c>
+      <c r="P48">
+        <v>7.2</v>
+      </c>
+      <c r="Q48">
+        <v>0.007307419060184716</v>
+      </c>
+      <c r="R48">
+        <v>0.1094224924012158</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>255.6</v>
+      </c>
+      <c r="V48">
+        <v>0.2594133766365574</v>
+      </c>
+      <c r="W48">
+        <v>0.1325543916196616</v>
+      </c>
+      <c r="X48">
+        <v>0.07006395877347477</v>
+      </c>
+      <c r="Y48">
+        <v>0.0624904328461868</v>
+      </c>
+      <c r="Z48">
+        <v>1.108377659574468</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0.06536540950839048</v>
+      </c>
+      <c r="AC48">
+        <v>-0.06536540950839048</v>
+      </c>
+      <c r="AD48">
+        <v>248.2</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>248.2</v>
+      </c>
+      <c r="AG48">
+        <v>-7.400000000000006</v>
+      </c>
+      <c r="AH48">
+        <v>0.2012160518848804</v>
+      </c>
+      <c r="AI48">
+        <v>0.3043531575720417</v>
+      </c>
+      <c r="AJ48">
+        <v>-0.007567235913692612</v>
+      </c>
+      <c r="AK48">
+        <v>-0.01321664582961244</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>China Renaissance Holdings Limited (SEHK:1911)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>-0.182</v>
+      </c>
+      <c r="G49">
+        <v>0.07691256830601093</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>-50.3</v>
+      </c>
+      <c r="L49">
+        <v>-0.6871584699453551</v>
+      </c>
+      <c r="M49">
+        <v>-0</v>
+      </c>
+      <c r="N49">
+        <v>-0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>-0</v>
+      </c>
+      <c r="Q49">
+        <v>-0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>171.3</v>
+      </c>
+      <c r="V49">
+        <v>0.8130042714760324</v>
+      </c>
+      <c r="W49">
+        <v>-0.05637749383546289</v>
+      </c>
+      <c r="X49">
+        <v>0.07263005845883176</v>
+      </c>
+      <c r="Y49">
+        <v>-0.1290075522942947</v>
+      </c>
+      <c r="Z49">
+        <v>0.08604678500058775</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0.06552440460365601</v>
+      </c>
+      <c r="AC49">
+        <v>-0.06552440460365601</v>
+      </c>
+      <c r="AD49">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="AG49">
+        <v>-82.90000000000001</v>
+      </c>
+      <c r="AH49">
+        <v>0.2955533266466065</v>
+      </c>
+      <c r="AI49">
+        <v>0.08261682242990655</v>
+      </c>
+      <c r="AJ49">
+        <v>-0.6486697965571206</v>
+      </c>
+      <c r="AK49">
+        <v>-0.09224435295426728</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-4</v>
+      </c>
+      <c r="AQ49">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ChinaLin Securities Co., Ltd (SZSE:002945)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>0.0515</v>
+      </c>
+      <c r="E50">
+        <v>-0.179</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>20.9</v>
+      </c>
+      <c r="L50">
+        <v>0.1192241871078152</v>
+      </c>
+      <c r="M50">
+        <v>11.7</v>
+      </c>
+      <c r="N50">
+        <v>0.002063237342832455</v>
+      </c>
+      <c r="O50">
+        <v>0.5598086124401914</v>
+      </c>
+      <c r="P50">
+        <v>11.7</v>
+      </c>
+      <c r="Q50">
+        <v>0.002063237342832455</v>
+      </c>
+      <c r="R50">
+        <v>0.5598086124401914</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>184.1</v>
+      </c>
+      <c r="V50">
+        <v>0.03246512776200469</v>
+      </c>
+      <c r="W50">
+        <v>0.02349634626194491</v>
+      </c>
+      <c r="X50">
+        <v>0.06883403616408383</v>
+      </c>
+      <c r="Y50">
+        <v>-0.04533768990213892</v>
+      </c>
+      <c r="Z50">
+        <v>0.1512034605150233</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0.06559490648733252</v>
+      </c>
+      <c r="AC50">
+        <v>-0.06559490648733252</v>
+      </c>
+      <c r="AD50">
+        <v>972.8</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>972.8</v>
+      </c>
+      <c r="AG50">
+        <v>788.6999999999999</v>
+      </c>
+      <c r="AH50">
+        <v>0.1464288402197637</v>
+      </c>
+      <c r="AI50">
+        <v>0.5076184512627844</v>
+      </c>
+      <c r="AJ50">
+        <v>0.1221011239434003</v>
+      </c>
+      <c r="AK50">
+        <v>0.4552906540437568</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Orient Securities Company Limited (SHSE:600958)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>0.00062</v>
+      </c>
+      <c r="E51">
+        <v>0.0911</v>
+      </c>
+      <c r="F51">
+        <v>0.26</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>456</v>
+      </c>
+      <c r="L51">
+        <v>0.1838709677419355</v>
+      </c>
+      <c r="M51">
+        <v>586</v>
+      </c>
+      <c r="N51">
+        <v>0.05129013058852361</v>
+      </c>
+      <c r="O51">
+        <v>1.285087719298246</v>
+      </c>
+      <c r="P51">
+        <v>543.3</v>
+      </c>
+      <c r="Q51">
+        <v>0.0475527780695305</v>
+      </c>
+      <c r="R51">
+        <v>1.191447368421052</v>
+      </c>
+      <c r="S51">
+        <v>42.70000000000005</v>
+      </c>
+      <c r="T51">
+        <v>0.07286689419795229</v>
+      </c>
+      <c r="U51">
+        <v>3135.4</v>
+      </c>
+      <c r="V51">
+        <v>0.2744284563946364</v>
+      </c>
+      <c r="W51">
+        <v>0.04228761139910788</v>
+      </c>
+      <c r="X51">
+        <v>0.09807451230046768</v>
+      </c>
+      <c r="Y51">
+        <v>-0.0557869009013598</v>
+      </c>
+      <c r="Z51">
+        <v>0.08448103775416699</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0.06565848258749135</v>
+      </c>
+      <c r="AC51">
+        <v>-0.06565848258749135</v>
+      </c>
+      <c r="AD51">
+        <v>23786.3</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>23786.3</v>
+      </c>
+      <c r="AG51">
+        <v>20650.9</v>
+      </c>
+      <c r="AH51">
+        <v>0.6755264615253539</v>
+      </c>
+      <c r="AI51">
+        <v>0.6724080418829222</v>
+      </c>
+      <c r="AJ51">
+        <v>0.643809565377337</v>
+      </c>
+      <c r="AK51">
+        <v>0.6405485213744673</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Zhongtai Securities Co., Ltd. (SHSE:600918)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D12">
+      <c r="D52">
         <v>0.0383</v>
       </c>
-      <c r="E12">
+      <c r="E52">
         <v>-0.272</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
         <v>58.3</v>
       </c>
-      <c r="L12">
+      <c r="L52">
         <v>0.03797798189043059</v>
       </c>
-      <c r="M12">
+      <c r="M52">
         <v>323.5</v>
       </c>
-      <c r="N12">
+      <c r="N52">
         <v>0.05157433240334795</v>
       </c>
-      <c r="O12">
+      <c r="O52">
         <v>5.548885077186965</v>
       </c>
-      <c r="P12">
+      <c r="P52">
         <v>323.5</v>
       </c>
-      <c r="Q12">
+      <c r="Q52">
         <v>0.05157433240334795</v>
       </c>
-      <c r="R12">
+      <c r="R52">
         <v>5.548885077186965</v>
       </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
         <v>1760.5</v>
       </c>
-      <c r="V12">
+      <c r="V52">
         <v>0.2806695894778796</v>
       </c>
-      <c r="W12">
+      <c r="W52">
         <v>0.01064276456306249</v>
       </c>
-      <c r="X12">
-        <v>0.09517852046846062</v>
-      </c>
-      <c r="Y12">
-        <v>-0.08453575590539814</v>
-      </c>
-      <c r="Z12">
+      <c r="X52">
+        <v>0.09515671946724308</v>
+      </c>
+      <c r="Y52">
+        <v>-0.08451395490418059</v>
+      </c>
+      <c r="Z52">
         <v>0.09491158649684679</v>
       </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.06568343425862667</v>
-      </c>
-      <c r="AC12">
-        <v>-0.06568343425862667</v>
-      </c>
-      <c r="AD12">
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0.06567589401842855</v>
+      </c>
+      <c r="AC52">
+        <v>-0.06567589401842855</v>
+      </c>
+      <c r="AD52">
         <v>11863.1</v>
       </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
         <v>11863.1</v>
       </c>
-      <c r="AG12">
+      <c r="AG52">
         <v>10102.6</v>
       </c>
-      <c r="AH12">
+      <c r="AH52">
         <v>0.6541333068660535</v>
       </c>
-      <c r="AI12">
+      <c r="AI52">
         <v>0.6504891101704209</v>
       </c>
-      <c r="AJ12">
+      <c r="AJ52">
         <v>0.6169489041288297</v>
       </c>
-      <c r="AK12">
+      <c r="AK52">
         <v>0.6131446224061857</v>
       </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ruida Futures Co.,Ltd. (SZSE:002961)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>0.174</v>
+      </c>
+      <c r="E53">
+        <v>0.228</v>
+      </c>
+      <c r="G53">
+        <v>0.003393213572854291</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>47.9</v>
+      </c>
+      <c r="L53">
+        <v>0.1912175648702595</v>
+      </c>
+      <c r="M53">
+        <v>16.4</v>
+      </c>
+      <c r="N53">
+        <v>0.01871932427805045</v>
+      </c>
+      <c r="O53">
+        <v>0.3423799582463465</v>
+      </c>
+      <c r="P53">
+        <v>16.4</v>
+      </c>
+      <c r="Q53">
+        <v>0.01871932427805045</v>
+      </c>
+      <c r="R53">
+        <v>0.3423799582463465</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>78.7</v>
+      </c>
+      <c r="V53">
+        <v>0.08982992809040063</v>
+      </c>
+      <c r="W53">
+        <v>0.1345505617977528</v>
+      </c>
+      <c r="X53">
+        <v>0.06829953954872951</v>
+      </c>
+      <c r="Y53">
+        <v>0.06625102224902328</v>
+      </c>
+      <c r="Z53">
+        <v>0.6034108975285446</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0.0657047555553615</v>
+      </c>
+      <c r="AC53">
+        <v>-0.0657047555553615</v>
+      </c>
+      <c r="AD53">
+        <v>119.7</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>119.7</v>
+      </c>
+      <c r="AG53">
+        <v>41</v>
+      </c>
+      <c r="AH53">
+        <v>0.1202048604137377</v>
+      </c>
+      <c r="AI53">
+        <v>0.2263187748156552</v>
+      </c>
+      <c r="AJ53">
+        <v>0.04470613891614873</v>
+      </c>
+      <c r="AK53">
+        <v>0.09107063527321191</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Yongan Futures Co.,Ltd. (SHSE:600927)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>0.013</v>
+      </c>
+      <c r="E54">
+        <v>-0.09039999999999999</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="L54">
+        <v>0.02484380089425839</v>
+      </c>
+      <c r="M54">
+        <v>35.5</v>
+      </c>
+      <c r="N54">
+        <v>0.01349655932783333</v>
+      </c>
+      <c r="O54">
+        <v>0.4231227651966626</v>
+      </c>
+      <c r="P54">
+        <v>35.5</v>
+      </c>
+      <c r="Q54">
+        <v>0.01349655932783333</v>
+      </c>
+      <c r="R54">
+        <v>0.4231227651966626</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>511.8</v>
+      </c>
+      <c r="V54">
+        <v>0.1945785651826788</v>
+      </c>
+      <c r="W54">
+        <v>0.04959801371482621</v>
+      </c>
+      <c r="X54">
+        <v>0.06667497797531272</v>
+      </c>
+      <c r="Y54">
+        <v>-0.01707696426048651</v>
+      </c>
+      <c r="Z54">
+        <v>2.673236760864403</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0.06600666574452151</v>
+      </c>
+      <c r="AC54">
+        <v>-0.06600666574452151</v>
+      </c>
+      <c r="AD54">
+        <v>80.2</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>80.2</v>
+      </c>
+      <c r="AG54">
+        <v>-431.6</v>
+      </c>
+      <c r="AH54">
+        <v>0.02958863678288139</v>
+      </c>
+      <c r="AI54">
+        <v>0.04269136591078462</v>
+      </c>
+      <c r="AJ54">
+        <v>-0.1962978123436576</v>
+      </c>
+      <c r="AK54">
+        <v>-0.3157740708223588</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>The Pacific Securities Co., Ltd (SHSE:601099)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>0.0106</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>19.4</v>
+      </c>
+      <c r="L55">
+        <v>0.1136496777973052</v>
+      </c>
+      <c r="M55">
+        <v>0.729</v>
+      </c>
+      <c r="N55">
+        <v>0.0001832487054446735</v>
+      </c>
+      <c r="O55">
+        <v>0.03757731958762887</v>
+      </c>
+      <c r="P55">
+        <v>0.729</v>
+      </c>
+      <c r="Q55">
+        <v>0.0001832487054446735</v>
+      </c>
+      <c r="R55">
+        <v>0.03757731958762887</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>192.7</v>
+      </c>
+      <c r="V55">
+        <v>0.048438992509175</v>
+      </c>
+      <c r="W55">
+        <v>0.01493571483563015</v>
+      </c>
+      <c r="X55">
+        <v>0.0665610968294193</v>
+      </c>
+      <c r="Y55">
+        <v>-0.05162538199378915</v>
+      </c>
+      <c r="Z55">
+        <v>0.1372407139411481</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0.06611389838505709</v>
+      </c>
+      <c r="AC55">
+        <v>-0.06611389838505709</v>
+      </c>
+      <c r="AD55">
+        <v>91.7</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>91.7</v>
+      </c>
+      <c r="AG55">
+        <v>-101</v>
+      </c>
+      <c r="AH55">
+        <v>0.02253126612447481</v>
+      </c>
+      <c r="AI55">
+        <v>0.06271371905348105</v>
+      </c>
+      <c r="AJ55">
+        <v>-0.02604972660682967</v>
+      </c>
+      <c r="AK55">
+        <v>-0.07955888144938951</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Zhejiang Orient Financial Holdings Group Co., Ltd. (SHSE:600120)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>0.0197</v>
+      </c>
+      <c r="E56">
+        <v>-0.083</v>
+      </c>
+      <c r="G56">
+        <v>-0.01224166830999803</v>
+      </c>
+      <c r="H56">
+        <v>-0.01227568526917768</v>
+      </c>
+      <c r="I56">
+        <v>-0.02203707355551173</v>
+      </c>
+      <c r="J56">
+        <v>-0.01714308931276009</v>
+      </c>
+      <c r="K56">
+        <v>69.5</v>
+      </c>
+      <c r="L56">
+        <v>0.03426345888384934</v>
+      </c>
+      <c r="M56">
+        <v>53.8</v>
+      </c>
+      <c r="N56">
+        <v>0.02517665777528195</v>
+      </c>
+      <c r="O56">
+        <v>0.7741007194244603</v>
+      </c>
+      <c r="P56">
+        <v>53.8</v>
+      </c>
+      <c r="Q56">
+        <v>0.02517665777528195</v>
+      </c>
+      <c r="R56">
+        <v>0.7741007194244603</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>857.6</v>
+      </c>
+      <c r="V56">
+        <v>0.4013290280312602</v>
+      </c>
+      <c r="W56">
+        <v>0.03230905118311562</v>
+      </c>
+      <c r="X56">
+        <v>0.07473130710680063</v>
+      </c>
+      <c r="Y56">
+        <v>-0.04242225592368502</v>
+      </c>
+      <c r="Z56">
+        <v>0.951674955428357</v>
+      </c>
+      <c r="AA56">
+        <v>-0.0163146487576253</v>
+      </c>
+      <c r="AB56">
+        <v>0.06377115210805152</v>
+      </c>
+      <c r="AC56">
+        <v>-0.08008580086567682</v>
+      </c>
+      <c r="AD56">
+        <v>1189.9</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>1189.9</v>
+      </c>
+      <c r="AG56">
+        <v>332.3000000000001</v>
+      </c>
+      <c r="AH56">
+        <v>0.3576710352290489</v>
+      </c>
+      <c r="AI56">
+        <v>0.3223787591438635</v>
+      </c>
+      <c r="AJ56">
+        <v>0.1345780009719748</v>
+      </c>
+      <c r="AK56">
+        <v>0.1172795934213313</v>
+      </c>
+      <c r="AL56">
+        <v>28</v>
+      </c>
+      <c r="AM56">
+        <v>-93</v>
+      </c>
+      <c r="AN56">
+        <v>-50.20675105485233</v>
+      </c>
+      <c r="AO56">
+        <v>-1.596428571428572</v>
+      </c>
+      <c r="AP56">
+        <v>-14.02109704641351</v>
+      </c>
+      <c r="AQ56">
+        <v>0.4806451612903226</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Top KingWin Ltd (NasdaqCM:WAI)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G57">
+        <v>-0.6015037593984962</v>
+      </c>
+      <c r="H57">
+        <v>-0.6015037593984962</v>
+      </c>
+      <c r="I57">
+        <v>-1.254550198161884</v>
+      </c>
+      <c r="J57">
+        <v>-1.254550198161884</v>
+      </c>
+      <c r="K57">
+        <v>-5.13</v>
+      </c>
+      <c r="L57">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="M57">
+        <v>-0</v>
+      </c>
+      <c r="N57">
+        <v>-0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>-0</v>
+      </c>
+      <c r="Q57">
+        <v>-0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>3.1</v>
+      </c>
+      <c r="V57">
+        <v>0.04952076677316294</v>
+      </c>
+      <c r="W57">
+        <v>-0.5842824601366743</v>
+      </c>
+      <c r="X57">
+        <v>0.06629343555031833</v>
+      </c>
+      <c r="Y57">
+        <v>-0.6505758956869926</v>
+      </c>
+      <c r="Z57">
+        <v>0.9414204202902955</v>
+      </c>
+      <c r="AA57">
+        <v>-1</v>
+      </c>
+      <c r="AB57">
+        <v>0.066195477034779</v>
+      </c>
+      <c r="AC57">
+        <v>-1.066195477034779</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0.3482764533295847</v>
+      </c>
+      <c r="AF57">
+        <v>0.3482764533295847</v>
+      </c>
+      <c r="AG57">
+        <v>-2.751723546670415</v>
+      </c>
+      <c r="AH57">
+        <v>0.005532740099529174</v>
+      </c>
+      <c r="AI57">
+        <v>0.06016928461135368</v>
+      </c>
+      <c r="AJ57">
+        <v>-0.04597832568856419</v>
+      </c>
+      <c r="AK57">
+        <v>-1.023601402029262</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>0</v>
+      </c>
+      <c r="AN57">
+        <v>-0</v>
+      </c>
+      <c r="AP57">
+        <v>0.5552307398447166</v>
       </c>
     </row>
   </sheetData>
